--- a/Capital_Gains_Tax_Estimator.xlsx
+++ b/Capital_Gains_Tax_Estimator.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Capital Gains Tax Estimator" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Capital Gains Tax Calculator" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Tax Rates &amp; Assumptions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
@@ -21,7 +21,7 @@
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="$#,##0;($#,##0)"/>
   </numFmts>
-  <fonts count="33">
+  <fonts count="26">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -99,24 +99,6 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="8.5"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <i val="1"/>
-      <color rgb="00595959"/>
-      <sz val="8.5"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
       <color rgb="00000000"/>
       <sz val="10"/>
     </font>
@@ -127,26 +109,14 @@
     </font>
     <font>
       <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="001F3864"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Arial"/>
       <i val="1"/>
       <color rgb="00595959"/>
       <sz val="8"/>
     </font>
     <font>
       <name val="Arial"/>
-      <i val="1"/>
-      <color rgb="00595959"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
       <sz val="9"/>
     </font>
     <font>
@@ -185,23 +155,6 @@
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="00000000"/>
-      <sz val="8.5"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="8.5"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Arial"/>
       <b val="1"/>
       <color rgb="001F3864"/>
       <sz val="10"/>
@@ -210,10 +163,16 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="001F3864"/>
-      <sz val="14"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -250,14 +209,8 @@
         <bgColor rgb="00D9E2F3"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
-        <bgColor rgb="00E2EFDA"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="5">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -279,44 +232,11 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00BFBFBF"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00BFBFBF"/>
-      </right>
-      <top style="thin">
-        <color rgb="00BFBFBF"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00BFBFBF"/>
-      </right>
-      <top style="thin">
-        <color rgb="00BFBFBF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00BFBFBF"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -360,104 +280,61 @@
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="32" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="32" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="19" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="19" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="10" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="28" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="23" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="10" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="165" fontId="24" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="164" fontId="24" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="31" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="28" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
+    <xf numFmtId="165" fontId="25" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -546,7 +423,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Estimated Tax From Sale - By Type</a:t>
+              <a:t>Estimated Tax - By Type</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -560,7 +437,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Capital Gains Tax Estimator'!G69</f>
+              <f>'Capital Gains Tax Calculator'!G36</f>
             </strRef>
           </tx>
           <spPr>
@@ -570,12 +447,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Capital Gains Tax Estimator'!$F$70:$F$72</f>
+              <f>'Capital Gains Tax Calculator'!$F$37:$F$39</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Capital Gains Tax Estimator'!$G$70:$G$72</f>
+              <f>'Capital Gains Tax Calculator'!$G$37:$G$39</f>
             </numRef>
           </val>
         </ser>
@@ -600,7 +477,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>68</row>
+      <row>35</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="4320000" cy="2700000"/>
@@ -910,17 +787,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N176"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:N95"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="4" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="4" customWidth="1" min="8" max="8"/>
+    <col width="4" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
@@ -932,2072 +808,1055 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="19" t="inlineStr">
         <is>
-          <t>CAPITAL GAINS &amp; LOSSES TAX ESTIMATOR</t>
+          <t>CAPITAL GAINS TAX CALCULATOR</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="20" t="inlineStr">
         <is>
-          <t>Estimate the tax impact of selling an investment. For planning purposes only - not tax, legal, or accounting advice.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="26" customHeight="1">
-      <c r="A4" s="21" t="inlineStr">
-        <is>
-          <t>ESTIMATED TAX FROM PORTFOLIO SALE</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="28" customHeight="1">
-      <c r="B5" s="22" t="inlineStr">
+          <t>Estimated tax from capital gains and losses. For planning purposes only - not tax, legal, or accounting advice.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>YOUR INFO</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="n"/>
+      <c r="F4" s="4" t="n"/>
+    </row>
+    <row r="5">
+      <c r="B5" s="21" t="inlineStr">
+        <is>
+          <t>Tax Year</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>Filing Status</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>Married Filing Jointly</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t>State of Residence</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>New Jersey</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>State Tax Rate if 'Other (Manual Entry)' Selected</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t>Taxable Income (before these gains/losses)</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="n">
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="23" t="inlineStr">
+        <is>
+          <t>(your salary/other income after deductions - used only to determine which tax brackets your gains fall into)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>CAPITAL GAINS &amp; LOSSES</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="n"/>
+      <c r="C12" s="4" t="n"/>
+      <c r="D12" s="4" t="n"/>
+      <c r="E12" s="4" t="n"/>
+      <c r="F12" s="4" t="n"/>
+    </row>
+    <row r="13">
+      <c r="B13" s="24" t="inlineStr">
+        <is>
+          <t>Short-Term Capital Gains (held 1 year or less)</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="n">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="24" t="inlineStr">
+        <is>
+          <t>Long-Term Capital Gains (held more than 1 year)</t>
+        </is>
+      </c>
+      <c r="C14" s="13" t="n">
+        <v>155000</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="24" t="inlineStr">
+        <is>
+          <t>Short-Term Capital Losses</t>
+        </is>
+      </c>
+      <c r="C15" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="24" t="inlineStr">
+        <is>
+          <t>Long-Term Capital Losses</t>
+        </is>
+      </c>
+      <c r="C16" s="13" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="24" t="inlineStr">
+        <is>
+          <t>Capital Loss Carryforward (from prior years)</t>
+        </is>
+      </c>
+      <c r="C17" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>ESTIMATED TAX</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="n"/>
+      <c r="C19" s="4" t="n"/>
+      <c r="D19" s="4" t="n"/>
+      <c r="E19" s="4" t="n"/>
+      <c r="F19" s="4" t="n"/>
+    </row>
+    <row r="20" ht="28" customHeight="1">
+      <c r="B20" s="25" t="inlineStr">
+        <is>
+          <t>Total Estimated Tax</t>
+        </is>
+      </c>
+      <c r="C20" s="25" t="inlineStr">
+        <is>
+          <t>Effective Tax Rate</t>
+        </is>
+      </c>
+      <c r="D20" s="25" t="inlineStr">
         <is>
           <t>Federal Tax</t>
         </is>
       </c>
-      <c r="C5" s="22" t="inlineStr">
+      <c r="E20" s="25" t="inlineStr">
         <is>
           <t>State Tax</t>
         </is>
       </c>
-      <c r="D5" s="22" t="inlineStr">
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="B21" s="38">
+        <f>C80</f>
+        <v/>
+      </c>
+      <c r="C21" s="39">
+        <f>C81</f>
+        <v/>
+      </c>
+      <c r="D21" s="38">
+        <f>(C73+C74)</f>
+        <v/>
+      </c>
+      <c r="E21" s="38">
+        <f>C79</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="24" t="inlineStr">
+        <is>
+          <t>Net Short-Term Gain / (Loss)</t>
+        </is>
+      </c>
+      <c r="C23" s="40">
+        <f>C64</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="24" t="inlineStr">
+        <is>
+          <t>Net Long-Term Gain / (Loss)</t>
+        </is>
+      </c>
+      <c r="C24" s="40">
+        <f>C65</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="21" t="inlineStr">
+        <is>
+          <t>Total Net Capital Gain / (Loss)</t>
+        </is>
+      </c>
+      <c r="C25" s="41">
+        <f>C66</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="24" t="inlineStr">
+        <is>
+          <t>Capital Loss Deduction (against ordinary income)</t>
+        </is>
+      </c>
+      <c r="C26" s="40">
+        <f>IF(C66&lt;0,MAX(C66,-C60),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="24" t="inlineStr">
+        <is>
+          <t>Capital Loss Carryforward to Future Years</t>
+        </is>
+      </c>
+      <c r="C27" s="40">
+        <f>-C69</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="24" t="inlineStr">
+        <is>
+          <t>Federal Tax on Short-Term Gain (ordinary rates)</t>
+        </is>
+      </c>
+      <c r="C28" s="40">
+        <f>C73</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="24" t="inlineStr">
+        <is>
+          <t>Federal Tax on Long-Term Gain (preferential rates)</t>
+        </is>
+      </c>
+      <c r="C29" s="40">
+        <f>C74</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="24" t="inlineStr">
+        <is>
+          <t>Net Investment Income Tax (NIIT)</t>
+        </is>
+      </c>
+      <c r="C30" s="40">
+        <f>C77</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="24" t="inlineStr">
+        <is>
+          <t>State Tax</t>
+        </is>
+      </c>
+      <c r="C31" s="40">
+        <f>C79</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="21" t="inlineStr">
+        <is>
+          <t>Total Estimated Tax</t>
+        </is>
+      </c>
+      <c r="C32" s="41">
+        <f>C80</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="24" t="inlineStr">
+        <is>
+          <t>Effective Tax Rate on the Gain</t>
+        </is>
+      </c>
+      <c r="C33" s="42">
+        <f>C81</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="24" t="inlineStr">
+        <is>
+          <t>Marginal Long-Term Capital Gains Rate</t>
+        </is>
+      </c>
+      <c r="C34" s="42">
+        <f>C82</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>Tax Component</t>
+        </is>
+      </c>
+      <c r="G36" s="7" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="F37" s="28" t="inlineStr">
+        <is>
+          <t>Federal Tax</t>
+        </is>
+      </c>
+      <c r="G37" s="43">
+        <f>(C73+C74)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="F38" s="28" t="inlineStr">
+        <is>
+          <t>State Tax</t>
+        </is>
+      </c>
+      <c r="G38" s="43">
+        <f>C79</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="F39" s="28" t="inlineStr">
         <is>
           <t>NIIT</t>
         </is>
       </c>
-      <c r="E5" s="22" t="inlineStr">
+      <c r="G39" s="43">
+        <f>C77</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="26" t="inlineStr">
+        <is>
+          <t>Estimated for financial-planning purposes only. This calculator is not tax, legal, or accounting advice. Actual tax liability may differ based on individual circumstances, deductions, credits, tax elections, state/local rules, and other factors. Consult a qualified tax professional before making tax-related decisions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54"/>
+    <row r="55"/>
+    <row r="57" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A57" s="27" t="inlineStr">
+        <is>
+          <t>CALCULATION DETAIL (grouped - click + to expand)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" hidden="1" outlineLevel="1"/>
+    <row r="59" hidden="1" outlineLevel="1">
+      <c r="B59" s="32" t="inlineStr">
+        <is>
+          <t>Standard Deduction (add-back for MAGI estimate)</t>
+        </is>
+      </c>
+      <c r="C59" s="33">
+        <f>INDEX('Tax Rates &amp; Assumptions'!$D$28:$D$35,L65)</f>
+        <v/>
+      </c>
+      <c r="K59" s="7" t="inlineStr">
+        <is>
+          <t>Filing Status</t>
+        </is>
+      </c>
+      <c r="L59" s="28">
+        <f>C6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60" hidden="1" outlineLevel="1">
+      <c r="B60" s="32" t="inlineStr">
+        <is>
+          <t>Capital Loss Limit vs. Ordinary Income</t>
+        </is>
+      </c>
+      <c r="C60" s="33">
+        <f>INDEX('Tax Rates &amp; Assumptions'!$D$39:$D$42,L64)</f>
+        <v/>
+      </c>
+      <c r="K60" s="7" t="inlineStr">
+        <is>
+          <t>Tax Year</t>
+        </is>
+      </c>
+      <c r="L60" s="28">
+        <f>C5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61" hidden="1" outlineLevel="1">
+      <c r="B61" s="32" t="inlineStr">
+        <is>
+          <t>NIIT Threshold</t>
+        </is>
+      </c>
+      <c r="C61" s="33">
+        <f>INDEX('Tax Rates &amp; Assumptions'!$B$39:$B$42,L64)</f>
+        <v/>
+      </c>
+      <c r="K61" s="7" t="inlineStr">
+        <is>
+          <t>Federal Key</t>
+        </is>
+      </c>
+      <c r="L61" s="28">
+        <f>L60&amp;"|"&amp;L59</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62" hidden="1" outlineLevel="1">
+      <c r="B62" s="32" t="inlineStr">
+        <is>
+          <t>NIIT Rate</t>
+        </is>
+      </c>
+      <c r="C62" s="34">
+        <f>INDEX('Tax Rates &amp; Assumptions'!$C$39:$C$42,L64)</f>
+        <v/>
+      </c>
+      <c r="K62" s="7" t="inlineStr">
+        <is>
+          <t>Fed Bracket Row#</t>
+        </is>
+      </c>
+      <c r="L62" s="28">
+        <f>MATCH(L61,'Tax Rates &amp; Assumptions'!$C$6:$C$13,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63" hidden="1" outlineLevel="1">
+      <c r="B63" s="32" t="inlineStr">
+        <is>
+          <t>State Standard Deduction</t>
+        </is>
+      </c>
+      <c r="C63" s="33">
+        <f>IF(L68="MFJ",INDEX('Tax Rates &amp; Assumptions'!$E$46:$E$77,L71),INDEX('Tax Rates &amp; Assumptions'!$D$46:$D$77,L71))</f>
+        <v/>
+      </c>
+      <c r="K63" s="7" t="inlineStr">
+        <is>
+          <t>LTCG Bracket Row#</t>
+        </is>
+      </c>
+      <c r="L63" s="28">
+        <f>MATCH(L61,'Tax Rates &amp; Assumptions'!$C$17:$C$24,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64" hidden="1" outlineLevel="1">
+      <c r="B64" s="32" t="inlineStr">
+        <is>
+          <t>Net Short-Term Gain / (Loss)</t>
+        </is>
+      </c>
+      <c r="C64" s="33">
+        <f>(C13-C15)</f>
+        <v/>
+      </c>
+      <c r="K64" s="7" t="inlineStr">
+        <is>
+          <t>Status Row# (NIIT/CapLoss)</t>
+        </is>
+      </c>
+      <c r="L64" s="28">
+        <f>MATCH(L59,'Tax Rates &amp; Assumptions'!$A$39:$A$42,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65" hidden="1" outlineLevel="1">
+      <c r="B65" s="32" t="inlineStr">
+        <is>
+          <t>Net Long-Term Gain / (Loss), net of carryforward</t>
+        </is>
+      </c>
+      <c r="C65" s="33">
+        <f>(C14-C16-C17)</f>
+        <v/>
+      </c>
+      <c r="K65" s="7" t="inlineStr">
+        <is>
+          <t>StdDed Row#</t>
+        </is>
+      </c>
+      <c r="L65" s="28">
+        <f>MATCH(L61,'Tax Rates &amp; Assumptions'!$C$28:$C$35,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66" hidden="1" outlineLevel="1">
+      <c r="B66" s="32" t="inlineStr">
+        <is>
+          <t>Combined Net Capital Gain / (Loss)</t>
+        </is>
+      </c>
+      <c r="C66" s="33">
+        <f>(C64+C65)</f>
+        <v/>
+      </c>
+      <c r="K66" s="7" t="inlineStr">
+        <is>
+          <t>State Name</t>
+        </is>
+      </c>
+      <c r="L66" s="28">
+        <f>C7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67" hidden="1" outlineLevel="1">
+      <c r="B67" s="32" t="inlineStr">
+        <is>
+          <t>Ordinary-Taxed Capital Gain / (Loss Deduction, capped)</t>
+        </is>
+      </c>
+      <c r="C67" s="33">
+        <f>IF(C66&lt;=0,MAX(C66,-C60),IF(AND(C64&gt;=0,C65&gt;=0),C64,IF(AND(C64&lt;0,C65&gt;=0),0,IF(AND(C64&gt;=0,C65&lt;0),C66,0))))</f>
+        <v/>
+      </c>
+      <c r="K67" s="7" t="inlineStr">
+        <is>
+          <t>State Code</t>
+        </is>
+      </c>
+      <c r="L67" s="28">
+        <f>INDEX('Tax Rates &amp; Assumptions'!$A$46:$A$77,MATCH(L66,'Tax Rates &amp; Assumptions'!$B$46:$B$77,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68" hidden="1" outlineLevel="1">
+      <c r="B68" s="32" t="inlineStr">
+        <is>
+          <t>Preferential (LTCG-Rate) Net Capital Gain</t>
+        </is>
+      </c>
+      <c r="C68" s="33">
+        <f>IF(C66&lt;=0,0,IF(AND(C64&gt;=0,C65&gt;=0),C65,IF(AND(C64&lt;0,C65&gt;=0),C66,IF(AND(C64&gt;=0,C65&lt;0),0,0))))</f>
+        <v/>
+      </c>
+      <c r="K68" s="7" t="inlineStr">
+        <is>
+          <t>State Category</t>
+        </is>
+      </c>
+      <c r="L68" s="28">
+        <f>IF(L59="Married Filing Jointly","MFJ","Single")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69" hidden="1" outlineLevel="1">
+      <c r="B69" s="32" t="inlineStr">
+        <is>
+          <t>Capital Loss Carryforward to Future Years</t>
+        </is>
+      </c>
+      <c r="C69" s="33">
+        <f>IF(C66&lt;=0,C66-MAX(C66,-C60),0)</f>
+        <v/>
+      </c>
+      <c r="K69" s="7" t="inlineStr">
+        <is>
+          <t>State Key</t>
+        </is>
+      </c>
+      <c r="L69" s="28">
+        <f>L67&amp;"|"&amp;L68</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70" hidden="1" outlineLevel="1">
+      <c r="B70" s="32" t="inlineStr">
+        <is>
+          <t>Ordinary Taxable Income Including Gain</t>
+        </is>
+      </c>
+      <c r="C70" s="33">
+        <f>MAX(0,C9+C67)</f>
+        <v/>
+      </c>
+      <c r="K70" s="7" t="inlineStr">
+        <is>
+          <t>State Bracket Row#</t>
+        </is>
+      </c>
+      <c r="L70" s="28">
+        <f>MATCH(L69,'Tax Rates &amp; Assumptions'!$C$81:$C$144,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71" hidden="1" outlineLevel="1">
+      <c r="B71" s="32" t="inlineStr">
+        <is>
+          <t>Federal Tax on Taxable Income Alone (no gain)</t>
+        </is>
+      </c>
+      <c r="C71" s="33">
+        <f>SUMPRODUCT((C9&gt;$M$74:$M$80)*($L$74:$L$80)*(MIN(C9,$N$74:$N$80)-$M$74:$M$80))</f>
+        <v/>
+      </c>
+      <c r="K71" s="7" t="inlineStr">
+        <is>
+          <t>State Master Row#</t>
+        </is>
+      </c>
+      <c r="L71" s="28">
+        <f>MATCH(L67,'Tax Rates &amp; Assumptions'!$A$46:$A$77,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72" hidden="1" outlineLevel="1">
+      <c r="B72" s="32" t="inlineStr">
+        <is>
+          <t>Federal Tax on Taxable Income Including Short-Term Gain</t>
+        </is>
+      </c>
+      <c r="C72" s="33">
+        <f>SUMPRODUCT((C70&gt;$M$74:$M$80)*($L$74:$L$80)*(MIN(C70,$N$74:$N$80)-$M$74:$M$80))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73" hidden="1" outlineLevel="1">
+      <c r="B73" s="35" t="inlineStr">
+        <is>
+          <t>Federal Tax on Short-Term Gain</t>
+        </is>
+      </c>
+      <c r="C73" s="33">
+        <f>MAX(0,C72-C71)</f>
+        <v/>
+      </c>
+      <c r="K73" s="29" t="inlineStr">
+        <is>
+          <t>Federal Ordinary Brackets</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" hidden="1" outlineLevel="1">
+      <c r="B74" s="35" t="inlineStr">
+        <is>
+          <t>Federal Tax on Long-Term Gain (stacked)</t>
+        </is>
+      </c>
+      <c r="C74" s="33">
+        <f>SUMPRODUCT($L$83:$L$85*(MAX(0,MIN((C70+C68),$N$83:$N$85)-MAX(C70,$M$83:$M$85))))</f>
+        <v/>
+      </c>
+      <c r="L74" s="30">
+        <f>INDEX('Tax Rates &amp; Assumptions'!D$6:D$1005,L62)</f>
+        <v/>
+      </c>
+      <c r="M74" s="31">
+        <f>INDEX('Tax Rates &amp; Assumptions'!E$6:E$1005,L62)</f>
+        <v/>
+      </c>
+      <c r="N74" s="31">
+        <f>INDEX('Tax Rates &amp; Assumptions'!F$6:F$1005,L62)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75" hidden="1" outlineLevel="1">
+      <c r="B75" s="32" t="inlineStr">
+        <is>
+          <t>MAGI Estimate (Taxable Income + Std. Ded. Add-Back + Net Gain)</t>
+        </is>
+      </c>
+      <c r="C75" s="33">
+        <f>(C9+C59+C67+C68)</f>
+        <v/>
+      </c>
+      <c r="L75" s="30">
+        <f>INDEX('Tax Rates &amp; Assumptions'!G$6:G$1005,L62)</f>
+        <v/>
+      </c>
+      <c r="M75" s="31">
+        <f>INDEX('Tax Rates &amp; Assumptions'!H$6:H$1005,L62)</f>
+        <v/>
+      </c>
+      <c r="N75" s="31">
+        <f>INDEX('Tax Rates &amp; Assumptions'!I$6:I$1005,L62)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76" hidden="1" outlineLevel="1">
+      <c r="B76" s="32" t="inlineStr">
+        <is>
+          <t>Net Investment Income (the modeled capital gain)</t>
+        </is>
+      </c>
+      <c r="C76" s="33">
+        <f>MAX(0,C67+C68)</f>
+        <v/>
+      </c>
+      <c r="L76" s="30">
+        <f>INDEX('Tax Rates &amp; Assumptions'!J$6:J$1005,L62)</f>
+        <v/>
+      </c>
+      <c r="M76" s="31">
+        <f>INDEX('Tax Rates &amp; Assumptions'!K$6:K$1005,L62)</f>
+        <v/>
+      </c>
+      <c r="N76" s="31">
+        <f>INDEX('Tax Rates &amp; Assumptions'!L$6:L$1005,L62)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77" hidden="1" outlineLevel="1">
+      <c r="B77" s="35" t="inlineStr">
+        <is>
+          <t>NIIT</t>
+        </is>
+      </c>
+      <c r="C77" s="33">
+        <f>C62*MIN(C76,MAX(0,C75-C61))</f>
+        <v/>
+      </c>
+      <c r="L77" s="30">
+        <f>INDEX('Tax Rates &amp; Assumptions'!M$6:M$1005,L62)</f>
+        <v/>
+      </c>
+      <c r="M77" s="31">
+        <f>INDEX('Tax Rates &amp; Assumptions'!N$6:N$1005,L62)</f>
+        <v/>
+      </c>
+      <c r="N77" s="31">
+        <f>INDEX('Tax Rates &amp; Assumptions'!O$6:O$1005,L62)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78" hidden="1" outlineLevel="1">
+      <c r="B78" s="32" t="inlineStr">
+        <is>
+          <t>State Taxable Income (gain taxed as ordinary income)</t>
+        </is>
+      </c>
+      <c r="C78" s="33">
+        <f>MAX(0,C9+C67+C68-C63)</f>
+        <v/>
+      </c>
+      <c r="L78" s="30">
+        <f>INDEX('Tax Rates &amp; Assumptions'!P$6:P$1005,L62)</f>
+        <v/>
+      </c>
+      <c r="M78" s="31">
+        <f>INDEX('Tax Rates &amp; Assumptions'!Q$6:Q$1005,L62)</f>
+        <v/>
+      </c>
+      <c r="N78" s="31">
+        <f>INDEX('Tax Rates &amp; Assumptions'!R$6:R$1005,L62)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79" hidden="1" outlineLevel="1">
+      <c r="B79" s="35" t="inlineStr">
+        <is>
+          <t>State Tax</t>
+        </is>
+      </c>
+      <c r="C79" s="33">
+        <f>IF(L67="OTHER",C8*C78,SUMPRODUCT((C78&gt;$M$88:$M$95)*($L$88:$L$95)*(MIN(C78,$N$88:$N$95)-$M$88:$M$95)))</f>
+        <v/>
+      </c>
+      <c r="L79" s="30">
+        <f>INDEX('Tax Rates &amp; Assumptions'!S$6:S$1005,L62)</f>
+        <v/>
+      </c>
+      <c r="M79" s="31">
+        <f>INDEX('Tax Rates &amp; Assumptions'!T$6:T$1005,L62)</f>
+        <v/>
+      </c>
+      <c r="N79" s="31">
+        <f>INDEX('Tax Rates &amp; Assumptions'!U$6:U$1005,L62)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80" hidden="1" outlineLevel="1">
+      <c r="B80" s="21" t="inlineStr">
         <is>
           <t>Total Estimated Tax</t>
         </is>
       </c>
-      <c r="F5" s="22" t="inlineStr">
-        <is>
-          <t>After-Tax Proceeds</t>
-        </is>
-      </c>
-      <c r="G5" s="22" t="inlineStr">
-        <is>
-          <t>Effective Tax Rate on Gain</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="B6" s="23">
-        <f>E62</f>
-        <v/>
-      </c>
-      <c r="C6" s="23">
-        <f>E63</f>
-        <v/>
-      </c>
-      <c r="D6" s="23">
-        <f>E64</f>
-        <v/>
-      </c>
-      <c r="E6" s="23">
-        <f>E65</f>
-        <v/>
-      </c>
-      <c r="F6" s="23">
-        <f>C90</f>
-        <v/>
-      </c>
-      <c r="G6" s="24">
-        <f>C91</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" s="25" t="inlineStr">
-        <is>
-          <t>This reflects the incremental tax created by the Portfolio Sale Scenario in Section 4. See Section 5 for the full before/after comparison.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>1. PERSONAL INFORMATION</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="n"/>
-      <c r="C10" s="4" t="n"/>
-      <c r="D10" s="4" t="n"/>
-      <c r="E10" s="4" t="n"/>
-      <c r="F10" s="4" t="n"/>
-      <c r="G10" s="4" t="n"/>
-    </row>
-    <row r="11">
-      <c r="B11" s="26" t="inlineStr">
-        <is>
-          <t>Tax Year</t>
-        </is>
-      </c>
-      <c r="C11" s="12" t="n">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="26" t="inlineStr">
-        <is>
-          <t>Filing Status</t>
-        </is>
-      </c>
-      <c r="C12" s="12" t="inlineStr">
-        <is>
-          <t>Married Filing Jointly</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="26" t="inlineStr">
-        <is>
-          <t>State of Residence</t>
-        </is>
-      </c>
-      <c r="C13" s="12" t="inlineStr">
-        <is>
-          <t>New Jersey</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="27" t="inlineStr">
-        <is>
-          <t>State Tax Rate if 'Other (Manual Entry)' Selected</t>
-        </is>
-      </c>
-      <c r="C14" s="14" t="n">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="28" t="inlineStr">
-        <is>
-          <t>YOUR STATE</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="n"/>
-      <c r="D16" s="4" t="n"/>
-    </row>
-    <row r="17">
-      <c r="B17" s="29" t="inlineStr">
-        <is>
-          <t>State</t>
-        </is>
-      </c>
-      <c r="C17" s="30">
-        <f>L116</f>
-        <v/>
-      </c>
-      <c r="D17" s="31" t="n"/>
-    </row>
-    <row r="18">
-      <c r="B18" s="29" t="inlineStr">
-        <is>
-          <t>Estimated State Marginal Tax Rate</t>
-        </is>
-      </c>
-      <c r="C18" s="32">
-        <f>C176</f>
-        <v/>
-      </c>
-      <c r="D18" s="31" t="n"/>
-    </row>
-    <row r="19">
-      <c r="B19" s="33" t="inlineStr">
-        <is>
-          <t>(automatically pulled from the Tax Rates &amp; Assumptions tab; updates once you enter income below)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>2. ORDINARY TAXABLE INCOME</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="n"/>
-      <c r="C21" s="4" t="n"/>
-      <c r="D21" s="4" t="n"/>
-      <c r="E21" s="4" t="n"/>
-      <c r="F21" s="4" t="n"/>
-      <c r="G21" s="4" t="n"/>
-    </row>
-    <row r="22">
-      <c r="B22" s="34" t="inlineStr">
-        <is>
-          <t>Used only to determine where your capital gains fall within the tax brackets - this is your income BEFORE adding the gains being modeled below.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="26" t="inlineStr">
-        <is>
-          <t>Income Entry Method</t>
-        </is>
-      </c>
-      <c r="C23" s="12" t="inlineStr">
-        <is>
-          <t>Option B: Gross Income + Deductions</t>
-        </is>
-      </c>
-      <c r="D23" s="31" t="n"/>
-    </row>
-    <row r="24">
-      <c r="B24" s="27" t="inlineStr">
-        <is>
-          <t>Option A - Estimated Taxable Income</t>
-        </is>
-      </c>
-      <c r="C24" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="27" t="inlineStr">
-        <is>
-          <t>Option B - W-2 / Salary Income</t>
-        </is>
-      </c>
-      <c r="C25" s="13" t="n">
-        <v>200000</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="27" t="inlineStr">
-        <is>
-          <t>Option B - Other Ordinary Income (business, pension, interest, etc.)</t>
-        </is>
-      </c>
-      <c r="C26" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="27" t="inlineStr">
-        <is>
-          <t>Option B - Pre-Tax Retirement Contributions</t>
-        </is>
-      </c>
-      <c r="C27" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" s="27" t="inlineStr">
-        <is>
-          <t>Option B - Estimated Deductions (standard or itemized)</t>
-        </is>
-      </c>
-      <c r="C28" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="26" t="inlineStr">
-        <is>
-          <t>Estimated Taxable Ordinary Income</t>
-        </is>
-      </c>
-      <c r="C29" s="35">
-        <f>C112</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>3. CAPITAL GAINS &amp; LOSSES (current year, before the sale scenario below)</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="n"/>
-      <c r="C31" s="4" t="n"/>
-      <c r="D31" s="4" t="n"/>
-      <c r="E31" s="4" t="n"/>
-      <c r="F31" s="4" t="n"/>
-      <c r="G31" s="4" t="n"/>
-    </row>
-    <row r="32">
-      <c r="B32" s="29" t="inlineStr">
-        <is>
-          <t>Short-Term Capital Gains (held one year or less)</t>
-        </is>
-      </c>
-      <c r="C32" s="13" t="n">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="29" t="inlineStr">
-        <is>
-          <t>Long-Term Capital Gains (held more than one year)</t>
-        </is>
-      </c>
-      <c r="C33" s="13" t="n">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="B34" s="29" t="inlineStr">
-        <is>
-          <t>Short-Term Capital Losses</t>
-        </is>
-      </c>
-      <c r="C34" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="29" t="inlineStr">
-        <is>
-          <t>Long-Term Capital Losses</t>
-        </is>
-      </c>
-      <c r="C35" s="13" t="n">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="29" t="inlineStr">
-        <is>
-          <t>Existing Capital Loss Carryforward</t>
-        </is>
-      </c>
-      <c r="C36" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" s="29" t="inlineStr">
-        <is>
-          <t>Net Short-Term Gain / (Loss)</t>
-        </is>
-      </c>
-      <c r="C37" s="36">
-        <f>(C32-C34)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="29" t="inlineStr">
-        <is>
-          <t>Net Long-Term Gain / (Loss)</t>
-        </is>
-      </c>
-      <c r="C38" s="36">
-        <f>(C33-C35-C36)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="26" t="inlineStr">
-        <is>
-          <t>Total Net Capital Gain / (Loss)</t>
-        </is>
-      </c>
-      <c r="C39" s="35">
-        <f>(C37+C38)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41" ht="18" customHeight="1">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>4. PORTFOLIO SALE SCENARIO (optional - model a potential sale)</t>
-        </is>
-      </c>
-      <c r="B41" s="4" t="n"/>
-      <c r="C41" s="4" t="n"/>
-      <c r="D41" s="4" t="n"/>
-      <c r="E41" s="4" t="n"/>
-      <c r="F41" s="4" t="n"/>
-      <c r="G41" s="4" t="n"/>
-    </row>
-    <row r="42">
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>Investment</t>
-        </is>
-      </c>
-      <c r="C42" s="5" t="inlineStr">
-        <is>
-          <t>Current Value</t>
-        </is>
-      </c>
-      <c r="D42" s="5" t="inlineStr">
-        <is>
-          <t>Cost Basis</t>
-        </is>
-      </c>
-      <c r="E42" s="5" t="inlineStr">
-        <is>
-          <t>Holding Period</t>
-        </is>
-      </c>
-      <c r="F42" s="5" t="inlineStr">
-        <is>
-          <t>Estimated Gain / (Loss)</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="B43" s="12" t="inlineStr">
-        <is>
-          <t>XYZ Stock</t>
-        </is>
-      </c>
-      <c r="C43" s="13" t="n">
-        <v>250000</v>
-      </c>
-      <c r="D43" s="13" t="n">
-        <v>100000</v>
-      </c>
-      <c r="E43" s="12" t="inlineStr">
-        <is>
-          <t>Long-Term</t>
-        </is>
-      </c>
-      <c r="F43" s="36">
-        <f>C43-D43</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44">
-      <c r="B44" s="12" t="inlineStr"/>
-      <c r="C44" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D44" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E44" s="12" t="inlineStr">
-        <is>
-          <t>Long-Term</t>
-        </is>
-      </c>
-      <c r="F44" s="36">
-        <f>C44-D44</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" s="12" t="inlineStr"/>
-      <c r="C45" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D45" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E45" s="12" t="inlineStr">
-        <is>
-          <t>Long-Term</t>
-        </is>
-      </c>
-      <c r="F45" s="36">
-        <f>C45-D45</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46">
-      <c r="B46" s="12" t="inlineStr"/>
-      <c r="C46" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D46" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E46" s="12" t="inlineStr">
-        <is>
-          <t>Long-Term</t>
-        </is>
-      </c>
-      <c r="F46" s="36">
-        <f>C46-D46</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47">
-      <c r="B47" s="12" t="inlineStr"/>
-      <c r="C47" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D47" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E47" s="12" t="inlineStr">
-        <is>
-          <t>Long-Term</t>
-        </is>
-      </c>
-      <c r="F47" s="36">
-        <f>C47-D47</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48">
-      <c r="B48" s="12" t="inlineStr"/>
-      <c r="C48" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D48" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E48" s="12" t="inlineStr">
-        <is>
-          <t>Long-Term</t>
-        </is>
-      </c>
-      <c r="F48" s="36">
-        <f>C48-D48</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49">
-      <c r="B49" s="26" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C49" s="37">
-        <f>SUM(C43:C48)</f>
-        <v/>
-      </c>
-      <c r="F49" s="37">
-        <f>SUM(F43:F48)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50">
-      <c r="B50" s="33" t="inlineStr">
-        <is>
-          <t>Leave the Investment name blank on any row you don't need. Gain/Loss is calculated automatically as Current Value minus Cost Basis.</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="18" customHeight="1">
-      <c r="A52" s="3" t="inlineStr">
-        <is>
-          <t>5. ESTIMATED TAX</t>
-        </is>
-      </c>
-      <c r="B52" s="4" t="n"/>
-      <c r="C52" s="4" t="n"/>
-      <c r="D52" s="4" t="n"/>
-      <c r="E52" s="4" t="n"/>
-      <c r="F52" s="4" t="n"/>
-      <c r="G52" s="4" t="n"/>
-    </row>
-    <row r="53" ht="18" customHeight="1">
-      <c r="B53" s="38" t="inlineStr">
-        <is>
-          <t>Net Capital Gain / Loss (including the sale scenario above)</t>
-        </is>
-      </c>
-      <c r="C53" s="39" t="n"/>
-    </row>
-    <row r="54">
-      <c r="B54" s="29" t="inlineStr">
-        <is>
-          <t>Total Capital Gains</t>
-        </is>
-      </c>
-      <c r="C54" s="40">
-        <f>((C32+C117)+(C33+C119))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55">
-      <c r="B55" s="29" t="inlineStr">
-        <is>
-          <t>Total Capital Losses</t>
-        </is>
-      </c>
-      <c r="C55" s="40">
-        <f>-((C34+C118)+(C35+C120)+C36)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="56">
-      <c r="B56" s="26" t="inlineStr">
-        <is>
-          <t>Net Capital Gain / (Loss)</t>
-        </is>
-      </c>
-      <c r="C56" s="41">
-        <f>C143</f>
-        <v/>
-      </c>
-    </row>
-    <row r="57">
-      <c r="B57" s="29" t="inlineStr">
-        <is>
-          <t>Current-Year Capital Loss Deduction</t>
-        </is>
-      </c>
-      <c r="C57" s="40">
-        <f>IF(C143&lt;0,MAX(C143,-C113),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="58">
-      <c r="B58" s="29" t="inlineStr">
-        <is>
-          <t>Capital Loss Carryforward to Future Years</t>
-        </is>
-      </c>
-      <c r="C58" s="40">
-        <f>-C146</f>
-        <v/>
-      </c>
-    </row>
-    <row r="60" ht="18" customHeight="1">
-      <c r="B60" s="38" t="inlineStr">
-        <is>
-          <t>Before vs. After the Sale</t>
-        </is>
-      </c>
-      <c r="C60" s="39" t="n"/>
-    </row>
-    <row r="61" ht="28" customHeight="1">
-      <c r="C61" s="5" t="inlineStr">
-        <is>
-          <t>Without Realizing
-the Gain</t>
-        </is>
-      </c>
-      <c r="D61" s="5" t="inlineStr">
-        <is>
-          <t>After Realizing
-the Gain</t>
-        </is>
-      </c>
-      <c r="E61" s="5" t="inlineStr">
-        <is>
-          <t>Incremental
-(From the Sale)</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="B62" s="29" t="inlineStr">
-        <is>
-          <t>Estimated Federal Tax</t>
-        </is>
-      </c>
-      <c r="C62" s="36">
-        <f>C132</f>
-        <v/>
-      </c>
-      <c r="D62" s="36">
-        <f>C150</f>
-        <v/>
-      </c>
-      <c r="E62" s="36">
-        <f>D62-C62</f>
-        <v/>
-      </c>
-    </row>
-    <row r="63">
-      <c r="B63" s="29" t="inlineStr">
-        <is>
-          <t>Estimated State Tax</t>
-        </is>
-      </c>
-      <c r="C63" s="36">
-        <f>C137</f>
-        <v/>
-      </c>
-      <c r="D63" s="36">
-        <f>C155</f>
-        <v/>
-      </c>
-      <c r="E63" s="36">
-        <f>D63-C63</f>
-        <v/>
-      </c>
-    </row>
-    <row r="64">
-      <c r="B64" s="29" t="inlineStr">
-        <is>
-          <t>Estimated NIIT</t>
-        </is>
-      </c>
-      <c r="C64" s="36">
-        <f>C135</f>
-        <v/>
-      </c>
-      <c r="D64" s="36">
-        <f>C153</f>
-        <v/>
-      </c>
-      <c r="E64" s="36">
-        <f>D64-C64</f>
-        <v/>
-      </c>
-    </row>
-    <row r="65">
-      <c r="B65" s="26" t="inlineStr">
-        <is>
-          <t>Total Estimated Tax</t>
-        </is>
-      </c>
-      <c r="C65" s="35">
-        <f>C138</f>
-        <v/>
-      </c>
-      <c r="D65" s="35">
-        <f>C156</f>
-        <v/>
-      </c>
-      <c r="E65" s="35">
-        <f>D65-C65</f>
-        <v/>
-      </c>
-    </row>
-    <row r="67">
-      <c r="B67" s="29" t="inlineStr">
-        <is>
-          <t>Your Long-Term Capital Gains Rate (marginal, after the sale)</t>
-        </is>
-      </c>
-      <c r="C67" s="32">
-        <f>C157</f>
-        <v/>
-      </c>
-    </row>
-    <row r="69">
-      <c r="F69" s="7" t="inlineStr">
-        <is>
-          <t>Tax Component</t>
-        </is>
-      </c>
-      <c r="G69" s="7" t="inlineStr">
-        <is>
-          <t>Amount</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="F70" s="42" t="inlineStr">
-        <is>
-          <t>Federal Tax</t>
-        </is>
-      </c>
-      <c r="G70" s="43">
-        <f>E62</f>
-        <v/>
-      </c>
-    </row>
-    <row r="71">
-      <c r="F71" s="42" t="inlineStr">
-        <is>
-          <t>State Tax</t>
-        </is>
-      </c>
-      <c r="G71" s="43">
-        <f>E63</f>
-        <v/>
-      </c>
-    </row>
-    <row r="72">
-      <c r="F72" s="42" t="inlineStr">
-        <is>
-          <t>NIIT</t>
-        </is>
-      </c>
-      <c r="G72" s="43">
-        <f>E64</f>
-        <v/>
-      </c>
-    </row>
-    <row r="87" ht="18" customHeight="1">
-      <c r="A87" s="3" t="inlineStr">
-        <is>
-          <t>6. AFTER-TAX PROCEEDS (from the Portfolio Sale Scenario)</t>
-        </is>
-      </c>
-      <c r="B87" s="4" t="n"/>
-      <c r="C87" s="4" t="n"/>
-      <c r="D87" s="4" t="n"/>
-      <c r="E87" s="4" t="n"/>
-      <c r="F87" s="4" t="n"/>
-      <c r="G87" s="4" t="n"/>
-    </row>
-    <row r="88">
-      <c r="B88" s="29" t="inlineStr">
-        <is>
-          <t>Sale Proceeds</t>
-        </is>
-      </c>
-      <c r="C88" s="35">
-        <f>C49</f>
-        <v/>
-      </c>
-    </row>
-    <row r="89">
-      <c r="B89" s="29" t="inlineStr">
-        <is>
-          <t>Less: Estimated Tax From Sale</t>
-        </is>
-      </c>
-      <c r="C89" s="36">
-        <f>-E65</f>
-        <v/>
-      </c>
-    </row>
-    <row r="90">
-      <c r="B90" s="26" t="inlineStr">
-        <is>
-          <t>Estimated After-Tax Proceeds</t>
-        </is>
-      </c>
-      <c r="C90" s="35">
-        <f>C88+C89</f>
-        <v/>
-      </c>
-    </row>
-    <row r="91">
-      <c r="B91" s="29" t="inlineStr">
-        <is>
-          <t>Estimated Tax Rate on Gain</t>
-        </is>
-      </c>
-      <c r="C91" s="44">
-        <f>IFERROR(E65/F49,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="93" ht="18" customHeight="1">
-      <c r="A93" s="3" t="inlineStr">
-        <is>
-          <t>7. TAX-LOSS HARVESTING - WHAT IF?</t>
-        </is>
-      </c>
-      <c r="B93" s="4" t="n"/>
-      <c r="C93" s="4" t="n"/>
-      <c r="D93" s="4" t="n"/>
-      <c r="E93" s="4" t="n"/>
-      <c r="F93" s="4" t="n"/>
-      <c r="G93" s="4" t="n"/>
-    </row>
-    <row r="94">
-      <c r="B94" s="25" t="inlineStr">
-        <is>
-          <t>Model harvesting an additional loss on top of the sale scenario above (assumed long-term).</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="B95" s="26" t="inlineStr">
-        <is>
-          <t>Potential Additional Loss to Harvest</t>
-        </is>
-      </c>
-      <c r="C95" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="B96" s="29" t="inlineStr">
-        <is>
-          <t>Current Estimated Tax (with sale, before harvesting)</t>
-        </is>
-      </c>
-      <c r="C96" s="36">
-        <f>C156</f>
-        <v/>
-      </c>
-    </row>
-    <row r="97">
-      <c r="B97" s="29" t="inlineStr">
-        <is>
-          <t>Estimated Tax After Harvesting</t>
-        </is>
-      </c>
-      <c r="C97" s="36">
-        <f>C174</f>
-        <v/>
-      </c>
-    </row>
-    <row r="98">
-      <c r="B98" s="26" t="inlineStr">
-        <is>
-          <t>Estimated Tax Savings From Harvesting</t>
-        </is>
-      </c>
-      <c r="C98" s="35">
-        <f>C96-C97</f>
-        <v/>
-      </c>
-    </row>
-    <row r="99">
-      <c r="B99" s="29" t="inlineStr">
-        <is>
-          <t>Remaining Capital Loss Carryforward After Harvesting</t>
-        </is>
-      </c>
-      <c r="C99" s="36">
-        <f>-C164</f>
-        <v/>
-      </c>
-    </row>
-    <row r="101">
-      <c r="B101" s="45" t="inlineStr">
-        <is>
-          <t>Full calculation detail is available below for your advisor. Click the [+] in the row-number margin to expand.</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="B103" s="46" t="inlineStr">
-        <is>
-          <t>Estimated for financial-planning purposes only. This calculator is not tax, legal, or accounting advice. Actual tax liability may differ based on individual circumstances, deductions, credits, tax elections, state/local rules, and other factors. Consult a qualified tax professional before making tax-related decisions.</t>
-        </is>
-      </c>
-    </row>
-    <row r="104"/>
-    <row r="105"/>
-    <row r="107" hidden="1" outlineLevel="1" collapsed="1">
-      <c r="A107" s="47" t="inlineStr">
-        <is>
-          <t>CALCULATION DETAIL (grouped - click + to expand)</t>
-        </is>
-      </c>
-    </row>
-    <row r="108" hidden="1" outlineLevel="1"/>
-    <row r="109" hidden="1" outlineLevel="1">
-      <c r="B109" s="48" t="inlineStr">
-        <is>
-          <t>Standard Deduction (add-back for MAGI estimate)</t>
-        </is>
-      </c>
-      <c r="C109" s="49">
-        <f>INDEX('Tax Rates &amp; Assumptions'!$D$28:$D$35,L114)</f>
-        <v/>
-      </c>
-      <c r="K109" s="7" t="inlineStr">
-        <is>
-          <t>Filing Status</t>
-        </is>
-      </c>
-      <c r="L109" s="42">
-        <f>C12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="110" hidden="1" outlineLevel="1">
-      <c r="B110" s="48" t="inlineStr">
-        <is>
-          <t>Taxable Ordinary Income - Option A (direct entry)</t>
-        </is>
-      </c>
-      <c r="C110" s="49">
-        <f>C24</f>
-        <v/>
-      </c>
-      <c r="K110" s="7" t="inlineStr">
-        <is>
-          <t>Tax Year</t>
-        </is>
-      </c>
-      <c r="L110" s="42">
-        <f>C11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="111" hidden="1" outlineLevel="1">
-      <c r="B111" s="48" t="inlineStr">
-        <is>
-          <t>Taxable Ordinary Income - Option B (Gross - Pretax - Deductions)</t>
-        </is>
-      </c>
-      <c r="C111" s="49">
-        <f>MAX(0,C25+C26-C27-C28)</f>
-        <v/>
-      </c>
-      <c r="K111" s="7" t="inlineStr">
-        <is>
-          <t>Federal Key</t>
-        </is>
-      </c>
-      <c r="L111" s="42">
-        <f>L110&amp;"|"&amp;L109</f>
-        <v/>
-      </c>
-    </row>
-    <row r="112" hidden="1" outlineLevel="1">
-      <c r="B112" s="50" t="inlineStr">
-        <is>
-          <t>Estimated Taxable Ordinary Income (per method selected)</t>
-        </is>
-      </c>
-      <c r="C112" s="49">
-        <f>IF(C23="Option A: Enter Taxable Income Directly",C110,C111)</f>
-        <v/>
-      </c>
-      <c r="K112" s="7" t="inlineStr">
-        <is>
-          <t>Fed Bracket Row#</t>
-        </is>
-      </c>
-      <c r="L112" s="42">
-        <f>MATCH(L111,'Tax Rates &amp; Assumptions'!$C$6:$C$13,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="113" hidden="1" outlineLevel="1">
-      <c r="B113" s="48" t="inlineStr">
-        <is>
-          <t>Capital Loss Limit vs. Ordinary Income</t>
-        </is>
-      </c>
-      <c r="C113" s="49">
-        <f>INDEX('Tax Rates &amp; Assumptions'!$D$39:$D$42,L115)</f>
-        <v/>
-      </c>
-      <c r="K113" s="7" t="inlineStr">
-        <is>
-          <t>LTCG Bracket Row#</t>
-        </is>
-      </c>
-      <c r="L113" s="42">
-        <f>MATCH(L111,'Tax Rates &amp; Assumptions'!$C$17:$C$24,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="114" hidden="1" outlineLevel="1">
-      <c r="B114" s="48" t="inlineStr">
-        <is>
-          <t>NIIT Threshold</t>
-        </is>
-      </c>
-      <c r="C114" s="49">
-        <f>INDEX('Tax Rates &amp; Assumptions'!$B$39:$B$42,L115)</f>
-        <v/>
-      </c>
-      <c r="K114" s="7" t="inlineStr">
-        <is>
-          <t>StdDed Row#</t>
-        </is>
-      </c>
-      <c r="L114" s="42">
-        <f>MATCH(L111,'Tax Rates &amp; Assumptions'!$C$28:$C$35,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="115" hidden="1" outlineLevel="1">
-      <c r="B115" s="48" t="inlineStr">
-        <is>
-          <t>NIIT Rate</t>
-        </is>
-      </c>
-      <c r="C115" s="51">
-        <f>INDEX('Tax Rates &amp; Assumptions'!$C$39:$C$42,L115)</f>
-        <v/>
-      </c>
-      <c r="K115" s="7" t="inlineStr">
-        <is>
-          <t>Status Row# (NIIT/CapLoss)</t>
-        </is>
-      </c>
-      <c r="L115" s="42">
-        <f>MATCH(L109,'Tax Rates &amp; Assumptions'!$A$39:$A$42,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="116" hidden="1" outlineLevel="1">
-      <c r="B116" s="48" t="inlineStr">
-        <is>
-          <t>State Standard Deduction</t>
-        </is>
-      </c>
-      <c r="C116" s="49">
-        <f>IF(L118="MFJ",INDEX('Tax Rates &amp; Assumptions'!$E$46:$E$77,L121),INDEX('Tax Rates &amp; Assumptions'!$D$46:$D$77,L121))</f>
-        <v/>
-      </c>
-      <c r="K116" s="7" t="inlineStr">
-        <is>
-          <t>State Name</t>
-        </is>
-      </c>
-      <c r="L116" s="42">
-        <f>C13</f>
-        <v/>
-      </c>
-    </row>
-    <row r="117" hidden="1" outlineLevel="1">
-      <c r="B117" s="48" t="inlineStr">
-        <is>
-          <t>Sale Scenario - Short-Term Gain Total</t>
-        </is>
-      </c>
-      <c r="C117" s="49">
-        <f>SUMIFS(F43:F48,E43:E48,"Short-Term",F43:F48,"&gt;0")</f>
-        <v/>
-      </c>
-      <c r="K117" s="7" t="inlineStr">
-        <is>
-          <t>State Code</t>
-        </is>
-      </c>
-      <c r="L117" s="42">
-        <f>INDEX('Tax Rates &amp; Assumptions'!$A$46:$A$77,MATCH(L116,'Tax Rates &amp; Assumptions'!$B$46:$B$77,0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="118" hidden="1" outlineLevel="1">
-      <c r="B118" s="48" t="inlineStr">
-        <is>
-          <t>Sale Scenario - Short-Term Loss Total</t>
-        </is>
-      </c>
-      <c r="C118" s="49">
-        <f>-SUMIFS(F43:F48,E43:E48,"Short-Term",F43:F48,"&lt;0")</f>
-        <v/>
-      </c>
-      <c r="K118" s="7" t="inlineStr">
-        <is>
-          <t>State Category</t>
-        </is>
-      </c>
-      <c r="L118" s="42">
-        <f>IF(L109="Married Filing Jointly","MFJ","Single")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="119" hidden="1" outlineLevel="1">
-      <c r="B119" s="48" t="inlineStr">
-        <is>
-          <t>Sale Scenario - Long-Term Gain Total</t>
-        </is>
-      </c>
-      <c r="C119" s="49">
-        <f>SUMIFS(F43:F48,E43:E48,"Long-Term",F43:F48,"&gt;0")</f>
-        <v/>
-      </c>
-      <c r="K119" s="7" t="inlineStr">
-        <is>
-          <t>State Key</t>
-        </is>
-      </c>
-      <c r="L119" s="42">
-        <f>L117&amp;"|"&amp;L118</f>
-        <v/>
-      </c>
-    </row>
-    <row r="120" hidden="1" outlineLevel="1">
-      <c r="B120" s="48" t="inlineStr">
-        <is>
-          <t>Sale Scenario - Long-Term Loss Total</t>
-        </is>
-      </c>
-      <c r="C120" s="49">
-        <f>-SUMIFS(F43:F48,E43:E48,"Long-Term",F43:F48,"&lt;0")</f>
-        <v/>
-      </c>
-      <c r="K120" s="7" t="inlineStr">
-        <is>
-          <t>State Bracket Row#</t>
-        </is>
-      </c>
-      <c r="L120" s="42">
-        <f>MATCH(L119,'Tax Rates &amp; Assumptions'!$C$81:$C$144,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="121" hidden="1" outlineLevel="1">
-      <c r="K121" s="7" t="inlineStr">
-        <is>
-          <t>State Master Row#</t>
-        </is>
-      </c>
-      <c r="L121" s="42">
-        <f>MATCH(L117,'Tax Rates &amp; Assumptions'!$A$46:$A$77,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="122" hidden="1" outlineLevel="1">
-      <c r="A122" s="52" t="inlineStr">
-        <is>
-          <t>-- BEFORE (current year only) --</t>
-        </is>
-      </c>
-    </row>
-    <row r="123" hidden="1" outlineLevel="1">
-      <c r="B123" s="53" t="inlineStr">
-        <is>
-          <t>Net Short-Term Gain / (Loss)</t>
-        </is>
-      </c>
-      <c r="C123" s="54">
-        <f>(C32-C34)</f>
-        <v/>
-      </c>
-      <c r="K123" s="52" t="inlineStr">
-        <is>
-          <t>Federal Ordinary Brackets</t>
-        </is>
-      </c>
-    </row>
-    <row r="124" hidden="1" outlineLevel="1">
-      <c r="B124" s="53" t="inlineStr">
-        <is>
-          <t>Net Long-Term Gain / (Loss), net of carryforward</t>
-        </is>
-      </c>
-      <c r="C124" s="54">
-        <f>(C33-C35-C36)</f>
-        <v/>
-      </c>
-      <c r="L124" s="55">
-        <f>INDEX('Tax Rates &amp; Assumptions'!D$6:D$1005,L112)</f>
-        <v/>
-      </c>
-      <c r="M124" s="56">
-        <f>INDEX('Tax Rates &amp; Assumptions'!E$6:E$1005,L112)</f>
-        <v/>
-      </c>
-      <c r="N124" s="56">
-        <f>INDEX('Tax Rates &amp; Assumptions'!F$6:F$1005,L112)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="125" hidden="1" outlineLevel="1">
-      <c r="B125" s="53" t="inlineStr">
-        <is>
-          <t>Combined Net Capital Gain / (Loss)</t>
-        </is>
-      </c>
-      <c r="C125" s="54">
-        <f>(C123+C124)</f>
-        <v/>
-      </c>
-      <c r="L125" s="55">
-        <f>INDEX('Tax Rates &amp; Assumptions'!G$6:G$1005,L112)</f>
-        <v/>
-      </c>
-      <c r="M125" s="56">
-        <f>INDEX('Tax Rates &amp; Assumptions'!H$6:H$1005,L112)</f>
-        <v/>
-      </c>
-      <c r="N125" s="56">
-        <f>INDEX('Tax Rates &amp; Assumptions'!I$6:I$1005,L112)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="126" hidden="1" outlineLevel="1">
-      <c r="B126" s="53" t="inlineStr">
-        <is>
-          <t>Ordinary-Taxed Capital Gain / (Loss Deduction, capped)</t>
-        </is>
-      </c>
-      <c r="C126" s="54">
-        <f>IF(C125&lt;=0,MAX(C125,-C113),IF(AND(C123&gt;=0,C124&gt;=0),C123,IF(AND(C123&lt;0,C124&gt;=0),0,IF(AND(C123&gt;=0,C124&lt;0),C125,0))))</f>
-        <v/>
-      </c>
-      <c r="L126" s="55">
-        <f>INDEX('Tax Rates &amp; Assumptions'!J$6:J$1005,L112)</f>
-        <v/>
-      </c>
-      <c r="M126" s="56">
-        <f>INDEX('Tax Rates &amp; Assumptions'!K$6:K$1005,L112)</f>
-        <v/>
-      </c>
-      <c r="N126" s="56">
-        <f>INDEX('Tax Rates &amp; Assumptions'!L$6:L$1005,L112)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="127" hidden="1" outlineLevel="1">
-      <c r="B127" s="53" t="inlineStr">
-        <is>
-          <t>Preferential (LTCG-Rate) Net Capital Gain</t>
-        </is>
-      </c>
-      <c r="C127" s="54">
-        <f>IF(C125&lt;=0,0,IF(AND(C123&gt;=0,C124&gt;=0),C124,IF(AND(C123&lt;0,C124&gt;=0),C125,IF(AND(C123&gt;=0,C124&lt;0),0,0))))</f>
-        <v/>
-      </c>
-      <c r="L127" s="55">
-        <f>INDEX('Tax Rates &amp; Assumptions'!M$6:M$1005,L112)</f>
-        <v/>
-      </c>
-      <c r="M127" s="56">
-        <f>INDEX('Tax Rates &amp; Assumptions'!N$6:N$1005,L112)</f>
-        <v/>
-      </c>
-      <c r="N127" s="56">
-        <f>INDEX('Tax Rates &amp; Assumptions'!O$6:O$1005,L112)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="128" hidden="1" outlineLevel="1">
-      <c r="B128" s="53" t="inlineStr">
-        <is>
-          <t>Capital Loss Carryforward to Future Years</t>
-        </is>
-      </c>
-      <c r="C128" s="54">
-        <f>IF(C125&lt;=0,C125-MAX(C125,-C113),0)</f>
-        <v/>
-      </c>
-      <c r="L128" s="55">
-        <f>INDEX('Tax Rates &amp; Assumptions'!P$6:P$1005,L112)</f>
-        <v/>
-      </c>
-      <c r="M128" s="56">
-        <f>INDEX('Tax Rates &amp; Assumptions'!Q$6:Q$1005,L112)</f>
-        <v/>
-      </c>
-      <c r="N128" s="56">
-        <f>INDEX('Tax Rates &amp; Assumptions'!R$6:R$1005,L112)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="129" hidden="1" outlineLevel="1">
-      <c r="B129" s="53" t="inlineStr">
-        <is>
-          <t>Ordinary Taxable Income Including Gain</t>
-        </is>
-      </c>
-      <c r="C129" s="54">
-        <f>MAX(0,C112+C126)</f>
-        <v/>
-      </c>
-      <c r="L129" s="55">
-        <f>INDEX('Tax Rates &amp; Assumptions'!S$6:S$1005,L112)</f>
-        <v/>
-      </c>
-      <c r="M129" s="56">
-        <f>INDEX('Tax Rates &amp; Assumptions'!T$6:T$1005,L112)</f>
-        <v/>
-      </c>
-      <c r="N129" s="56">
-        <f>INDEX('Tax Rates &amp; Assumptions'!U$6:U$1005,L112)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="130" hidden="1" outlineLevel="1">
-      <c r="B130" s="53" t="inlineStr">
-        <is>
-          <t>Federal Ordinary Tax</t>
-        </is>
-      </c>
-      <c r="C130" s="54">
-        <f>SUMPRODUCT((C129&gt;$M$124:$M$130)*($L$124:$L$130)*(MIN(C129,$N$124:$N$130)-$M$124:$M$130))</f>
-        <v/>
-      </c>
-      <c r="L130" s="55">
-        <f>INDEX('Tax Rates &amp; Assumptions'!V$6:V$1005,L112)</f>
-        <v/>
-      </c>
-      <c r="M130" s="56">
-        <f>INDEX('Tax Rates &amp; Assumptions'!W$6:W$1005,L112)</f>
-        <v/>
-      </c>
-      <c r="N130" s="56">
-        <f>INDEX('Tax Rates &amp; Assumptions'!X$6:X$1005,L112)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="131" hidden="1" outlineLevel="1">
-      <c r="B131" s="53" t="inlineStr">
-        <is>
-          <t>Federal Long-Term Capital Gains Tax (stacked)</t>
-        </is>
-      </c>
-      <c r="C131" s="54">
-        <f>SUMPRODUCT($L$133:$L$135*(MAX(0,MIN((C129+C127),$N$133:$N$135)-MAX(C129,$M$133:$M$135))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="132" hidden="1" outlineLevel="1">
-      <c r="B132" s="57" t="inlineStr">
-        <is>
-          <t>Total Federal Tax</t>
-        </is>
-      </c>
-      <c r="C132" s="54">
-        <f>(C130+C131)</f>
-        <v/>
-      </c>
-      <c r="K132" s="52" t="inlineStr">
+      <c r="C80" s="36">
+        <f>(C73+C74+C77+C79)</f>
+        <v/>
+      </c>
+      <c r="L80" s="30">
+        <f>INDEX('Tax Rates &amp; Assumptions'!V$6:V$1005,L62)</f>
+        <v/>
+      </c>
+      <c r="M80" s="31">
+        <f>INDEX('Tax Rates &amp; Assumptions'!W$6:W$1005,L62)</f>
+        <v/>
+      </c>
+      <c r="N80" s="31">
+        <f>INDEX('Tax Rates &amp; Assumptions'!X$6:X$1005,L62)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81" hidden="1" outlineLevel="1">
+      <c r="B81" s="32" t="inlineStr">
+        <is>
+          <t>Effective Tax Rate on the Gain</t>
+        </is>
+      </c>
+      <c r="C81" s="37">
+        <f>IFERROR(C80/MAX(0.0001,C66),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82" hidden="1" outlineLevel="1">
+      <c r="B82" s="32" t="inlineStr">
+        <is>
+          <t>Marginal LTCG Rate Applied</t>
+        </is>
+      </c>
+      <c r="C82" s="37">
+        <f>IFERROR(INDEX($L$83:$L$85,MATCH(C70,$M$83:$M$85,1)),0)</f>
+        <v/>
+      </c>
+      <c r="K82" s="29" t="inlineStr">
         <is>
           <t>LTCG Brackets</t>
         </is>
       </c>
     </row>
-    <row r="133" hidden="1" outlineLevel="1">
-      <c r="B133" s="53" t="inlineStr">
-        <is>
-          <t>MAGI Estimate (Taxable Income + Std. Ded. Add-Back + Net Gain)</t>
-        </is>
-      </c>
-      <c r="C133" s="54">
-        <f>(C112+C109+C126+C127)</f>
-        <v/>
-      </c>
-      <c r="L133" s="55">
-        <f>INDEX('Tax Rates &amp; Assumptions'!D$17:D$1016,L113)</f>
-        <v/>
-      </c>
-      <c r="M133" s="56">
-        <f>INDEX('Tax Rates &amp; Assumptions'!E$17:E$1016,L113)</f>
-        <v/>
-      </c>
-      <c r="N133" s="56">
-        <f>INDEX('Tax Rates &amp; Assumptions'!F$17:F$1016,L113)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="134" hidden="1" outlineLevel="1">
-      <c r="B134" s="53" t="inlineStr">
-        <is>
-          <t>Net Investment Income (the modeled capital gain)</t>
-        </is>
-      </c>
-      <c r="C134" s="54">
-        <f>MAX(0,C126+C127)</f>
-        <v/>
-      </c>
-      <c r="L134" s="55">
-        <f>INDEX('Tax Rates &amp; Assumptions'!G$17:G$1016,L113)</f>
-        <v/>
-      </c>
-      <c r="M134" s="56">
-        <f>INDEX('Tax Rates &amp; Assumptions'!H$17:H$1016,L113)</f>
-        <v/>
-      </c>
-      <c r="N134" s="56">
-        <f>INDEX('Tax Rates &amp; Assumptions'!I$17:I$1016,L113)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="135" hidden="1" outlineLevel="1">
-      <c r="B135" s="57" t="inlineStr">
-        <is>
-          <t>NIIT</t>
-        </is>
-      </c>
-      <c r="C135" s="54">
-        <f>C115*MIN(C134,MAX(0,C133-C114))</f>
-        <v/>
-      </c>
-      <c r="L135" s="55">
-        <f>INDEX('Tax Rates &amp; Assumptions'!J$17:J$1016,L113)</f>
-        <v/>
-      </c>
-      <c r="M135" s="56">
-        <f>INDEX('Tax Rates &amp; Assumptions'!K$17:K$1016,L113)</f>
-        <v/>
-      </c>
-      <c r="N135" s="56">
-        <f>INDEX('Tax Rates &amp; Assumptions'!L$17:L$1016,L113)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="136" hidden="1" outlineLevel="1">
-      <c r="B136" s="53" t="inlineStr">
-        <is>
-          <t>State Taxable Income (gain taxed as ordinary income)</t>
-        </is>
-      </c>
-      <c r="C136" s="54">
-        <f>MAX(0,C112+C126+C127-C116)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="137" hidden="1" outlineLevel="1">
-      <c r="B137" s="57" t="inlineStr">
-        <is>
-          <t>State Tax</t>
-        </is>
-      </c>
-      <c r="C137" s="54">
-        <f>IF(L117="OTHER",C14*C136,SUMPRODUCT((C136&gt;$M$138:$M$145)*($L$138:$L$145)*(MIN(C136,$N$138:$N$145)-$M$138:$M$145)))</f>
-        <v/>
-      </c>
-      <c r="K137" s="52" t="inlineStr">
+    <row r="83" hidden="1" outlineLevel="1">
+      <c r="L83" s="30">
+        <f>INDEX('Tax Rates &amp; Assumptions'!D$17:D$1016,L63)</f>
+        <v/>
+      </c>
+      <c r="M83" s="31">
+        <f>INDEX('Tax Rates &amp; Assumptions'!E$17:E$1016,L63)</f>
+        <v/>
+      </c>
+      <c r="N83" s="31">
+        <f>INDEX('Tax Rates &amp; Assumptions'!F$17:F$1016,L63)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84" hidden="1" outlineLevel="1">
+      <c r="L84" s="30">
+        <f>INDEX('Tax Rates &amp; Assumptions'!G$17:G$1016,L63)</f>
+        <v/>
+      </c>
+      <c r="M84" s="31">
+        <f>INDEX('Tax Rates &amp; Assumptions'!H$17:H$1016,L63)</f>
+        <v/>
+      </c>
+      <c r="N84" s="31">
+        <f>INDEX('Tax Rates &amp; Assumptions'!I$17:I$1016,L63)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85" hidden="1" outlineLevel="1">
+      <c r="L85" s="30">
+        <f>INDEX('Tax Rates &amp; Assumptions'!J$17:J$1016,L63)</f>
+        <v/>
+      </c>
+      <c r="M85" s="31">
+        <f>INDEX('Tax Rates &amp; Assumptions'!K$17:K$1016,L63)</f>
+        <v/>
+      </c>
+      <c r="N85" s="31">
+        <f>INDEX('Tax Rates &amp; Assumptions'!L$17:L$1016,L63)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86" hidden="1" outlineLevel="1"/>
+    <row r="87" hidden="1" outlineLevel="1">
+      <c r="K87" s="29" t="inlineStr">
         <is>
           <t>State Brackets</t>
         </is>
       </c>
     </row>
-    <row r="138" hidden="1" outlineLevel="1">
-      <c r="B138" s="58" t="inlineStr">
-        <is>
-          <t>Total Estimated Tax (Federal + State + NIIT)</t>
-        </is>
-      </c>
-      <c r="C138" s="59">
-        <f>(C132+C137+C135)</f>
-        <v/>
-      </c>
-      <c r="L138" s="55">
-        <f>INDEX('Tax Rates &amp; Assumptions'!D$81:D$1080,L120)</f>
-        <v/>
-      </c>
-      <c r="M138" s="56">
-        <f>INDEX('Tax Rates &amp; Assumptions'!E$81:E$1080,L120)</f>
-        <v/>
-      </c>
-      <c r="N138" s="56">
-        <f>INDEX('Tax Rates &amp; Assumptions'!F$81:F$1080,L120)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="139" hidden="1" outlineLevel="1">
-      <c r="B139" s="53" t="inlineStr">
-        <is>
-          <t>Marginal LTCG Rate Applied</t>
-        </is>
-      </c>
-      <c r="C139" s="60">
-        <f>IFERROR(INDEX($L$133:$L$135,MATCH(C129,$M$133:$M$135,1)),0)</f>
-        <v/>
-      </c>
-      <c r="L139" s="55">
-        <f>INDEX('Tax Rates &amp; Assumptions'!G$81:G$1080,L120)</f>
-        <v/>
-      </c>
-      <c r="M139" s="56">
-        <f>INDEX('Tax Rates &amp; Assumptions'!H$81:H$1080,L120)</f>
-        <v/>
-      </c>
-      <c r="N139" s="56">
-        <f>INDEX('Tax Rates &amp; Assumptions'!I$81:I$1080,L120)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="140" hidden="1" outlineLevel="1">
-      <c r="A140" s="52" t="inlineStr">
-        <is>
-          <t>-- AFTER (current year + sale scenario) --</t>
-        </is>
-      </c>
-      <c r="L140" s="55">
-        <f>INDEX('Tax Rates &amp; Assumptions'!J$81:J$1080,L120)</f>
-        <v/>
-      </c>
-      <c r="M140" s="56">
-        <f>INDEX('Tax Rates &amp; Assumptions'!K$81:K$1080,L120)</f>
-        <v/>
-      </c>
-      <c r="N140" s="56">
-        <f>INDEX('Tax Rates &amp; Assumptions'!L$81:L$1080,L120)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="141" hidden="1" outlineLevel="1">
-      <c r="B141" s="53" t="inlineStr">
-        <is>
-          <t>Net Short-Term Gain / (Loss)</t>
-        </is>
-      </c>
-      <c r="C141" s="54">
-        <f>((C32+C117)-(C34+C118))</f>
-        <v/>
-      </c>
-      <c r="L141" s="55">
-        <f>INDEX('Tax Rates &amp; Assumptions'!M$81:M$1080,L120)</f>
-        <v/>
-      </c>
-      <c r="M141" s="56">
-        <f>INDEX('Tax Rates &amp; Assumptions'!N$81:N$1080,L120)</f>
-        <v/>
-      </c>
-      <c r="N141" s="56">
-        <f>INDEX('Tax Rates &amp; Assumptions'!O$81:O$1080,L120)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="142" hidden="1" outlineLevel="1">
-      <c r="B142" s="53" t="inlineStr">
-        <is>
-          <t>Net Long-Term Gain / (Loss), net of carryforward</t>
-        </is>
-      </c>
-      <c r="C142" s="54">
-        <f>((C33+C119)-(C35+C120)-C36)</f>
-        <v/>
-      </c>
-      <c r="L142" s="55">
-        <f>INDEX('Tax Rates &amp; Assumptions'!P$81:P$1080,L120)</f>
-        <v/>
-      </c>
-      <c r="M142" s="56">
-        <f>INDEX('Tax Rates &amp; Assumptions'!Q$81:Q$1080,L120)</f>
-        <v/>
-      </c>
-      <c r="N142" s="56">
-        <f>INDEX('Tax Rates &amp; Assumptions'!R$81:R$1080,L120)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="143" hidden="1" outlineLevel="1">
-      <c r="B143" s="53" t="inlineStr">
-        <is>
-          <t>Combined Net Capital Gain / (Loss)</t>
-        </is>
-      </c>
-      <c r="C143" s="54">
-        <f>(C141+C142)</f>
-        <v/>
-      </c>
-      <c r="L143" s="55">
-        <f>INDEX('Tax Rates &amp; Assumptions'!S$81:S$1080,L120)</f>
-        <v/>
-      </c>
-      <c r="M143" s="56">
-        <f>INDEX('Tax Rates &amp; Assumptions'!T$81:T$1080,L120)</f>
-        <v/>
-      </c>
-      <c r="N143" s="56">
-        <f>INDEX('Tax Rates &amp; Assumptions'!U$81:U$1080,L120)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="144" hidden="1" outlineLevel="1">
-      <c r="B144" s="53" t="inlineStr">
-        <is>
-          <t>Ordinary-Taxed Capital Gain / (Loss Deduction, capped)</t>
-        </is>
-      </c>
-      <c r="C144" s="54">
-        <f>IF(C143&lt;=0,MAX(C143,-C113),IF(AND(C141&gt;=0,C142&gt;=0),C141,IF(AND(C141&lt;0,C142&gt;=0),0,IF(AND(C141&gt;=0,C142&lt;0),C143,0))))</f>
-        <v/>
-      </c>
-      <c r="L144" s="55">
-        <f>INDEX('Tax Rates &amp; Assumptions'!V$81:V$1080,L120)</f>
-        <v/>
-      </c>
-      <c r="M144" s="56">
-        <f>INDEX('Tax Rates &amp; Assumptions'!W$81:W$1080,L120)</f>
-        <v/>
-      </c>
-      <c r="N144" s="56">
-        <f>INDEX('Tax Rates &amp; Assumptions'!X$81:X$1080,L120)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="145" hidden="1" outlineLevel="1">
-      <c r="B145" s="53" t="inlineStr">
-        <is>
-          <t>Preferential (LTCG-Rate) Net Capital Gain</t>
-        </is>
-      </c>
-      <c r="C145" s="54">
-        <f>IF(C143&lt;=0,0,IF(AND(C141&gt;=0,C142&gt;=0),C142,IF(AND(C141&lt;0,C142&gt;=0),C143,IF(AND(C141&gt;=0,C142&lt;0),0,0))))</f>
-        <v/>
-      </c>
-      <c r="L145" s="55">
-        <f>INDEX('Tax Rates &amp; Assumptions'!Y$81:Y$1080,L120)</f>
-        <v/>
-      </c>
-      <c r="M145" s="56">
-        <f>INDEX('Tax Rates &amp; Assumptions'!Z$81:Z$1080,L120)</f>
-        <v/>
-      </c>
-      <c r="N145" s="56">
-        <f>INDEX('Tax Rates &amp; Assumptions'!AA$81:AA$1080,L120)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="146" hidden="1" outlineLevel="1">
-      <c r="B146" s="53" t="inlineStr">
-        <is>
-          <t>Capital Loss Carryforward to Future Years</t>
-        </is>
-      </c>
-      <c r="C146" s="54">
-        <f>IF(C143&lt;=0,C143-MAX(C143,-C113),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="147" hidden="1" outlineLevel="1">
-      <c r="B147" s="53" t="inlineStr">
-        <is>
-          <t>Ordinary Taxable Income Including Gain</t>
-        </is>
-      </c>
-      <c r="C147" s="54">
-        <f>MAX(0,C112+C144)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="148" hidden="1" outlineLevel="1">
-      <c r="B148" s="53" t="inlineStr">
-        <is>
-          <t>Federal Ordinary Tax</t>
-        </is>
-      </c>
-      <c r="C148" s="54">
-        <f>SUMPRODUCT((C147&gt;$M$124:$M$130)*($L$124:$L$130)*(MIN(C147,$N$124:$N$130)-$M$124:$M$130))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="149" hidden="1" outlineLevel="1">
-      <c r="B149" s="53" t="inlineStr">
-        <is>
-          <t>Federal Long-Term Capital Gains Tax (stacked)</t>
-        </is>
-      </c>
-      <c r="C149" s="54">
-        <f>SUMPRODUCT($L$133:$L$135*(MAX(0,MIN((C147+C145),$N$133:$N$135)-MAX(C147,$M$133:$M$135))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="150" hidden="1" outlineLevel="1">
-      <c r="B150" s="57" t="inlineStr">
-        <is>
-          <t>Total Federal Tax</t>
-        </is>
-      </c>
-      <c r="C150" s="54">
-        <f>(C148+C149)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="151" hidden="1" outlineLevel="1">
-      <c r="B151" s="53" t="inlineStr">
-        <is>
-          <t>MAGI Estimate (Taxable Income + Std. Ded. Add-Back + Net Gain)</t>
-        </is>
-      </c>
-      <c r="C151" s="54">
-        <f>(C112+C109+C144+C145)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="152" hidden="1" outlineLevel="1">
-      <c r="B152" s="53" t="inlineStr">
-        <is>
-          <t>Net Investment Income (the modeled capital gain)</t>
-        </is>
-      </c>
-      <c r="C152" s="54">
-        <f>MAX(0,C144+C145)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="153" hidden="1" outlineLevel="1">
-      <c r="B153" s="57" t="inlineStr">
-        <is>
-          <t>NIIT</t>
-        </is>
-      </c>
-      <c r="C153" s="54">
-        <f>C115*MIN(C152,MAX(0,C151-C114))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="154" hidden="1" outlineLevel="1">
-      <c r="B154" s="53" t="inlineStr">
-        <is>
-          <t>State Taxable Income (gain taxed as ordinary income)</t>
-        </is>
-      </c>
-      <c r="C154" s="54">
-        <f>MAX(0,C112+C144+C145-C116)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="155" hidden="1" outlineLevel="1">
-      <c r="B155" s="57" t="inlineStr">
-        <is>
-          <t>State Tax</t>
-        </is>
-      </c>
-      <c r="C155" s="54">
-        <f>IF(L117="OTHER",C14*C154,SUMPRODUCT((C154&gt;$M$138:$M$145)*($L$138:$L$145)*(MIN(C154,$N$138:$N$145)-$M$138:$M$145)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="156" hidden="1" outlineLevel="1">
-      <c r="B156" s="58" t="inlineStr">
-        <is>
-          <t>Total Estimated Tax (Federal + State + NIIT)</t>
-        </is>
-      </c>
-      <c r="C156" s="59">
-        <f>(C150+C155+C153)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="157" hidden="1" outlineLevel="1">
-      <c r="B157" s="53" t="inlineStr">
-        <is>
-          <t>Marginal LTCG Rate Applied</t>
-        </is>
-      </c>
-      <c r="C157" s="60">
-        <f>IFERROR(INDEX($L$133:$L$135,MATCH(C147,$M$133:$M$135,1)),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="158" hidden="1" outlineLevel="1">
-      <c r="A158" s="52" t="inlineStr">
-        <is>
-          <t>-- AFTER SALE + TAX-LOSS HARVESTING --</t>
-        </is>
-      </c>
-    </row>
-    <row r="159" hidden="1" outlineLevel="1">
-      <c r="B159" s="53" t="inlineStr">
-        <is>
-          <t>Net Short-Term Gain / (Loss)</t>
-        </is>
-      </c>
-      <c r="C159" s="54">
-        <f>((C32+C117)-(C34+C118))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="160" hidden="1" outlineLevel="1">
-      <c r="B160" s="53" t="inlineStr">
-        <is>
-          <t>Net Long-Term Gain / (Loss), net of carryforward</t>
-        </is>
-      </c>
-      <c r="C160" s="54">
-        <f>((C33+C119)-(C35+C120+C95)-C36)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="161" hidden="1" outlineLevel="1">
-      <c r="B161" s="53" t="inlineStr">
-        <is>
-          <t>Combined Net Capital Gain / (Loss)</t>
-        </is>
-      </c>
-      <c r="C161" s="54">
-        <f>(C159+C160)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="162" hidden="1" outlineLevel="1">
-      <c r="B162" s="53" t="inlineStr">
-        <is>
-          <t>Ordinary-Taxed Capital Gain / (Loss Deduction, capped)</t>
-        </is>
-      </c>
-      <c r="C162" s="54">
-        <f>IF(C161&lt;=0,MAX(C161,-C113),IF(AND(C159&gt;=0,C160&gt;=0),C159,IF(AND(C159&lt;0,C160&gt;=0),0,IF(AND(C159&gt;=0,C160&lt;0),C161,0))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="163" hidden="1" outlineLevel="1">
-      <c r="B163" s="53" t="inlineStr">
-        <is>
-          <t>Preferential (LTCG-Rate) Net Capital Gain</t>
-        </is>
-      </c>
-      <c r="C163" s="54">
-        <f>IF(C161&lt;=0,0,IF(AND(C159&gt;=0,C160&gt;=0),C160,IF(AND(C159&lt;0,C160&gt;=0),C161,IF(AND(C159&gt;=0,C160&lt;0),0,0))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="164" hidden="1" outlineLevel="1">
-      <c r="B164" s="53" t="inlineStr">
-        <is>
-          <t>Capital Loss Carryforward to Future Years</t>
-        </is>
-      </c>
-      <c r="C164" s="54">
-        <f>IF(C161&lt;=0,C161-MAX(C161,-C113),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="165" hidden="1" outlineLevel="1">
-      <c r="B165" s="53" t="inlineStr">
-        <is>
-          <t>Ordinary Taxable Income Including Gain</t>
-        </is>
-      </c>
-      <c r="C165" s="54">
-        <f>MAX(0,C112+C162)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="166" hidden="1" outlineLevel="1">
-      <c r="B166" s="53" t="inlineStr">
-        <is>
-          <t>Federal Ordinary Tax</t>
-        </is>
-      </c>
-      <c r="C166" s="54">
-        <f>SUMPRODUCT((C165&gt;$M$124:$M$130)*($L$124:$L$130)*(MIN(C165,$N$124:$N$130)-$M$124:$M$130))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="167" hidden="1" outlineLevel="1">
-      <c r="B167" s="53" t="inlineStr">
-        <is>
-          <t>Federal Long-Term Capital Gains Tax (stacked)</t>
-        </is>
-      </c>
-      <c r="C167" s="54">
-        <f>SUMPRODUCT($L$133:$L$135*(MAX(0,MIN((C165+C163),$N$133:$N$135)-MAX(C165,$M$133:$M$135))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="168" hidden="1" outlineLevel="1">
-      <c r="B168" s="57" t="inlineStr">
-        <is>
-          <t>Total Federal Tax</t>
-        </is>
-      </c>
-      <c r="C168" s="54">
-        <f>(C166+C167)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="169" hidden="1" outlineLevel="1">
-      <c r="B169" s="53" t="inlineStr">
-        <is>
-          <t>MAGI Estimate (Taxable Income + Std. Ded. Add-Back + Net Gain)</t>
-        </is>
-      </c>
-      <c r="C169" s="54">
-        <f>(C112+C109+C162+C163)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="170" hidden="1" outlineLevel="1">
-      <c r="B170" s="53" t="inlineStr">
-        <is>
-          <t>Net Investment Income (the modeled capital gain)</t>
-        </is>
-      </c>
-      <c r="C170" s="54">
-        <f>MAX(0,C162+C163)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="171" hidden="1" outlineLevel="1">
-      <c r="B171" s="57" t="inlineStr">
-        <is>
-          <t>NIIT</t>
-        </is>
-      </c>
-      <c r="C171" s="54">
-        <f>C115*MIN(C170,MAX(0,C169-C114))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="172" hidden="1" outlineLevel="1">
-      <c r="B172" s="53" t="inlineStr">
-        <is>
-          <t>State Taxable Income (gain taxed as ordinary income)</t>
-        </is>
-      </c>
-      <c r="C172" s="54">
-        <f>MAX(0,C112+C162+C163-C116)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="173" hidden="1" outlineLevel="1">
-      <c r="B173" s="57" t="inlineStr">
-        <is>
-          <t>State Tax</t>
-        </is>
-      </c>
-      <c r="C173" s="54">
-        <f>IF(L117="OTHER",C14*C172,SUMPRODUCT((C172&gt;$M$138:$M$145)*($L$138:$L$145)*(MIN(C172,$N$138:$N$145)-$M$138:$M$145)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="174" hidden="1" outlineLevel="1">
-      <c r="B174" s="58" t="inlineStr">
-        <is>
-          <t>Total Estimated Tax (Federal + State + NIIT)</t>
-        </is>
-      </c>
-      <c r="C174" s="59">
-        <f>(C168+C173+C171)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="175" hidden="1" outlineLevel="1">
-      <c r="B175" s="53" t="inlineStr">
-        <is>
-          <t>Marginal LTCG Rate Applied</t>
-        </is>
-      </c>
-      <c r="C175" s="60">
-        <f>IFERROR(INDEX($L$133:$L$135,MATCH(C165,$M$133:$M$135,1)),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="176" hidden="1" outlineLevel="1">
-      <c r="B176" s="53" t="inlineStr">
-        <is>
-          <t>State Marginal Tax Rate (on ordinary income, before any gain)</t>
-        </is>
-      </c>
-      <c r="C176" s="60">
-        <f>IF(L117="OTHER",C14,IFERROR(INDEX($L$138:$L$145,MATCH(MAX(0,C112-C116),$M$138:$M$145,1)),0))</f>
-        <v/>
-      </c>
-    </row>
+    <row r="88" hidden="1" outlineLevel="1">
+      <c r="L88" s="30">
+        <f>INDEX('Tax Rates &amp; Assumptions'!D$81:D$1080,L70)</f>
+        <v/>
+      </c>
+      <c r="M88" s="31">
+        <f>INDEX('Tax Rates &amp; Assumptions'!E$81:E$1080,L70)</f>
+        <v/>
+      </c>
+      <c r="N88" s="31">
+        <f>INDEX('Tax Rates &amp; Assumptions'!F$81:F$1080,L70)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89" hidden="1" outlineLevel="1">
+      <c r="L89" s="30">
+        <f>INDEX('Tax Rates &amp; Assumptions'!G$81:G$1080,L70)</f>
+        <v/>
+      </c>
+      <c r="M89" s="31">
+        <f>INDEX('Tax Rates &amp; Assumptions'!H$81:H$1080,L70)</f>
+        <v/>
+      </c>
+      <c r="N89" s="31">
+        <f>INDEX('Tax Rates &amp; Assumptions'!I$81:I$1080,L70)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90" hidden="1" outlineLevel="1">
+      <c r="L90" s="30">
+        <f>INDEX('Tax Rates &amp; Assumptions'!J$81:J$1080,L70)</f>
+        <v/>
+      </c>
+      <c r="M90" s="31">
+        <f>INDEX('Tax Rates &amp; Assumptions'!K$81:K$1080,L70)</f>
+        <v/>
+      </c>
+      <c r="N90" s="31">
+        <f>INDEX('Tax Rates &amp; Assumptions'!L$81:L$1080,L70)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91" hidden="1" outlineLevel="1">
+      <c r="L91" s="30">
+        <f>INDEX('Tax Rates &amp; Assumptions'!M$81:M$1080,L70)</f>
+        <v/>
+      </c>
+      <c r="M91" s="31">
+        <f>INDEX('Tax Rates &amp; Assumptions'!N$81:N$1080,L70)</f>
+        <v/>
+      </c>
+      <c r="N91" s="31">
+        <f>INDEX('Tax Rates &amp; Assumptions'!O$81:O$1080,L70)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92" hidden="1" outlineLevel="1">
+      <c r="L92" s="30">
+        <f>INDEX('Tax Rates &amp; Assumptions'!P$81:P$1080,L70)</f>
+        <v/>
+      </c>
+      <c r="M92" s="31">
+        <f>INDEX('Tax Rates &amp; Assumptions'!Q$81:Q$1080,L70)</f>
+        <v/>
+      </c>
+      <c r="N92" s="31">
+        <f>INDEX('Tax Rates &amp; Assumptions'!R$81:R$1080,L70)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93" hidden="1" outlineLevel="1">
+      <c r="L93" s="30">
+        <f>INDEX('Tax Rates &amp; Assumptions'!S$81:S$1080,L70)</f>
+        <v/>
+      </c>
+      <c r="M93" s="31">
+        <f>INDEX('Tax Rates &amp; Assumptions'!T$81:T$1080,L70)</f>
+        <v/>
+      </c>
+      <c r="N93" s="31">
+        <f>INDEX('Tax Rates &amp; Assumptions'!U$81:U$1080,L70)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94" hidden="1" outlineLevel="1">
+      <c r="L94" s="30">
+        <f>INDEX('Tax Rates &amp; Assumptions'!V$81:V$1080,L70)</f>
+        <v/>
+      </c>
+      <c r="M94" s="31">
+        <f>INDEX('Tax Rates &amp; Assumptions'!W$81:W$1080,L70)</f>
+        <v/>
+      </c>
+      <c r="N94" s="31">
+        <f>INDEX('Tax Rates &amp; Assumptions'!X$81:X$1080,L70)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95" hidden="1" outlineLevel="1">
+      <c r="L95" s="30">
+        <f>INDEX('Tax Rates &amp; Assumptions'!Y$81:Y$1080,L70)</f>
+        <v/>
+      </c>
+      <c r="M95" s="31">
+        <f>INDEX('Tax Rates &amp; Assumptions'!Z$81:Z$1080,L70)</f>
+        <v/>
+      </c>
+      <c r="N95" s="31">
+        <f>INDEX('Tax Rates &amp; Assumptions'!AA$81:AA$1080,L70)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96" hidden="1" outlineLevel="1"/>
   </sheetData>
-  <mergeCells count="23">
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="B8:G8"/>
-    <mergeCell ref="A52:G52"/>
-    <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A93:G93"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="B103:G105"/>
-    <mergeCell ref="A31:G31"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="B94:G94"/>
-    <mergeCell ref="A87:G87"/>
-    <mergeCell ref="B50:G50"/>
-    <mergeCell ref="A41:G41"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="B22:G22"/>
-    <mergeCell ref="A21:G21"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="C18:D18"/>
+  <mergeCells count="7">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="B53:F55"/>
   </mergeCells>
-  <dataValidations count="10">
-    <dataValidation sqref="C11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+  <dataValidations count="3">
+    <dataValidation sqref="C5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"2024,2025"</formula1>
     </dataValidation>
-    <dataValidation sqref="C12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="C6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Single,Married Filing Jointly,Married Filing Separately,Head of Household"</formula1>
     </dataValidation>
-    <dataValidation sqref="C13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="C7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>='Tax Rates &amp; Assumptions'!$B$46:$B$77</formula1>
-    </dataValidation>
-    <dataValidation sqref="C23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>"Option A: Enter Taxable Income Directly,Option B: Gross Income + Deductions"</formula1>
-    </dataValidation>
-    <dataValidation sqref="E43" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>"Short-Term,Long-Term"</formula1>
-    </dataValidation>
-    <dataValidation sqref="E44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>"Short-Term,Long-Term"</formula1>
-    </dataValidation>
-    <dataValidation sqref="E45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>"Short-Term,Long-Term"</formula1>
-    </dataValidation>
-    <dataValidation sqref="E46" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>"Short-Term,Long-Term"</formula1>
-    </dataValidation>
-    <dataValidation sqref="E47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>"Short-Term,Long-Term"</formula1>
-    </dataValidation>
-    <dataValidation sqref="E48" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>"Short-Term,Long-Term"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Capital_Gains_Tax_Estimator.xlsx
+++ b/Capital_Gains_Tax_Estimator.xlsx
@@ -104,14 +104,20 @@
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="00000000"/>
-      <sz val="10"/>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
       <i val="1"/>
       <color rgb="00595959"/>
       <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -164,12 +170,6 @@
       <b val="1"/>
       <color rgb="001F3864"/>
       <sz val="16"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="001F3864"/>
-      <sz val="11"/>
     </font>
   </fonts>
   <fills count="7">
@@ -236,7 +236,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -283,24 +283,27 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="14" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -310,28 +313,28 @@
     <xf numFmtId="10" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="23" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="24" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="24" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="25" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="24" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="25" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="25" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="14" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -437,7 +440,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Capital Gains Tax Calculator'!G36</f>
+              <f>'Capital Gains Tax Calculator'!G38</f>
             </strRef>
           </tx>
           <spPr>
@@ -447,12 +450,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Capital Gains Tax Calculator'!$F$37:$F$39</f>
+              <f>'Capital Gains Tax Calculator'!$F$39:$F$41</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Capital Gains Tax Calculator'!$G$37:$G$39</f>
+              <f>'Capital Gains Tax Calculator'!$G$39:$G$41</f>
             </numRef>
           </val>
         </ser>
@@ -477,7 +480,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>35</row>
+      <row>37</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="4320000" cy="2700000"/>
@@ -787,7 +790,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N95"/>
+  <dimension ref="A1:N97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -866,172 +869,168 @@
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="22" t="inlineStr">
-        <is>
-          <t>State Tax Rate if 'Other (Manual Entry)' Selected</t>
-        </is>
-      </c>
-      <c r="C8" s="14" t="n">
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>Estimated State Marginal Tax Rate</t>
+        </is>
+      </c>
+      <c r="C8" s="22">
+        <f>C85</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="23" t="inlineStr">
+        <is>
+          <t>(automatically pulled from the Tax Rates &amp; Assumptions tab based on your state and taxable income below)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="24" t="inlineStr">
+        <is>
+          <t>Manual State Tax Rate Override - used ONLY if State of Residence = 'Other (Manual Entry)'</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="n">
         <v>0.05</v>
       </c>
     </row>
-    <row r="9">
-      <c r="B9" s="21" t="inlineStr">
+    <row r="11">
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t>Taxable Income (before these gains/losses)</t>
         </is>
       </c>
-      <c r="C9" s="13" t="n">
+      <c r="C11" s="13" t="n">
         <v>200000</v>
       </c>
     </row>
-    <row r="10">
-      <c r="B10" s="23" t="inlineStr">
+    <row r="12">
+      <c r="B12" s="23" t="inlineStr">
         <is>
           <t>(your salary/other income after deductions - used only to determine which tax brackets your gains fall into)</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>CAPITAL GAINS &amp; LOSSES</t>
         </is>
       </c>
-      <c r="B12" s="4" t="n"/>
-      <c r="C12" s="4" t="n"/>
-      <c r="D12" s="4" t="n"/>
-      <c r="E12" s="4" t="n"/>
-      <c r="F12" s="4" t="n"/>
-    </row>
-    <row r="13">
-      <c r="B13" s="24" t="inlineStr">
+      <c r="B14" s="4" t="n"/>
+      <c r="C14" s="4" t="n"/>
+      <c r="D14" s="4" t="n"/>
+      <c r="E14" s="4" t="n"/>
+      <c r="F14" s="4" t="n"/>
+    </row>
+    <row r="15">
+      <c r="B15" s="25" t="inlineStr">
         <is>
           <t>Short-Term Capital Gains (held 1 year or less)</t>
         </is>
       </c>
-      <c r="C13" s="13" t="n">
+      <c r="C15" s="13" t="n">
         <v>3000</v>
       </c>
     </row>
-    <row r="14">
-      <c r="B14" s="24" t="inlineStr">
+    <row r="16">
+      <c r="B16" s="25" t="inlineStr">
         <is>
           <t>Long-Term Capital Gains (held more than 1 year)</t>
         </is>
       </c>
-      <c r="C14" s="13" t="n">
+      <c r="C16" s="13" t="n">
         <v>155000</v>
       </c>
     </row>
-    <row r="15">
-      <c r="B15" s="24" t="inlineStr">
+    <row r="17">
+      <c r="B17" s="25" t="inlineStr">
         <is>
           <t>Short-Term Capital Losses</t>
         </is>
       </c>
-      <c r="C15" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="24" t="inlineStr">
+      <c r="C17" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="25" t="inlineStr">
         <is>
           <t>Long-Term Capital Losses</t>
         </is>
       </c>
-      <c r="C16" s="13" t="n">
+      <c r="C18" s="13" t="n">
         <v>2000</v>
       </c>
     </row>
-    <row r="17">
-      <c r="B17" s="24" t="inlineStr">
+    <row r="19">
+      <c r="B19" s="25" t="inlineStr">
         <is>
           <t>Capital Loss Carryforward (from prior years)</t>
         </is>
       </c>
-      <c r="C17" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="C19" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>ESTIMATED TAX</t>
         </is>
       </c>
-      <c r="B19" s="4" t="n"/>
-      <c r="C19" s="4" t="n"/>
-      <c r="D19" s="4" t="n"/>
-      <c r="E19" s="4" t="n"/>
-      <c r="F19" s="4" t="n"/>
-    </row>
-    <row r="20" ht="28" customHeight="1">
-      <c r="B20" s="25" t="inlineStr">
+      <c r="B21" s="4" t="n"/>
+      <c r="C21" s="4" t="n"/>
+      <c r="D21" s="4" t="n"/>
+      <c r="E21" s="4" t="n"/>
+      <c r="F21" s="4" t="n"/>
+    </row>
+    <row r="22" ht="28" customHeight="1">
+      <c r="B22" s="26" t="inlineStr">
         <is>
           <t>Total Estimated Tax</t>
         </is>
       </c>
-      <c r="C20" s="25" t="inlineStr">
+      <c r="C22" s="26" t="inlineStr">
         <is>
           <t>Effective Tax Rate</t>
         </is>
       </c>
-      <c r="D20" s="25" t="inlineStr">
+      <c r="D22" s="26" t="inlineStr">
         <is>
           <t>Federal Tax</t>
         </is>
       </c>
-      <c r="E20" s="25" t="inlineStr">
+      <c r="E22" s="26" t="inlineStr">
         <is>
           <t>State Tax</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="30" customHeight="1">
-      <c r="B21" s="38">
-        <f>C80</f>
-        <v/>
-      </c>
-      <c r="C21" s="39">
+    <row r="23" ht="30" customHeight="1">
+      <c r="B23" s="39">
+        <f>C82</f>
+        <v/>
+      </c>
+      <c r="C23" s="40">
+        <f>C83</f>
+        <v/>
+      </c>
+      <c r="D23" s="39">
+        <f>(C75+C76)</f>
+        <v/>
+      </c>
+      <c r="E23" s="39">
         <f>C81</f>
         <v/>
       </c>
-      <c r="D21" s="38">
-        <f>(C73+C74)</f>
-        <v/>
-      </c>
-      <c r="E21" s="38">
-        <f>C79</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="24" t="inlineStr">
+    </row>
+    <row r="25">
+      <c r="B25" s="25" t="inlineStr">
         <is>
           <t>Net Short-Term Gain / (Loss)</t>
-        </is>
-      </c>
-      <c r="C23" s="40">
-        <f>C64</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="24" t="inlineStr">
-        <is>
-          <t>Net Long-Term Gain / (Loss)</t>
-        </is>
-      </c>
-      <c r="C24" s="40">
-        <f>C65</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="21" t="inlineStr">
-        <is>
-          <t>Total Net Capital Gain / (Loss)</t>
         </is>
       </c>
       <c r="C25" s="41">
@@ -1040,97 +1039,97 @@
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="24" t="inlineStr">
+      <c r="B26" s="25" t="inlineStr">
+        <is>
+          <t>Net Long-Term Gain / (Loss)</t>
+        </is>
+      </c>
+      <c r="C26" s="41">
+        <f>C67</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="21" t="inlineStr">
+        <is>
+          <t>Total Net Capital Gain / (Loss)</t>
+        </is>
+      </c>
+      <c r="C27" s="42">
+        <f>C68</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="25" t="inlineStr">
         <is>
           <t>Capital Loss Deduction (against ordinary income)</t>
         </is>
       </c>
-      <c r="C26" s="40">
-        <f>IF(C66&lt;0,MAX(C66,-C60),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="24" t="inlineStr">
+      <c r="C28" s="41">
+        <f>IF(C68&lt;0,MAX(C68,-C62),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="25" t="inlineStr">
         <is>
           <t>Capital Loss Carryforward to Future Years</t>
         </is>
       </c>
-      <c r="C27" s="40">
-        <f>-C69</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" s="24" t="inlineStr">
+      <c r="C29" s="41">
+        <f>-C71</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="25" t="inlineStr">
         <is>
           <t>Federal Tax on Short-Term Gain (ordinary rates)</t>
         </is>
       </c>
-      <c r="C28" s="40">
-        <f>C73</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="24" t="inlineStr">
+      <c r="C30" s="41">
+        <f>C75</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="25" t="inlineStr">
         <is>
           <t>Federal Tax on Long-Term Gain (preferential rates)</t>
         </is>
       </c>
-      <c r="C29" s="40">
-        <f>C74</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="24" t="inlineStr">
+      <c r="C31" s="41">
+        <f>C76</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="25" t="inlineStr">
         <is>
           <t>Net Investment Income Tax (NIIT)</t>
         </is>
       </c>
-      <c r="C30" s="40">
-        <f>C77</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" s="24" t="inlineStr">
+      <c r="C32" s="41">
+        <f>C79</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="25" t="inlineStr">
         <is>
           <t>State Tax</t>
         </is>
       </c>
-      <c r="C31" s="40">
-        <f>C79</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="21" t="inlineStr">
+      <c r="C33" s="41">
+        <f>C81</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="21" t="inlineStr">
         <is>
           <t>Total Estimated Tax</t>
-        </is>
-      </c>
-      <c r="C32" s="41">
-        <f>C80</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="24" t="inlineStr">
-        <is>
-          <t>Effective Tax Rate on the Gain</t>
-        </is>
-      </c>
-      <c r="C33" s="42">
-        <f>C81</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34">
-      <c r="B34" s="24" t="inlineStr">
-        <is>
-          <t>Marginal Long-Term Capital Gains Rate</t>
         </is>
       </c>
       <c r="C34" s="42">
@@ -1138,715 +1137,747 @@
         <v/>
       </c>
     </row>
+    <row r="35">
+      <c r="B35" s="25" t="inlineStr">
+        <is>
+          <t>Effective Tax Rate on the Gain</t>
+        </is>
+      </c>
+      <c r="C35" s="43">
+        <f>C83</f>
+        <v/>
+      </c>
+    </row>
     <row r="36">
-      <c r="F36" s="7" t="inlineStr">
+      <c r="B36" s="25" t="inlineStr">
+        <is>
+          <t>Marginal Long-Term Capital Gains Rate</t>
+        </is>
+      </c>
+      <c r="C36" s="43">
+        <f>C84</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="F38" s="7" t="inlineStr">
         <is>
           <t>Tax Component</t>
         </is>
       </c>
-      <c r="G36" s="7" t="inlineStr">
+      <c r="G38" s="7" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="F37" s="28" t="inlineStr">
+    <row r="39">
+      <c r="F39" s="29" t="inlineStr">
         <is>
           <t>Federal Tax</t>
         </is>
       </c>
-      <c r="G37" s="43">
-        <f>(C73+C74)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="F38" s="28" t="inlineStr">
+      <c r="G39" s="44">
+        <f>(C75+C76)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="F40" s="29" t="inlineStr">
         <is>
           <t>State Tax</t>
         </is>
       </c>
-      <c r="G38" s="43">
+      <c r="G40" s="44">
+        <f>C81</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="F41" s="29" t="inlineStr">
+        <is>
+          <t>NIIT</t>
+        </is>
+      </c>
+      <c r="G41" s="44">
         <f>C79</f>
         <v/>
       </c>
     </row>
-    <row r="39">
-      <c r="F39" s="28" t="inlineStr">
+    <row r="55">
+      <c r="B55" s="27" t="inlineStr">
+        <is>
+          <t>Estimated for financial-planning purposes only. This calculator is not tax, legal, or accounting advice. Actual tax liability may differ based on individual circumstances, deductions, credits, tax elections, state/local rules, and other factors. Consult a qualified tax professional before making tax-related decisions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="59" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A59" s="28" t="inlineStr">
+        <is>
+          <t>CALCULATION DETAIL (grouped - click + to expand)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" hidden="1" outlineLevel="1"/>
+    <row r="61" hidden="1" outlineLevel="1">
+      <c r="B61" s="33" t="inlineStr">
+        <is>
+          <t>Standard Deduction (add-back for MAGI estimate)</t>
+        </is>
+      </c>
+      <c r="C61" s="34">
+        <f>INDEX('Tax Rates &amp; Assumptions'!$D$28:$D$35,L67)</f>
+        <v/>
+      </c>
+      <c r="K61" s="7" t="inlineStr">
+        <is>
+          <t>Filing Status</t>
+        </is>
+      </c>
+      <c r="L61" s="29">
+        <f>C6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62" hidden="1" outlineLevel="1">
+      <c r="B62" s="33" t="inlineStr">
+        <is>
+          <t>Capital Loss Limit vs. Ordinary Income</t>
+        </is>
+      </c>
+      <c r="C62" s="34">
+        <f>INDEX('Tax Rates &amp; Assumptions'!$D$39:$D$42,L66)</f>
+        <v/>
+      </c>
+      <c r="K62" s="7" t="inlineStr">
+        <is>
+          <t>Tax Year</t>
+        </is>
+      </c>
+      <c r="L62" s="29">
+        <f>C5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63" hidden="1" outlineLevel="1">
+      <c r="B63" s="33" t="inlineStr">
+        <is>
+          <t>NIIT Threshold</t>
+        </is>
+      </c>
+      <c r="C63" s="34">
+        <f>INDEX('Tax Rates &amp; Assumptions'!$B$39:$B$42,L66)</f>
+        <v/>
+      </c>
+      <c r="K63" s="7" t="inlineStr">
+        <is>
+          <t>Federal Key</t>
+        </is>
+      </c>
+      <c r="L63" s="29">
+        <f>L62&amp;"|"&amp;L61</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64" hidden="1" outlineLevel="1">
+      <c r="B64" s="33" t="inlineStr">
+        <is>
+          <t>NIIT Rate</t>
+        </is>
+      </c>
+      <c r="C64" s="35">
+        <f>INDEX('Tax Rates &amp; Assumptions'!$C$39:$C$42,L66)</f>
+        <v/>
+      </c>
+      <c r="K64" s="7" t="inlineStr">
+        <is>
+          <t>Fed Bracket Row#</t>
+        </is>
+      </c>
+      <c r="L64" s="29">
+        <f>MATCH(L63,'Tax Rates &amp; Assumptions'!$C$6:$C$13,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65" hidden="1" outlineLevel="1">
+      <c r="B65" s="33" t="inlineStr">
+        <is>
+          <t>State Standard Deduction</t>
+        </is>
+      </c>
+      <c r="C65" s="34">
+        <f>IF(L70="MFJ",INDEX('Tax Rates &amp; Assumptions'!$E$46:$E$77,L73),INDEX('Tax Rates &amp; Assumptions'!$D$46:$D$77,L73))</f>
+        <v/>
+      </c>
+      <c r="K65" s="7" t="inlineStr">
+        <is>
+          <t>LTCG Bracket Row#</t>
+        </is>
+      </c>
+      <c r="L65" s="29">
+        <f>MATCH(L63,'Tax Rates &amp; Assumptions'!$C$17:$C$24,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66" hidden="1" outlineLevel="1">
+      <c r="B66" s="33" t="inlineStr">
+        <is>
+          <t>Net Short-Term Gain / (Loss)</t>
+        </is>
+      </c>
+      <c r="C66" s="34">
+        <f>(C15-C17)</f>
+        <v/>
+      </c>
+      <c r="K66" s="7" t="inlineStr">
+        <is>
+          <t>Status Row# (NIIT/CapLoss)</t>
+        </is>
+      </c>
+      <c r="L66" s="29">
+        <f>MATCH(L61,'Tax Rates &amp; Assumptions'!$A$39:$A$42,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67" hidden="1" outlineLevel="1">
+      <c r="B67" s="33" t="inlineStr">
+        <is>
+          <t>Net Long-Term Gain / (Loss), net of carryforward</t>
+        </is>
+      </c>
+      <c r="C67" s="34">
+        <f>(C16-C18-C19)</f>
+        <v/>
+      </c>
+      <c r="K67" s="7" t="inlineStr">
+        <is>
+          <t>StdDed Row#</t>
+        </is>
+      </c>
+      <c r="L67" s="29">
+        <f>MATCH(L63,'Tax Rates &amp; Assumptions'!$C$28:$C$35,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68" hidden="1" outlineLevel="1">
+      <c r="B68" s="33" t="inlineStr">
+        <is>
+          <t>Combined Net Capital Gain / (Loss)</t>
+        </is>
+      </c>
+      <c r="C68" s="34">
+        <f>(C66+C67)</f>
+        <v/>
+      </c>
+      <c r="K68" s="7" t="inlineStr">
+        <is>
+          <t>State Name</t>
+        </is>
+      </c>
+      <c r="L68" s="29">
+        <f>C7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69" hidden="1" outlineLevel="1">
+      <c r="B69" s="33" t="inlineStr">
+        <is>
+          <t>Ordinary-Taxed Capital Gain / (Loss Deduction, capped)</t>
+        </is>
+      </c>
+      <c r="C69" s="34">
+        <f>IF(C68&lt;=0,MAX(C68,-C62),IF(AND(C66&gt;=0,C67&gt;=0),C66,IF(AND(C66&lt;0,C67&gt;=0),0,IF(AND(C66&gt;=0,C67&lt;0),C68,0))))</f>
+        <v/>
+      </c>
+      <c r="K69" s="7" t="inlineStr">
+        <is>
+          <t>State Code</t>
+        </is>
+      </c>
+      <c r="L69" s="29">
+        <f>INDEX('Tax Rates &amp; Assumptions'!$A$46:$A$77,MATCH(L68,'Tax Rates &amp; Assumptions'!$B$46:$B$77,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70" hidden="1" outlineLevel="1">
+      <c r="B70" s="33" t="inlineStr">
+        <is>
+          <t>Preferential (LTCG-Rate) Net Capital Gain</t>
+        </is>
+      </c>
+      <c r="C70" s="34">
+        <f>IF(C68&lt;=0,0,IF(AND(C66&gt;=0,C67&gt;=0),C67,IF(AND(C66&lt;0,C67&gt;=0),C68,IF(AND(C66&gt;=0,C67&lt;0),0,0))))</f>
+        <v/>
+      </c>
+      <c r="K70" s="7" t="inlineStr">
+        <is>
+          <t>State Category</t>
+        </is>
+      </c>
+      <c r="L70" s="29">
+        <f>IF(L61="Married Filing Jointly","MFJ","Single")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71" hidden="1" outlineLevel="1">
+      <c r="B71" s="33" t="inlineStr">
+        <is>
+          <t>Capital Loss Carryforward to Future Years</t>
+        </is>
+      </c>
+      <c r="C71" s="34">
+        <f>IF(C68&lt;=0,C68-MAX(C68,-C62),0)</f>
+        <v/>
+      </c>
+      <c r="K71" s="7" t="inlineStr">
+        <is>
+          <t>State Key</t>
+        </is>
+      </c>
+      <c r="L71" s="29">
+        <f>L69&amp;"|"&amp;L70</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72" hidden="1" outlineLevel="1">
+      <c r="B72" s="33" t="inlineStr">
+        <is>
+          <t>Ordinary Taxable Income Including Gain</t>
+        </is>
+      </c>
+      <c r="C72" s="34">
+        <f>MAX(0,C11+C69)</f>
+        <v/>
+      </c>
+      <c r="K72" s="7" t="inlineStr">
+        <is>
+          <t>State Bracket Row#</t>
+        </is>
+      </c>
+      <c r="L72" s="29">
+        <f>MATCH(L71,'Tax Rates &amp; Assumptions'!$C$81:$C$144,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73" hidden="1" outlineLevel="1">
+      <c r="B73" s="33" t="inlineStr">
+        <is>
+          <t>Federal Tax on Taxable Income Alone (no gain)</t>
+        </is>
+      </c>
+      <c r="C73" s="34">
+        <f>SUMPRODUCT((C11&gt;$M$76:$M$82)*($L$76:$L$82)*(MIN(C11,$N$76:$N$82)-$M$76:$M$82))</f>
+        <v/>
+      </c>
+      <c r="K73" s="7" t="inlineStr">
+        <is>
+          <t>State Master Row#</t>
+        </is>
+      </c>
+      <c r="L73" s="29">
+        <f>MATCH(L69,'Tax Rates &amp; Assumptions'!$A$46:$A$77,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74" hidden="1" outlineLevel="1">
+      <c r="B74" s="33" t="inlineStr">
+        <is>
+          <t>Federal Tax on Taxable Income Including Short-Term Gain</t>
+        </is>
+      </c>
+      <c r="C74" s="34">
+        <f>SUMPRODUCT((C72&gt;$M$76:$M$82)*($L$76:$L$82)*(MIN(C72,$N$76:$N$82)-$M$76:$M$82))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75" hidden="1" outlineLevel="1">
+      <c r="B75" s="36" t="inlineStr">
+        <is>
+          <t>Federal Tax on Short-Term Gain</t>
+        </is>
+      </c>
+      <c r="C75" s="34">
+        <f>MAX(0,C74-C73)</f>
+        <v/>
+      </c>
+      <c r="K75" s="30" t="inlineStr">
+        <is>
+          <t>Federal Ordinary Brackets</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" hidden="1" outlineLevel="1">
+      <c r="B76" s="36" t="inlineStr">
+        <is>
+          <t>Federal Tax on Long-Term Gain (stacked)</t>
+        </is>
+      </c>
+      <c r="C76" s="34">
+        <f>SUMPRODUCT($L$85:$L$87*(MAX(0,MIN((C72+C70),$N$85:$N$87)-MAX(C72,$M$85:$M$87))))</f>
+        <v/>
+      </c>
+      <c r="L76" s="31">
+        <f>INDEX('Tax Rates &amp; Assumptions'!D$6:D$1005,L64)</f>
+        <v/>
+      </c>
+      <c r="M76" s="32">
+        <f>INDEX('Tax Rates &amp; Assumptions'!E$6:E$1005,L64)</f>
+        <v/>
+      </c>
+      <c r="N76" s="32">
+        <f>INDEX('Tax Rates &amp; Assumptions'!F$6:F$1005,L64)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77" hidden="1" outlineLevel="1">
+      <c r="B77" s="33" t="inlineStr">
+        <is>
+          <t>MAGI Estimate (Taxable Income + Std. Ded. Add-Back + Net Gain)</t>
+        </is>
+      </c>
+      <c r="C77" s="34">
+        <f>(C11+C61+C69+C70)</f>
+        <v/>
+      </c>
+      <c r="L77" s="31">
+        <f>INDEX('Tax Rates &amp; Assumptions'!G$6:G$1005,L64)</f>
+        <v/>
+      </c>
+      <c r="M77" s="32">
+        <f>INDEX('Tax Rates &amp; Assumptions'!H$6:H$1005,L64)</f>
+        <v/>
+      </c>
+      <c r="N77" s="32">
+        <f>INDEX('Tax Rates &amp; Assumptions'!I$6:I$1005,L64)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78" hidden="1" outlineLevel="1">
+      <c r="B78" s="33" t="inlineStr">
+        <is>
+          <t>Net Investment Income (the modeled capital gain)</t>
+        </is>
+      </c>
+      <c r="C78" s="34">
+        <f>MAX(0,C69+C70)</f>
+        <v/>
+      </c>
+      <c r="L78" s="31">
+        <f>INDEX('Tax Rates &amp; Assumptions'!J$6:J$1005,L64)</f>
+        <v/>
+      </c>
+      <c r="M78" s="32">
+        <f>INDEX('Tax Rates &amp; Assumptions'!K$6:K$1005,L64)</f>
+        <v/>
+      </c>
+      <c r="N78" s="32">
+        <f>INDEX('Tax Rates &amp; Assumptions'!L$6:L$1005,L64)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79" hidden="1" outlineLevel="1">
+      <c r="B79" s="36" t="inlineStr">
         <is>
           <t>NIIT</t>
         </is>
       </c>
-      <c r="G39" s="43">
-        <f>C77</f>
-        <v/>
-      </c>
-    </row>
-    <row r="53">
-      <c r="B53" s="26" t="inlineStr">
-        <is>
-          <t>Estimated for financial-planning purposes only. This calculator is not tax, legal, or accounting advice. Actual tax liability may differ based on individual circumstances, deductions, credits, tax elections, state/local rules, and other factors. Consult a qualified tax professional before making tax-related decisions.</t>
-        </is>
-      </c>
-    </row>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="57" hidden="1" outlineLevel="1" collapsed="1">
-      <c r="A57" s="27" t="inlineStr">
-        <is>
-          <t>CALCULATION DETAIL (grouped - click + to expand)</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" hidden="1" outlineLevel="1"/>
-    <row r="59" hidden="1" outlineLevel="1">
-      <c r="B59" s="32" t="inlineStr">
-        <is>
-          <t>Standard Deduction (add-back for MAGI estimate)</t>
-        </is>
-      </c>
-      <c r="C59" s="33">
-        <f>INDEX('Tax Rates &amp; Assumptions'!$D$28:$D$35,L65)</f>
-        <v/>
-      </c>
-      <c r="K59" s="7" t="inlineStr">
-        <is>
-          <t>Filing Status</t>
-        </is>
-      </c>
-      <c r="L59" s="28">
-        <f>C6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="60" hidden="1" outlineLevel="1">
-      <c r="B60" s="32" t="inlineStr">
-        <is>
-          <t>Capital Loss Limit vs. Ordinary Income</t>
-        </is>
-      </c>
-      <c r="C60" s="33">
-        <f>INDEX('Tax Rates &amp; Assumptions'!$D$39:$D$42,L64)</f>
-        <v/>
-      </c>
-      <c r="K60" s="7" t="inlineStr">
-        <is>
-          <t>Tax Year</t>
-        </is>
-      </c>
-      <c r="L60" s="28">
-        <f>C5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="61" hidden="1" outlineLevel="1">
-      <c r="B61" s="32" t="inlineStr">
-        <is>
-          <t>NIIT Threshold</t>
-        </is>
-      </c>
-      <c r="C61" s="33">
-        <f>INDEX('Tax Rates &amp; Assumptions'!$B$39:$B$42,L64)</f>
-        <v/>
-      </c>
-      <c r="K61" s="7" t="inlineStr">
-        <is>
-          <t>Federal Key</t>
-        </is>
-      </c>
-      <c r="L61" s="28">
-        <f>L60&amp;"|"&amp;L59</f>
-        <v/>
-      </c>
-    </row>
-    <row r="62" hidden="1" outlineLevel="1">
-      <c r="B62" s="32" t="inlineStr">
-        <is>
-          <t>NIIT Rate</t>
-        </is>
-      </c>
-      <c r="C62" s="34">
-        <f>INDEX('Tax Rates &amp; Assumptions'!$C$39:$C$42,L64)</f>
-        <v/>
-      </c>
-      <c r="K62" s="7" t="inlineStr">
-        <is>
-          <t>Fed Bracket Row#</t>
-        </is>
-      </c>
-      <c r="L62" s="28">
-        <f>MATCH(L61,'Tax Rates &amp; Assumptions'!$C$6:$C$13,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="63" hidden="1" outlineLevel="1">
-      <c r="B63" s="32" t="inlineStr">
-        <is>
-          <t>State Standard Deduction</t>
-        </is>
-      </c>
-      <c r="C63" s="33">
-        <f>IF(L68="MFJ",INDEX('Tax Rates &amp; Assumptions'!$E$46:$E$77,L71),INDEX('Tax Rates &amp; Assumptions'!$D$46:$D$77,L71))</f>
-        <v/>
-      </c>
-      <c r="K63" s="7" t="inlineStr">
-        <is>
-          <t>LTCG Bracket Row#</t>
-        </is>
-      </c>
-      <c r="L63" s="28">
-        <f>MATCH(L61,'Tax Rates &amp; Assumptions'!$C$17:$C$24,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="64" hidden="1" outlineLevel="1">
-      <c r="B64" s="32" t="inlineStr">
-        <is>
-          <t>Net Short-Term Gain / (Loss)</t>
-        </is>
-      </c>
-      <c r="C64" s="33">
-        <f>(C13-C15)</f>
-        <v/>
-      </c>
-      <c r="K64" s="7" t="inlineStr">
-        <is>
-          <t>Status Row# (NIIT/CapLoss)</t>
-        </is>
-      </c>
-      <c r="L64" s="28">
-        <f>MATCH(L59,'Tax Rates &amp; Assumptions'!$A$39:$A$42,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="65" hidden="1" outlineLevel="1">
-      <c r="B65" s="32" t="inlineStr">
-        <is>
-          <t>Net Long-Term Gain / (Loss), net of carryforward</t>
-        </is>
-      </c>
-      <c r="C65" s="33">
-        <f>(C14-C16-C17)</f>
-        <v/>
-      </c>
-      <c r="K65" s="7" t="inlineStr">
-        <is>
-          <t>StdDed Row#</t>
-        </is>
-      </c>
-      <c r="L65" s="28">
-        <f>MATCH(L61,'Tax Rates &amp; Assumptions'!$C$28:$C$35,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="66" hidden="1" outlineLevel="1">
-      <c r="B66" s="32" t="inlineStr">
-        <is>
-          <t>Combined Net Capital Gain / (Loss)</t>
-        </is>
-      </c>
-      <c r="C66" s="33">
-        <f>(C64+C65)</f>
-        <v/>
-      </c>
-      <c r="K66" s="7" t="inlineStr">
-        <is>
-          <t>State Name</t>
-        </is>
-      </c>
-      <c r="L66" s="28">
-        <f>C7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="67" hidden="1" outlineLevel="1">
-      <c r="B67" s="32" t="inlineStr">
-        <is>
-          <t>Ordinary-Taxed Capital Gain / (Loss Deduction, capped)</t>
-        </is>
-      </c>
-      <c r="C67" s="33">
-        <f>IF(C66&lt;=0,MAX(C66,-C60),IF(AND(C64&gt;=0,C65&gt;=0),C64,IF(AND(C64&lt;0,C65&gt;=0),0,IF(AND(C64&gt;=0,C65&lt;0),C66,0))))</f>
-        <v/>
-      </c>
-      <c r="K67" s="7" t="inlineStr">
-        <is>
-          <t>State Code</t>
-        </is>
-      </c>
-      <c r="L67" s="28">
-        <f>INDEX('Tax Rates &amp; Assumptions'!$A$46:$A$77,MATCH(L66,'Tax Rates &amp; Assumptions'!$B$46:$B$77,0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="68" hidden="1" outlineLevel="1">
-      <c r="B68" s="32" t="inlineStr">
-        <is>
-          <t>Preferential (LTCG-Rate) Net Capital Gain</t>
-        </is>
-      </c>
-      <c r="C68" s="33">
-        <f>IF(C66&lt;=0,0,IF(AND(C64&gt;=0,C65&gt;=0),C65,IF(AND(C64&lt;0,C65&gt;=0),C66,IF(AND(C64&gt;=0,C65&lt;0),0,0))))</f>
-        <v/>
-      </c>
-      <c r="K68" s="7" t="inlineStr">
-        <is>
-          <t>State Category</t>
-        </is>
-      </c>
-      <c r="L68" s="28">
-        <f>IF(L59="Married Filing Jointly","MFJ","Single")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="69" hidden="1" outlineLevel="1">
-      <c r="B69" s="32" t="inlineStr">
-        <is>
-          <t>Capital Loss Carryforward to Future Years</t>
-        </is>
-      </c>
-      <c r="C69" s="33">
-        <f>IF(C66&lt;=0,C66-MAX(C66,-C60),0)</f>
-        <v/>
-      </c>
-      <c r="K69" s="7" t="inlineStr">
-        <is>
-          <t>State Key</t>
-        </is>
-      </c>
-      <c r="L69" s="28">
-        <f>L67&amp;"|"&amp;L68</f>
-        <v/>
-      </c>
-    </row>
-    <row r="70" hidden="1" outlineLevel="1">
-      <c r="B70" s="32" t="inlineStr">
-        <is>
-          <t>Ordinary Taxable Income Including Gain</t>
-        </is>
-      </c>
-      <c r="C70" s="33">
-        <f>MAX(0,C9+C67)</f>
-        <v/>
-      </c>
-      <c r="K70" s="7" t="inlineStr">
-        <is>
-          <t>State Bracket Row#</t>
-        </is>
-      </c>
-      <c r="L70" s="28">
-        <f>MATCH(L69,'Tax Rates &amp; Assumptions'!$C$81:$C$144,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="71" hidden="1" outlineLevel="1">
-      <c r="B71" s="32" t="inlineStr">
-        <is>
-          <t>Federal Tax on Taxable Income Alone (no gain)</t>
-        </is>
-      </c>
-      <c r="C71" s="33">
-        <f>SUMPRODUCT((C9&gt;$M$74:$M$80)*($L$74:$L$80)*(MIN(C9,$N$74:$N$80)-$M$74:$M$80))</f>
-        <v/>
-      </c>
-      <c r="K71" s="7" t="inlineStr">
-        <is>
-          <t>State Master Row#</t>
-        </is>
-      </c>
-      <c r="L71" s="28">
-        <f>MATCH(L67,'Tax Rates &amp; Assumptions'!$A$46:$A$77,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="72" hidden="1" outlineLevel="1">
-      <c r="B72" s="32" t="inlineStr">
-        <is>
-          <t>Federal Tax on Taxable Income Including Short-Term Gain</t>
-        </is>
-      </c>
-      <c r="C72" s="33">
-        <f>SUMPRODUCT((C70&gt;$M$74:$M$80)*($L$74:$L$80)*(MIN(C70,$N$74:$N$80)-$M$74:$M$80))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="73" hidden="1" outlineLevel="1">
-      <c r="B73" s="35" t="inlineStr">
-        <is>
-          <t>Federal Tax on Short-Term Gain</t>
-        </is>
-      </c>
-      <c r="C73" s="33">
-        <f>MAX(0,C72-C71)</f>
-        <v/>
-      </c>
-      <c r="K73" s="29" t="inlineStr">
-        <is>
-          <t>Federal Ordinary Brackets</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" hidden="1" outlineLevel="1">
-      <c r="B74" s="35" t="inlineStr">
-        <is>
-          <t>Federal Tax on Long-Term Gain (stacked)</t>
-        </is>
-      </c>
-      <c r="C74" s="33">
-        <f>SUMPRODUCT($L$83:$L$85*(MAX(0,MIN((C70+C68),$N$83:$N$85)-MAX(C70,$M$83:$M$85))))</f>
-        <v/>
-      </c>
-      <c r="L74" s="30">
-        <f>INDEX('Tax Rates &amp; Assumptions'!D$6:D$1005,L62)</f>
-        <v/>
-      </c>
-      <c r="M74" s="31">
-        <f>INDEX('Tax Rates &amp; Assumptions'!E$6:E$1005,L62)</f>
-        <v/>
-      </c>
-      <c r="N74" s="31">
-        <f>INDEX('Tax Rates &amp; Assumptions'!F$6:F$1005,L62)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="75" hidden="1" outlineLevel="1">
-      <c r="B75" s="32" t="inlineStr">
-        <is>
-          <t>MAGI Estimate (Taxable Income + Std. Ded. Add-Back + Net Gain)</t>
-        </is>
-      </c>
-      <c r="C75" s="33">
-        <f>(C9+C59+C67+C68)</f>
-        <v/>
-      </c>
-      <c r="L75" s="30">
-        <f>INDEX('Tax Rates &amp; Assumptions'!G$6:G$1005,L62)</f>
-        <v/>
-      </c>
-      <c r="M75" s="31">
-        <f>INDEX('Tax Rates &amp; Assumptions'!H$6:H$1005,L62)</f>
-        <v/>
-      </c>
-      <c r="N75" s="31">
-        <f>INDEX('Tax Rates &amp; Assumptions'!I$6:I$1005,L62)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="76" hidden="1" outlineLevel="1">
-      <c r="B76" s="32" t="inlineStr">
-        <is>
-          <t>Net Investment Income (the modeled capital gain)</t>
-        </is>
-      </c>
-      <c r="C76" s="33">
-        <f>MAX(0,C67+C68)</f>
-        <v/>
-      </c>
-      <c r="L76" s="30">
-        <f>INDEX('Tax Rates &amp; Assumptions'!J$6:J$1005,L62)</f>
-        <v/>
-      </c>
-      <c r="M76" s="31">
-        <f>INDEX('Tax Rates &amp; Assumptions'!K$6:K$1005,L62)</f>
-        <v/>
-      </c>
-      <c r="N76" s="31">
-        <f>INDEX('Tax Rates &amp; Assumptions'!L$6:L$1005,L62)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="77" hidden="1" outlineLevel="1">
-      <c r="B77" s="35" t="inlineStr">
-        <is>
-          <t>NIIT</t>
-        </is>
-      </c>
-      <c r="C77" s="33">
-        <f>C62*MIN(C76,MAX(0,C75-C61))</f>
-        <v/>
-      </c>
-      <c r="L77" s="30">
-        <f>INDEX('Tax Rates &amp; Assumptions'!M$6:M$1005,L62)</f>
-        <v/>
-      </c>
-      <c r="M77" s="31">
-        <f>INDEX('Tax Rates &amp; Assumptions'!N$6:N$1005,L62)</f>
-        <v/>
-      </c>
-      <c r="N77" s="31">
-        <f>INDEX('Tax Rates &amp; Assumptions'!O$6:O$1005,L62)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="78" hidden="1" outlineLevel="1">
-      <c r="B78" s="32" t="inlineStr">
+      <c r="C79" s="34">
+        <f>C64*MIN(C78,MAX(0,C77-C63))</f>
+        <v/>
+      </c>
+      <c r="L79" s="31">
+        <f>INDEX('Tax Rates &amp; Assumptions'!M$6:M$1005,L64)</f>
+        <v/>
+      </c>
+      <c r="M79" s="32">
+        <f>INDEX('Tax Rates &amp; Assumptions'!N$6:N$1005,L64)</f>
+        <v/>
+      </c>
+      <c r="N79" s="32">
+        <f>INDEX('Tax Rates &amp; Assumptions'!O$6:O$1005,L64)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80" hidden="1" outlineLevel="1">
+      <c r="B80" s="33" t="inlineStr">
         <is>
           <t>State Taxable Income (gain taxed as ordinary income)</t>
         </is>
       </c>
-      <c r="C78" s="33">
-        <f>MAX(0,C9+C67+C68-C63)</f>
-        <v/>
-      </c>
-      <c r="L78" s="30">
-        <f>INDEX('Tax Rates &amp; Assumptions'!P$6:P$1005,L62)</f>
-        <v/>
-      </c>
-      <c r="M78" s="31">
-        <f>INDEX('Tax Rates &amp; Assumptions'!Q$6:Q$1005,L62)</f>
-        <v/>
-      </c>
-      <c r="N78" s="31">
-        <f>INDEX('Tax Rates &amp; Assumptions'!R$6:R$1005,L62)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="79" hidden="1" outlineLevel="1">
-      <c r="B79" s="35" t="inlineStr">
+      <c r="C80" s="34">
+        <f>MAX(0,C11+C69+C70-C65)</f>
+        <v/>
+      </c>
+      <c r="L80" s="31">
+        <f>INDEX('Tax Rates &amp; Assumptions'!P$6:P$1005,L64)</f>
+        <v/>
+      </c>
+      <c r="M80" s="32">
+        <f>INDEX('Tax Rates &amp; Assumptions'!Q$6:Q$1005,L64)</f>
+        <v/>
+      </c>
+      <c r="N80" s="32">
+        <f>INDEX('Tax Rates &amp; Assumptions'!R$6:R$1005,L64)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81" hidden="1" outlineLevel="1">
+      <c r="B81" s="36" t="inlineStr">
         <is>
           <t>State Tax</t>
         </is>
       </c>
-      <c r="C79" s="33">
-        <f>IF(L67="OTHER",C8*C78,SUMPRODUCT((C78&gt;$M$88:$M$95)*($L$88:$L$95)*(MIN(C78,$N$88:$N$95)-$M$88:$M$95)))</f>
-        <v/>
-      </c>
-      <c r="L79" s="30">
-        <f>INDEX('Tax Rates &amp; Assumptions'!S$6:S$1005,L62)</f>
-        <v/>
-      </c>
-      <c r="M79" s="31">
-        <f>INDEX('Tax Rates &amp; Assumptions'!T$6:T$1005,L62)</f>
-        <v/>
-      </c>
-      <c r="N79" s="31">
-        <f>INDEX('Tax Rates &amp; Assumptions'!U$6:U$1005,L62)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="80" hidden="1" outlineLevel="1">
-      <c r="B80" s="21" t="inlineStr">
+      <c r="C81" s="34">
+        <f>IF(L69="OTHER",C10*C80,SUMPRODUCT((C80&gt;$M$90:$M$97)*($L$90:$L$97)*(MIN(C80,$N$90:$N$97)-$M$90:$M$97)))</f>
+        <v/>
+      </c>
+      <c r="L81" s="31">
+        <f>INDEX('Tax Rates &amp; Assumptions'!S$6:S$1005,L64)</f>
+        <v/>
+      </c>
+      <c r="M81" s="32">
+        <f>INDEX('Tax Rates &amp; Assumptions'!T$6:T$1005,L64)</f>
+        <v/>
+      </c>
+      <c r="N81" s="32">
+        <f>INDEX('Tax Rates &amp; Assumptions'!U$6:U$1005,L64)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82" hidden="1" outlineLevel="1">
+      <c r="B82" s="21" t="inlineStr">
         <is>
           <t>Total Estimated Tax</t>
         </is>
       </c>
-      <c r="C80" s="36">
-        <f>(C73+C74+C77+C79)</f>
-        <v/>
-      </c>
-      <c r="L80" s="30">
-        <f>INDEX('Tax Rates &amp; Assumptions'!V$6:V$1005,L62)</f>
-        <v/>
-      </c>
-      <c r="M80" s="31">
-        <f>INDEX('Tax Rates &amp; Assumptions'!W$6:W$1005,L62)</f>
-        <v/>
-      </c>
-      <c r="N80" s="31">
-        <f>INDEX('Tax Rates &amp; Assumptions'!X$6:X$1005,L62)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="81" hidden="1" outlineLevel="1">
-      <c r="B81" s="32" t="inlineStr">
+      <c r="C82" s="37">
+        <f>(C75+C76+C79+C81)</f>
+        <v/>
+      </c>
+      <c r="L82" s="31">
+        <f>INDEX('Tax Rates &amp; Assumptions'!V$6:V$1005,L64)</f>
+        <v/>
+      </c>
+      <c r="M82" s="32">
+        <f>INDEX('Tax Rates &amp; Assumptions'!W$6:W$1005,L64)</f>
+        <v/>
+      </c>
+      <c r="N82" s="32">
+        <f>INDEX('Tax Rates &amp; Assumptions'!X$6:X$1005,L64)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83" hidden="1" outlineLevel="1">
+      <c r="B83" s="33" t="inlineStr">
         <is>
           <t>Effective Tax Rate on the Gain</t>
         </is>
       </c>
-      <c r="C81" s="37">
-        <f>IFERROR(C80/MAX(0.0001,C66),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="82" hidden="1" outlineLevel="1">
-      <c r="B82" s="32" t="inlineStr">
+      <c r="C83" s="38">
+        <f>IFERROR(C82/MAX(0.0001,C68),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84" hidden="1" outlineLevel="1">
+      <c r="B84" s="33" t="inlineStr">
         <is>
           <t>Marginal LTCG Rate Applied</t>
         </is>
       </c>
-      <c r="C82" s="37">
-        <f>IFERROR(INDEX($L$83:$L$85,MATCH(C70,$M$83:$M$85,1)),0)</f>
-        <v/>
-      </c>
-      <c r="K82" s="29" t="inlineStr">
+      <c r="C84" s="38">
+        <f>IFERROR(INDEX($L$85:$L$87,MATCH(C72,$M$85:$M$87,1)),0)</f>
+        <v/>
+      </c>
+      <c r="K84" s="30" t="inlineStr">
         <is>
           <t>LTCG Brackets</t>
         </is>
       </c>
     </row>
-    <row r="83" hidden="1" outlineLevel="1">
-      <c r="L83" s="30">
-        <f>INDEX('Tax Rates &amp; Assumptions'!D$17:D$1016,L63)</f>
-        <v/>
-      </c>
-      <c r="M83" s="31">
-        <f>INDEX('Tax Rates &amp; Assumptions'!E$17:E$1016,L63)</f>
-        <v/>
-      </c>
-      <c r="N83" s="31">
-        <f>INDEX('Tax Rates &amp; Assumptions'!F$17:F$1016,L63)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="84" hidden="1" outlineLevel="1">
-      <c r="L84" s="30">
-        <f>INDEX('Tax Rates &amp; Assumptions'!G$17:G$1016,L63)</f>
-        <v/>
-      </c>
-      <c r="M84" s="31">
-        <f>INDEX('Tax Rates &amp; Assumptions'!H$17:H$1016,L63)</f>
-        <v/>
-      </c>
-      <c r="N84" s="31">
-        <f>INDEX('Tax Rates &amp; Assumptions'!I$17:I$1016,L63)</f>
-        <v/>
-      </c>
-    </row>
     <row r="85" hidden="1" outlineLevel="1">
-      <c r="L85" s="30">
-        <f>INDEX('Tax Rates &amp; Assumptions'!J$17:J$1016,L63)</f>
-        <v/>
-      </c>
-      <c r="M85" s="31">
-        <f>INDEX('Tax Rates &amp; Assumptions'!K$17:K$1016,L63)</f>
-        <v/>
-      </c>
-      <c r="N85" s="31">
-        <f>INDEX('Tax Rates &amp; Assumptions'!L$17:L$1016,L63)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="86" hidden="1" outlineLevel="1"/>
+      <c r="B85" s="33" t="inlineStr">
+        <is>
+          <t>State Marginal Tax Rate (on taxable income before any gain)</t>
+        </is>
+      </c>
+      <c r="C85" s="38">
+        <f>IF(L69="OTHER",C10,IFERROR(INDEX($L$90:$L$97,MATCH(MAX(0,C11-C65),$M$90:$M$97,1)),0))</f>
+        <v/>
+      </c>
+      <c r="L85" s="31">
+        <f>INDEX('Tax Rates &amp; Assumptions'!D$17:D$1016,L65)</f>
+        <v/>
+      </c>
+      <c r="M85" s="32">
+        <f>INDEX('Tax Rates &amp; Assumptions'!E$17:E$1016,L65)</f>
+        <v/>
+      </c>
+      <c r="N85" s="32">
+        <f>INDEX('Tax Rates &amp; Assumptions'!F$17:F$1016,L65)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86" hidden="1" outlineLevel="1">
+      <c r="L86" s="31">
+        <f>INDEX('Tax Rates &amp; Assumptions'!G$17:G$1016,L65)</f>
+        <v/>
+      </c>
+      <c r="M86" s="32">
+        <f>INDEX('Tax Rates &amp; Assumptions'!H$17:H$1016,L65)</f>
+        <v/>
+      </c>
+      <c r="N86" s="32">
+        <f>INDEX('Tax Rates &amp; Assumptions'!I$17:I$1016,L65)</f>
+        <v/>
+      </c>
+    </row>
     <row r="87" hidden="1" outlineLevel="1">
-      <c r="K87" s="29" t="inlineStr">
+      <c r="L87" s="31">
+        <f>INDEX('Tax Rates &amp; Assumptions'!J$17:J$1016,L65)</f>
+        <v/>
+      </c>
+      <c r="M87" s="32">
+        <f>INDEX('Tax Rates &amp; Assumptions'!K$17:K$1016,L65)</f>
+        <v/>
+      </c>
+      <c r="N87" s="32">
+        <f>INDEX('Tax Rates &amp; Assumptions'!L$17:L$1016,L65)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88" hidden="1" outlineLevel="1"/>
+    <row r="89" hidden="1" outlineLevel="1">
+      <c r="K89" s="30" t="inlineStr">
         <is>
           <t>State Brackets</t>
         </is>
       </c>
     </row>
-    <row r="88" hidden="1" outlineLevel="1">
-      <c r="L88" s="30">
-        <f>INDEX('Tax Rates &amp; Assumptions'!D$81:D$1080,L70)</f>
-        <v/>
-      </c>
-      <c r="M88" s="31">
-        <f>INDEX('Tax Rates &amp; Assumptions'!E$81:E$1080,L70)</f>
-        <v/>
-      </c>
-      <c r="N88" s="31">
-        <f>INDEX('Tax Rates &amp; Assumptions'!F$81:F$1080,L70)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="89" hidden="1" outlineLevel="1">
-      <c r="L89" s="30">
-        <f>INDEX('Tax Rates &amp; Assumptions'!G$81:G$1080,L70)</f>
-        <v/>
-      </c>
-      <c r="M89" s="31">
-        <f>INDEX('Tax Rates &amp; Assumptions'!H$81:H$1080,L70)</f>
-        <v/>
-      </c>
-      <c r="N89" s="31">
-        <f>INDEX('Tax Rates &amp; Assumptions'!I$81:I$1080,L70)</f>
-        <v/>
-      </c>
-    </row>
     <row r="90" hidden="1" outlineLevel="1">
-      <c r="L90" s="30">
-        <f>INDEX('Tax Rates &amp; Assumptions'!J$81:J$1080,L70)</f>
-        <v/>
-      </c>
-      <c r="M90" s="31">
-        <f>INDEX('Tax Rates &amp; Assumptions'!K$81:K$1080,L70)</f>
-        <v/>
-      </c>
-      <c r="N90" s="31">
-        <f>INDEX('Tax Rates &amp; Assumptions'!L$81:L$1080,L70)</f>
+      <c r="L90" s="31">
+        <f>INDEX('Tax Rates &amp; Assumptions'!D$81:D$1080,L72)</f>
+        <v/>
+      </c>
+      <c r="M90" s="32">
+        <f>INDEX('Tax Rates &amp; Assumptions'!E$81:E$1080,L72)</f>
+        <v/>
+      </c>
+      <c r="N90" s="32">
+        <f>INDEX('Tax Rates &amp; Assumptions'!F$81:F$1080,L72)</f>
         <v/>
       </c>
     </row>
     <row r="91" hidden="1" outlineLevel="1">
-      <c r="L91" s="30">
-        <f>INDEX('Tax Rates &amp; Assumptions'!M$81:M$1080,L70)</f>
-        <v/>
-      </c>
-      <c r="M91" s="31">
-        <f>INDEX('Tax Rates &amp; Assumptions'!N$81:N$1080,L70)</f>
-        <v/>
-      </c>
-      <c r="N91" s="31">
-        <f>INDEX('Tax Rates &amp; Assumptions'!O$81:O$1080,L70)</f>
+      <c r="L91" s="31">
+        <f>INDEX('Tax Rates &amp; Assumptions'!G$81:G$1080,L72)</f>
+        <v/>
+      </c>
+      <c r="M91" s="32">
+        <f>INDEX('Tax Rates &amp; Assumptions'!H$81:H$1080,L72)</f>
+        <v/>
+      </c>
+      <c r="N91" s="32">
+        <f>INDEX('Tax Rates &amp; Assumptions'!I$81:I$1080,L72)</f>
         <v/>
       </c>
     </row>
     <row r="92" hidden="1" outlineLevel="1">
-      <c r="L92" s="30">
-        <f>INDEX('Tax Rates &amp; Assumptions'!P$81:P$1080,L70)</f>
-        <v/>
-      </c>
-      <c r="M92" s="31">
-        <f>INDEX('Tax Rates &amp; Assumptions'!Q$81:Q$1080,L70)</f>
-        <v/>
-      </c>
-      <c r="N92" s="31">
-        <f>INDEX('Tax Rates &amp; Assumptions'!R$81:R$1080,L70)</f>
+      <c r="L92" s="31">
+        <f>INDEX('Tax Rates &amp; Assumptions'!J$81:J$1080,L72)</f>
+        <v/>
+      </c>
+      <c r="M92" s="32">
+        <f>INDEX('Tax Rates &amp; Assumptions'!K$81:K$1080,L72)</f>
+        <v/>
+      </c>
+      <c r="N92" s="32">
+        <f>INDEX('Tax Rates &amp; Assumptions'!L$81:L$1080,L72)</f>
         <v/>
       </c>
     </row>
     <row r="93" hidden="1" outlineLevel="1">
-      <c r="L93" s="30">
-        <f>INDEX('Tax Rates &amp; Assumptions'!S$81:S$1080,L70)</f>
-        <v/>
-      </c>
-      <c r="M93" s="31">
-        <f>INDEX('Tax Rates &amp; Assumptions'!T$81:T$1080,L70)</f>
-        <v/>
-      </c>
-      <c r="N93" s="31">
-        <f>INDEX('Tax Rates &amp; Assumptions'!U$81:U$1080,L70)</f>
+      <c r="L93" s="31">
+        <f>INDEX('Tax Rates &amp; Assumptions'!M$81:M$1080,L72)</f>
+        <v/>
+      </c>
+      <c r="M93" s="32">
+        <f>INDEX('Tax Rates &amp; Assumptions'!N$81:N$1080,L72)</f>
+        <v/>
+      </c>
+      <c r="N93" s="32">
+        <f>INDEX('Tax Rates &amp; Assumptions'!O$81:O$1080,L72)</f>
         <v/>
       </c>
     </row>
     <row r="94" hidden="1" outlineLevel="1">
-      <c r="L94" s="30">
-        <f>INDEX('Tax Rates &amp; Assumptions'!V$81:V$1080,L70)</f>
-        <v/>
-      </c>
-      <c r="M94" s="31">
-        <f>INDEX('Tax Rates &amp; Assumptions'!W$81:W$1080,L70)</f>
-        <v/>
-      </c>
-      <c r="N94" s="31">
-        <f>INDEX('Tax Rates &amp; Assumptions'!X$81:X$1080,L70)</f>
+      <c r="L94" s="31">
+        <f>INDEX('Tax Rates &amp; Assumptions'!P$81:P$1080,L72)</f>
+        <v/>
+      </c>
+      <c r="M94" s="32">
+        <f>INDEX('Tax Rates &amp; Assumptions'!Q$81:Q$1080,L72)</f>
+        <v/>
+      </c>
+      <c r="N94" s="32">
+        <f>INDEX('Tax Rates &amp; Assumptions'!R$81:R$1080,L72)</f>
         <v/>
       </c>
     </row>
     <row r="95" hidden="1" outlineLevel="1">
-      <c r="L95" s="30">
-        <f>INDEX('Tax Rates &amp; Assumptions'!Y$81:Y$1080,L70)</f>
-        <v/>
-      </c>
-      <c r="M95" s="31">
-        <f>INDEX('Tax Rates &amp; Assumptions'!Z$81:Z$1080,L70)</f>
-        <v/>
-      </c>
-      <c r="N95" s="31">
-        <f>INDEX('Tax Rates &amp; Assumptions'!AA$81:AA$1080,L70)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="96" hidden="1" outlineLevel="1"/>
+      <c r="L95" s="31">
+        <f>INDEX('Tax Rates &amp; Assumptions'!S$81:S$1080,L72)</f>
+        <v/>
+      </c>
+      <c r="M95" s="32">
+        <f>INDEX('Tax Rates &amp; Assumptions'!T$81:T$1080,L72)</f>
+        <v/>
+      </c>
+      <c r="N95" s="32">
+        <f>INDEX('Tax Rates &amp; Assumptions'!U$81:U$1080,L72)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96" hidden="1" outlineLevel="1">
+      <c r="L96" s="31">
+        <f>INDEX('Tax Rates &amp; Assumptions'!V$81:V$1080,L72)</f>
+        <v/>
+      </c>
+      <c r="M96" s="32">
+        <f>INDEX('Tax Rates &amp; Assumptions'!W$81:W$1080,L72)</f>
+        <v/>
+      </c>
+      <c r="N96" s="32">
+        <f>INDEX('Tax Rates &amp; Assumptions'!X$81:X$1080,L72)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97" hidden="1" outlineLevel="1">
+      <c r="L97" s="31">
+        <f>INDEX('Tax Rates &amp; Assumptions'!Y$81:Y$1080,L72)</f>
+        <v/>
+      </c>
+      <c r="M97" s="32">
+        <f>INDEX('Tax Rates &amp; Assumptions'!Z$81:Z$1080,L72)</f>
+        <v/>
+      </c>
+      <c r="N97" s="32">
+        <f>INDEX('Tax Rates &amp; Assumptions'!AA$81:AA$1080,L72)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98" hidden="1" outlineLevel="1"/>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A19:F19"/>
-    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="B55:F57"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A12:F12"/>
     <mergeCell ref="A4:F4"/>
-    <mergeCell ref="B53:F55"/>
+    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="B9:F9"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation sqref="C5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">

--- a/Capital_Gains_Tax_Estimator.xlsx
+++ b/Capital_Gains_Tax_Estimator.xlsx
@@ -17,11 +17,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="$#,##0;($#,##0)"/>
+    <numFmt numFmtId="166" formatCode="&quot;Total Capital Gains Tax You Will Pay: &quot;$#,##0"/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="28">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -75,6 +76,17 @@
     </font>
     <font>
       <name val="Arial"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00595959"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00C00000"/>
       <sz val="11"/>
@@ -94,7 +106,7 @@
       <name val="Arial"/>
       <i val="1"/>
       <color rgb="00C00000"/>
-      <sz val="9.5"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -105,31 +117,32 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="001F3864"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <i val="1"/>
-      <color rgb="00595959"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="00000000"/>
-      <sz val="10"/>
+      <color rgb="002E5395"/>
+      <sz val="9.5"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="9"/>
+      <color rgb="001F3864"/>
+      <sz val="20"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00BF8F00"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
       <i val="1"/>
       <color rgb="00C00000"/>
       <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00595959"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -169,7 +182,7 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="001F3864"/>
-      <sz val="16"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="7">
@@ -236,7 +249,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -269,75 +282,69 @@
     <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="17" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="24" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="24" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="10" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="26" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="10" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="24" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="25" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="25" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="27" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -412,93 +419,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Estimated Tax - By Type</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <pieChart>
-        <varyColors val="1"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'Capital Gains Tax Calculator'!G38</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Capital Gains Tax Calculator'!$F$39:$F$41</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Capital Gains Tax Calculator'!$G$39:$G$41</f>
-            </numRef>
-          </val>
-        </ser>
-        <dLbls>
-          <showPercent val="1"/>
-        </dLbls>
-        <firstSliceAng val="0"/>
-      </pieChart>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>37</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="4320000" cy="2700000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="1" name="Chart 1"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -790,16 +710,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N97"/>
+  <dimension ref="A1:N74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
-    <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="4" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="4" customWidth="1" min="7" max="7"/>
+    <col width="2" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="3" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="3" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="2" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
@@ -809,176 +732,161 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="19" t="inlineStr">
+      <c r="A1" s="21" t="inlineStr">
         <is>
           <t>CAPITAL GAINS TAX CALCULATOR</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="20" t="inlineStr">
-        <is>
-          <t>Estimated tax from capital gains and losses. For planning purposes only - not tax, legal, or accounting advice.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>YOUR INFO</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="n"/>
-      <c r="C4" s="4" t="n"/>
-      <c r="D4" s="4" t="n"/>
-      <c r="E4" s="4" t="n"/>
-      <c r="F4" s="4" t="n"/>
+      <c r="A2" s="22" t="inlineStr">
+        <is>
+          <t>Estimated for planning purposes only - not tax, legal, or accounting advice.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="23" t="inlineStr">
+        <is>
+          <t>Initial Value</t>
+        </is>
+      </c>
+      <c r="E4" s="23" t="inlineStr">
+        <is>
+          <t>Sale Value</t>
+        </is>
+      </c>
+      <c r="H4" s="23" t="inlineStr">
+        <is>
+          <t>Length of Ownership</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="B5" s="21" t="inlineStr">
+      <c r="C5" s="13" t="n">
+        <v>10000</v>
+      </c>
+      <c r="F5" s="13" t="n">
+        <v>50000</v>
+      </c>
+      <c r="I5" s="12" t="inlineStr">
+        <is>
+          <t>More than a year</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="23" t="inlineStr">
+        <is>
+          <t>Location (State)</t>
+        </is>
+      </c>
+      <c r="E7" s="23" t="inlineStr">
+        <is>
+          <t>Annual Income</t>
+        </is>
+      </c>
+      <c r="H7" s="23" t="inlineStr">
+        <is>
+          <t>Filing Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>New Jersey</t>
+        </is>
+      </c>
+      <c r="F8" s="13" t="n">
+        <v>200000</v>
+      </c>
+      <c r="I8" s="12" t="inlineStr">
+        <is>
+          <t>Married Filing Jointly</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="16" t="inlineStr">
         <is>
           <t>Tax Year</t>
         </is>
       </c>
-      <c r="C5" s="12" t="n">
+    </row>
+    <row r="10">
+      <c r="C10" s="12" t="n">
         <v>2025</v>
       </c>
     </row>
-    <row r="6">
-      <c r="B6" s="21" t="inlineStr">
-        <is>
-          <t>Filing Status</t>
-        </is>
-      </c>
-      <c r="C6" s="12" t="inlineStr">
-        <is>
-          <t>Married Filing Jointly</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="21" t="inlineStr">
-        <is>
-          <t>State of Residence</t>
-        </is>
-      </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>New Jersey</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" s="21" t="inlineStr">
-        <is>
-          <t>Estimated State Marginal Tax Rate</t>
-        </is>
-      </c>
-      <c r="C8" s="22">
-        <f>C85</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" s="23" t="inlineStr">
-        <is>
-          <t>(automatically pulled from the Tax Rates &amp; Assumptions tab based on your state and taxable income below)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" s="24" t="inlineStr">
-        <is>
-          <t>Manual State Tax Rate Override - used ONLY if State of Residence = 'Other (Manual Entry)'</t>
-        </is>
-      </c>
-      <c r="C10" s="14" t="n">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="21" t="inlineStr">
-        <is>
-          <t>Taxable Income (before these gains/losses)</t>
-        </is>
-      </c>
-      <c r="C11" s="13" t="n">
-        <v>200000</v>
-      </c>
-    </row>
     <row r="12">
-      <c r="B12" s="23" t="inlineStr">
-        <is>
-          <t>(your salary/other income after deductions - used only to determine which tax brackets your gains fall into)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>CAPITAL GAINS &amp; LOSSES</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="n"/>
-      <c r="C14" s="4" t="n"/>
-      <c r="D14" s="4" t="n"/>
-      <c r="E14" s="4" t="n"/>
-      <c r="F14" s="4" t="n"/>
-    </row>
-    <row r="15">
-      <c r="B15" s="25" t="inlineStr">
-        <is>
-          <t>Short-Term Capital Gains (held 1 year or less)</t>
-        </is>
-      </c>
-      <c r="C15" s="13" t="n">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="25" t="inlineStr">
-        <is>
-          <t>Long-Term Capital Gains (held more than 1 year)</t>
-        </is>
-      </c>
-      <c r="C16" s="13" t="n">
-        <v>155000</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="25" t="inlineStr">
-        <is>
-          <t>Short-Term Capital Losses</t>
-        </is>
-      </c>
-      <c r="C17" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="25" t="inlineStr">
-        <is>
-          <t>Long-Term Capital Losses</t>
-        </is>
-      </c>
-      <c r="C18" s="13" t="n">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="25" t="inlineStr">
-        <is>
-          <t>Capital Loss Carryforward (from prior years)</t>
-        </is>
-      </c>
-      <c r="C19" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
+      <c r="B12" s="24" t="inlineStr">
+        <is>
+          <t>ADVANCED (optional - click the [+] in the row-number margin to expand)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="B13" s="16" t="inlineStr">
+        <is>
+          <t>401(k) Contribution</t>
+        </is>
+      </c>
+      <c r="E13" s="16" t="inlineStr">
+        <is>
+          <t>IRA Contribution</t>
+        </is>
+      </c>
+      <c r="H13" s="16" t="inlineStr">
+        <is>
+          <t>Itemized Deductions</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" hidden="1" outlineLevel="1">
+      <c r="C14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" hidden="1" outlineLevel="1">
+      <c r="B15" s="16" t="inlineStr">
+        <is>
+          <t>Number of Personal Exemptions (state only)</t>
+        </is>
+      </c>
+      <c r="E15" s="16" t="inlineStr">
+        <is>
+          <t>Locality / City (optional)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" hidden="1" outlineLevel="1">
+      <c r="C16" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="12" t="inlineStr">
+        <is>
+          <t>None / Not Applicable</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="B18" s="25">
+        <f>C63</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1"/>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>ESTIMATED TAX</t>
+          <t>YOUR CAPITAL GAINS TAXES</t>
         </is>
       </c>
       <c r="B21" s="4" t="n"/>
@@ -986,912 +894,893 @@
       <c r="D21" s="4" t="n"/>
       <c r="E21" s="4" t="n"/>
       <c r="F21" s="4" t="n"/>
-    </row>
-    <row r="22" ht="28" customHeight="1">
-      <c r="B22" s="26" t="inlineStr">
+      <c r="G21" s="4" t="n"/>
+      <c r="H21" s="4" t="n"/>
+    </row>
+    <row r="22">
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Tax Type</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>Marginal Tax Rate</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>Effective Tax Rate</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>Tax Amount</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="23" t="inlineStr">
+        <is>
+          <t>Federal</t>
+        </is>
+      </c>
+      <c r="D23" s="40">
+        <f>C64</f>
+        <v/>
+      </c>
+      <c r="F23" s="40">
+        <f>C65</f>
+        <v/>
+      </c>
+      <c r="H23" s="41">
+        <f>C56</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="23" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="D24" s="40">
+        <f>C66</f>
+        <v/>
+      </c>
+      <c r="F24" s="40">
+        <f>C67</f>
+        <v/>
+      </c>
+      <c r="H24" s="41">
+        <f>C61</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="23" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="D25" s="40">
+        <f>C42</f>
+        <v/>
+      </c>
+      <c r="F25" s="40">
+        <f>C68</f>
+        <v/>
+      </c>
+      <c r="H25" s="41">
+        <f>C62</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="26" t="inlineStr">
         <is>
           <t>Total Estimated Tax</t>
         </is>
       </c>
-      <c r="C22" s="26" t="inlineStr">
-        <is>
-          <t>Effective Tax Rate</t>
-        </is>
-      </c>
-      <c r="D22" s="26" t="inlineStr">
-        <is>
-          <t>Federal Tax</t>
-        </is>
-      </c>
-      <c r="E22" s="26" t="inlineStr">
-        <is>
-          <t>State Tax</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="30" customHeight="1">
-      <c r="B23" s="39">
-        <f>C82</f>
-        <v/>
-      </c>
-      <c r="C23" s="40">
-        <f>C83</f>
-        <v/>
-      </c>
-      <c r="D23" s="39">
-        <f>(C75+C76)</f>
-        <v/>
-      </c>
-      <c r="E23" s="39">
-        <f>C81</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="25" t="inlineStr">
-        <is>
-          <t>Net Short-Term Gain / (Loss)</t>
-        </is>
-      </c>
-      <c r="C25" s="41">
-        <f>C66</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="25" t="inlineStr">
-        <is>
-          <t>Net Long-Term Gain / (Loss)</t>
-        </is>
-      </c>
-      <c r="C26" s="41">
-        <f>C67</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="21" t="inlineStr">
-        <is>
-          <t>Total Net Capital Gain / (Loss)</t>
-        </is>
-      </c>
-      <c r="C27" s="42">
-        <f>C68</f>
+      <c r="H26" s="42">
+        <f>C63</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="25" t="inlineStr">
-        <is>
-          <t>Capital Loss Deduction (against ordinary income)</t>
-        </is>
-      </c>
-      <c r="C28" s="41">
-        <f>IF(C68&lt;0,MAX(C68,-C62),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="25" t="inlineStr">
-        <is>
-          <t>Capital Loss Carryforward to Future Years</t>
-        </is>
-      </c>
-      <c r="C29" s="41">
-        <f>-C71</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="25" t="inlineStr">
-        <is>
-          <t>Federal Tax on Short-Term Gain (ordinary rates)</t>
-        </is>
-      </c>
-      <c r="C30" s="41">
-        <f>C75</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" s="25" t="inlineStr">
-        <is>
-          <t>Federal Tax on Long-Term Gain (preferential rates)</t>
-        </is>
-      </c>
-      <c r="C31" s="41">
-        <f>C76</f>
-        <v/>
-      </c>
-    </row>
+      <c r="B28" s="27" t="inlineStr">
+        <is>
+          <t>Estimated for financial-planning purposes only. This calculator is not tax, legal, or accounting advice. Actual tax liability may differ based on individual circumstances, deductions, credits, tax elections, state/local rules, and other factors. Consult a qualified tax professional before making tax-related decisions. "Federal" includes the Net Investment Income Tax (3.8%) where applicable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29"/>
+    <row r="30"/>
     <row r="32">
-      <c r="B32" s="25" t="inlineStr">
-        <is>
-          <t>Net Investment Income Tax (NIIT)</t>
-        </is>
-      </c>
-      <c r="C32" s="41">
-        <f>C79</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="25" t="inlineStr">
-        <is>
-          <t>State Tax</t>
-        </is>
-      </c>
-      <c r="C33" s="41">
-        <f>C81</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34">
-      <c r="B34" s="21" t="inlineStr">
+      <c r="B32" s="28" t="inlineStr">
+        <is>
+          <t>Full calculation detail is available below for your advisor. Click the [+] in the row-number margin to expand.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A34" s="29" t="inlineStr">
+        <is>
+          <t>CALCULATION DETAIL (grouped - click + to expand)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" hidden="1" outlineLevel="1"/>
+    <row r="36" hidden="1" outlineLevel="1">
+      <c r="B36" s="34" t="inlineStr">
+        <is>
+          <t>Standard Deduction (add-back for MAGI estimate)</t>
+        </is>
+      </c>
+      <c r="C36" s="35">
+        <f>INDEX('Tax Rates &amp; Assumptions'!$D$28:$D$35,L42)</f>
+        <v/>
+      </c>
+      <c r="K36" s="7" t="inlineStr">
+        <is>
+          <t>Filing Status</t>
+        </is>
+      </c>
+      <c r="L36" s="30">
+        <f>I8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" hidden="1" outlineLevel="1">
+      <c r="B37" s="34" t="inlineStr">
+        <is>
+          <t>Capital Loss Limit vs. Ordinary Income</t>
+        </is>
+      </c>
+      <c r="C37" s="35">
+        <f>INDEX('Tax Rates &amp; Assumptions'!$D$39:$D$42,L41)</f>
+        <v/>
+      </c>
+      <c r="K37" s="7" t="inlineStr">
+        <is>
+          <t>Tax Year</t>
+        </is>
+      </c>
+      <c r="L37" s="30">
+        <f>C10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" hidden="1" outlineLevel="1">
+      <c r="B38" s="34" t="inlineStr">
+        <is>
+          <t>NIIT Threshold</t>
+        </is>
+      </c>
+      <c r="C38" s="35">
+        <f>INDEX('Tax Rates &amp; Assumptions'!$B$39:$B$42,L41)</f>
+        <v/>
+      </c>
+      <c r="K38" s="7" t="inlineStr">
+        <is>
+          <t>Federal Key</t>
+        </is>
+      </c>
+      <c r="L38" s="30">
+        <f>L37&amp;"|"&amp;L36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39" hidden="1" outlineLevel="1">
+      <c r="B39" s="34" t="inlineStr">
+        <is>
+          <t>NIIT Rate</t>
+        </is>
+      </c>
+      <c r="C39" s="36">
+        <f>INDEX('Tax Rates &amp; Assumptions'!$C$39:$C$42,L41)</f>
+        <v/>
+      </c>
+      <c r="K39" s="7" t="inlineStr">
+        <is>
+          <t>Fed Bracket Row#</t>
+        </is>
+      </c>
+      <c r="L39" s="30">
+        <f>MATCH(L38,'Tax Rates &amp; Assumptions'!$C$6:$C$13,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" hidden="1" outlineLevel="1">
+      <c r="B40" s="34" t="inlineStr">
+        <is>
+          <t>State Standard Deduction</t>
+        </is>
+      </c>
+      <c r="C40" s="35">
+        <f>IF(L45="MFJ",INDEX('Tax Rates &amp; Assumptions'!$E$46:$E$77,L48),INDEX('Tax Rates &amp; Assumptions'!$D$46:$D$77,L48))</f>
+        <v/>
+      </c>
+      <c r="K40" s="7" t="inlineStr">
+        <is>
+          <t>LTCG Bracket Row#</t>
+        </is>
+      </c>
+      <c r="L40" s="30">
+        <f>MATCH(L38,'Tax Rates &amp; Assumptions'!$C$17:$C$24,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" hidden="1" outlineLevel="1">
+      <c r="B41" s="34" t="inlineStr">
+        <is>
+          <t>Personal Exemption Amount (per exemption, state)</t>
+        </is>
+      </c>
+      <c r="C41" s="35">
+        <f>INDEX('Tax Rates &amp; Assumptions'!$C$164:$C$164,1)</f>
+        <v/>
+      </c>
+      <c r="K41" s="7" t="inlineStr">
+        <is>
+          <t>Status Row# (NIIT/CapLoss)</t>
+        </is>
+      </c>
+      <c r="L41" s="30">
+        <f>MATCH(L36,'Tax Rates &amp; Assumptions'!$A$39:$A$42,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42" hidden="1" outlineLevel="1">
+      <c r="B42" s="34" t="inlineStr">
+        <is>
+          <t>Local Tax Rate</t>
+        </is>
+      </c>
+      <c r="C42" s="36">
+        <f>IF(L50=0,0,INDEX('Tax Rates &amp; Assumptions'!$D$148:$D$161,L50))</f>
+        <v/>
+      </c>
+      <c r="K42" s="7" t="inlineStr">
+        <is>
+          <t>StdDed Row#</t>
+        </is>
+      </c>
+      <c r="L42" s="30">
+        <f>MATCH(L38,'Tax Rates &amp; Assumptions'!$C$28:$C$35,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" hidden="1" outlineLevel="1">
+      <c r="B43" s="34" t="inlineStr">
+        <is>
+          <t>Capital Gain / (Loss) on Sale</t>
+        </is>
+      </c>
+      <c r="C43" s="35">
+        <f>(F5-C5)</f>
+        <v/>
+      </c>
+      <c r="K43" s="7" t="inlineStr">
+        <is>
+          <t>State Name</t>
+        </is>
+      </c>
+      <c r="L43" s="30">
+        <f>C8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" hidden="1" outlineLevel="1">
+      <c r="B44" s="34" t="inlineStr">
+        <is>
+          <t>Is Long-Term?</t>
+        </is>
+      </c>
+      <c r="C44" s="35">
+        <f>IF(I5="More than a year",1,0)</f>
+        <v/>
+      </c>
+      <c r="K44" s="7" t="inlineStr">
+        <is>
+          <t>State Code</t>
+        </is>
+      </c>
+      <c r="L44" s="30">
+        <f>INDEX('Tax Rates &amp; Assumptions'!$A$46:$A$77,MATCH(L43,'Tax Rates &amp; Assumptions'!$B$46:$B$77,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45" hidden="1" outlineLevel="1">
+      <c r="B45" s="34" t="inlineStr">
+        <is>
+          <t>Ordinary-Taxed Portion (short-term gain, or loss deduction capped)</t>
+        </is>
+      </c>
+      <c r="C45" s="35">
+        <f>IF(C43&gt;=0,IF(C44=1,0,C43),MAX(C43,-C37))</f>
+        <v/>
+      </c>
+      <c r="K45" s="7" t="inlineStr">
+        <is>
+          <t>State Category</t>
+        </is>
+      </c>
+      <c r="L45" s="30">
+        <f>IF(L36="Married Filing Jointly","MFJ","Single")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" hidden="1" outlineLevel="1">
+      <c r="B46" s="34" t="inlineStr">
+        <is>
+          <t>Preferential-Rate Portion (long-term gain)</t>
+        </is>
+      </c>
+      <c r="C46" s="35">
+        <f>IF(C43&gt;=0,IF(C44=1,C43,0),0)</f>
+        <v/>
+      </c>
+      <c r="K46" s="7" t="inlineStr">
+        <is>
+          <t>State Key</t>
+        </is>
+      </c>
+      <c r="L46" s="30">
+        <f>L44&amp;"|"&amp;L45</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" hidden="1" outlineLevel="1">
+      <c r="B47" s="34" t="inlineStr">
+        <is>
+          <t>Taxable Income Before the Gain</t>
+        </is>
+      </c>
+      <c r="C47" s="35">
+        <f>MAX(0,F8-C14-F14-MAX(I14,INDEX('Tax Rates &amp; Assumptions'!$D$28:$D$35,L42)))</f>
+        <v/>
+      </c>
+      <c r="K47" s="7" t="inlineStr">
+        <is>
+          <t>State Bracket Row#</t>
+        </is>
+      </c>
+      <c r="L47" s="30">
+        <f>MATCH(L46,'Tax Rates &amp; Assumptions'!$C$81:$C$144,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48" hidden="1" outlineLevel="1">
+      <c r="B48" s="34" t="inlineStr">
+        <is>
+          <t>Taxable Income Including the Gain</t>
+        </is>
+      </c>
+      <c r="C48" s="35">
+        <f>MAX(0,C47+C45)</f>
+        <v/>
+      </c>
+      <c r="K48" s="7" t="inlineStr">
+        <is>
+          <t>State Master Row#</t>
+        </is>
+      </c>
+      <c r="L48" s="30">
+        <f>MATCH(L44,'Tax Rates &amp; Assumptions'!$A$46:$A$77,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49" hidden="1" outlineLevel="1">
+      <c r="B49" s="34" t="inlineStr">
+        <is>
+          <t>Federal Tax on Income Alone (no gain)</t>
+        </is>
+      </c>
+      <c r="C49" s="35">
+        <f>SUMPRODUCT((C47&gt;$M$53:$M$59)*($L$53:$L$59)*(MIN(C47,$N$53:$N$59)-$M$53:$M$59))</f>
+        <v/>
+      </c>
+      <c r="K49" s="7" t="inlineStr">
+        <is>
+          <t>Locality Name</t>
+        </is>
+      </c>
+      <c r="L49" s="30">
+        <f>F16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50" hidden="1" outlineLevel="1">
+      <c r="B50" s="34" t="inlineStr">
+        <is>
+          <t>Federal Tax on Income Including the Gain</t>
+        </is>
+      </c>
+      <c r="C50" s="35">
+        <f>SUMPRODUCT((C48&gt;$M$53:$M$59)*($L$53:$L$59)*(MIN(C48,$N$53:$N$59)-$M$53:$M$59))</f>
+        <v/>
+      </c>
+      <c r="K50" s="7" t="inlineStr">
+        <is>
+          <t>Locality Row#</t>
+        </is>
+      </c>
+      <c r="L50" s="30">
+        <f>IFERROR(MATCH(L49,'Tax Rates &amp; Assumptions'!$B$148:$B$161,0),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51" hidden="1" outlineLevel="1">
+      <c r="B51" s="34" t="inlineStr">
+        <is>
+          <t>Federal Tax on Ordinary Portion of the Gain</t>
+        </is>
+      </c>
+      <c r="C51" s="35">
+        <f>C50-C49</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52" hidden="1" outlineLevel="1">
+      <c r="B52" s="34" t="inlineStr">
+        <is>
+          <t>Federal Tax on Preferential (Long-Term) Portion (stacked)</t>
+        </is>
+      </c>
+      <c r="C52" s="35">
+        <f>SUMPRODUCT($L$62:$L$64*(MAX(0,MIN((C48+C46),$N$62:$N$64)-MAX(C48,$M$62:$M$64))))</f>
+        <v/>
+      </c>
+      <c r="K52" s="31" t="inlineStr">
+        <is>
+          <t>Federal Ordinary Brackets</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" hidden="1" outlineLevel="1">
+      <c r="B53" s="34" t="inlineStr">
+        <is>
+          <t>MAGI Estimate (Taxable Income + Std. Ded. Add-Back + Net Gain)</t>
+        </is>
+      </c>
+      <c r="C53" s="35">
+        <f>(C47+C36+C45+C46)</f>
+        <v/>
+      </c>
+      <c r="L53" s="32">
+        <f>INDEX('Tax Rates &amp; Assumptions'!D$6:D$1005,L39)</f>
+        <v/>
+      </c>
+      <c r="M53" s="33">
+        <f>INDEX('Tax Rates &amp; Assumptions'!E$6:E$1005,L39)</f>
+        <v/>
+      </c>
+      <c r="N53" s="33">
+        <f>INDEX('Tax Rates &amp; Assumptions'!F$6:F$1005,L39)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54" hidden="1" outlineLevel="1">
+      <c r="B54" s="34" t="inlineStr">
+        <is>
+          <t>Net Investment Income (the modeled gain)</t>
+        </is>
+      </c>
+      <c r="C54" s="35">
+        <f>MAX(0,C45+C46)</f>
+        <v/>
+      </c>
+      <c r="L54" s="32">
+        <f>INDEX('Tax Rates &amp; Assumptions'!G$6:G$1005,L39)</f>
+        <v/>
+      </c>
+      <c r="M54" s="33">
+        <f>INDEX('Tax Rates &amp; Assumptions'!H$6:H$1005,L39)</f>
+        <v/>
+      </c>
+      <c r="N54" s="33">
+        <f>INDEX('Tax Rates &amp; Assumptions'!I$6:I$1005,L39)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55" hidden="1" outlineLevel="1">
+      <c r="B55" s="34" t="inlineStr">
+        <is>
+          <t>NIIT</t>
+        </is>
+      </c>
+      <c r="C55" s="35">
+        <f>C39*MIN(C54,MAX(0,C53-C38))</f>
+        <v/>
+      </c>
+      <c r="L55" s="32">
+        <f>INDEX('Tax Rates &amp; Assumptions'!J$6:J$1005,L39)</f>
+        <v/>
+      </c>
+      <c r="M55" s="33">
+        <f>INDEX('Tax Rates &amp; Assumptions'!K$6:K$1005,L39)</f>
+        <v/>
+      </c>
+      <c r="N55" s="33">
+        <f>INDEX('Tax Rates &amp; Assumptions'!L$6:L$1005,L39)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56" hidden="1" outlineLevel="1">
+      <c r="B56" s="37" t="inlineStr">
+        <is>
+          <t>Total Federal Tax From the Gain (incl. NIIT)</t>
+        </is>
+      </c>
+      <c r="C56" s="35">
+        <f>(C51+C52+C55)</f>
+        <v/>
+      </c>
+      <c r="L56" s="32">
+        <f>INDEX('Tax Rates &amp; Assumptions'!M$6:M$1005,L39)</f>
+        <v/>
+      </c>
+      <c r="M56" s="33">
+        <f>INDEX('Tax Rates &amp; Assumptions'!N$6:N$1005,L39)</f>
+        <v/>
+      </c>
+      <c r="N56" s="33">
+        <f>INDEX('Tax Rates &amp; Assumptions'!O$6:O$1005,L39)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57" hidden="1" outlineLevel="1">
+      <c r="B57" s="34" t="inlineStr">
+        <is>
+          <t>State Taxable Income Before the Gain</t>
+        </is>
+      </c>
+      <c r="C57" s="35">
+        <f>MAX(0,C47-C40-C16*C41)</f>
+        <v/>
+      </c>
+      <c r="L57" s="32">
+        <f>INDEX('Tax Rates &amp; Assumptions'!P$6:P$1005,L39)</f>
+        <v/>
+      </c>
+      <c r="M57" s="33">
+        <f>INDEX('Tax Rates &amp; Assumptions'!Q$6:Q$1005,L39)</f>
+        <v/>
+      </c>
+      <c r="N57" s="33">
+        <f>INDEX('Tax Rates &amp; Assumptions'!R$6:R$1005,L39)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58" hidden="1" outlineLevel="1">
+      <c r="B58" s="34" t="inlineStr">
+        <is>
+          <t>State Taxable Income Including the Gain</t>
+        </is>
+      </c>
+      <c r="C58" s="35">
+        <f>MAX(0,C47+C45+C46-C40-C16*C41)</f>
+        <v/>
+      </c>
+      <c r="L58" s="32">
+        <f>INDEX('Tax Rates &amp; Assumptions'!S$6:S$1005,L39)</f>
+        <v/>
+      </c>
+      <c r="M58" s="33">
+        <f>INDEX('Tax Rates &amp; Assumptions'!T$6:T$1005,L39)</f>
+        <v/>
+      </c>
+      <c r="N58" s="33">
+        <f>INDEX('Tax Rates &amp; Assumptions'!U$6:U$1005,L39)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59" hidden="1" outlineLevel="1">
+      <c r="B59" s="34" t="inlineStr">
+        <is>
+          <t>State Tax on Income Alone</t>
+        </is>
+      </c>
+      <c r="C59" s="35">
+        <f>IF(L44="OTHER",0,SUMPRODUCT((C57&gt;$M$67:$M$74)*($L$67:$L$74)*(MIN(C57,$N$67:$N$74)-$M$67:$M$74)))</f>
+        <v/>
+      </c>
+      <c r="L59" s="32">
+        <f>INDEX('Tax Rates &amp; Assumptions'!V$6:V$1005,L39)</f>
+        <v/>
+      </c>
+      <c r="M59" s="33">
+        <f>INDEX('Tax Rates &amp; Assumptions'!W$6:W$1005,L39)</f>
+        <v/>
+      </c>
+      <c r="N59" s="33">
+        <f>INDEX('Tax Rates &amp; Assumptions'!X$6:X$1005,L39)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60" hidden="1" outlineLevel="1">
+      <c r="B60" s="34" t="inlineStr">
+        <is>
+          <t>State Tax on Income Including the Gain</t>
+        </is>
+      </c>
+      <c r="C60" s="35">
+        <f>IF(L44="OTHER",0,SUMPRODUCT((C58&gt;$M$67:$M$74)*($L$67:$L$74)*(MIN(C58,$N$67:$N$74)-$M$67:$M$74)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61" hidden="1" outlineLevel="1">
+      <c r="B61" s="37" t="inlineStr">
+        <is>
+          <t>State Tax From the Gain</t>
+        </is>
+      </c>
+      <c r="C61" s="35">
+        <f>(C60-C59)</f>
+        <v/>
+      </c>
+      <c r="K61" s="31" t="inlineStr">
+        <is>
+          <t>LTCG Brackets</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" hidden="1" outlineLevel="1">
+      <c r="B62" s="37" t="inlineStr">
+        <is>
+          <t>Local Tax From the Gain</t>
+        </is>
+      </c>
+      <c r="C62" s="35">
+        <f>C42*MAX(0,C43)</f>
+        <v/>
+      </c>
+      <c r="L62" s="32">
+        <f>INDEX('Tax Rates &amp; Assumptions'!D$17:D$1016,L40)</f>
+        <v/>
+      </c>
+      <c r="M62" s="33">
+        <f>INDEX('Tax Rates &amp; Assumptions'!E$17:E$1016,L40)</f>
+        <v/>
+      </c>
+      <c r="N62" s="33">
+        <f>INDEX('Tax Rates &amp; Assumptions'!F$17:F$1016,L40)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63" hidden="1" outlineLevel="1">
+      <c r="B63" s="23" t="inlineStr">
         <is>
           <t>Total Estimated Tax</t>
         </is>
       </c>
-      <c r="C34" s="42">
-        <f>C82</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="25" t="inlineStr">
-        <is>
-          <t>Effective Tax Rate on the Gain</t>
-        </is>
-      </c>
-      <c r="C35" s="43">
-        <f>C83</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="25" t="inlineStr">
-        <is>
-          <t>Marginal Long-Term Capital Gains Rate</t>
-        </is>
-      </c>
-      <c r="C36" s="43">
-        <f>C84</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="F38" s="7" t="inlineStr">
-        <is>
-          <t>Tax Component</t>
-        </is>
-      </c>
-      <c r="G38" s="7" t="inlineStr">
-        <is>
-          <t>Amount</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="F39" s="29" t="inlineStr">
-        <is>
-          <t>Federal Tax</t>
-        </is>
-      </c>
-      <c r="G39" s="44">
-        <f>(C75+C76)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40">
-      <c r="F40" s="29" t="inlineStr">
-        <is>
-          <t>State Tax</t>
-        </is>
-      </c>
-      <c r="G40" s="44">
-        <f>C81</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41">
-      <c r="F41" s="29" t="inlineStr">
-        <is>
-          <t>NIIT</t>
-        </is>
-      </c>
-      <c r="G41" s="44">
-        <f>C79</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55">
-      <c r="B55" s="27" t="inlineStr">
-        <is>
-          <t>Estimated for financial-planning purposes only. This calculator is not tax, legal, or accounting advice. Actual tax liability may differ based on individual circumstances, deductions, credits, tax elections, state/local rules, and other factors. Consult a qualified tax professional before making tax-related decisions.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="59" hidden="1" outlineLevel="1" collapsed="1">
-      <c r="A59" s="28" t="inlineStr">
-        <is>
-          <t>CALCULATION DETAIL (grouped - click + to expand)</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" hidden="1" outlineLevel="1"/>
-    <row r="61" hidden="1" outlineLevel="1">
-      <c r="B61" s="33" t="inlineStr">
-        <is>
-          <t>Standard Deduction (add-back for MAGI estimate)</t>
-        </is>
-      </c>
-      <c r="C61" s="34">
-        <f>INDEX('Tax Rates &amp; Assumptions'!$D$28:$D$35,L67)</f>
-        <v/>
-      </c>
-      <c r="K61" s="7" t="inlineStr">
-        <is>
-          <t>Filing Status</t>
-        </is>
-      </c>
-      <c r="L61" s="29">
-        <f>C6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="62" hidden="1" outlineLevel="1">
-      <c r="B62" s="33" t="inlineStr">
-        <is>
-          <t>Capital Loss Limit vs. Ordinary Income</t>
-        </is>
-      </c>
-      <c r="C62" s="34">
-        <f>INDEX('Tax Rates &amp; Assumptions'!$D$39:$D$42,L66)</f>
-        <v/>
-      </c>
-      <c r="K62" s="7" t="inlineStr">
-        <is>
-          <t>Tax Year</t>
-        </is>
-      </c>
-      <c r="L62" s="29">
-        <f>C5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="63" hidden="1" outlineLevel="1">
-      <c r="B63" s="33" t="inlineStr">
-        <is>
-          <t>NIIT Threshold</t>
-        </is>
-      </c>
-      <c r="C63" s="34">
-        <f>INDEX('Tax Rates &amp; Assumptions'!$B$39:$B$42,L66)</f>
-        <v/>
-      </c>
-      <c r="K63" s="7" t="inlineStr">
-        <is>
-          <t>Federal Key</t>
-        </is>
-      </c>
-      <c r="L63" s="29">
-        <f>L62&amp;"|"&amp;L61</f>
+      <c r="C63" s="38">
+        <f>(C56+C61+C62)</f>
+        <v/>
+      </c>
+      <c r="L63" s="32">
+        <f>INDEX('Tax Rates &amp; Assumptions'!G$17:G$1016,L40)</f>
+        <v/>
+      </c>
+      <c r="M63" s="33">
+        <f>INDEX('Tax Rates &amp; Assumptions'!H$17:H$1016,L40)</f>
+        <v/>
+      </c>
+      <c r="N63" s="33">
+        <f>INDEX('Tax Rates &amp; Assumptions'!I$17:I$1016,L40)</f>
         <v/>
       </c>
     </row>
     <row r="64" hidden="1" outlineLevel="1">
-      <c r="B64" s="33" t="inlineStr">
-        <is>
-          <t>NIIT Rate</t>
-        </is>
-      </c>
-      <c r="C64" s="35">
-        <f>INDEX('Tax Rates &amp; Assumptions'!$C$39:$C$42,L66)</f>
-        <v/>
-      </c>
-      <c r="K64" s="7" t="inlineStr">
-        <is>
-          <t>Fed Bracket Row#</t>
-        </is>
-      </c>
-      <c r="L64" s="29">
-        <f>MATCH(L63,'Tax Rates &amp; Assumptions'!$C$6:$C$13,0)</f>
+      <c r="B64" s="34" t="inlineStr">
+        <is>
+          <t>Federal Marginal Rate Applied to the Gain</t>
+        </is>
+      </c>
+      <c r="C64" s="39">
+        <f>IF(AND(C43&gt;=0,C44=1),IFERROR(INDEX($L$62:$L$64,MATCH(C48,$M$62:$M$64,1)),0),IFERROR(INDEX($L$53:$L$59,MATCH(C48,$M$53:$M$59,1)),0))</f>
+        <v/>
+      </c>
+      <c r="L64" s="32">
+        <f>INDEX('Tax Rates &amp; Assumptions'!J$17:J$1016,L40)</f>
+        <v/>
+      </c>
+      <c r="M64" s="33">
+        <f>INDEX('Tax Rates &amp; Assumptions'!K$17:K$1016,L40)</f>
+        <v/>
+      </c>
+      <c r="N64" s="33">
+        <f>INDEX('Tax Rates &amp; Assumptions'!L$17:L$1016,L40)</f>
         <v/>
       </c>
     </row>
     <row r="65" hidden="1" outlineLevel="1">
-      <c r="B65" s="33" t="inlineStr">
-        <is>
-          <t>State Standard Deduction</t>
-        </is>
-      </c>
-      <c r="C65" s="34">
-        <f>IF(L70="MFJ",INDEX('Tax Rates &amp; Assumptions'!$E$46:$E$77,L73),INDEX('Tax Rates &amp; Assumptions'!$D$46:$D$77,L73))</f>
-        <v/>
-      </c>
-      <c r="K65" s="7" t="inlineStr">
-        <is>
-          <t>LTCG Bracket Row#</t>
-        </is>
-      </c>
-      <c r="L65" s="29">
-        <f>MATCH(L63,'Tax Rates &amp; Assumptions'!$C$17:$C$24,0)</f>
+      <c r="B65" s="34" t="inlineStr">
+        <is>
+          <t>Federal Effective Rate on the Gain</t>
+        </is>
+      </c>
+      <c r="C65" s="39">
+        <f>IFERROR(C56/C43,0)</f>
         <v/>
       </c>
     </row>
     <row r="66" hidden="1" outlineLevel="1">
-      <c r="B66" s="33" t="inlineStr">
-        <is>
-          <t>Net Short-Term Gain / (Loss)</t>
-        </is>
-      </c>
-      <c r="C66" s="34">
-        <f>(C15-C17)</f>
-        <v/>
-      </c>
-      <c r="K66" s="7" t="inlineStr">
-        <is>
-          <t>Status Row# (NIIT/CapLoss)</t>
-        </is>
-      </c>
-      <c r="L66" s="29">
-        <f>MATCH(L61,'Tax Rates &amp; Assumptions'!$A$39:$A$42,0)</f>
-        <v/>
+      <c r="B66" s="34" t="inlineStr">
+        <is>
+          <t>State Marginal Rate Applied to the Gain</t>
+        </is>
+      </c>
+      <c r="C66" s="39">
+        <f>IF(L44="OTHER",0,IFERROR(INDEX($L$67:$L$74,MATCH(C58,$M$67:$M$74,1)),0))</f>
+        <v/>
+      </c>
+      <c r="K66" s="31" t="inlineStr">
+        <is>
+          <t>State Brackets</t>
+        </is>
       </c>
     </row>
     <row r="67" hidden="1" outlineLevel="1">
-      <c r="B67" s="33" t="inlineStr">
-        <is>
-          <t>Net Long-Term Gain / (Loss), net of carryforward</t>
-        </is>
-      </c>
-      <c r="C67" s="34">
-        <f>(C16-C18-C19)</f>
-        <v/>
-      </c>
-      <c r="K67" s="7" t="inlineStr">
-        <is>
-          <t>StdDed Row#</t>
-        </is>
-      </c>
-      <c r="L67" s="29">
-        <f>MATCH(L63,'Tax Rates &amp; Assumptions'!$C$28:$C$35,0)</f>
+      <c r="B67" s="34" t="inlineStr">
+        <is>
+          <t>State Effective Rate on the Gain</t>
+        </is>
+      </c>
+      <c r="C67" s="39">
+        <f>IFERROR(C61/C43,0)</f>
+        <v/>
+      </c>
+      <c r="L67" s="32">
+        <f>INDEX('Tax Rates &amp; Assumptions'!D$81:D$1080,L47)</f>
+        <v/>
+      </c>
+      <c r="M67" s="33">
+        <f>INDEX('Tax Rates &amp; Assumptions'!E$81:E$1080,L47)</f>
+        <v/>
+      </c>
+      <c r="N67" s="33">
+        <f>INDEX('Tax Rates &amp; Assumptions'!F$81:F$1080,L47)</f>
         <v/>
       </c>
     </row>
     <row r="68" hidden="1" outlineLevel="1">
-      <c r="B68" s="33" t="inlineStr">
-        <is>
-          <t>Combined Net Capital Gain / (Loss)</t>
-        </is>
-      </c>
-      <c r="C68" s="34">
-        <f>(C66+C67)</f>
-        <v/>
-      </c>
-      <c r="K68" s="7" t="inlineStr">
-        <is>
-          <t>State Name</t>
-        </is>
-      </c>
-      <c r="L68" s="29">
-        <f>C7</f>
+      <c r="B68" s="34" t="inlineStr">
+        <is>
+          <t>Local Effective Rate on the Gain</t>
+        </is>
+      </c>
+      <c r="C68" s="39">
+        <f>IFERROR(C62/C43,0)</f>
+        <v/>
+      </c>
+      <c r="L68" s="32">
+        <f>INDEX('Tax Rates &amp; Assumptions'!G$81:G$1080,L47)</f>
+        <v/>
+      </c>
+      <c r="M68" s="33">
+        <f>INDEX('Tax Rates &amp; Assumptions'!H$81:H$1080,L47)</f>
+        <v/>
+      </c>
+      <c r="N68" s="33">
+        <f>INDEX('Tax Rates &amp; Assumptions'!I$81:I$1080,L47)</f>
         <v/>
       </c>
     </row>
     <row r="69" hidden="1" outlineLevel="1">
-      <c r="B69" s="33" t="inlineStr">
-        <is>
-          <t>Ordinary-Taxed Capital Gain / (Loss Deduction, capped)</t>
-        </is>
-      </c>
-      <c r="C69" s="34">
-        <f>IF(C68&lt;=0,MAX(C68,-C62),IF(AND(C66&gt;=0,C67&gt;=0),C66,IF(AND(C66&lt;0,C67&gt;=0),0,IF(AND(C66&gt;=0,C67&lt;0),C68,0))))</f>
-        <v/>
-      </c>
-      <c r="K69" s="7" t="inlineStr">
-        <is>
-          <t>State Code</t>
-        </is>
-      </c>
-      <c r="L69" s="29">
-        <f>INDEX('Tax Rates &amp; Assumptions'!$A$46:$A$77,MATCH(L68,'Tax Rates &amp; Assumptions'!$B$46:$B$77,0))</f>
+      <c r="L69" s="32">
+        <f>INDEX('Tax Rates &amp; Assumptions'!J$81:J$1080,L47)</f>
+        <v/>
+      </c>
+      <c r="M69" s="33">
+        <f>INDEX('Tax Rates &amp; Assumptions'!K$81:K$1080,L47)</f>
+        <v/>
+      </c>
+      <c r="N69" s="33">
+        <f>INDEX('Tax Rates &amp; Assumptions'!L$81:L$1080,L47)</f>
         <v/>
       </c>
     </row>
     <row r="70" hidden="1" outlineLevel="1">
-      <c r="B70" s="33" t="inlineStr">
-        <is>
-          <t>Preferential (LTCG-Rate) Net Capital Gain</t>
-        </is>
-      </c>
-      <c r="C70" s="34">
-        <f>IF(C68&lt;=0,0,IF(AND(C66&gt;=0,C67&gt;=0),C67,IF(AND(C66&lt;0,C67&gt;=0),C68,IF(AND(C66&gt;=0,C67&lt;0),0,0))))</f>
-        <v/>
-      </c>
-      <c r="K70" s="7" t="inlineStr">
-        <is>
-          <t>State Category</t>
-        </is>
-      </c>
-      <c r="L70" s="29">
-        <f>IF(L61="Married Filing Jointly","MFJ","Single")</f>
+      <c r="L70" s="32">
+        <f>INDEX('Tax Rates &amp; Assumptions'!M$81:M$1080,L47)</f>
+        <v/>
+      </c>
+      <c r="M70" s="33">
+        <f>INDEX('Tax Rates &amp; Assumptions'!N$81:N$1080,L47)</f>
+        <v/>
+      </c>
+      <c r="N70" s="33">
+        <f>INDEX('Tax Rates &amp; Assumptions'!O$81:O$1080,L47)</f>
         <v/>
       </c>
     </row>
     <row r="71" hidden="1" outlineLevel="1">
-      <c r="B71" s="33" t="inlineStr">
-        <is>
-          <t>Capital Loss Carryforward to Future Years</t>
-        </is>
-      </c>
-      <c r="C71" s="34">
-        <f>IF(C68&lt;=0,C68-MAX(C68,-C62),0)</f>
-        <v/>
-      </c>
-      <c r="K71" s="7" t="inlineStr">
-        <is>
-          <t>State Key</t>
-        </is>
-      </c>
-      <c r="L71" s="29">
-        <f>L69&amp;"|"&amp;L70</f>
+      <c r="L71" s="32">
+        <f>INDEX('Tax Rates &amp; Assumptions'!P$81:P$1080,L47)</f>
+        <v/>
+      </c>
+      <c r="M71" s="33">
+        <f>INDEX('Tax Rates &amp; Assumptions'!Q$81:Q$1080,L47)</f>
+        <v/>
+      </c>
+      <c r="N71" s="33">
+        <f>INDEX('Tax Rates &amp; Assumptions'!R$81:R$1080,L47)</f>
         <v/>
       </c>
     </row>
     <row r="72" hidden="1" outlineLevel="1">
-      <c r="B72" s="33" t="inlineStr">
-        <is>
-          <t>Ordinary Taxable Income Including Gain</t>
-        </is>
-      </c>
-      <c r="C72" s="34">
-        <f>MAX(0,C11+C69)</f>
-        <v/>
-      </c>
-      <c r="K72" s="7" t="inlineStr">
-        <is>
-          <t>State Bracket Row#</t>
-        </is>
-      </c>
-      <c r="L72" s="29">
-        <f>MATCH(L71,'Tax Rates &amp; Assumptions'!$C$81:$C$144,0)</f>
+      <c r="L72" s="32">
+        <f>INDEX('Tax Rates &amp; Assumptions'!S$81:S$1080,L47)</f>
+        <v/>
+      </c>
+      <c r="M72" s="33">
+        <f>INDEX('Tax Rates &amp; Assumptions'!T$81:T$1080,L47)</f>
+        <v/>
+      </c>
+      <c r="N72" s="33">
+        <f>INDEX('Tax Rates &amp; Assumptions'!U$81:U$1080,L47)</f>
         <v/>
       </c>
     </row>
     <row r="73" hidden="1" outlineLevel="1">
-      <c r="B73" s="33" t="inlineStr">
-        <is>
-          <t>Federal Tax on Taxable Income Alone (no gain)</t>
-        </is>
-      </c>
-      <c r="C73" s="34">
-        <f>SUMPRODUCT((C11&gt;$M$76:$M$82)*($L$76:$L$82)*(MIN(C11,$N$76:$N$82)-$M$76:$M$82))</f>
-        <v/>
-      </c>
-      <c r="K73" s="7" t="inlineStr">
-        <is>
-          <t>State Master Row#</t>
-        </is>
-      </c>
-      <c r="L73" s="29">
-        <f>MATCH(L69,'Tax Rates &amp; Assumptions'!$A$46:$A$77,0)</f>
+      <c r="L73" s="32">
+        <f>INDEX('Tax Rates &amp; Assumptions'!V$81:V$1080,L47)</f>
+        <v/>
+      </c>
+      <c r="M73" s="33">
+        <f>INDEX('Tax Rates &amp; Assumptions'!W$81:W$1080,L47)</f>
+        <v/>
+      </c>
+      <c r="N73" s="33">
+        <f>INDEX('Tax Rates &amp; Assumptions'!X$81:X$1080,L47)</f>
         <v/>
       </c>
     </row>
     <row r="74" hidden="1" outlineLevel="1">
-      <c r="B74" s="33" t="inlineStr">
-        <is>
-          <t>Federal Tax on Taxable Income Including Short-Term Gain</t>
-        </is>
-      </c>
-      <c r="C74" s="34">
-        <f>SUMPRODUCT((C72&gt;$M$76:$M$82)*($L$76:$L$82)*(MIN(C72,$N$76:$N$82)-$M$76:$M$82))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="75" hidden="1" outlineLevel="1">
-      <c r="B75" s="36" t="inlineStr">
-        <is>
-          <t>Federal Tax on Short-Term Gain</t>
-        </is>
-      </c>
-      <c r="C75" s="34">
-        <f>MAX(0,C74-C73)</f>
-        <v/>
-      </c>
-      <c r="K75" s="30" t="inlineStr">
-        <is>
-          <t>Federal Ordinary Brackets</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" hidden="1" outlineLevel="1">
-      <c r="B76" s="36" t="inlineStr">
-        <is>
-          <t>Federal Tax on Long-Term Gain (stacked)</t>
-        </is>
-      </c>
-      <c r="C76" s="34">
-        <f>SUMPRODUCT($L$85:$L$87*(MAX(0,MIN((C72+C70),$N$85:$N$87)-MAX(C72,$M$85:$M$87))))</f>
-        <v/>
-      </c>
-      <c r="L76" s="31">
-        <f>INDEX('Tax Rates &amp; Assumptions'!D$6:D$1005,L64)</f>
-        <v/>
-      </c>
-      <c r="M76" s="32">
-        <f>INDEX('Tax Rates &amp; Assumptions'!E$6:E$1005,L64)</f>
-        <v/>
-      </c>
-      <c r="N76" s="32">
-        <f>INDEX('Tax Rates &amp; Assumptions'!F$6:F$1005,L64)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="77" hidden="1" outlineLevel="1">
-      <c r="B77" s="33" t="inlineStr">
-        <is>
-          <t>MAGI Estimate (Taxable Income + Std. Ded. Add-Back + Net Gain)</t>
-        </is>
-      </c>
-      <c r="C77" s="34">
-        <f>(C11+C61+C69+C70)</f>
-        <v/>
-      </c>
-      <c r="L77" s="31">
-        <f>INDEX('Tax Rates &amp; Assumptions'!G$6:G$1005,L64)</f>
-        <v/>
-      </c>
-      <c r="M77" s="32">
-        <f>INDEX('Tax Rates &amp; Assumptions'!H$6:H$1005,L64)</f>
-        <v/>
-      </c>
-      <c r="N77" s="32">
-        <f>INDEX('Tax Rates &amp; Assumptions'!I$6:I$1005,L64)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="78" hidden="1" outlineLevel="1">
-      <c r="B78" s="33" t="inlineStr">
-        <is>
-          <t>Net Investment Income (the modeled capital gain)</t>
-        </is>
-      </c>
-      <c r="C78" s="34">
-        <f>MAX(0,C69+C70)</f>
-        <v/>
-      </c>
-      <c r="L78" s="31">
-        <f>INDEX('Tax Rates &amp; Assumptions'!J$6:J$1005,L64)</f>
-        <v/>
-      </c>
-      <c r="M78" s="32">
-        <f>INDEX('Tax Rates &amp; Assumptions'!K$6:K$1005,L64)</f>
-        <v/>
-      </c>
-      <c r="N78" s="32">
-        <f>INDEX('Tax Rates &amp; Assumptions'!L$6:L$1005,L64)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="79" hidden="1" outlineLevel="1">
-      <c r="B79" s="36" t="inlineStr">
-        <is>
-          <t>NIIT</t>
-        </is>
-      </c>
-      <c r="C79" s="34">
-        <f>C64*MIN(C78,MAX(0,C77-C63))</f>
-        <v/>
-      </c>
-      <c r="L79" s="31">
-        <f>INDEX('Tax Rates &amp; Assumptions'!M$6:M$1005,L64)</f>
-        <v/>
-      </c>
-      <c r="M79" s="32">
-        <f>INDEX('Tax Rates &amp; Assumptions'!N$6:N$1005,L64)</f>
-        <v/>
-      </c>
-      <c r="N79" s="32">
-        <f>INDEX('Tax Rates &amp; Assumptions'!O$6:O$1005,L64)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="80" hidden="1" outlineLevel="1">
-      <c r="B80" s="33" t="inlineStr">
-        <is>
-          <t>State Taxable Income (gain taxed as ordinary income)</t>
-        </is>
-      </c>
-      <c r="C80" s="34">
-        <f>MAX(0,C11+C69+C70-C65)</f>
-        <v/>
-      </c>
-      <c r="L80" s="31">
-        <f>INDEX('Tax Rates &amp; Assumptions'!P$6:P$1005,L64)</f>
-        <v/>
-      </c>
-      <c r="M80" s="32">
-        <f>INDEX('Tax Rates &amp; Assumptions'!Q$6:Q$1005,L64)</f>
-        <v/>
-      </c>
-      <c r="N80" s="32">
-        <f>INDEX('Tax Rates &amp; Assumptions'!R$6:R$1005,L64)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="81" hidden="1" outlineLevel="1">
-      <c r="B81" s="36" t="inlineStr">
-        <is>
-          <t>State Tax</t>
-        </is>
-      </c>
-      <c r="C81" s="34">
-        <f>IF(L69="OTHER",C10*C80,SUMPRODUCT((C80&gt;$M$90:$M$97)*($L$90:$L$97)*(MIN(C80,$N$90:$N$97)-$M$90:$M$97)))</f>
-        <v/>
-      </c>
-      <c r="L81" s="31">
-        <f>INDEX('Tax Rates &amp; Assumptions'!S$6:S$1005,L64)</f>
-        <v/>
-      </c>
-      <c r="M81" s="32">
-        <f>INDEX('Tax Rates &amp; Assumptions'!T$6:T$1005,L64)</f>
-        <v/>
-      </c>
-      <c r="N81" s="32">
-        <f>INDEX('Tax Rates &amp; Assumptions'!U$6:U$1005,L64)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="82" hidden="1" outlineLevel="1">
-      <c r="B82" s="21" t="inlineStr">
-        <is>
-          <t>Total Estimated Tax</t>
-        </is>
-      </c>
-      <c r="C82" s="37">
-        <f>(C75+C76+C79+C81)</f>
-        <v/>
-      </c>
-      <c r="L82" s="31">
-        <f>INDEX('Tax Rates &amp; Assumptions'!V$6:V$1005,L64)</f>
-        <v/>
-      </c>
-      <c r="M82" s="32">
-        <f>INDEX('Tax Rates &amp; Assumptions'!W$6:W$1005,L64)</f>
-        <v/>
-      </c>
-      <c r="N82" s="32">
-        <f>INDEX('Tax Rates &amp; Assumptions'!X$6:X$1005,L64)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="83" hidden="1" outlineLevel="1">
-      <c r="B83" s="33" t="inlineStr">
-        <is>
-          <t>Effective Tax Rate on the Gain</t>
-        </is>
-      </c>
-      <c r="C83" s="38">
-        <f>IFERROR(C82/MAX(0.0001,C68),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="84" hidden="1" outlineLevel="1">
-      <c r="B84" s="33" t="inlineStr">
-        <is>
-          <t>Marginal LTCG Rate Applied</t>
-        </is>
-      </c>
-      <c r="C84" s="38">
-        <f>IFERROR(INDEX($L$85:$L$87,MATCH(C72,$M$85:$M$87,1)),0)</f>
-        <v/>
-      </c>
-      <c r="K84" s="30" t="inlineStr">
-        <is>
-          <t>LTCG Brackets</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" hidden="1" outlineLevel="1">
-      <c r="B85" s="33" t="inlineStr">
-        <is>
-          <t>State Marginal Tax Rate (on taxable income before any gain)</t>
-        </is>
-      </c>
-      <c r="C85" s="38">
-        <f>IF(L69="OTHER",C10,IFERROR(INDEX($L$90:$L$97,MATCH(MAX(0,C11-C65),$M$90:$M$97,1)),0))</f>
-        <v/>
-      </c>
-      <c r="L85" s="31">
-        <f>INDEX('Tax Rates &amp; Assumptions'!D$17:D$1016,L65)</f>
-        <v/>
-      </c>
-      <c r="M85" s="32">
-        <f>INDEX('Tax Rates &amp; Assumptions'!E$17:E$1016,L65)</f>
-        <v/>
-      </c>
-      <c r="N85" s="32">
-        <f>INDEX('Tax Rates &amp; Assumptions'!F$17:F$1016,L65)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="86" hidden="1" outlineLevel="1">
-      <c r="L86" s="31">
-        <f>INDEX('Tax Rates &amp; Assumptions'!G$17:G$1016,L65)</f>
-        <v/>
-      </c>
-      <c r="M86" s="32">
-        <f>INDEX('Tax Rates &amp; Assumptions'!H$17:H$1016,L65)</f>
-        <v/>
-      </c>
-      <c r="N86" s="32">
-        <f>INDEX('Tax Rates &amp; Assumptions'!I$17:I$1016,L65)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="87" hidden="1" outlineLevel="1">
-      <c r="L87" s="31">
-        <f>INDEX('Tax Rates &amp; Assumptions'!J$17:J$1016,L65)</f>
-        <v/>
-      </c>
-      <c r="M87" s="32">
-        <f>INDEX('Tax Rates &amp; Assumptions'!K$17:K$1016,L65)</f>
-        <v/>
-      </c>
-      <c r="N87" s="32">
-        <f>INDEX('Tax Rates &amp; Assumptions'!L$17:L$1016,L65)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="88" hidden="1" outlineLevel="1"/>
-    <row r="89" hidden="1" outlineLevel="1">
-      <c r="K89" s="30" t="inlineStr">
-        <is>
-          <t>State Brackets</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" hidden="1" outlineLevel="1">
-      <c r="L90" s="31">
-        <f>INDEX('Tax Rates &amp; Assumptions'!D$81:D$1080,L72)</f>
-        <v/>
-      </c>
-      <c r="M90" s="32">
-        <f>INDEX('Tax Rates &amp; Assumptions'!E$81:E$1080,L72)</f>
-        <v/>
-      </c>
-      <c r="N90" s="32">
-        <f>INDEX('Tax Rates &amp; Assumptions'!F$81:F$1080,L72)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="91" hidden="1" outlineLevel="1">
-      <c r="L91" s="31">
-        <f>INDEX('Tax Rates &amp; Assumptions'!G$81:G$1080,L72)</f>
-        <v/>
-      </c>
-      <c r="M91" s="32">
-        <f>INDEX('Tax Rates &amp; Assumptions'!H$81:H$1080,L72)</f>
-        <v/>
-      </c>
-      <c r="N91" s="32">
-        <f>INDEX('Tax Rates &amp; Assumptions'!I$81:I$1080,L72)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="92" hidden="1" outlineLevel="1">
-      <c r="L92" s="31">
-        <f>INDEX('Tax Rates &amp; Assumptions'!J$81:J$1080,L72)</f>
-        <v/>
-      </c>
-      <c r="M92" s="32">
-        <f>INDEX('Tax Rates &amp; Assumptions'!K$81:K$1080,L72)</f>
-        <v/>
-      </c>
-      <c r="N92" s="32">
-        <f>INDEX('Tax Rates &amp; Assumptions'!L$81:L$1080,L72)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="93" hidden="1" outlineLevel="1">
-      <c r="L93" s="31">
-        <f>INDEX('Tax Rates &amp; Assumptions'!M$81:M$1080,L72)</f>
-        <v/>
-      </c>
-      <c r="M93" s="32">
-        <f>INDEX('Tax Rates &amp; Assumptions'!N$81:N$1080,L72)</f>
-        <v/>
-      </c>
-      <c r="N93" s="32">
-        <f>INDEX('Tax Rates &amp; Assumptions'!O$81:O$1080,L72)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="94" hidden="1" outlineLevel="1">
-      <c r="L94" s="31">
-        <f>INDEX('Tax Rates &amp; Assumptions'!P$81:P$1080,L72)</f>
-        <v/>
-      </c>
-      <c r="M94" s="32">
-        <f>INDEX('Tax Rates &amp; Assumptions'!Q$81:Q$1080,L72)</f>
-        <v/>
-      </c>
-      <c r="N94" s="32">
-        <f>INDEX('Tax Rates &amp; Assumptions'!R$81:R$1080,L72)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="95" hidden="1" outlineLevel="1">
-      <c r="L95" s="31">
-        <f>INDEX('Tax Rates &amp; Assumptions'!S$81:S$1080,L72)</f>
-        <v/>
-      </c>
-      <c r="M95" s="32">
-        <f>INDEX('Tax Rates &amp; Assumptions'!T$81:T$1080,L72)</f>
-        <v/>
-      </c>
-      <c r="N95" s="32">
-        <f>INDEX('Tax Rates &amp; Assumptions'!U$81:U$1080,L72)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="96" hidden="1" outlineLevel="1">
-      <c r="L96" s="31">
-        <f>INDEX('Tax Rates &amp; Assumptions'!V$81:V$1080,L72)</f>
-        <v/>
-      </c>
-      <c r="M96" s="32">
-        <f>INDEX('Tax Rates &amp; Assumptions'!W$81:W$1080,L72)</f>
-        <v/>
-      </c>
-      <c r="N96" s="32">
-        <f>INDEX('Tax Rates &amp; Assumptions'!X$81:X$1080,L72)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="97" hidden="1" outlineLevel="1">
-      <c r="L97" s="31">
-        <f>INDEX('Tax Rates &amp; Assumptions'!Y$81:Y$1080,L72)</f>
-        <v/>
-      </c>
-      <c r="M97" s="32">
-        <f>INDEX('Tax Rates &amp; Assumptions'!Z$81:Z$1080,L72)</f>
-        <v/>
-      </c>
-      <c r="N97" s="32">
-        <f>INDEX('Tax Rates &amp; Assumptions'!AA$81:AA$1080,L72)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="98" hidden="1" outlineLevel="1"/>
+      <c r="L74" s="32">
+        <f>INDEX('Tax Rates &amp; Assumptions'!Y$81:Y$1080,L47)</f>
+        <v/>
+      </c>
+      <c r="M74" s="33">
+        <f>INDEX('Tax Rates &amp; Assumptions'!Z$81:Z$1080,L47)</f>
+        <v/>
+      </c>
+      <c r="N74" s="33">
+        <f>INDEX('Tax Rates &amp; Assumptions'!AA$81:AA$1080,L47)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75" hidden="1" outlineLevel="1"/>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="A14:F14"/>
-    <mergeCell ref="B55:F57"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A21:F21"/>
-    <mergeCell ref="B9:F9"/>
+  <mergeCells count="7">
+    <mergeCell ref="B12:I12"/>
+    <mergeCell ref="B18:I19"/>
+    <mergeCell ref="A21:H21"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="B28:I30"/>
+    <mergeCell ref="B32:F32"/>
   </mergeCells>
-  <dataValidations count="3">
-    <dataValidation sqref="C5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+  <dataValidations count="5">
+    <dataValidation sqref="I5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"One year or less,More than a year"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>='Tax Rates &amp; Assumptions'!$B$46:$B$77</formula1>
+    </dataValidation>
+    <dataValidation sqref="I8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"Single,Married Filing Jointly,Married Filing Separately,Head of Household"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"2024,2025"</formula1>
     </dataValidation>
-    <dataValidation sqref="C6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>"Single,Married Filing Jointly,Married Filing Separately,Head of Household"</formula1>
-    </dataValidation>
-    <dataValidation sqref="C7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>='Tax Rates &amp; Assumptions'!$B$46:$B$77</formula1>
+    <dataValidation sqref="F16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>='Tax Rates &amp; Assumptions'!$B$148:$B$161</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1901,7 +1790,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA160"/>
+  <dimension ref="A1:AA181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -10872,168 +10761,617 @@
         <v>999999999</v>
       </c>
     </row>
+    <row r="146" ht="18" customHeight="1">
+      <c r="A146" s="3" t="inlineStr">
+        <is>
+          <t>Local / Municipal Tax Table</t>
+        </is>
+      </c>
+      <c r="B146" s="4" t="n"/>
+      <c r="C146" s="4" t="n"/>
+      <c r="D146" s="4" t="n"/>
+      <c r="E146" s="4" t="n"/>
+      <c r="F146" s="4" t="n"/>
+      <c r="G146" s="4" t="n"/>
+      <c r="H146" s="4" t="n"/>
+      <c r="I146" s="4" t="n"/>
+      <c r="J146" s="4" t="n"/>
+      <c r="K146" s="4" t="n"/>
+      <c r="L146" s="4" t="n"/>
+      <c r="M146" s="4" t="n"/>
+      <c r="N146" s="4" t="n"/>
+      <c r="O146" s="4" t="n"/>
+      <c r="P146" s="4" t="n"/>
+      <c r="Q146" s="4" t="n"/>
+      <c r="R146" s="4" t="n"/>
+      <c r="S146" s="4" t="n"/>
+      <c r="T146" s="4" t="n"/>
+      <c r="U146" s="4" t="n"/>
+      <c r="V146" s="4" t="n"/>
+      <c r="W146" s="4" t="n"/>
+      <c r="X146" s="4" t="n"/>
+    </row>
     <row r="147">
-      <c r="A147" s="16" t="inlineStr">
+      <c r="A147" s="5" t="inlineStr">
+        <is>
+          <t>Locality Code</t>
+        </is>
+      </c>
+      <c r="B147" s="5" t="inlineStr">
+        <is>
+          <t>Locality Name</t>
+        </is>
+      </c>
+      <c r="C147" s="5" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="D147" s="5" t="inlineStr">
+        <is>
+          <t>Rate</t>
+        </is>
+      </c>
+      <c r="E147" s="5" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="12" t="inlineStr">
+        <is>
+          <t>NYC</t>
+        </is>
+      </c>
+      <c r="B148" s="12" t="inlineStr">
+        <is>
+          <t>New York City</t>
+        </is>
+      </c>
+      <c r="C148" s="12" t="inlineStr">
+        <is>
+          <t>NY</t>
+        </is>
+      </c>
+      <c r="D148" s="14" t="n">
+        <v>0.03648</v>
+      </c>
+      <c r="E148" s="15" t="inlineStr">
+        <is>
+          <t>Approximate blended NYC resident rate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="12" t="inlineStr">
+        <is>
+          <t>YONK</t>
+        </is>
+      </c>
+      <c r="B149" s="12" t="inlineStr">
+        <is>
+          <t>Yonkers (NY)</t>
+        </is>
+      </c>
+      <c r="C149" s="12" t="inlineStr">
+        <is>
+          <t>NY</t>
+        </is>
+      </c>
+      <c r="D149" s="14" t="n">
+        <v>0.1675</v>
+      </c>
+      <c r="E149" s="15" t="inlineStr">
+        <is>
+          <t>Resident surcharge as % of NY State tax.</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="12" t="inlineStr">
+        <is>
+          <t>PHIL</t>
+        </is>
+      </c>
+      <c r="B150" s="12" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA</t>
+        </is>
+      </c>
+      <c r="C150" s="12" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="D150" s="14" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="E150" s="15" t="inlineStr">
+        <is>
+          <t>Philadelphia wage tax (resident).</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="12" t="inlineStr">
+        <is>
+          <t>PIT</t>
+        </is>
+      </c>
+      <c r="B151" s="12" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA</t>
+        </is>
+      </c>
+      <c r="C151" s="12" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="D151" s="14" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E151" s="15" t="inlineStr">
+        <is>
+          <t>Local earned income tax (approx.).</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="12" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
+      <c r="B152" s="12" t="inlineStr">
+        <is>
+          <t>Detroit, MI</t>
+        </is>
+      </c>
+      <c r="C152" s="12" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
+      <c r="D152" s="14" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="E152" s="15" t="inlineStr">
+        <is>
+          <t>Detroit resident income tax.</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="12" t="inlineStr">
+        <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="B153" s="12" t="inlineStr">
+        <is>
+          <t>Columbus, OH</t>
+        </is>
+      </c>
+      <c r="C153" s="12" t="inlineStr">
+        <is>
+          <t>OH</t>
+        </is>
+      </c>
+      <c r="D153" s="14" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="E153" s="15" t="inlineStr">
+        <is>
+          <t>Ohio municipal income tax (approx.).</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="12" t="inlineStr">
+        <is>
+          <t>CIN</t>
+        </is>
+      </c>
+      <c r="B154" s="12" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH</t>
+        </is>
+      </c>
+      <c r="C154" s="12" t="inlineStr">
+        <is>
+          <t>OH</t>
+        </is>
+      </c>
+      <c r="D154" s="14" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="E154" s="15" t="inlineStr">
+        <is>
+          <t>Ohio municipal income tax (approx.).</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="12" t="inlineStr">
+        <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="B155" s="12" t="inlineStr">
+        <is>
+          <t>Cleveland, OH</t>
+        </is>
+      </c>
+      <c r="C155" s="12" t="inlineStr">
+        <is>
+          <t>OH</t>
+        </is>
+      </c>
+      <c r="D155" s="14" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="E155" s="15" t="inlineStr">
+        <is>
+          <t>Ohio municipal income tax (approx.).</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="12" t="inlineStr">
+        <is>
+          <t>MDCO</t>
+        </is>
+      </c>
+      <c r="B156" s="12" t="inlineStr">
+        <is>
+          <t>Maryland County (avg.)</t>
+        </is>
+      </c>
+      <c r="C156" s="12" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="D156" s="14" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="E156" s="15" t="inlineStr">
+        <is>
+          <t>Average MD county piggyback tax as % of state taxable income equivalent (approx.).</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="12" t="inlineStr">
+        <is>
+          <t>INCO</t>
+        </is>
+      </c>
+      <c r="B157" s="12" t="inlineStr">
+        <is>
+          <t>Indiana County (avg.)</t>
+        </is>
+      </c>
+      <c r="C157" s="12" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="D157" s="14" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="E157" s="15" t="inlineStr">
+        <is>
+          <t>Average Indiana county income tax (approx.).</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="12" t="inlineStr">
+        <is>
+          <t>KCMO</t>
+        </is>
+      </c>
+      <c r="B158" s="12" t="inlineStr">
+        <is>
+          <t>Kansas City, MO</t>
+        </is>
+      </c>
+      <c r="C158" s="12" t="inlineStr">
+        <is>
+          <t>MO</t>
+        </is>
+      </c>
+      <c r="D158" s="14" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E158" s="15" t="inlineStr">
+        <is>
+          <t>Local earnings tax.</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="12" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="B159" s="12" t="inlineStr">
+        <is>
+          <t>St. Louis, MO</t>
+        </is>
+      </c>
+      <c r="C159" s="12" t="inlineStr">
+        <is>
+          <t>MO</t>
+        </is>
+      </c>
+      <c r="D159" s="14" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E159" s="15" t="inlineStr">
+        <is>
+          <t>Local earnings tax.</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="12" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="B160" s="12" t="inlineStr">
+        <is>
+          <t>None / Not Applicable</t>
+        </is>
+      </c>
+      <c r="C160" s="12" t="inlineStr"/>
+      <c r="D160" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E160" s="15" t="inlineStr">
+        <is>
+          <t>No local tax.</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="12" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="B161" s="12" t="inlineStr">
+        <is>
+          <t>Other (Manual Entry)</t>
+        </is>
+      </c>
+      <c r="C161" s="12" t="inlineStr"/>
+      <c r="D161" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E161" s="15" t="inlineStr">
+        <is>
+          <t>Enter a custom local rate on the Inputs tab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="18" customHeight="1">
+      <c r="A163" s="3" t="inlineStr">
+        <is>
+          <t>Personal Exemption Assumption</t>
+        </is>
+      </c>
+      <c r="B163" s="4" t="n"/>
+      <c r="C163" s="4" t="n"/>
+      <c r="D163" s="4" t="n"/>
+      <c r="E163" s="4" t="n"/>
+      <c r="F163" s="4" t="n"/>
+      <c r="G163" s="4" t="n"/>
+      <c r="H163" s="4" t="n"/>
+      <c r="I163" s="4" t="n"/>
+      <c r="J163" s="4" t="n"/>
+      <c r="K163" s="4" t="n"/>
+      <c r="L163" s="4" t="n"/>
+      <c r="M163" s="4" t="n"/>
+      <c r="N163" s="4" t="n"/>
+      <c r="O163" s="4" t="n"/>
+      <c r="P163" s="4" t="n"/>
+      <c r="Q163" s="4" t="n"/>
+      <c r="R163" s="4" t="n"/>
+      <c r="S163" s="4" t="n"/>
+      <c r="T163" s="4" t="n"/>
+      <c r="U163" s="4" t="n"/>
+      <c r="V163" s="4" t="n"/>
+      <c r="W163" s="4" t="n"/>
+      <c r="X163" s="4" t="n"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="16" t="inlineStr">
+        <is>
+          <t>Generic State Personal Exemption Amount (per exemption)</t>
+        </is>
+      </c>
+      <c r="C164" s="13" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="17" t="inlineStr">
+        <is>
+          <t>Federal personal exemptions are suspended (set to $0) under current law. Most states that still allow a personal exemption use their own amount; this workbook applies one generic per-exemption reduction to state taxable income for simplicity - update the figure above or refine per state as needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="18" t="inlineStr">
         <is>
           <t>DISCLAIMER: Estimated for financial-planning purposes only. This calculator is not tax, legal, or accounting advice. Actual tax liability may differ based on individual circumstances, deductions, credits, tax elections, state/local rules, and other factors. Consult a qualified tax professional before making tax-related decisions.</t>
         </is>
       </c>
-      <c r="B147" s="17" t="n"/>
-      <c r="C147" s="17" t="n"/>
-      <c r="D147" s="17" t="n"/>
-      <c r="E147" s="17" t="n"/>
-      <c r="F147" s="17" t="n"/>
-      <c r="G147" s="17" t="n"/>
-      <c r="H147" s="17" t="n"/>
-      <c r="I147" s="17" t="n"/>
-      <c r="J147" s="17" t="n"/>
-    </row>
-    <row r="148">
-      <c r="A148" s="17" t="n"/>
-      <c r="B148" s="17" t="n"/>
-      <c r="C148" s="17" t="n"/>
-      <c r="D148" s="17" t="n"/>
-      <c r="E148" s="17" t="n"/>
-      <c r="F148" s="17" t="n"/>
-      <c r="G148" s="17" t="n"/>
-      <c r="H148" s="17" t="n"/>
-      <c r="I148" s="17" t="n"/>
-      <c r="J148" s="17" t="n"/>
-    </row>
-    <row r="149">
-      <c r="A149" s="17" t="n"/>
-      <c r="B149" s="17" t="n"/>
-      <c r="C149" s="17" t="n"/>
-      <c r="D149" s="17" t="n"/>
-      <c r="E149" s="17" t="n"/>
-      <c r="F149" s="17" t="n"/>
-      <c r="G149" s="17" t="n"/>
-      <c r="H149" s="17" t="n"/>
-      <c r="I149" s="17" t="n"/>
-      <c r="J149" s="17" t="n"/>
-    </row>
-    <row r="150">
-      <c r="A150" s="17" t="n"/>
-      <c r="B150" s="17" t="n"/>
-      <c r="C150" s="17" t="n"/>
-      <c r="D150" s="17" t="n"/>
-      <c r="E150" s="17" t="n"/>
-      <c r="F150" s="17" t="n"/>
-      <c r="G150" s="17" t="n"/>
-      <c r="H150" s="17" t="n"/>
-      <c r="I150" s="17" t="n"/>
-      <c r="J150" s="17" t="n"/>
-    </row>
-    <row r="151">
-      <c r="A151" s="17" t="n"/>
-      <c r="B151" s="17" t="n"/>
-      <c r="C151" s="17" t="n"/>
-      <c r="D151" s="17" t="n"/>
-      <c r="E151" s="17" t="n"/>
-      <c r="F151" s="17" t="n"/>
-      <c r="G151" s="17" t="n"/>
-      <c r="H151" s="17" t="n"/>
-      <c r="I151" s="17" t="n"/>
-      <c r="J151" s="17" t="n"/>
-    </row>
-    <row r="153" ht="18" customHeight="1">
-      <c r="A153" s="3" t="inlineStr">
+      <c r="B168" s="19" t="n"/>
+      <c r="C168" s="19" t="n"/>
+      <c r="D168" s="19" t="n"/>
+      <c r="E168" s="19" t="n"/>
+      <c r="F168" s="19" t="n"/>
+      <c r="G168" s="19" t="n"/>
+      <c r="H168" s="19" t="n"/>
+      <c r="I168" s="19" t="n"/>
+      <c r="J168" s="19" t="n"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="19" t="n"/>
+      <c r="B169" s="19" t="n"/>
+      <c r="C169" s="19" t="n"/>
+      <c r="D169" s="19" t="n"/>
+      <c r="E169" s="19" t="n"/>
+      <c r="F169" s="19" t="n"/>
+      <c r="G169" s="19" t="n"/>
+      <c r="H169" s="19" t="n"/>
+      <c r="I169" s="19" t="n"/>
+      <c r="J169" s="19" t="n"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="19" t="n"/>
+      <c r="B170" s="19" t="n"/>
+      <c r="C170" s="19" t="n"/>
+      <c r="D170" s="19" t="n"/>
+      <c r="E170" s="19" t="n"/>
+      <c r="F170" s="19" t="n"/>
+      <c r="G170" s="19" t="n"/>
+      <c r="H170" s="19" t="n"/>
+      <c r="I170" s="19" t="n"/>
+      <c r="J170" s="19" t="n"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="19" t="n"/>
+      <c r="B171" s="19" t="n"/>
+      <c r="C171" s="19" t="n"/>
+      <c r="D171" s="19" t="n"/>
+      <c r="E171" s="19" t="n"/>
+      <c r="F171" s="19" t="n"/>
+      <c r="G171" s="19" t="n"/>
+      <c r="H171" s="19" t="n"/>
+      <c r="I171" s="19" t="n"/>
+      <c r="J171" s="19" t="n"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="19" t="n"/>
+      <c r="B172" s="19" t="n"/>
+      <c r="C172" s="19" t="n"/>
+      <c r="D172" s="19" t="n"/>
+      <c r="E172" s="19" t="n"/>
+      <c r="F172" s="19" t="n"/>
+      <c r="G172" s="19" t="n"/>
+      <c r="H172" s="19" t="n"/>
+      <c r="I172" s="19" t="n"/>
+      <c r="J172" s="19" t="n"/>
+    </row>
+    <row r="174" ht="18" customHeight="1">
+      <c r="A174" s="3" t="inlineStr">
         <is>
           <t>Key Assumptions</t>
         </is>
       </c>
-      <c r="B153" s="4" t="n"/>
-      <c r="C153" s="4" t="n"/>
-      <c r="D153" s="4" t="n"/>
-      <c r="E153" s="4" t="n"/>
-      <c r="F153" s="4" t="n"/>
-      <c r="G153" s="4" t="n"/>
-      <c r="H153" s="4" t="n"/>
-      <c r="I153" s="4" t="n"/>
-      <c r="J153" s="4" t="n"/>
-      <c r="K153" s="4" t="n"/>
-      <c r="L153" s="4" t="n"/>
-      <c r="M153" s="4" t="n"/>
-      <c r="N153" s="4" t="n"/>
-      <c r="O153" s="4" t="n"/>
-      <c r="P153" s="4" t="n"/>
-      <c r="Q153" s="4" t="n"/>
-      <c r="R153" s="4" t="n"/>
-      <c r="S153" s="4" t="n"/>
-      <c r="T153" s="4" t="n"/>
-      <c r="U153" s="4" t="n"/>
-      <c r="V153" s="4" t="n"/>
-      <c r="W153" s="4" t="n"/>
-      <c r="X153" s="4" t="n"/>
-    </row>
-    <row r="154" ht="40" customHeight="1">
-      <c r="A154" s="18" t="inlineStr">
+      <c r="B174" s="4" t="n"/>
+      <c r="C174" s="4" t="n"/>
+      <c r="D174" s="4" t="n"/>
+      <c r="E174" s="4" t="n"/>
+      <c r="F174" s="4" t="n"/>
+      <c r="G174" s="4" t="n"/>
+      <c r="H174" s="4" t="n"/>
+      <c r="I174" s="4" t="n"/>
+      <c r="J174" s="4" t="n"/>
+      <c r="K174" s="4" t="n"/>
+      <c r="L174" s="4" t="n"/>
+      <c r="M174" s="4" t="n"/>
+      <c r="N174" s="4" t="n"/>
+      <c r="O174" s="4" t="n"/>
+      <c r="P174" s="4" t="n"/>
+      <c r="Q174" s="4" t="n"/>
+      <c r="R174" s="4" t="n"/>
+      <c r="S174" s="4" t="n"/>
+      <c r="T174" s="4" t="n"/>
+      <c r="U174" s="4" t="n"/>
+      <c r="V174" s="4" t="n"/>
+      <c r="W174" s="4" t="n"/>
+      <c r="X174" s="4" t="n"/>
+    </row>
+    <row r="175" ht="40" customHeight="1">
+      <c r="A175" s="20" t="inlineStr">
         <is>
           <t>• Tax Year Coverage: 2024 and 2025. Every bracket, deduction, and threshold used by the calculator lives on this tab; nothing is hardcoded in the formulas on the Capital Gains Tax Estimator tab.</t>
         </is>
       </c>
     </row>
-    <row r="155" ht="40" customHeight="1">
-      <c r="A155" s="18" t="inlineStr">
+    <row r="176" ht="40" customHeight="1">
+      <c r="A176" s="20" t="inlineStr">
         <is>
           <t>• Short-term and long-term gains/losses are netted using standard IRC Sec. 1211/1222 ordering (Form 8949 / Schedule D concepts): a net short-term loss first offsets net long-term gain (and vice versa) before any loss is allowed against ordinary income, capped at the annual limit above (with the remainder carried forward indefinitely). Long-term capital gains are 'stacked' on top of ordinary taxable income when applying the 0%/15%/20% preferential brackets, so they are taxed at the rate(s) that actually apply given the household's total income - not an average rate. Short-term gains are taxed as ordinary income.</t>
         </is>
       </c>
     </row>
-    <row r="156" ht="40" customHeight="1">
-      <c r="A156" s="18" t="inlineStr">
+    <row r="177" ht="40" customHeight="1">
+      <c r="A177" s="20" t="inlineStr">
         <is>
           <t>• The Net Investment Income Tax (3.8%) MAGI thresholds are fixed by statute and have not been inflation-adjusted since enactment (2013). MAGI is approximated as taxable ordinary income plus the net capital gain being modeled.</t>
         </is>
       </c>
     </row>
-    <row r="157" ht="40" customHeight="1">
-      <c r="A157" s="18" t="inlineStr">
+    <row r="178" ht="40" customHeight="1">
+      <c r="A178" s="20" t="inlineStr">
         <is>
           <t>• 31 states plus Washington D.C. are modeled individually (no-tax, flat-tax, and progressive structures), plus a manual-entry option for any other state - not all 50 states are included. State brackets use two filing categories: 'Single' (applied to Single, Married Filing Separately, and Head of Household) and 'MFJ' (applied to Married Filing Jointly).</t>
         </is>
       </c>
     </row>
-    <row r="158" ht="40" customHeight="1">
-      <c r="A158" s="18" t="inlineStr">
+    <row r="179" ht="40" customHeight="1">
+      <c r="A179" s="20" t="inlineStr">
         <is>
           <t>• All states are assumed to tax capital gains as ordinary income (i.e., no separate state preferential capital-gains rate), which is accurate for the large majority of states. State tax uses a state-specific standard deduction where available; it does not model every state's exemption or credit nuance - this is a planning estimate, not a full state tax return.</t>
         </is>
       </c>
     </row>
-    <row r="159" ht="40" customHeight="1">
-      <c r="A159" s="18" t="inlineStr">
+    <row r="180" ht="40" customHeight="1">
+      <c r="A180" s="20" t="inlineStr">
         <is>
           <t>• Tax-loss harvesting losses entered in the What-If section are assumed to be long-term in character (the common case for most portfolios).</t>
         </is>
       </c>
     </row>
-    <row r="160" ht="40" customHeight="1">
-      <c r="A160" s="18" t="inlineStr">
+    <row r="181" ht="40" customHeight="1">
+      <c r="A181" s="20" t="inlineStr">
         <is>
           <t>• This workbook does not model AMT, Qualified Business Income deductions, or every state/local nuance.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="20">
     <mergeCell ref="A79:X79"/>
-    <mergeCell ref="A160:J160"/>
+    <mergeCell ref="A146:X146"/>
+    <mergeCell ref="A181:J181"/>
+    <mergeCell ref="A174:X174"/>
+    <mergeCell ref="A180:J180"/>
+    <mergeCell ref="A37:X37"/>
+    <mergeCell ref="A165:J165"/>
+    <mergeCell ref="A163:X163"/>
+    <mergeCell ref="A26:X26"/>
+    <mergeCell ref="A176:J176"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A153:X153"/>
-    <mergeCell ref="A155:J155"/>
+    <mergeCell ref="A178:J178"/>
     <mergeCell ref="A4:X4"/>
-    <mergeCell ref="A159:J159"/>
-    <mergeCell ref="A26:X26"/>
+    <mergeCell ref="A44:X44"/>
+    <mergeCell ref="A177:J177"/>
+    <mergeCell ref="A168:J172"/>
     <mergeCell ref="A15:X15"/>
-    <mergeCell ref="A158:J158"/>
-    <mergeCell ref="A154:J154"/>
-    <mergeCell ref="A37:X37"/>
-    <mergeCell ref="A147:J151"/>
-    <mergeCell ref="A156:J156"/>
-    <mergeCell ref="A157:J157"/>
     <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A44:X44"/>
+    <mergeCell ref="A179:J179"/>
+    <mergeCell ref="A175:J175"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Capital_Gains_Tax_Estimator.xlsx
+++ b/Capital_Gains_Tax_Estimator.xlsx
@@ -710,7 +710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N74"/>
+  <dimension ref="A1:N75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -748,200 +748,187 @@
     <row r="4">
       <c r="B4" s="23" t="inlineStr">
         <is>
-          <t>Initial Value</t>
+          <t>Long-Term Capital Gain</t>
         </is>
       </c>
       <c r="E4" s="23" t="inlineStr">
         <is>
-          <t>Sale Value</t>
+          <t>Long-Term Capital Loss</t>
         </is>
       </c>
       <c r="H4" s="23" t="inlineStr">
         <is>
-          <t>Length of Ownership</t>
+          <t>Short-Term Capital Gain</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="C5" s="13" t="n">
-        <v>10000</v>
+        <v>50000</v>
       </c>
       <c r="F5" s="13" t="n">
-        <v>50000</v>
-      </c>
-      <c r="I5" s="12" t="inlineStr">
-        <is>
-          <t>More than a year</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="I5" s="13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="23" t="inlineStr">
         <is>
+          <t>Short-Term Capital Loss</t>
+        </is>
+      </c>
+      <c r="E7" s="23" t="inlineStr">
+        <is>
           <t>Location (State)</t>
         </is>
       </c>
-      <c r="E7" s="23" t="inlineStr">
+      <c r="H7" s="23" t="inlineStr">
         <is>
           <t>Annual Income</t>
         </is>
       </c>
-      <c r="H7" s="23" t="inlineStr">
+    </row>
+    <row r="8">
+      <c r="C8" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="12" t="inlineStr">
+        <is>
+          <t>New Jersey</t>
+        </is>
+      </c>
+      <c r="I8" s="13" t="n">
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t>Filing Status</t>
         </is>
       </c>
-    </row>
-    <row r="8">
-      <c r="C8" s="12" t="inlineStr">
-        <is>
-          <t>New Jersey</t>
-        </is>
-      </c>
-      <c r="F8" s="13" t="n">
-        <v>200000</v>
-      </c>
-      <c r="I8" s="12" t="inlineStr">
+      <c r="E10" s="23" t="inlineStr">
+        <is>
+          <t>Tax Year</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="C11" s="12" t="inlineStr">
         <is>
           <t>Married Filing Jointly</t>
         </is>
       </c>
-    </row>
-    <row r="9">
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>Tax Year</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="C10" s="12" t="n">
+      <c r="F11" s="12" t="n">
         <v>2025</v>
       </c>
     </row>
-    <row r="12">
-      <c r="B12" s="24" t="inlineStr">
+    <row r="13">
+      <c r="B13" s="24" t="inlineStr">
         <is>
           <t>ADVANCED (optional - click the [+] in the row-number margin to expand)</t>
         </is>
       </c>
     </row>
-    <row r="13" hidden="1" outlineLevel="1" collapsed="1">
-      <c r="B13" s="16" t="inlineStr">
+    <row r="14" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="B14" s="16" t="inlineStr">
         <is>
           <t>401(k) Contribution</t>
         </is>
       </c>
-      <c r="E13" s="16" t="inlineStr">
+      <c r="E14" s="16" t="inlineStr">
         <is>
           <t>IRA Contribution</t>
         </is>
       </c>
-      <c r="H13" s="16" t="inlineStr">
+      <c r="H14" s="16" t="inlineStr">
         <is>
           <t>Itemized Deductions</t>
         </is>
       </c>
     </row>
-    <row r="14" hidden="1" outlineLevel="1">
-      <c r="C14" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
     <row r="15" hidden="1" outlineLevel="1">
-      <c r="B15" s="16" t="inlineStr">
+      <c r="C15" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" hidden="1" outlineLevel="1">
+      <c r="B16" s="16" t="inlineStr">
         <is>
           <t>Number of Personal Exemptions (state only)</t>
         </is>
       </c>
-      <c r="E15" s="16" t="inlineStr">
+      <c r="E16" s="16" t="inlineStr">
         <is>
           <t>Locality / City (optional)</t>
         </is>
       </c>
     </row>
-    <row r="16" hidden="1" outlineLevel="1">
-      <c r="C16" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="12" t="inlineStr">
+    <row r="17" hidden="1" outlineLevel="1">
+      <c r="C17" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="12" t="inlineStr">
         <is>
           <t>None / Not Applicable</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="20" customHeight="1">
-      <c r="B18" s="25">
-        <f>C63</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="20" customHeight="1"/>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="3" t="inlineStr">
+    <row r="19" ht="20" customHeight="1">
+      <c r="B19" s="25">
+        <f>C65</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1"/>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>YOUR CAPITAL GAINS TAXES</t>
         </is>
       </c>
-      <c r="B21" s="4" t="n"/>
-      <c r="C21" s="4" t="n"/>
-      <c r="D21" s="4" t="n"/>
-      <c r="E21" s="4" t="n"/>
-      <c r="F21" s="4" t="n"/>
-      <c r="G21" s="4" t="n"/>
-      <c r="H21" s="4" t="n"/>
-    </row>
-    <row r="22">
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B22" s="4" t="n"/>
+      <c r="C22" s="4" t="n"/>
+      <c r="D22" s="4" t="n"/>
+      <c r="E22" s="4" t="n"/>
+      <c r="F22" s="4" t="n"/>
+      <c r="G22" s="4" t="n"/>
+      <c r="H22" s="4" t="n"/>
+    </row>
+    <row r="23">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>Tax Type</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>Marginal Tax Rate</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="F23" s="5" t="inlineStr">
         <is>
           <t>Effective Tax Rate</t>
         </is>
       </c>
-      <c r="H22" s="5" t="inlineStr">
+      <c r="H23" s="5" t="inlineStr">
         <is>
           <t>Tax Amount</t>
         </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="23" t="inlineStr">
-        <is>
-          <t>Federal</t>
-        </is>
-      </c>
-      <c r="D23" s="40">
-        <f>C64</f>
-        <v/>
-      </c>
-      <c r="F23" s="40">
-        <f>C65</f>
-        <v/>
-      </c>
-      <c r="H23" s="41">
-        <f>C56</f>
-        <v/>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="23" t="inlineStr">
         <is>
-          <t>State</t>
+          <t>Federal</t>
         </is>
       </c>
       <c r="D24" s="40">
@@ -953,830 +940,855 @@
         <v/>
       </c>
       <c r="H24" s="41">
-        <f>C61</f>
+        <f>C58</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="23" t="inlineStr">
         <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="D25" s="40">
+        <f>C68</f>
+        <v/>
+      </c>
+      <c r="F25" s="40">
+        <f>C69</f>
+        <v/>
+      </c>
+      <c r="H25" s="41">
+        <f>C63</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="23" t="inlineStr">
+        <is>
           <t>Local</t>
         </is>
       </c>
-      <c r="D25" s="40">
-        <f>C42</f>
-        <v/>
-      </c>
-      <c r="F25" s="40">
-        <f>C68</f>
-        <v/>
-      </c>
-      <c r="H25" s="41">
-        <f>C62</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="26" t="inlineStr">
+      <c r="D26" s="40">
+        <f>C43</f>
+        <v/>
+      </c>
+      <c r="F26" s="40">
+        <f>C70</f>
+        <v/>
+      </c>
+      <c r="H26" s="41">
+        <f>C64</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="26" t="inlineStr">
         <is>
           <t>Total Estimated Tax</t>
         </is>
       </c>
-      <c r="H26" s="42">
-        <f>C63</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" s="27" t="inlineStr">
+      <c r="H27" s="42">
+        <f>C65</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="27" t="inlineStr">
         <is>
           <t>Estimated for financial-planning purposes only. This calculator is not tax, legal, or accounting advice. Actual tax liability may differ based on individual circumstances, deductions, credits, tax elections, state/local rules, and other factors. Consult a qualified tax professional before making tax-related decisions. "Federal" includes the Net Investment Income Tax (3.8%) where applicable.</t>
         </is>
       </c>
     </row>
-    <row r="29"/>
     <row r="30"/>
-    <row r="32">
-      <c r="B32" s="28" t="inlineStr">
+    <row r="31"/>
+    <row r="33">
+      <c r="B33" s="28" t="inlineStr">
         <is>
           <t>Full calculation detail is available below for your advisor. Click the [+] in the row-number margin to expand.</t>
         </is>
       </c>
     </row>
-    <row r="34" hidden="1" outlineLevel="1" collapsed="1">
-      <c r="A34" s="29" t="inlineStr">
+    <row r="35" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A35" s="29" t="inlineStr">
         <is>
           <t>CALCULATION DETAIL (grouped - click + to expand)</t>
         </is>
       </c>
     </row>
-    <row r="35" hidden="1" outlineLevel="1"/>
-    <row r="36" hidden="1" outlineLevel="1">
-      <c r="B36" s="34" t="inlineStr">
-        <is>
-          <t>Standard Deduction (add-back for MAGI estimate)</t>
-        </is>
-      </c>
-      <c r="C36" s="35">
-        <f>INDEX('Tax Rates &amp; Assumptions'!$D$28:$D$35,L42)</f>
-        <v/>
-      </c>
-      <c r="K36" s="7" t="inlineStr">
-        <is>
-          <t>Filing Status</t>
-        </is>
-      </c>
-      <c r="L36" s="30">
-        <f>I8</f>
-        <v/>
-      </c>
-    </row>
+    <row r="36" hidden="1" outlineLevel="1"/>
     <row r="37" hidden="1" outlineLevel="1">
       <c r="B37" s="34" t="inlineStr">
         <is>
-          <t>Capital Loss Limit vs. Ordinary Income</t>
+          <t>Standard Deduction (add-back for MAGI estimate)</t>
         </is>
       </c>
       <c r="C37" s="35">
-        <f>INDEX('Tax Rates &amp; Assumptions'!$D$39:$D$42,L41)</f>
+        <f>INDEX('Tax Rates &amp; Assumptions'!$D$28:$D$35,L43)</f>
         <v/>
       </c>
       <c r="K37" s="7" t="inlineStr">
         <is>
-          <t>Tax Year</t>
+          <t>Filing Status</t>
         </is>
       </c>
       <c r="L37" s="30">
-        <f>C10</f>
+        <f>C11</f>
         <v/>
       </c>
     </row>
     <row r="38" hidden="1" outlineLevel="1">
       <c r="B38" s="34" t="inlineStr">
         <is>
-          <t>NIIT Threshold</t>
+          <t>Capital Loss Limit vs. Ordinary Income</t>
         </is>
       </c>
       <c r="C38" s="35">
-        <f>INDEX('Tax Rates &amp; Assumptions'!$B$39:$B$42,L41)</f>
+        <f>INDEX('Tax Rates &amp; Assumptions'!$D$39:$D$42,L42)</f>
         <v/>
       </c>
       <c r="K38" s="7" t="inlineStr">
         <is>
-          <t>Federal Key</t>
+          <t>Tax Year</t>
         </is>
       </c>
       <c r="L38" s="30">
-        <f>L37&amp;"|"&amp;L36</f>
+        <f>F11</f>
         <v/>
       </c>
     </row>
     <row r="39" hidden="1" outlineLevel="1">
       <c r="B39" s="34" t="inlineStr">
         <is>
-          <t>NIIT Rate</t>
-        </is>
-      </c>
-      <c r="C39" s="36">
-        <f>INDEX('Tax Rates &amp; Assumptions'!$C$39:$C$42,L41)</f>
+          <t>NIIT Threshold</t>
+        </is>
+      </c>
+      <c r="C39" s="35">
+        <f>INDEX('Tax Rates &amp; Assumptions'!$B$39:$B$42,L42)</f>
         <v/>
       </c>
       <c r="K39" s="7" t="inlineStr">
         <is>
-          <t>Fed Bracket Row#</t>
+          <t>Federal Key</t>
         </is>
       </c>
       <c r="L39" s="30">
-        <f>MATCH(L38,'Tax Rates &amp; Assumptions'!$C$6:$C$13,0)</f>
+        <f>L38&amp;"|"&amp;L37</f>
         <v/>
       </c>
     </row>
     <row r="40" hidden="1" outlineLevel="1">
       <c r="B40" s="34" t="inlineStr">
         <is>
-          <t>State Standard Deduction</t>
-        </is>
-      </c>
-      <c r="C40" s="35">
-        <f>IF(L45="MFJ",INDEX('Tax Rates &amp; Assumptions'!$E$46:$E$77,L48),INDEX('Tax Rates &amp; Assumptions'!$D$46:$D$77,L48))</f>
+          <t>NIIT Rate</t>
+        </is>
+      </c>
+      <c r="C40" s="36">
+        <f>INDEX('Tax Rates &amp; Assumptions'!$C$39:$C$42,L42)</f>
         <v/>
       </c>
       <c r="K40" s="7" t="inlineStr">
         <is>
-          <t>LTCG Bracket Row#</t>
+          <t>Fed Bracket Row#</t>
         </is>
       </c>
       <c r="L40" s="30">
-        <f>MATCH(L38,'Tax Rates &amp; Assumptions'!$C$17:$C$24,0)</f>
+        <f>MATCH(L39,'Tax Rates &amp; Assumptions'!$C$6:$C$13,0)</f>
         <v/>
       </c>
     </row>
     <row r="41" hidden="1" outlineLevel="1">
       <c r="B41" s="34" t="inlineStr">
         <is>
-          <t>Personal Exemption Amount (per exemption, state)</t>
+          <t>State Standard Deduction</t>
         </is>
       </c>
       <c r="C41" s="35">
-        <f>INDEX('Tax Rates &amp; Assumptions'!$C$164:$C$164,1)</f>
+        <f>IF(L46="MFJ",INDEX('Tax Rates &amp; Assumptions'!$E$46:$E$77,L49),INDEX('Tax Rates &amp; Assumptions'!$D$46:$D$77,L49))</f>
         <v/>
       </c>
       <c r="K41" s="7" t="inlineStr">
         <is>
-          <t>Status Row# (NIIT/CapLoss)</t>
+          <t>LTCG Bracket Row#</t>
         </is>
       </c>
       <c r="L41" s="30">
-        <f>MATCH(L36,'Tax Rates &amp; Assumptions'!$A$39:$A$42,0)</f>
+        <f>MATCH(L39,'Tax Rates &amp; Assumptions'!$C$17:$C$24,0)</f>
         <v/>
       </c>
     </row>
     <row r="42" hidden="1" outlineLevel="1">
       <c r="B42" s="34" t="inlineStr">
         <is>
-          <t>Local Tax Rate</t>
-        </is>
-      </c>
-      <c r="C42" s="36">
-        <f>IF(L50=0,0,INDEX('Tax Rates &amp; Assumptions'!$D$148:$D$161,L50))</f>
+          <t>Personal Exemption Amount (per exemption, state)</t>
+        </is>
+      </c>
+      <c r="C42" s="35">
+        <f>INDEX('Tax Rates &amp; Assumptions'!$C$164:$C$164,1)</f>
         <v/>
       </c>
       <c r="K42" s="7" t="inlineStr">
         <is>
-          <t>StdDed Row#</t>
+          <t>Status Row# (NIIT/CapLoss)</t>
         </is>
       </c>
       <c r="L42" s="30">
-        <f>MATCH(L38,'Tax Rates &amp; Assumptions'!$C$28:$C$35,0)</f>
+        <f>MATCH(L37,'Tax Rates &amp; Assumptions'!$A$39:$A$42,0)</f>
         <v/>
       </c>
     </row>
     <row r="43" hidden="1" outlineLevel="1">
       <c r="B43" s="34" t="inlineStr">
         <is>
-          <t>Capital Gain / (Loss) on Sale</t>
-        </is>
-      </c>
-      <c r="C43" s="35">
-        <f>(F5-C5)</f>
+          <t>Local Tax Rate</t>
+        </is>
+      </c>
+      <c r="C43" s="36">
+        <f>IF(L51=0,0,INDEX('Tax Rates &amp; Assumptions'!$D$148:$D$161,L51))</f>
         <v/>
       </c>
       <c r="K43" s="7" t="inlineStr">
         <is>
-          <t>State Name</t>
+          <t>StdDed Row#</t>
         </is>
       </c>
       <c r="L43" s="30">
-        <f>C8</f>
+        <f>MATCH(L39,'Tax Rates &amp; Assumptions'!$C$28:$C$35,0)</f>
         <v/>
       </c>
     </row>
     <row r="44" hidden="1" outlineLevel="1">
       <c r="B44" s="34" t="inlineStr">
         <is>
-          <t>Is Long-Term?</t>
+          <t>Net Short-Term Gain / (Loss)</t>
         </is>
       </c>
       <c r="C44" s="35">
-        <f>IF(I5="More than a year",1,0)</f>
+        <f>(I5-C8)</f>
         <v/>
       </c>
       <c r="K44" s="7" t="inlineStr">
         <is>
-          <t>State Code</t>
+          <t>State Name</t>
         </is>
       </c>
       <c r="L44" s="30">
-        <f>INDEX('Tax Rates &amp; Assumptions'!$A$46:$A$77,MATCH(L43,'Tax Rates &amp; Assumptions'!$B$46:$B$77,0))</f>
+        <f>F8</f>
         <v/>
       </c>
     </row>
     <row r="45" hidden="1" outlineLevel="1">
       <c r="B45" s="34" t="inlineStr">
         <is>
-          <t>Ordinary-Taxed Portion (short-term gain, or loss deduction capped)</t>
+          <t>Net Long-Term Gain / (Loss)</t>
         </is>
       </c>
       <c r="C45" s="35">
-        <f>IF(C43&gt;=0,IF(C44=1,0,C43),MAX(C43,-C37))</f>
+        <f>(C5-F5)</f>
         <v/>
       </c>
       <c r="K45" s="7" t="inlineStr">
         <is>
-          <t>State Category</t>
+          <t>State Code</t>
         </is>
       </c>
       <c r="L45" s="30">
-        <f>IF(L36="Married Filing Jointly","MFJ","Single")</f>
+        <f>INDEX('Tax Rates &amp; Assumptions'!$A$46:$A$77,MATCH(L44,'Tax Rates &amp; Assumptions'!$B$46:$B$77,0))</f>
         <v/>
       </c>
     </row>
     <row r="46" hidden="1" outlineLevel="1">
       <c r="B46" s="34" t="inlineStr">
         <is>
-          <t>Preferential-Rate Portion (long-term gain)</t>
+          <t>Combined Net Capital Gain / (Loss)</t>
         </is>
       </c>
       <c r="C46" s="35">
-        <f>IF(C43&gt;=0,IF(C44=1,C43,0),0)</f>
+        <f>(C44+C45)</f>
         <v/>
       </c>
       <c r="K46" s="7" t="inlineStr">
         <is>
-          <t>State Key</t>
+          <t>State Category</t>
         </is>
       </c>
       <c r="L46" s="30">
-        <f>L44&amp;"|"&amp;L45</f>
+        <f>IF(L37="Married Filing Jointly","MFJ","Single")</f>
         <v/>
       </c>
     </row>
     <row r="47" hidden="1" outlineLevel="1">
       <c r="B47" s="34" t="inlineStr">
         <is>
-          <t>Taxable Income Before the Gain</t>
+          <t>Ordinary-Taxed Portion (net short-term gain, or loss deduction capped)</t>
         </is>
       </c>
       <c r="C47" s="35">
-        <f>MAX(0,F8-C14-F14-MAX(I14,INDEX('Tax Rates &amp; Assumptions'!$D$28:$D$35,L42)))</f>
+        <f>IF(C46&lt;=0,MAX(C46,-C38),IF(AND(C44&gt;=0,C45&gt;=0),C44,IF(AND(C44&lt;0,C45&gt;=0),0,IF(AND(C44&gt;=0,C45&lt;0),C46,0))))</f>
         <v/>
       </c>
       <c r="K47" s="7" t="inlineStr">
         <is>
-          <t>State Bracket Row#</t>
+          <t>State Key</t>
         </is>
       </c>
       <c r="L47" s="30">
-        <f>MATCH(L46,'Tax Rates &amp; Assumptions'!$C$81:$C$144,0)</f>
+        <f>L45&amp;"|"&amp;L46</f>
         <v/>
       </c>
     </row>
     <row r="48" hidden="1" outlineLevel="1">
       <c r="B48" s="34" t="inlineStr">
         <is>
-          <t>Taxable Income Including the Gain</t>
+          <t>Preferential-Rate Portion (net long-term gain)</t>
         </is>
       </c>
       <c r="C48" s="35">
-        <f>MAX(0,C47+C45)</f>
+        <f>IF(C46&lt;=0,0,IF(AND(C44&gt;=0,C45&gt;=0),C45,IF(AND(C44&lt;0,C45&gt;=0),C46,IF(AND(C44&gt;=0,C45&lt;0),0,0))))</f>
         <v/>
       </c>
       <c r="K48" s="7" t="inlineStr">
         <is>
-          <t>State Master Row#</t>
+          <t>State Bracket Row#</t>
         </is>
       </c>
       <c r="L48" s="30">
-        <f>MATCH(L44,'Tax Rates &amp; Assumptions'!$A$46:$A$77,0)</f>
+        <f>MATCH(L47,'Tax Rates &amp; Assumptions'!$C$81:$C$144,0)</f>
         <v/>
       </c>
     </row>
     <row r="49" hidden="1" outlineLevel="1">
       <c r="B49" s="34" t="inlineStr">
         <is>
-          <t>Federal Tax on Income Alone (no gain)</t>
+          <t>Taxable Income Before the Gain</t>
         </is>
       </c>
       <c r="C49" s="35">
-        <f>SUMPRODUCT((C47&gt;$M$53:$M$59)*($L$53:$L$59)*(MIN(C47,$N$53:$N$59)-$M$53:$M$59))</f>
+        <f>MAX(0,I8-C15-F15-MAX(I15,INDEX('Tax Rates &amp; Assumptions'!$D$28:$D$35,L43)))</f>
         <v/>
       </c>
       <c r="K49" s="7" t="inlineStr">
         <is>
-          <t>Locality Name</t>
+          <t>State Master Row#</t>
         </is>
       </c>
       <c r="L49" s="30">
-        <f>F16</f>
+        <f>MATCH(L45,'Tax Rates &amp; Assumptions'!$A$46:$A$77,0)</f>
         <v/>
       </c>
     </row>
     <row r="50" hidden="1" outlineLevel="1">
       <c r="B50" s="34" t="inlineStr">
         <is>
-          <t>Federal Tax on Income Including the Gain</t>
+          <t>Taxable Income Including the Gain</t>
         </is>
       </c>
       <c r="C50" s="35">
-        <f>SUMPRODUCT((C48&gt;$M$53:$M$59)*($L$53:$L$59)*(MIN(C48,$N$53:$N$59)-$M$53:$M$59))</f>
+        <f>MAX(0,C49+C47)</f>
         <v/>
       </c>
       <c r="K50" s="7" t="inlineStr">
         <is>
-          <t>Locality Row#</t>
+          <t>Locality Name</t>
         </is>
       </c>
       <c r="L50" s="30">
-        <f>IFERROR(MATCH(L49,'Tax Rates &amp; Assumptions'!$B$148:$B$161,0),0)</f>
+        <f>F17</f>
         <v/>
       </c>
     </row>
     <row r="51" hidden="1" outlineLevel="1">
       <c r="B51" s="34" t="inlineStr">
         <is>
-          <t>Federal Tax on Ordinary Portion of the Gain</t>
+          <t>Federal Tax on Income Alone (no gain)</t>
         </is>
       </c>
       <c r="C51" s="35">
-        <f>C50-C49</f>
+        <f>SUMPRODUCT((C49&gt;$M$54:$M$60)*($L$54:$L$60)*(MIN(C49,$N$54:$N$60)-$M$54:$M$60))</f>
+        <v/>
+      </c>
+      <c r="K51" s="7" t="inlineStr">
+        <is>
+          <t>Locality Row#</t>
+        </is>
+      </c>
+      <c r="L51" s="30">
+        <f>IFERROR(MATCH(L50,'Tax Rates &amp; Assumptions'!$B$148:$B$161,0),0)</f>
         <v/>
       </c>
     </row>
     <row r="52" hidden="1" outlineLevel="1">
       <c r="B52" s="34" t="inlineStr">
         <is>
-          <t>Federal Tax on Preferential (Long-Term) Portion (stacked)</t>
+          <t>Federal Tax on Income Including the Gain</t>
         </is>
       </c>
       <c r="C52" s="35">
-        <f>SUMPRODUCT($L$62:$L$64*(MAX(0,MIN((C48+C46),$N$62:$N$64)-MAX(C48,$M$62:$M$64))))</f>
-        <v/>
-      </c>
-      <c r="K52" s="31" t="inlineStr">
-        <is>
-          <t>Federal Ordinary Brackets</t>
-        </is>
+        <f>SUMPRODUCT((C50&gt;$M$54:$M$60)*($L$54:$L$60)*(MIN(C50,$N$54:$N$60)-$M$54:$M$60))</f>
+        <v/>
       </c>
     </row>
     <row r="53" hidden="1" outlineLevel="1">
       <c r="B53" s="34" t="inlineStr">
         <is>
-          <t>MAGI Estimate (Taxable Income + Std. Ded. Add-Back + Net Gain)</t>
+          <t>Federal Tax on Ordinary Portion of the Gain</t>
         </is>
       </c>
       <c r="C53" s="35">
-        <f>(C47+C36+C45+C46)</f>
-        <v/>
-      </c>
-      <c r="L53" s="32">
-        <f>INDEX('Tax Rates &amp; Assumptions'!D$6:D$1005,L39)</f>
-        <v/>
-      </c>
-      <c r="M53" s="33">
-        <f>INDEX('Tax Rates &amp; Assumptions'!E$6:E$1005,L39)</f>
-        <v/>
-      </c>
-      <c r="N53" s="33">
-        <f>INDEX('Tax Rates &amp; Assumptions'!F$6:F$1005,L39)</f>
-        <v/>
+        <f>C52-C51</f>
+        <v/>
+      </c>
+      <c r="K53" s="31" t="inlineStr">
+        <is>
+          <t>Federal Ordinary Brackets</t>
+        </is>
       </c>
     </row>
     <row r="54" hidden="1" outlineLevel="1">
       <c r="B54" s="34" t="inlineStr">
         <is>
-          <t>Net Investment Income (the modeled gain)</t>
+          <t>Federal Tax on Preferential (Long-Term) Portion (stacked)</t>
         </is>
       </c>
       <c r="C54" s="35">
-        <f>MAX(0,C45+C46)</f>
+        <f>SUMPRODUCT($L$63:$L$65*(MAX(0,MIN((C50+C48),$N$63:$N$65)-MAX(C50,$M$63:$M$65))))</f>
         <v/>
       </c>
       <c r="L54" s="32">
-        <f>INDEX('Tax Rates &amp; Assumptions'!G$6:G$1005,L39)</f>
+        <f>INDEX('Tax Rates &amp; Assumptions'!D$6:D$1005,L40)</f>
         <v/>
       </c>
       <c r="M54" s="33">
-        <f>INDEX('Tax Rates &amp; Assumptions'!H$6:H$1005,L39)</f>
+        <f>INDEX('Tax Rates &amp; Assumptions'!E$6:E$1005,L40)</f>
         <v/>
       </c>
       <c r="N54" s="33">
-        <f>INDEX('Tax Rates &amp; Assumptions'!I$6:I$1005,L39)</f>
+        <f>INDEX('Tax Rates &amp; Assumptions'!F$6:F$1005,L40)</f>
         <v/>
       </c>
     </row>
     <row r="55" hidden="1" outlineLevel="1">
       <c r="B55" s="34" t="inlineStr">
         <is>
-          <t>NIIT</t>
+          <t>MAGI Estimate (Taxable Income + Std. Ded. Add-Back + Net Gain)</t>
         </is>
       </c>
       <c r="C55" s="35">
-        <f>C39*MIN(C54,MAX(0,C53-C38))</f>
+        <f>(C49+C37+C47+C48)</f>
         <v/>
       </c>
       <c r="L55" s="32">
-        <f>INDEX('Tax Rates &amp; Assumptions'!J$6:J$1005,L39)</f>
+        <f>INDEX('Tax Rates &amp; Assumptions'!G$6:G$1005,L40)</f>
         <v/>
       </c>
       <c r="M55" s="33">
-        <f>INDEX('Tax Rates &amp; Assumptions'!K$6:K$1005,L39)</f>
+        <f>INDEX('Tax Rates &amp; Assumptions'!H$6:H$1005,L40)</f>
         <v/>
       </c>
       <c r="N55" s="33">
-        <f>INDEX('Tax Rates &amp; Assumptions'!L$6:L$1005,L39)</f>
+        <f>INDEX('Tax Rates &amp; Assumptions'!I$6:I$1005,L40)</f>
         <v/>
       </c>
     </row>
     <row r="56" hidden="1" outlineLevel="1">
-      <c r="B56" s="37" t="inlineStr">
-        <is>
-          <t>Total Federal Tax From the Gain (incl. NIIT)</t>
+      <c r="B56" s="34" t="inlineStr">
+        <is>
+          <t>Net Investment Income (the modeled gain)</t>
         </is>
       </c>
       <c r="C56" s="35">
-        <f>(C51+C52+C55)</f>
+        <f>MAX(0,C47+C48)</f>
         <v/>
       </c>
       <c r="L56" s="32">
-        <f>INDEX('Tax Rates &amp; Assumptions'!M$6:M$1005,L39)</f>
+        <f>INDEX('Tax Rates &amp; Assumptions'!J$6:J$1005,L40)</f>
         <v/>
       </c>
       <c r="M56" s="33">
-        <f>INDEX('Tax Rates &amp; Assumptions'!N$6:N$1005,L39)</f>
+        <f>INDEX('Tax Rates &amp; Assumptions'!K$6:K$1005,L40)</f>
         <v/>
       </c>
       <c r="N56" s="33">
-        <f>INDEX('Tax Rates &amp; Assumptions'!O$6:O$1005,L39)</f>
+        <f>INDEX('Tax Rates &amp; Assumptions'!L$6:L$1005,L40)</f>
         <v/>
       </c>
     </row>
     <row r="57" hidden="1" outlineLevel="1">
       <c r="B57" s="34" t="inlineStr">
         <is>
-          <t>State Taxable Income Before the Gain</t>
+          <t>NIIT</t>
         </is>
       </c>
       <c r="C57" s="35">
-        <f>MAX(0,C47-C40-C16*C41)</f>
+        <f>C40*MIN(C56,MAX(0,C55-C39))</f>
         <v/>
       </c>
       <c r="L57" s="32">
-        <f>INDEX('Tax Rates &amp; Assumptions'!P$6:P$1005,L39)</f>
+        <f>INDEX('Tax Rates &amp; Assumptions'!M$6:M$1005,L40)</f>
         <v/>
       </c>
       <c r="M57" s="33">
-        <f>INDEX('Tax Rates &amp; Assumptions'!Q$6:Q$1005,L39)</f>
+        <f>INDEX('Tax Rates &amp; Assumptions'!N$6:N$1005,L40)</f>
         <v/>
       </c>
       <c r="N57" s="33">
-        <f>INDEX('Tax Rates &amp; Assumptions'!R$6:R$1005,L39)</f>
+        <f>INDEX('Tax Rates &amp; Assumptions'!O$6:O$1005,L40)</f>
         <v/>
       </c>
     </row>
     <row r="58" hidden="1" outlineLevel="1">
-      <c r="B58" s="34" t="inlineStr">
-        <is>
-          <t>State Taxable Income Including the Gain</t>
+      <c r="B58" s="37" t="inlineStr">
+        <is>
+          <t>Total Federal Tax From the Gain (incl. NIIT)</t>
         </is>
       </c>
       <c r="C58" s="35">
-        <f>MAX(0,C47+C45+C46-C40-C16*C41)</f>
+        <f>(C53+C54+C57)</f>
         <v/>
       </c>
       <c r="L58" s="32">
-        <f>INDEX('Tax Rates &amp; Assumptions'!S$6:S$1005,L39)</f>
+        <f>INDEX('Tax Rates &amp; Assumptions'!P$6:P$1005,L40)</f>
         <v/>
       </c>
       <c r="M58" s="33">
-        <f>INDEX('Tax Rates &amp; Assumptions'!T$6:T$1005,L39)</f>
+        <f>INDEX('Tax Rates &amp; Assumptions'!Q$6:Q$1005,L40)</f>
         <v/>
       </c>
       <c r="N58" s="33">
-        <f>INDEX('Tax Rates &amp; Assumptions'!U$6:U$1005,L39)</f>
+        <f>INDEX('Tax Rates &amp; Assumptions'!R$6:R$1005,L40)</f>
         <v/>
       </c>
     </row>
     <row r="59" hidden="1" outlineLevel="1">
       <c r="B59" s="34" t="inlineStr">
         <is>
-          <t>State Tax on Income Alone</t>
+          <t>State Taxable Income Before the Gain</t>
         </is>
       </c>
       <c r="C59" s="35">
-        <f>IF(L44="OTHER",0,SUMPRODUCT((C57&gt;$M$67:$M$74)*($L$67:$L$74)*(MIN(C57,$N$67:$N$74)-$M$67:$M$74)))</f>
+        <f>MAX(0,C49-C41-C17*C42)</f>
         <v/>
       </c>
       <c r="L59" s="32">
-        <f>INDEX('Tax Rates &amp; Assumptions'!V$6:V$1005,L39)</f>
+        <f>INDEX('Tax Rates &amp; Assumptions'!S$6:S$1005,L40)</f>
         <v/>
       </c>
       <c r="M59" s="33">
-        <f>INDEX('Tax Rates &amp; Assumptions'!W$6:W$1005,L39)</f>
+        <f>INDEX('Tax Rates &amp; Assumptions'!T$6:T$1005,L40)</f>
         <v/>
       </c>
       <c r="N59" s="33">
-        <f>INDEX('Tax Rates &amp; Assumptions'!X$6:X$1005,L39)</f>
+        <f>INDEX('Tax Rates &amp; Assumptions'!U$6:U$1005,L40)</f>
         <v/>
       </c>
     </row>
     <row r="60" hidden="1" outlineLevel="1">
       <c r="B60" s="34" t="inlineStr">
         <is>
+          <t>State Taxable Income Including the Gain</t>
+        </is>
+      </c>
+      <c r="C60" s="35">
+        <f>MAX(0,C49+C47+C48-C41-C17*C42)</f>
+        <v/>
+      </c>
+      <c r="L60" s="32">
+        <f>INDEX('Tax Rates &amp; Assumptions'!V$6:V$1005,L40)</f>
+        <v/>
+      </c>
+      <c r="M60" s="33">
+        <f>INDEX('Tax Rates &amp; Assumptions'!W$6:W$1005,L40)</f>
+        <v/>
+      </c>
+      <c r="N60" s="33">
+        <f>INDEX('Tax Rates &amp; Assumptions'!X$6:X$1005,L40)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61" hidden="1" outlineLevel="1">
+      <c r="B61" s="34" t="inlineStr">
+        <is>
+          <t>State Tax on Income Alone</t>
+        </is>
+      </c>
+      <c r="C61" s="35">
+        <f>IF(L45="OTHER",0,SUMPRODUCT((C59&gt;$M$68:$M$75)*($L$68:$L$75)*(MIN(C59,$N$68:$N$75)-$M$68:$M$75)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62" hidden="1" outlineLevel="1">
+      <c r="B62" s="34" t="inlineStr">
+        <is>
           <t>State Tax on Income Including the Gain</t>
         </is>
       </c>
-      <c r="C60" s="35">
-        <f>IF(L44="OTHER",0,SUMPRODUCT((C58&gt;$M$67:$M$74)*($L$67:$L$74)*(MIN(C58,$N$67:$N$74)-$M$67:$M$74)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="61" hidden="1" outlineLevel="1">
-      <c r="B61" s="37" t="inlineStr">
+      <c r="C62" s="35">
+        <f>IF(L45="OTHER",0,SUMPRODUCT((C60&gt;$M$68:$M$75)*($L$68:$L$75)*(MIN(C60,$N$68:$N$75)-$M$68:$M$75)))</f>
+        <v/>
+      </c>
+      <c r="K62" s="31" t="inlineStr">
+        <is>
+          <t>LTCG Brackets</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" hidden="1" outlineLevel="1">
+      <c r="B63" s="37" t="inlineStr">
         <is>
           <t>State Tax From the Gain</t>
         </is>
       </c>
-      <c r="C61" s="35">
-        <f>(C60-C59)</f>
-        <v/>
-      </c>
-      <c r="K61" s="31" t="inlineStr">
-        <is>
-          <t>LTCG Brackets</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" hidden="1" outlineLevel="1">
-      <c r="B62" s="37" t="inlineStr">
+      <c r="C63" s="35">
+        <f>(C62-C61)</f>
+        <v/>
+      </c>
+      <c r="L63" s="32">
+        <f>INDEX('Tax Rates &amp; Assumptions'!D$17:D$1016,L41)</f>
+        <v/>
+      </c>
+      <c r="M63" s="33">
+        <f>INDEX('Tax Rates &amp; Assumptions'!E$17:E$1016,L41)</f>
+        <v/>
+      </c>
+      <c r="N63" s="33">
+        <f>INDEX('Tax Rates &amp; Assumptions'!F$17:F$1016,L41)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64" hidden="1" outlineLevel="1">
+      <c r="B64" s="37" t="inlineStr">
         <is>
           <t>Local Tax From the Gain</t>
         </is>
       </c>
-      <c r="C62" s="35">
-        <f>C42*MAX(0,C43)</f>
-        <v/>
-      </c>
-      <c r="L62" s="32">
-        <f>INDEX('Tax Rates &amp; Assumptions'!D$17:D$1016,L40)</f>
-        <v/>
-      </c>
-      <c r="M62" s="33">
-        <f>INDEX('Tax Rates &amp; Assumptions'!E$17:E$1016,L40)</f>
-        <v/>
-      </c>
-      <c r="N62" s="33">
-        <f>INDEX('Tax Rates &amp; Assumptions'!F$17:F$1016,L40)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="63" hidden="1" outlineLevel="1">
-      <c r="B63" s="23" t="inlineStr">
+      <c r="C64" s="35">
+        <f>C43*MAX(0,C46)</f>
+        <v/>
+      </c>
+      <c r="L64" s="32">
+        <f>INDEX('Tax Rates &amp; Assumptions'!G$17:G$1016,L41)</f>
+        <v/>
+      </c>
+      <c r="M64" s="33">
+        <f>INDEX('Tax Rates &amp; Assumptions'!H$17:H$1016,L41)</f>
+        <v/>
+      </c>
+      <c r="N64" s="33">
+        <f>INDEX('Tax Rates &amp; Assumptions'!I$17:I$1016,L41)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65" hidden="1" outlineLevel="1">
+      <c r="B65" s="23" t="inlineStr">
         <is>
           <t>Total Estimated Tax</t>
         </is>
       </c>
-      <c r="C63" s="38">
-        <f>(C56+C61+C62)</f>
-        <v/>
-      </c>
-      <c r="L63" s="32">
-        <f>INDEX('Tax Rates &amp; Assumptions'!G$17:G$1016,L40)</f>
-        <v/>
-      </c>
-      <c r="M63" s="33">
-        <f>INDEX('Tax Rates &amp; Assumptions'!H$17:H$1016,L40)</f>
-        <v/>
-      </c>
-      <c r="N63" s="33">
-        <f>INDEX('Tax Rates &amp; Assumptions'!I$17:I$1016,L40)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="64" hidden="1" outlineLevel="1">
-      <c r="B64" s="34" t="inlineStr">
-        <is>
-          <t>Federal Marginal Rate Applied to the Gain</t>
-        </is>
-      </c>
-      <c r="C64" s="39">
-        <f>IF(AND(C43&gt;=0,C44=1),IFERROR(INDEX($L$62:$L$64,MATCH(C48,$M$62:$M$64,1)),0),IFERROR(INDEX($L$53:$L$59,MATCH(C48,$M$53:$M$59,1)),0))</f>
-        <v/>
-      </c>
-      <c r="L64" s="32">
-        <f>INDEX('Tax Rates &amp; Assumptions'!J$17:J$1016,L40)</f>
-        <v/>
-      </c>
-      <c r="M64" s="33">
-        <f>INDEX('Tax Rates &amp; Assumptions'!K$17:K$1016,L40)</f>
-        <v/>
-      </c>
-      <c r="N64" s="33">
-        <f>INDEX('Tax Rates &amp; Assumptions'!L$17:L$1016,L40)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="65" hidden="1" outlineLevel="1">
-      <c r="B65" s="34" t="inlineStr">
-        <is>
-          <t>Federal Effective Rate on the Gain</t>
-        </is>
-      </c>
-      <c r="C65" s="39">
-        <f>IFERROR(C56/C43,0)</f>
+      <c r="C65" s="38">
+        <f>(C58+C63+C64)</f>
+        <v/>
+      </c>
+      <c r="L65" s="32">
+        <f>INDEX('Tax Rates &amp; Assumptions'!J$17:J$1016,L41)</f>
+        <v/>
+      </c>
+      <c r="M65" s="33">
+        <f>INDEX('Tax Rates &amp; Assumptions'!K$17:K$1016,L41)</f>
+        <v/>
+      </c>
+      <c r="N65" s="33">
+        <f>INDEX('Tax Rates &amp; Assumptions'!L$17:L$1016,L41)</f>
         <v/>
       </c>
     </row>
     <row r="66" hidden="1" outlineLevel="1">
       <c r="B66" s="34" t="inlineStr">
         <is>
-          <t>State Marginal Rate Applied to the Gain</t>
+          <t>Federal Marginal Rate Applied to the Gain</t>
         </is>
       </c>
       <c r="C66" s="39">
-        <f>IF(L44="OTHER",0,IFERROR(INDEX($L$67:$L$74,MATCH(C58,$M$67:$M$74,1)),0))</f>
-        <v/>
-      </c>
-      <c r="K66" s="31" t="inlineStr">
-        <is>
-          <t>State Brackets</t>
-        </is>
+        <f>IF(C48&gt;0,IFERROR(INDEX($L$63:$L$65,MATCH((C50+C48),$M$63:$M$65,1)),0),IFERROR(INDEX($L$54:$L$60,MATCH(C50,$M$54:$M$60,1)),0))</f>
+        <v/>
       </c>
     </row>
     <row r="67" hidden="1" outlineLevel="1">
       <c r="B67" s="34" t="inlineStr">
         <is>
-          <t>State Effective Rate on the Gain</t>
+          <t>Federal Effective Rate on the Gain</t>
         </is>
       </c>
       <c r="C67" s="39">
-        <f>IFERROR(C61/C43,0)</f>
-        <v/>
-      </c>
-      <c r="L67" s="32">
-        <f>INDEX('Tax Rates &amp; Assumptions'!D$81:D$1080,L47)</f>
-        <v/>
-      </c>
-      <c r="M67" s="33">
-        <f>INDEX('Tax Rates &amp; Assumptions'!E$81:E$1080,L47)</f>
-        <v/>
-      </c>
-      <c r="N67" s="33">
-        <f>INDEX('Tax Rates &amp; Assumptions'!F$81:F$1080,L47)</f>
-        <v/>
+        <f>IFERROR(C58/C46,0)</f>
+        <v/>
+      </c>
+      <c r="K67" s="31" t="inlineStr">
+        <is>
+          <t>State Brackets</t>
+        </is>
       </c>
     </row>
     <row r="68" hidden="1" outlineLevel="1">
       <c r="B68" s="34" t="inlineStr">
         <is>
+          <t>State Marginal Rate Applied to the Gain</t>
+        </is>
+      </c>
+      <c r="C68" s="39">
+        <f>IF(L45="OTHER",0,IFERROR(INDEX($L$68:$L$75,MATCH(C60,$M$68:$M$75,1)),0))</f>
+        <v/>
+      </c>
+      <c r="L68" s="32">
+        <f>INDEX('Tax Rates &amp; Assumptions'!D$81:D$1080,L48)</f>
+        <v/>
+      </c>
+      <c r="M68" s="33">
+        <f>INDEX('Tax Rates &amp; Assumptions'!E$81:E$1080,L48)</f>
+        <v/>
+      </c>
+      <c r="N68" s="33">
+        <f>INDEX('Tax Rates &amp; Assumptions'!F$81:F$1080,L48)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69" hidden="1" outlineLevel="1">
+      <c r="B69" s="34" t="inlineStr">
+        <is>
+          <t>State Effective Rate on the Gain</t>
+        </is>
+      </c>
+      <c r="C69" s="39">
+        <f>IFERROR(C63/C46,0)</f>
+        <v/>
+      </c>
+      <c r="L69" s="32">
+        <f>INDEX('Tax Rates &amp; Assumptions'!G$81:G$1080,L48)</f>
+        <v/>
+      </c>
+      <c r="M69" s="33">
+        <f>INDEX('Tax Rates &amp; Assumptions'!H$81:H$1080,L48)</f>
+        <v/>
+      </c>
+      <c r="N69" s="33">
+        <f>INDEX('Tax Rates &amp; Assumptions'!I$81:I$1080,L48)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70" hidden="1" outlineLevel="1">
+      <c r="B70" s="34" t="inlineStr">
+        <is>
           <t>Local Effective Rate on the Gain</t>
         </is>
       </c>
-      <c r="C68" s="39">
-        <f>IFERROR(C62/C43,0)</f>
-        <v/>
-      </c>
-      <c r="L68" s="32">
-        <f>INDEX('Tax Rates &amp; Assumptions'!G$81:G$1080,L47)</f>
-        <v/>
-      </c>
-      <c r="M68" s="33">
-        <f>INDEX('Tax Rates &amp; Assumptions'!H$81:H$1080,L47)</f>
-        <v/>
-      </c>
-      <c r="N68" s="33">
-        <f>INDEX('Tax Rates &amp; Assumptions'!I$81:I$1080,L47)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="69" hidden="1" outlineLevel="1">
-      <c r="L69" s="32">
-        <f>INDEX('Tax Rates &amp; Assumptions'!J$81:J$1080,L47)</f>
-        <v/>
-      </c>
-      <c r="M69" s="33">
-        <f>INDEX('Tax Rates &amp; Assumptions'!K$81:K$1080,L47)</f>
-        <v/>
-      </c>
-      <c r="N69" s="33">
-        <f>INDEX('Tax Rates &amp; Assumptions'!L$81:L$1080,L47)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="70" hidden="1" outlineLevel="1">
+      <c r="C70" s="39">
+        <f>IFERROR(C64/C46,0)</f>
+        <v/>
+      </c>
       <c r="L70" s="32">
-        <f>INDEX('Tax Rates &amp; Assumptions'!M$81:M$1080,L47)</f>
+        <f>INDEX('Tax Rates &amp; Assumptions'!J$81:J$1080,L48)</f>
         <v/>
       </c>
       <c r="M70" s="33">
-        <f>INDEX('Tax Rates &amp; Assumptions'!N$81:N$1080,L47)</f>
+        <f>INDEX('Tax Rates &amp; Assumptions'!K$81:K$1080,L48)</f>
         <v/>
       </c>
       <c r="N70" s="33">
-        <f>INDEX('Tax Rates &amp; Assumptions'!O$81:O$1080,L47)</f>
+        <f>INDEX('Tax Rates &amp; Assumptions'!L$81:L$1080,L48)</f>
         <v/>
       </c>
     </row>
     <row r="71" hidden="1" outlineLevel="1">
       <c r="L71" s="32">
-        <f>INDEX('Tax Rates &amp; Assumptions'!P$81:P$1080,L47)</f>
+        <f>INDEX('Tax Rates &amp; Assumptions'!M$81:M$1080,L48)</f>
         <v/>
       </c>
       <c r="M71" s="33">
-        <f>INDEX('Tax Rates &amp; Assumptions'!Q$81:Q$1080,L47)</f>
+        <f>INDEX('Tax Rates &amp; Assumptions'!N$81:N$1080,L48)</f>
         <v/>
       </c>
       <c r="N71" s="33">
-        <f>INDEX('Tax Rates &amp; Assumptions'!R$81:R$1080,L47)</f>
+        <f>INDEX('Tax Rates &amp; Assumptions'!O$81:O$1080,L48)</f>
         <v/>
       </c>
     </row>
     <row r="72" hidden="1" outlineLevel="1">
       <c r="L72" s="32">
-        <f>INDEX('Tax Rates &amp; Assumptions'!S$81:S$1080,L47)</f>
+        <f>INDEX('Tax Rates &amp; Assumptions'!P$81:P$1080,L48)</f>
         <v/>
       </c>
       <c r="M72" s="33">
-        <f>INDEX('Tax Rates &amp; Assumptions'!T$81:T$1080,L47)</f>
+        <f>INDEX('Tax Rates &amp; Assumptions'!Q$81:Q$1080,L48)</f>
         <v/>
       </c>
       <c r="N72" s="33">
-        <f>INDEX('Tax Rates &amp; Assumptions'!U$81:U$1080,L47)</f>
+        <f>INDEX('Tax Rates &amp; Assumptions'!R$81:R$1080,L48)</f>
         <v/>
       </c>
     </row>
     <row r="73" hidden="1" outlineLevel="1">
       <c r="L73" s="32">
-        <f>INDEX('Tax Rates &amp; Assumptions'!V$81:V$1080,L47)</f>
+        <f>INDEX('Tax Rates &amp; Assumptions'!S$81:S$1080,L48)</f>
         <v/>
       </c>
       <c r="M73" s="33">
-        <f>INDEX('Tax Rates &amp; Assumptions'!W$81:W$1080,L47)</f>
+        <f>INDEX('Tax Rates &amp; Assumptions'!T$81:T$1080,L48)</f>
         <v/>
       </c>
       <c r="N73" s="33">
-        <f>INDEX('Tax Rates &amp; Assumptions'!X$81:X$1080,L47)</f>
+        <f>INDEX('Tax Rates &amp; Assumptions'!U$81:U$1080,L48)</f>
         <v/>
       </c>
     </row>
     <row r="74" hidden="1" outlineLevel="1">
       <c r="L74" s="32">
-        <f>INDEX('Tax Rates &amp; Assumptions'!Y$81:Y$1080,L47)</f>
+        <f>INDEX('Tax Rates &amp; Assumptions'!V$81:V$1080,L48)</f>
         <v/>
       </c>
       <c r="M74" s="33">
-        <f>INDEX('Tax Rates &amp; Assumptions'!Z$81:Z$1080,L47)</f>
+        <f>INDEX('Tax Rates &amp; Assumptions'!W$81:W$1080,L48)</f>
         <v/>
       </c>
       <c r="N74" s="33">
-        <f>INDEX('Tax Rates &amp; Assumptions'!AA$81:AA$1080,L47)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="75" hidden="1" outlineLevel="1"/>
+        <f>INDEX('Tax Rates &amp; Assumptions'!X$81:X$1080,L48)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75" hidden="1" outlineLevel="1">
+      <c r="L75" s="32">
+        <f>INDEX('Tax Rates &amp; Assumptions'!Y$81:Y$1080,L48)</f>
+        <v/>
+      </c>
+      <c r="M75" s="33">
+        <f>INDEX('Tax Rates &amp; Assumptions'!Z$81:Z$1080,L48)</f>
+        <v/>
+      </c>
+      <c r="N75" s="33">
+        <f>INDEX('Tax Rates &amp; Assumptions'!AA$81:AA$1080,L48)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76" hidden="1" outlineLevel="1"/>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="B12:I12"/>
-    <mergeCell ref="B18:I19"/>
-    <mergeCell ref="A21:H21"/>
+    <mergeCell ref="B13:I13"/>
     <mergeCell ref="A2:I2"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B29:I31"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="B28:I30"/>
-    <mergeCell ref="B32:F32"/>
+    <mergeCell ref="B19:I20"/>
+    <mergeCell ref="A22:H22"/>
   </mergeCells>
-  <dataValidations count="5">
-    <dataValidation sqref="I5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>"One year or less,More than a year"</formula1>
-    </dataValidation>
-    <dataValidation sqref="C8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+  <dataValidations count="4">
+    <dataValidation sqref="F8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>='Tax Rates &amp; Assumptions'!$B$46:$B$77</formula1>
     </dataValidation>
-    <dataValidation sqref="I8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="C11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Single,Married Filing Jointly,Married Filing Separately,Head of Household"</formula1>
     </dataValidation>
-    <dataValidation sqref="C10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="F11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"2024,2025"</formula1>
     </dataValidation>
-    <dataValidation sqref="F16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="F17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>='Tax Rates &amp; Assumptions'!$B$148:$B$161</formula1>
     </dataValidation>
   </dataValidations>

--- a/Capital_Gains_Tax_Estimator.xlsx
+++ b/Capital_Gains_Tax_Estimator.xlsx
@@ -764,7 +764,7 @@
     </row>
     <row r="5">
       <c r="C5" s="13" t="n">
-        <v>50000</v>
+        <v>40000</v>
       </c>
       <c r="F5" s="13" t="n">
         <v>0</v>
@@ -800,7 +800,7 @@
         </is>
       </c>
       <c r="I8" s="13" t="n">
-        <v>200000</v>
+        <v>500000</v>
       </c>
     </row>
     <row r="10">
@@ -874,7 +874,7 @@
     </row>
     <row r="17" hidden="1" outlineLevel="1">
       <c r="C17" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F17" s="12" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
     <row r="19" ht="20" customHeight="1">
       <c r="B19" s="25">
         <f>C65</f>
-        <v/>
+        <v>10276</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1"/>
@@ -933,15 +933,15 @@
       </c>
       <c r="D24" s="40">
         <f>C66</f>
-        <v/>
+        <v>0.15</v>
       </c>
       <c r="F24" s="40">
         <f>C67</f>
-        <v/>
+        <v>0.188</v>
       </c>
       <c r="H24" s="41">
         <f>C58</f>
-        <v/>
+        <v>7520</v>
       </c>
     </row>
     <row r="25">
@@ -952,15 +952,15 @@
       </c>
       <c r="D25" s="40">
         <f>C68</f>
-        <v/>
+        <v>0.0897</v>
       </c>
       <c r="F25" s="40">
         <f>C69</f>
-        <v/>
+        <v>0.0689</v>
       </c>
       <c r="H25" s="41">
         <f>C63</f>
-        <v/>
+        <v>2756</v>
       </c>
     </row>
     <row r="26">
@@ -971,15 +971,15 @@
       </c>
       <c r="D26" s="40">
         <f>C43</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F26" s="40">
         <f>C70</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H26" s="41">
         <f>C64</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -990,7 +990,7 @@
       </c>
       <c r="H27" s="42">
         <f>C65</f>
-        <v/>
+        <v>10276</v>
       </c>
     </row>
     <row r="29">
@@ -1025,16 +1025,16 @@
       </c>
       <c r="C37" s="35">
         <f>INDEX('Tax Rates &amp; Assumptions'!$D$28:$D$35,L43)</f>
-        <v/>
+        <v>30000</v>
       </c>
       <c r="K37" s="7" t="inlineStr">
         <is>
           <t>Filing Status</t>
         </is>
       </c>
-      <c r="L37" s="30">
+      <c r="L37" s="30" t="str">
         <f>C11</f>
-        <v/>
+        <v>Married Filing Jointly</v>
       </c>
     </row>
     <row r="38" hidden="1" outlineLevel="1">
@@ -1045,7 +1045,7 @@
       </c>
       <c r="C38" s="35">
         <f>INDEX('Tax Rates &amp; Assumptions'!$D$39:$D$42,L42)</f>
-        <v/>
+        <v>3000</v>
       </c>
       <c r="K38" s="7" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="L38" s="30">
         <f>F11</f>
-        <v/>
+        <v>2025</v>
       </c>
     </row>
     <row r="39" hidden="1" outlineLevel="1">
@@ -1065,16 +1065,16 @@
       </c>
       <c r="C39" s="35">
         <f>INDEX('Tax Rates &amp; Assumptions'!$B$39:$B$42,L42)</f>
-        <v/>
+        <v>250000</v>
       </c>
       <c r="K39" s="7" t="inlineStr">
         <is>
           <t>Federal Key</t>
         </is>
       </c>
-      <c r="L39" s="30">
+      <c r="L39" s="30" t="str">
         <f>L38&amp;"|"&amp;L37</f>
-        <v/>
+        <v>2025|Married Filing Jointly</v>
       </c>
     </row>
     <row r="40" hidden="1" outlineLevel="1">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="C40" s="36">
         <f>INDEX('Tax Rates &amp; Assumptions'!$C$39:$C$42,L42)</f>
-        <v/>
+        <v>0.038</v>
       </c>
       <c r="K40" s="7" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="L40" s="30">
         <f>MATCH(L39,'Tax Rates &amp; Assumptions'!$C$6:$C$13,0)</f>
-        <v/>
+        <v>6</v>
       </c>
     </row>
     <row r="41" hidden="1" outlineLevel="1">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="C41" s="35">
         <f>IF(L46="MFJ",INDEX('Tax Rates &amp; Assumptions'!$E$46:$E$77,L49),INDEX('Tax Rates &amp; Assumptions'!$D$46:$D$77,L49))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K41" s="7" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="L41" s="30">
         <f>MATCH(L39,'Tax Rates &amp; Assumptions'!$C$17:$C$24,0)</f>
-        <v/>
+        <v>6</v>
       </c>
     </row>
     <row r="42" hidden="1" outlineLevel="1">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="C42" s="35">
         <f>INDEX('Tax Rates &amp; Assumptions'!$C$164:$C$164,1)</f>
-        <v/>
+        <v>1000</v>
       </c>
       <c r="K42" s="7" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="L42" s="30">
         <f>MATCH(L37,'Tax Rates &amp; Assumptions'!$A$39:$A$42,0)</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="43" hidden="1" outlineLevel="1">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="C43" s="36">
         <f>IF(L51=0,0,INDEX('Tax Rates &amp; Assumptions'!$D$148:$D$161,L51))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K43" s="7" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="L43" s="30">
         <f>MATCH(L39,'Tax Rates &amp; Assumptions'!$C$28:$C$35,0)</f>
-        <v/>
+        <v>6</v>
       </c>
     </row>
     <row r="44" hidden="1" outlineLevel="1">
@@ -1165,16 +1165,16 @@
       </c>
       <c r="C44" s="35">
         <f>(I5-C8)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K44" s="7" t="inlineStr">
         <is>
           <t>State Name</t>
         </is>
       </c>
-      <c r="L44" s="30">
+      <c r="L44" s="30" t="str">
         <f>F8</f>
-        <v/>
+        <v>New Jersey</v>
       </c>
     </row>
     <row r="45" hidden="1" outlineLevel="1">
@@ -1185,16 +1185,16 @@
       </c>
       <c r="C45" s="35">
         <f>(C5-F5)</f>
-        <v/>
+        <v>40000</v>
       </c>
       <c r="K45" s="7" t="inlineStr">
         <is>
           <t>State Code</t>
         </is>
       </c>
-      <c r="L45" s="30">
+      <c r="L45" s="30" t="str">
         <f>INDEX('Tax Rates &amp; Assumptions'!$A$46:$A$77,MATCH(L44,'Tax Rates &amp; Assumptions'!$B$46:$B$77,0))</f>
-        <v/>
+        <v>NJ</v>
       </c>
     </row>
     <row r="46" hidden="1" outlineLevel="1">
@@ -1205,16 +1205,16 @@
       </c>
       <c r="C46" s="35">
         <f>(C44+C45)</f>
-        <v/>
+        <v>40000</v>
       </c>
       <c r="K46" s="7" t="inlineStr">
         <is>
           <t>State Category</t>
         </is>
       </c>
-      <c r="L46" s="30">
+      <c r="L46" s="30" t="str">
         <f>IF(L37="Married Filing Jointly","MFJ","Single")</f>
-        <v/>
+        <v>MFJ</v>
       </c>
     </row>
     <row r="47" hidden="1" outlineLevel="1">
@@ -1225,16 +1225,16 @@
       </c>
       <c r="C47" s="35">
         <f>IF(C46&lt;=0,MAX(C46,-C38),IF(AND(C44&gt;=0,C45&gt;=0),C44,IF(AND(C44&lt;0,C45&gt;=0),0,IF(AND(C44&gt;=0,C45&lt;0),C46,0))))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K47" s="7" t="inlineStr">
         <is>
           <t>State Key</t>
         </is>
       </c>
-      <c r="L47" s="30">
+      <c r="L47" s="30" t="str">
         <f>L45&amp;"|"&amp;L46</f>
-        <v/>
+        <v>NJ|MFJ</v>
       </c>
     </row>
     <row r="48" hidden="1" outlineLevel="1">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="C48" s="35">
         <f>IF(C46&lt;=0,0,IF(AND(C44&gt;=0,C45&gt;=0),C45,IF(AND(C44&lt;0,C45&gt;=0),C46,IF(AND(C44&gt;=0,C45&lt;0),0,0))))</f>
-        <v/>
+        <v>40000</v>
       </c>
       <c r="K48" s="7" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="L48" s="30">
         <f>MATCH(L47,'Tax Rates &amp; Assumptions'!$C$81:$C$144,0)</f>
-        <v/>
+        <v>44</v>
       </c>
     </row>
     <row r="49" hidden="1" outlineLevel="1">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="C49" s="35">
         <f>MAX(0,I8-C15-F15-MAX(I15,INDEX('Tax Rates &amp; Assumptions'!$D$28:$D$35,L43)))</f>
-        <v/>
+        <v>470000</v>
       </c>
       <c r="K49" s="7" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="L49" s="30">
         <f>MATCH(L45,'Tax Rates &amp; Assumptions'!$A$46:$A$77,0)</f>
-        <v/>
+        <v>22</v>
       </c>
     </row>
     <row r="50" hidden="1" outlineLevel="1">
@@ -1285,16 +1285,16 @@
       </c>
       <c r="C50" s="35">
         <f>MAX(0,C49+C47)</f>
-        <v/>
+        <v>470000</v>
       </c>
       <c r="K50" s="7" t="inlineStr">
         <is>
           <t>Locality Name</t>
         </is>
       </c>
-      <c r="L50" s="30">
+      <c r="L50" s="30" t="str">
         <f>F17</f>
-        <v/>
+        <v>None / Not Applicable</v>
       </c>
     </row>
     <row r="51" hidden="1" outlineLevel="1">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="C51" s="35">
         <f>SUMPRODUCT((C49&gt;$M$54:$M$60)*($L$54:$L$60)*(MIN(C49,$N$54:$N$60)-$M$54:$M$60))</f>
-        <v/>
+        <v>104526</v>
       </c>
       <c r="K51" s="7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="L51" s="30">
         <f>IFERROR(MATCH(L50,'Tax Rates &amp; Assumptions'!$B$148:$B$161,0),0)</f>
-        <v/>
+        <v>13</v>
       </c>
     </row>
     <row r="52" hidden="1" outlineLevel="1">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="C52" s="35">
         <f>SUMPRODUCT((C50&gt;$M$54:$M$60)*($L$54:$L$60)*(MIN(C50,$N$54:$N$60)-$M$54:$M$60))</f>
-        <v/>
+        <v>104526</v>
       </c>
     </row>
     <row r="53" hidden="1" outlineLevel="1">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="C53" s="35">
         <f>C52-C51</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K53" s="31" t="inlineStr">
         <is>
@@ -1352,19 +1352,19 @@
       </c>
       <c r="C54" s="35">
         <f>SUMPRODUCT($L$63:$L$65*(MAX(0,MIN((C50+C48),$N$63:$N$65)-MAX(C50,$M$63:$M$65))))</f>
-        <v/>
+        <v>6000</v>
       </c>
       <c r="L54" s="32">
         <f>INDEX('Tax Rates &amp; Assumptions'!D$6:D$1005,L40)</f>
-        <v/>
+        <v>0.1</v>
       </c>
       <c r="M54" s="33">
         <f>INDEX('Tax Rates &amp; Assumptions'!E$6:E$1005,L40)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N54" s="33">
         <f>INDEX('Tax Rates &amp; Assumptions'!F$6:F$1005,L40)</f>
-        <v/>
+        <v>23850</v>
       </c>
     </row>
     <row r="55" hidden="1" outlineLevel="1">
@@ -1375,19 +1375,19 @@
       </c>
       <c r="C55" s="35">
         <f>(C49+C37+C47+C48)</f>
-        <v/>
+        <v>540000</v>
       </c>
       <c r="L55" s="32">
         <f>INDEX('Tax Rates &amp; Assumptions'!G$6:G$1005,L40)</f>
-        <v/>
+        <v>0.12</v>
       </c>
       <c r="M55" s="33">
         <f>INDEX('Tax Rates &amp; Assumptions'!H$6:H$1005,L40)</f>
-        <v/>
+        <v>23850</v>
       </c>
       <c r="N55" s="33">
         <f>INDEX('Tax Rates &amp; Assumptions'!I$6:I$1005,L40)</f>
-        <v/>
+        <v>96950</v>
       </c>
     </row>
     <row r="56" hidden="1" outlineLevel="1">
@@ -1398,19 +1398,19 @@
       </c>
       <c r="C56" s="35">
         <f>MAX(0,C47+C48)</f>
-        <v/>
+        <v>40000</v>
       </c>
       <c r="L56" s="32">
         <f>INDEX('Tax Rates &amp; Assumptions'!J$6:J$1005,L40)</f>
-        <v/>
+        <v>0.22</v>
       </c>
       <c r="M56" s="33">
         <f>INDEX('Tax Rates &amp; Assumptions'!K$6:K$1005,L40)</f>
-        <v/>
+        <v>96950</v>
       </c>
       <c r="N56" s="33">
         <f>INDEX('Tax Rates &amp; Assumptions'!L$6:L$1005,L40)</f>
-        <v/>
+        <v>206700</v>
       </c>
     </row>
     <row r="57" hidden="1" outlineLevel="1">
@@ -1421,19 +1421,19 @@
       </c>
       <c r="C57" s="35">
         <f>C40*MIN(C56,MAX(0,C55-C39))</f>
-        <v/>
+        <v>1520</v>
       </c>
       <c r="L57" s="32">
         <f>INDEX('Tax Rates &amp; Assumptions'!M$6:M$1005,L40)</f>
-        <v/>
+        <v>0.24</v>
       </c>
       <c r="M57" s="33">
         <f>INDEX('Tax Rates &amp; Assumptions'!N$6:N$1005,L40)</f>
-        <v/>
+        <v>206700</v>
       </c>
       <c r="N57" s="33">
         <f>INDEX('Tax Rates &amp; Assumptions'!O$6:O$1005,L40)</f>
-        <v/>
+        <v>394600</v>
       </c>
     </row>
     <row r="58" hidden="1" outlineLevel="1">
@@ -1444,19 +1444,19 @@
       </c>
       <c r="C58" s="35">
         <f>(C53+C54+C57)</f>
-        <v/>
+        <v>7520</v>
       </c>
       <c r="L58" s="32">
         <f>INDEX('Tax Rates &amp; Assumptions'!P$6:P$1005,L40)</f>
-        <v/>
+        <v>0.32</v>
       </c>
       <c r="M58" s="33">
         <f>INDEX('Tax Rates &amp; Assumptions'!Q$6:Q$1005,L40)</f>
-        <v/>
+        <v>394600</v>
       </c>
       <c r="N58" s="33">
         <f>INDEX('Tax Rates &amp; Assumptions'!R$6:R$1005,L40)</f>
-        <v/>
+        <v>501050</v>
       </c>
     </row>
     <row r="59" hidden="1" outlineLevel="1">
@@ -1467,19 +1467,19 @@
       </c>
       <c r="C59" s="35">
         <f>MAX(0,C49-C41-C17*C42)</f>
-        <v/>
+        <v>468000</v>
       </c>
       <c r="L59" s="32">
         <f>INDEX('Tax Rates &amp; Assumptions'!S$6:S$1005,L40)</f>
-        <v/>
+        <v>0.35</v>
       </c>
       <c r="M59" s="33">
         <f>INDEX('Tax Rates &amp; Assumptions'!T$6:T$1005,L40)</f>
-        <v/>
+        <v>501050</v>
       </c>
       <c r="N59" s="33">
         <f>INDEX('Tax Rates &amp; Assumptions'!U$6:U$1005,L40)</f>
-        <v/>
+        <v>751600</v>
       </c>
     </row>
     <row r="60" hidden="1" outlineLevel="1">
@@ -1490,19 +1490,19 @@
       </c>
       <c r="C60" s="35">
         <f>MAX(0,C49+C47+C48-C41-C17*C42)</f>
-        <v/>
+        <v>508000</v>
       </c>
       <c r="L60" s="32">
         <f>INDEX('Tax Rates &amp; Assumptions'!V$6:V$1005,L40)</f>
-        <v/>
+        <v>0.37</v>
       </c>
       <c r="M60" s="33">
         <f>INDEX('Tax Rates &amp; Assumptions'!W$6:W$1005,L40)</f>
-        <v/>
+        <v>751600</v>
       </c>
       <c r="N60" s="33">
         <f>INDEX('Tax Rates &amp; Assumptions'!X$6:X$1005,L40)</f>
-        <v/>
+        <v>999999999</v>
       </c>
     </row>
     <row r="61" hidden="1" outlineLevel="1">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="C61" s="35">
         <f>IF(L45="OTHER",0,SUMPRODUCT((C59&gt;$M$68:$M$75)*($L$68:$L$75)*(MIN(C59,$N$68:$N$75)-$M$68:$M$75)))</f>
-        <v/>
+        <v>25769.100000000002</v>
       </c>
     </row>
     <row r="62" hidden="1" outlineLevel="1">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="C62" s="35">
         <f>IF(L45="OTHER",0,SUMPRODUCT((C60&gt;$M$68:$M$75)*($L$68:$L$75)*(MIN(C60,$N$68:$N$75)-$M$68:$M$75)))</f>
-        <v/>
+        <v>28525.100000000002</v>
       </c>
       <c r="K62" s="31" t="inlineStr">
         <is>
@@ -1540,19 +1540,19 @@
       </c>
       <c r="C63" s="35">
         <f>(C62-C61)</f>
-        <v/>
+        <v>2756</v>
       </c>
       <c r="L63" s="32">
         <f>INDEX('Tax Rates &amp; Assumptions'!D$17:D$1016,L41)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M63" s="33">
         <f>INDEX('Tax Rates &amp; Assumptions'!E$17:E$1016,L41)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N63" s="33">
         <f>INDEX('Tax Rates &amp; Assumptions'!F$17:F$1016,L41)</f>
-        <v/>
+        <v>96700</v>
       </c>
     </row>
     <row r="64" hidden="1" outlineLevel="1">
@@ -1563,19 +1563,19 @@
       </c>
       <c r="C64" s="35">
         <f>C43*MAX(0,C46)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="L64" s="32">
         <f>INDEX('Tax Rates &amp; Assumptions'!G$17:G$1016,L41)</f>
-        <v/>
+        <v>0.15</v>
       </c>
       <c r="M64" s="33">
         <f>INDEX('Tax Rates &amp; Assumptions'!H$17:H$1016,L41)</f>
-        <v/>
+        <v>96700</v>
       </c>
       <c r="N64" s="33">
         <f>INDEX('Tax Rates &amp; Assumptions'!I$17:I$1016,L41)</f>
-        <v/>
+        <v>600050</v>
       </c>
     </row>
     <row r="65" hidden="1" outlineLevel="1">
@@ -1586,19 +1586,19 @@
       </c>
       <c r="C65" s="38">
         <f>(C58+C63+C64)</f>
-        <v/>
+        <v>10276</v>
       </c>
       <c r="L65" s="32">
         <f>INDEX('Tax Rates &amp; Assumptions'!J$17:J$1016,L41)</f>
-        <v/>
+        <v>0.2</v>
       </c>
       <c r="M65" s="33">
         <f>INDEX('Tax Rates &amp; Assumptions'!K$17:K$1016,L41)</f>
-        <v/>
+        <v>600050</v>
       </c>
       <c r="N65" s="33">
         <f>INDEX('Tax Rates &amp; Assumptions'!L$17:L$1016,L41)</f>
-        <v/>
+        <v>999999999</v>
       </c>
     </row>
     <row r="66" hidden="1" outlineLevel="1">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="C66" s="39">
         <f>IF(C48&gt;0,IFERROR(INDEX($L$63:$L$65,MATCH((C50+C48),$M$63:$M$65,1)),0),IFERROR(INDEX($L$54:$L$60,MATCH(C50,$M$54:$M$60,1)),0))</f>
-        <v/>
+        <v>0.15</v>
       </c>
     </row>
     <row r="67" hidden="1" outlineLevel="1">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="C67" s="39">
         <f>IFERROR(C58/C46,0)</f>
-        <v/>
+        <v>0.188</v>
       </c>
       <c r="K67" s="31" t="inlineStr">
         <is>
@@ -1636,19 +1636,19 @@
       </c>
       <c r="C68" s="39">
         <f>IF(L45="OTHER",0,IFERROR(INDEX($L$68:$L$75,MATCH(C60,$M$68:$M$75,1)),0))</f>
-        <v/>
+        <v>0.0897</v>
       </c>
       <c r="L68" s="32">
         <f>INDEX('Tax Rates &amp; Assumptions'!D$81:D$1080,L48)</f>
-        <v/>
+        <v>0.014</v>
       </c>
       <c r="M68" s="33">
         <f>INDEX('Tax Rates &amp; Assumptions'!E$81:E$1080,L48)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N68" s="33">
         <f>INDEX('Tax Rates &amp; Assumptions'!F$81:F$1080,L48)</f>
-        <v/>
+        <v>20000</v>
       </c>
     </row>
     <row r="69" hidden="1" outlineLevel="1">
@@ -1659,19 +1659,19 @@
       </c>
       <c r="C69" s="39">
         <f>IFERROR(C63/C46,0)</f>
-        <v/>
+        <v>0.0689</v>
       </c>
       <c r="L69" s="32">
         <f>INDEX('Tax Rates &amp; Assumptions'!G$81:G$1080,L48)</f>
-        <v/>
+        <v>0.0175</v>
       </c>
       <c r="M69" s="33">
         <f>INDEX('Tax Rates &amp; Assumptions'!H$81:H$1080,L48)</f>
-        <v/>
+        <v>20000</v>
       </c>
       <c r="N69" s="33">
         <f>INDEX('Tax Rates &amp; Assumptions'!I$81:I$1080,L48)</f>
-        <v/>
+        <v>50000</v>
       </c>
     </row>
     <row r="70" hidden="1" outlineLevel="1">
@@ -1682,89 +1682,89 @@
       </c>
       <c r="C70" s="39">
         <f>IFERROR(C64/C46,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="L70" s="32">
         <f>INDEX('Tax Rates &amp; Assumptions'!J$81:J$1080,L48)</f>
-        <v/>
+        <v>0.0245</v>
       </c>
       <c r="M70" s="33">
         <f>INDEX('Tax Rates &amp; Assumptions'!K$81:K$1080,L48)</f>
-        <v/>
+        <v>50000</v>
       </c>
       <c r="N70" s="33">
         <f>INDEX('Tax Rates &amp; Assumptions'!L$81:L$1080,L48)</f>
-        <v/>
+        <v>70000</v>
       </c>
     </row>
     <row r="71" hidden="1" outlineLevel="1">
       <c r="L71" s="32">
         <f>INDEX('Tax Rates &amp; Assumptions'!M$81:M$1080,L48)</f>
-        <v/>
+        <v>0.035</v>
       </c>
       <c r="M71" s="33">
         <f>INDEX('Tax Rates &amp; Assumptions'!N$81:N$1080,L48)</f>
-        <v/>
+        <v>70000</v>
       </c>
       <c r="N71" s="33">
         <f>INDEX('Tax Rates &amp; Assumptions'!O$81:O$1080,L48)</f>
-        <v/>
+        <v>80000</v>
       </c>
     </row>
     <row r="72" hidden="1" outlineLevel="1">
       <c r="L72" s="32">
         <f>INDEX('Tax Rates &amp; Assumptions'!P$81:P$1080,L48)</f>
-        <v/>
+        <v>0.05525</v>
       </c>
       <c r="M72" s="33">
         <f>INDEX('Tax Rates &amp; Assumptions'!Q$81:Q$1080,L48)</f>
-        <v/>
+        <v>80000</v>
       </c>
       <c r="N72" s="33">
         <f>INDEX('Tax Rates &amp; Assumptions'!R$81:R$1080,L48)</f>
-        <v/>
+        <v>150000</v>
       </c>
     </row>
     <row r="73" hidden="1" outlineLevel="1">
       <c r="L73" s="32">
         <f>INDEX('Tax Rates &amp; Assumptions'!S$81:S$1080,L48)</f>
-        <v/>
+        <v>0.0637</v>
       </c>
       <c r="M73" s="33">
         <f>INDEX('Tax Rates &amp; Assumptions'!T$81:T$1080,L48)</f>
-        <v/>
+        <v>150000</v>
       </c>
       <c r="N73" s="33">
         <f>INDEX('Tax Rates &amp; Assumptions'!U$81:U$1080,L48)</f>
-        <v/>
+        <v>500000</v>
       </c>
     </row>
     <row r="74" hidden="1" outlineLevel="1">
       <c r="L74" s="32">
         <f>INDEX('Tax Rates &amp; Assumptions'!V$81:V$1080,L48)</f>
-        <v/>
+        <v>0.0897</v>
       </c>
       <c r="M74" s="33">
         <f>INDEX('Tax Rates &amp; Assumptions'!W$81:W$1080,L48)</f>
-        <v/>
+        <v>500000</v>
       </c>
       <c r="N74" s="33">
         <f>INDEX('Tax Rates &amp; Assumptions'!X$81:X$1080,L48)</f>
-        <v/>
+        <v>1000000</v>
       </c>
     </row>
     <row r="75" hidden="1" outlineLevel="1">
       <c r="L75" s="32">
         <f>INDEX('Tax Rates &amp; Assumptions'!Y$81:Y$1080,L48)</f>
-        <v/>
+        <v>0.1075</v>
       </c>
       <c r="M75" s="33">
         <f>INDEX('Tax Rates &amp; Assumptions'!Z$81:Z$1080,L48)</f>
-        <v/>
+        <v>1000000</v>
       </c>
       <c r="N75" s="33">
         <f>INDEX('Tax Rates &amp; Assumptions'!AA$81:AA$1080,L48)</f>
-        <v/>
+        <v>999999999</v>
       </c>
     </row>
     <row r="76" hidden="1" outlineLevel="1"/>
@@ -2008,9 +2008,9 @@
           <t>Single</t>
         </is>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="7" t="str">
         <f>A6&amp;"|"&amp;B6</f>
-        <v/>
+        <v>2024|Single</v>
       </c>
       <c r="D6" s="8" t="n">
         <v>0.1</v>
@@ -2020,7 +2020,7 @@
       </c>
       <c r="F6" s="10">
         <f>H6</f>
-        <v/>
+        <v>11600</v>
       </c>
       <c r="G6" s="8" t="n">
         <v>0.12</v>
@@ -2030,7 +2030,7 @@
       </c>
       <c r="I6" s="10">
         <f>K6</f>
-        <v/>
+        <v>47150</v>
       </c>
       <c r="J6" s="8" t="n">
         <v>0.22</v>
@@ -2040,7 +2040,7 @@
       </c>
       <c r="L6" s="10">
         <f>N6</f>
-        <v/>
+        <v>100525</v>
       </c>
       <c r="M6" s="8" t="n">
         <v>0.24</v>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="O6" s="10">
         <f>Q6</f>
-        <v/>
+        <v>191950</v>
       </c>
       <c r="P6" s="8" t="n">
         <v>0.32</v>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="R6" s="10">
         <f>T6</f>
-        <v/>
+        <v>243725</v>
       </c>
       <c r="S6" s="8" t="n">
         <v>0.35</v>
@@ -2070,7 +2070,7 @@
       </c>
       <c r="U6" s="10">
         <f>W6</f>
-        <v/>
+        <v>609350</v>
       </c>
       <c r="V6" s="8" t="n">
         <v>0.37</v>
@@ -2091,9 +2091,9 @@
           <t>Married Filing Jointly</t>
         </is>
       </c>
-      <c r="C7" s="7">
+      <c r="C7" s="7" t="str">
         <f>A7&amp;"|"&amp;B7</f>
-        <v/>
+        <v>2024|Married Filing Jointly</v>
       </c>
       <c r="D7" s="8" t="n">
         <v>0.1</v>
@@ -2103,7 +2103,7 @@
       </c>
       <c r="F7" s="10">
         <f>H7</f>
-        <v/>
+        <v>23200</v>
       </c>
       <c r="G7" s="8" t="n">
         <v>0.12</v>
@@ -2113,7 +2113,7 @@
       </c>
       <c r="I7" s="10">
         <f>K7</f>
-        <v/>
+        <v>94300</v>
       </c>
       <c r="J7" s="8" t="n">
         <v>0.22</v>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="L7" s="10">
         <f>N7</f>
-        <v/>
+        <v>201050</v>
       </c>
       <c r="M7" s="8" t="n">
         <v>0.24</v>
@@ -2133,7 +2133,7 @@
       </c>
       <c r="O7" s="10">
         <f>Q7</f>
-        <v/>
+        <v>383900</v>
       </c>
       <c r="P7" s="8" t="n">
         <v>0.32</v>
@@ -2143,7 +2143,7 @@
       </c>
       <c r="R7" s="10">
         <f>T7</f>
-        <v/>
+        <v>487450</v>
       </c>
       <c r="S7" s="8" t="n">
         <v>0.35</v>
@@ -2153,7 +2153,7 @@
       </c>
       <c r="U7" s="10">
         <f>W7</f>
-        <v/>
+        <v>731200</v>
       </c>
       <c r="V7" s="8" t="n">
         <v>0.37</v>
@@ -2174,9 +2174,9 @@
           <t>Married Filing Separately</t>
         </is>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="7" t="str">
         <f>A8&amp;"|"&amp;B8</f>
-        <v/>
+        <v>2024|Married Filing Separately</v>
       </c>
       <c r="D8" s="8" t="n">
         <v>0.1</v>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F8" s="10">
         <f>H8</f>
-        <v/>
+        <v>11600</v>
       </c>
       <c r="G8" s="8" t="n">
         <v>0.12</v>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="I8" s="10">
         <f>K8</f>
-        <v/>
+        <v>47150</v>
       </c>
       <c r="J8" s="8" t="n">
         <v>0.22</v>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="L8" s="10">
         <f>N8</f>
-        <v/>
+        <v>100525</v>
       </c>
       <c r="M8" s="8" t="n">
         <v>0.24</v>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O8" s="10">
         <f>Q8</f>
-        <v/>
+        <v>191950</v>
       </c>
       <c r="P8" s="8" t="n">
         <v>0.32</v>
@@ -2226,7 +2226,7 @@
       </c>
       <c r="R8" s="10">
         <f>T8</f>
-        <v/>
+        <v>243725</v>
       </c>
       <c r="S8" s="8" t="n">
         <v>0.35</v>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="U8" s="10">
         <f>W8</f>
-        <v/>
+        <v>365600</v>
       </c>
       <c r="V8" s="8" t="n">
         <v>0.37</v>
@@ -2257,9 +2257,9 @@
           <t>Head of Household</t>
         </is>
       </c>
-      <c r="C9" s="7">
+      <c r="C9" s="7" t="str">
         <f>A9&amp;"|"&amp;B9</f>
-        <v/>
+        <v>2024|Head of Household</v>
       </c>
       <c r="D9" s="8" t="n">
         <v>0.1</v>
@@ -2269,7 +2269,7 @@
       </c>
       <c r="F9" s="10">
         <f>H9</f>
-        <v/>
+        <v>16550</v>
       </c>
       <c r="G9" s="8" t="n">
         <v>0.12</v>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="I9" s="10">
         <f>K9</f>
-        <v/>
+        <v>63100</v>
       </c>
       <c r="J9" s="8" t="n">
         <v>0.22</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="L9" s="10">
         <f>N9</f>
-        <v/>
+        <v>100500</v>
       </c>
       <c r="M9" s="8" t="n">
         <v>0.24</v>
@@ -2299,7 +2299,7 @@
       </c>
       <c r="O9" s="10">
         <f>Q9</f>
-        <v/>
+        <v>191950</v>
       </c>
       <c r="P9" s="8" t="n">
         <v>0.32</v>
@@ -2309,7 +2309,7 @@
       </c>
       <c r="R9" s="10">
         <f>T9</f>
-        <v/>
+        <v>243700</v>
       </c>
       <c r="S9" s="8" t="n">
         <v>0.35</v>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="U9" s="10">
         <f>W9</f>
-        <v/>
+        <v>609350</v>
       </c>
       <c r="V9" s="8" t="n">
         <v>0.37</v>
@@ -2340,9 +2340,9 @@
           <t>Single</t>
         </is>
       </c>
-      <c r="C10" s="7">
+      <c r="C10" s="7" t="str">
         <f>A10&amp;"|"&amp;B10</f>
-        <v/>
+        <v>2025|Single</v>
       </c>
       <c r="D10" s="8" t="n">
         <v>0.1</v>
@@ -2352,7 +2352,7 @@
       </c>
       <c r="F10" s="10">
         <f>H10</f>
-        <v/>
+        <v>11925</v>
       </c>
       <c r="G10" s="8" t="n">
         <v>0.12</v>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="I10" s="10">
         <f>K10</f>
-        <v/>
+        <v>48475</v>
       </c>
       <c r="J10" s="8" t="n">
         <v>0.22</v>
@@ -2372,7 +2372,7 @@
       </c>
       <c r="L10" s="10">
         <f>N10</f>
-        <v/>
+        <v>103350</v>
       </c>
       <c r="M10" s="8" t="n">
         <v>0.24</v>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="O10" s="10">
         <f>Q10</f>
-        <v/>
+        <v>197300</v>
       </c>
       <c r="P10" s="8" t="n">
         <v>0.32</v>
@@ -2392,7 +2392,7 @@
       </c>
       <c r="R10" s="10">
         <f>T10</f>
-        <v/>
+        <v>250525</v>
       </c>
       <c r="S10" s="8" t="n">
         <v>0.35</v>
@@ -2402,7 +2402,7 @@
       </c>
       <c r="U10" s="10">
         <f>W10</f>
-        <v/>
+        <v>626350</v>
       </c>
       <c r="V10" s="8" t="n">
         <v>0.37</v>
@@ -2423,9 +2423,9 @@
           <t>Married Filing Jointly</t>
         </is>
       </c>
-      <c r="C11" s="7">
+      <c r="C11" s="7" t="str">
         <f>A11&amp;"|"&amp;B11</f>
-        <v/>
+        <v>2025|Married Filing Jointly</v>
       </c>
       <c r="D11" s="8" t="n">
         <v>0.1</v>
@@ -2435,7 +2435,7 @@
       </c>
       <c r="F11" s="10">
         <f>H11</f>
-        <v/>
+        <v>23850</v>
       </c>
       <c r="G11" s="8" t="n">
         <v>0.12</v>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="I11" s="10">
         <f>K11</f>
-        <v/>
+        <v>96950</v>
       </c>
       <c r="J11" s="8" t="n">
         <v>0.22</v>
@@ -2455,7 +2455,7 @@
       </c>
       <c r="L11" s="10">
         <f>N11</f>
-        <v/>
+        <v>206700</v>
       </c>
       <c r="M11" s="8" t="n">
         <v>0.24</v>
@@ -2465,7 +2465,7 @@
       </c>
       <c r="O11" s="10">
         <f>Q11</f>
-        <v/>
+        <v>394600</v>
       </c>
       <c r="P11" s="8" t="n">
         <v>0.32</v>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="R11" s="10">
         <f>T11</f>
-        <v/>
+        <v>501050</v>
       </c>
       <c r="S11" s="8" t="n">
         <v>0.35</v>
@@ -2485,7 +2485,7 @@
       </c>
       <c r="U11" s="10">
         <f>W11</f>
-        <v/>
+        <v>751600</v>
       </c>
       <c r="V11" s="8" t="n">
         <v>0.37</v>
@@ -2506,9 +2506,9 @@
           <t>Married Filing Separately</t>
         </is>
       </c>
-      <c r="C12" s="7">
+      <c r="C12" s="7" t="str">
         <f>A12&amp;"|"&amp;B12</f>
-        <v/>
+        <v>2025|Married Filing Separately</v>
       </c>
       <c r="D12" s="8" t="n">
         <v>0.1</v>
@@ -2518,7 +2518,7 @@
       </c>
       <c r="F12" s="10">
         <f>H12</f>
-        <v/>
+        <v>11925</v>
       </c>
       <c r="G12" s="8" t="n">
         <v>0.12</v>
@@ -2528,7 +2528,7 @@
       </c>
       <c r="I12" s="10">
         <f>K12</f>
-        <v/>
+        <v>48475</v>
       </c>
       <c r="J12" s="8" t="n">
         <v>0.22</v>
@@ -2538,7 +2538,7 @@
       </c>
       <c r="L12" s="10">
         <f>N12</f>
-        <v/>
+        <v>103350</v>
       </c>
       <c r="M12" s="8" t="n">
         <v>0.24</v>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="O12" s="10">
         <f>Q12</f>
-        <v/>
+        <v>197300</v>
       </c>
       <c r="P12" s="8" t="n">
         <v>0.32</v>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="R12" s="10">
         <f>T12</f>
-        <v/>
+        <v>250525</v>
       </c>
       <c r="S12" s="8" t="n">
         <v>0.35</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="U12" s="10">
         <f>W12</f>
-        <v/>
+        <v>375800</v>
       </c>
       <c r="V12" s="8" t="n">
         <v>0.37</v>
@@ -2589,9 +2589,9 @@
           <t>Head of Household</t>
         </is>
       </c>
-      <c r="C13" s="7">
+      <c r="C13" s="7" t="str">
         <f>A13&amp;"|"&amp;B13</f>
-        <v/>
+        <v>2025|Head of Household</v>
       </c>
       <c r="D13" s="8" t="n">
         <v>0.1</v>
@@ -2601,7 +2601,7 @@
       </c>
       <c r="F13" s="10">
         <f>H13</f>
-        <v/>
+        <v>17000</v>
       </c>
       <c r="G13" s="8" t="n">
         <v>0.12</v>
@@ -2611,7 +2611,7 @@
       </c>
       <c r="I13" s="10">
         <f>K13</f>
-        <v/>
+        <v>64850</v>
       </c>
       <c r="J13" s="8" t="n">
         <v>0.22</v>
@@ -2621,7 +2621,7 @@
       </c>
       <c r="L13" s="10">
         <f>N13</f>
-        <v/>
+        <v>103350</v>
       </c>
       <c r="M13" s="8" t="n">
         <v>0.24</v>
@@ -2631,7 +2631,7 @@
       </c>
       <c r="O13" s="10">
         <f>Q13</f>
-        <v/>
+        <v>197300</v>
       </c>
       <c r="P13" s="8" t="n">
         <v>0.32</v>
@@ -2641,7 +2641,7 @@
       </c>
       <c r="R13" s="10">
         <f>T13</f>
-        <v/>
+        <v>250500</v>
       </c>
       <c r="S13" s="8" t="n">
         <v>0.35</v>
@@ -2651,7 +2651,7 @@
       </c>
       <c r="U13" s="10">
         <f>W13</f>
-        <v/>
+        <v>626350</v>
       </c>
       <c r="V13" s="8" t="n">
         <v>0.37</v>
@@ -2764,9 +2764,9 @@
           <t>Single</t>
         </is>
       </c>
-      <c r="C17" s="7">
+      <c r="C17" s="7" t="str">
         <f>A17&amp;"|"&amp;B17</f>
-        <v/>
+        <v>2024|Single</v>
       </c>
       <c r="D17" s="8" t="n">
         <v>0</v>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="F17" s="10">
         <f>H17</f>
-        <v/>
+        <v>47025</v>
       </c>
       <c r="G17" s="8" t="n">
         <v>0.15</v>
@@ -2786,7 +2786,7 @@
       </c>
       <c r="I17" s="10">
         <f>K17</f>
-        <v/>
+        <v>518900</v>
       </c>
       <c r="J17" s="8" t="n">
         <v>0.2</v>
@@ -2807,9 +2807,9 @@
           <t>Married Filing Jointly</t>
         </is>
       </c>
-      <c r="C18" s="7">
+      <c r="C18" s="7" t="str">
         <f>A18&amp;"|"&amp;B18</f>
-        <v/>
+        <v>2024|Married Filing Jointly</v>
       </c>
       <c r="D18" s="8" t="n">
         <v>0</v>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="F18" s="10">
         <f>H18</f>
-        <v/>
+        <v>94050</v>
       </c>
       <c r="G18" s="8" t="n">
         <v>0.15</v>
@@ -2829,7 +2829,7 @@
       </c>
       <c r="I18" s="10">
         <f>K18</f>
-        <v/>
+        <v>583750</v>
       </c>
       <c r="J18" s="8" t="n">
         <v>0.2</v>
@@ -2850,9 +2850,9 @@
           <t>Married Filing Separately</t>
         </is>
       </c>
-      <c r="C19" s="7">
+      <c r="C19" s="7" t="str">
         <f>A19&amp;"|"&amp;B19</f>
-        <v/>
+        <v>2024|Married Filing Separately</v>
       </c>
       <c r="D19" s="8" t="n">
         <v>0</v>
@@ -2862,7 +2862,7 @@
       </c>
       <c r="F19" s="10">
         <f>H19</f>
-        <v/>
+        <v>47025</v>
       </c>
       <c r="G19" s="8" t="n">
         <v>0.15</v>
@@ -2872,7 +2872,7 @@
       </c>
       <c r="I19" s="10">
         <f>K19</f>
-        <v/>
+        <v>291850</v>
       </c>
       <c r="J19" s="8" t="n">
         <v>0.2</v>
@@ -2893,9 +2893,9 @@
           <t>Head of Household</t>
         </is>
       </c>
-      <c r="C20" s="7">
+      <c r="C20" s="7" t="str">
         <f>A20&amp;"|"&amp;B20</f>
-        <v/>
+        <v>2024|Head of Household</v>
       </c>
       <c r="D20" s="8" t="n">
         <v>0</v>
@@ -2905,7 +2905,7 @@
       </c>
       <c r="F20" s="10">
         <f>H20</f>
-        <v/>
+        <v>63000</v>
       </c>
       <c r="G20" s="8" t="n">
         <v>0.15</v>
@@ -2915,7 +2915,7 @@
       </c>
       <c r="I20" s="10">
         <f>K20</f>
-        <v/>
+        <v>551350</v>
       </c>
       <c r="J20" s="8" t="n">
         <v>0.2</v>
@@ -2936,9 +2936,9 @@
           <t>Single</t>
         </is>
       </c>
-      <c r="C21" s="7">
+      <c r="C21" s="7" t="str">
         <f>A21&amp;"|"&amp;B21</f>
-        <v/>
+        <v>2025|Single</v>
       </c>
       <c r="D21" s="8" t="n">
         <v>0</v>
@@ -2948,7 +2948,7 @@
       </c>
       <c r="F21" s="10">
         <f>H21</f>
-        <v/>
+        <v>48350</v>
       </c>
       <c r="G21" s="8" t="n">
         <v>0.15</v>
@@ -2958,7 +2958,7 @@
       </c>
       <c r="I21" s="10">
         <f>K21</f>
-        <v/>
+        <v>533400</v>
       </c>
       <c r="J21" s="8" t="n">
         <v>0.2</v>
@@ -2979,9 +2979,9 @@
           <t>Married Filing Jointly</t>
         </is>
       </c>
-      <c r="C22" s="7">
+      <c r="C22" s="7" t="str">
         <f>A22&amp;"|"&amp;B22</f>
-        <v/>
+        <v>2025|Married Filing Jointly</v>
       </c>
       <c r="D22" s="8" t="n">
         <v>0</v>
@@ -2991,7 +2991,7 @@
       </c>
       <c r="F22" s="10">
         <f>H22</f>
-        <v/>
+        <v>96700</v>
       </c>
       <c r="G22" s="8" t="n">
         <v>0.15</v>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="I22" s="10">
         <f>K22</f>
-        <v/>
+        <v>600050</v>
       </c>
       <c r="J22" s="8" t="n">
         <v>0.2</v>
@@ -3022,9 +3022,9 @@
           <t>Married Filing Separately</t>
         </is>
       </c>
-      <c r="C23" s="7">
+      <c r="C23" s="7" t="str">
         <f>A23&amp;"|"&amp;B23</f>
-        <v/>
+        <v>2025|Married Filing Separately</v>
       </c>
       <c r="D23" s="8" t="n">
         <v>0</v>
@@ -3034,7 +3034,7 @@
       </c>
       <c r="F23" s="10">
         <f>H23</f>
-        <v/>
+        <v>48350</v>
       </c>
       <c r="G23" s="8" t="n">
         <v>0.15</v>
@@ -3044,7 +3044,7 @@
       </c>
       <c r="I23" s="10">
         <f>K23</f>
-        <v/>
+        <v>300000</v>
       </c>
       <c r="J23" s="8" t="n">
         <v>0.2</v>
@@ -3065,9 +3065,9 @@
           <t>Head of Household</t>
         </is>
       </c>
-      <c r="C24" s="7">
+      <c r="C24" s="7" t="str">
         <f>A24&amp;"|"&amp;B24</f>
-        <v/>
+        <v>2025|Head of Household</v>
       </c>
       <c r="D24" s="8" t="n">
         <v>0</v>
@@ -3077,7 +3077,7 @@
       </c>
       <c r="F24" s="10">
         <f>H24</f>
-        <v/>
+        <v>64750</v>
       </c>
       <c r="G24" s="8" t="n">
         <v>0.15</v>
@@ -3087,7 +3087,7 @@
       </c>
       <c r="I24" s="10">
         <f>K24</f>
-        <v/>
+        <v>566700</v>
       </c>
       <c r="J24" s="8" t="n">
         <v>0.2</v>
@@ -3160,9 +3160,9 @@
           <t>Single</t>
         </is>
       </c>
-      <c r="C28" s="7">
+      <c r="C28" s="7" t="str">
         <f>A28&amp;"|"&amp;B28</f>
-        <v/>
+        <v>2024|Single</v>
       </c>
       <c r="D28" s="13" t="n">
         <v>14600</v>
@@ -3177,9 +3177,9 @@
           <t>Married Filing Jointly</t>
         </is>
       </c>
-      <c r="C29" s="7">
+      <c r="C29" s="7" t="str">
         <f>A29&amp;"|"&amp;B29</f>
-        <v/>
+        <v>2024|Married Filing Jointly</v>
       </c>
       <c r="D29" s="13" t="n">
         <v>29200</v>
@@ -3194,9 +3194,9 @@
           <t>Married Filing Separately</t>
         </is>
       </c>
-      <c r="C30" s="7">
+      <c r="C30" s="7" t="str">
         <f>A30&amp;"|"&amp;B30</f>
-        <v/>
+        <v>2024|Married Filing Separately</v>
       </c>
       <c r="D30" s="13" t="n">
         <v>14600</v>
@@ -3211,9 +3211,9 @@
           <t>Head of Household</t>
         </is>
       </c>
-      <c r="C31" s="7">
+      <c r="C31" s="7" t="str">
         <f>A31&amp;"|"&amp;B31</f>
-        <v/>
+        <v>2024|Head of Household</v>
       </c>
       <c r="D31" s="13" t="n">
         <v>21900</v>
@@ -3228,9 +3228,9 @@
           <t>Single</t>
         </is>
       </c>
-      <c r="C32" s="7">
+      <c r="C32" s="7" t="str">
         <f>A32&amp;"|"&amp;B32</f>
-        <v/>
+        <v>2025|Single</v>
       </c>
       <c r="D32" s="13" t="n">
         <v>15000</v>
@@ -3245,9 +3245,9 @@
           <t>Married Filing Jointly</t>
         </is>
       </c>
-      <c r="C33" s="7">
+      <c r="C33" s="7" t="str">
         <f>A33&amp;"|"&amp;B33</f>
-        <v/>
+        <v>2025|Married Filing Jointly</v>
       </c>
       <c r="D33" s="13" t="n">
         <v>30000</v>
@@ -3262,9 +3262,9 @@
           <t>Married Filing Separately</t>
         </is>
       </c>
-      <c r="C34" s="7">
+      <c r="C34" s="7" t="str">
         <f>A34&amp;"|"&amp;B34</f>
-        <v/>
+        <v>2025|Married Filing Separately</v>
       </c>
       <c r="D34" s="13" t="n">
         <v>15000</v>
@@ -3279,9 +3279,9 @@
           <t>Head of Household</t>
         </is>
       </c>
-      <c r="C35" s="7">
+      <c r="C35" s="7" t="str">
         <f>A35&amp;"|"&amp;B35</f>
-        <v/>
+        <v>2025|Head of Household</v>
       </c>
       <c r="D35" s="13" t="n">
         <v>22500</v>
@@ -4704,9 +4704,9 @@
           <t>Single</t>
         </is>
       </c>
-      <c r="C81" s="7">
+      <c r="C81" s="7" t="str">
         <f>A81&amp;"|"&amp;B81</f>
-        <v/>
+        <v>FL|Single</v>
       </c>
       <c r="D81" s="14" t="n">
         <v>0</v>
@@ -4716,7 +4716,7 @@
       </c>
       <c r="F81" s="10">
         <f>H81</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="G81" s="14" t="n">
         <v>0</v>
@@ -4726,7 +4726,7 @@
       </c>
       <c r="I81" s="10">
         <f>K81</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="J81" s="14" t="n">
         <v>0</v>
@@ -4736,7 +4736,7 @@
       </c>
       <c r="L81" s="10">
         <f>N81</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="M81" s="14" t="n">
         <v>0</v>
@@ -4746,7 +4746,7 @@
       </c>
       <c r="O81" s="10">
         <f>Q81</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="P81" s="14" t="n">
         <v>0</v>
@@ -4756,7 +4756,7 @@
       </c>
       <c r="R81" s="10">
         <f>T81</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="S81" s="14" t="n">
         <v>0</v>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="U81" s="10">
         <f>W81</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="V81" s="14" t="n">
         <v>0</v>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="X81" s="10">
         <f>Z81</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="Y81" s="14" t="n">
         <v>0</v>
@@ -4799,9 +4799,9 @@
           <t>MFJ</t>
         </is>
       </c>
-      <c r="C82" s="7">
+      <c r="C82" s="7" t="str">
         <f>A82&amp;"|"&amp;B82</f>
-        <v/>
+        <v>FL|MFJ</v>
       </c>
       <c r="D82" s="14" t="n">
         <v>0</v>
@@ -4811,7 +4811,7 @@
       </c>
       <c r="F82" s="10">
         <f>H82</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="G82" s="14" t="n">
         <v>0</v>
@@ -4821,7 +4821,7 @@
       </c>
       <c r="I82" s="10">
         <f>K82</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="J82" s="14" t="n">
         <v>0</v>
@@ -4831,7 +4831,7 @@
       </c>
       <c r="L82" s="10">
         <f>N82</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="M82" s="14" t="n">
         <v>0</v>
@@ -4841,7 +4841,7 @@
       </c>
       <c r="O82" s="10">
         <f>Q82</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="P82" s="14" t="n">
         <v>0</v>
@@ -4851,7 +4851,7 @@
       </c>
       <c r="R82" s="10">
         <f>T82</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="S82" s="14" t="n">
         <v>0</v>
@@ -4861,7 +4861,7 @@
       </c>
       <c r="U82" s="10">
         <f>W82</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="V82" s="14" t="n">
         <v>0</v>
@@ -4871,7 +4871,7 @@
       </c>
       <c r="X82" s="10">
         <f>Z82</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="Y82" s="14" t="n">
         <v>0</v>
@@ -4894,9 +4894,9 @@
           <t>Single</t>
         </is>
       </c>
-      <c r="C83" s="7">
+      <c r="C83" s="7" t="str">
         <f>A83&amp;"|"&amp;B83</f>
-        <v/>
+        <v>TX|Single</v>
       </c>
       <c r="D83" s="14" t="n">
         <v>0</v>
@@ -4906,7 +4906,7 @@
       </c>
       <c r="F83" s="10">
         <f>H83</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="G83" s="14" t="n">
         <v>0</v>
@@ -4916,7 +4916,7 @@
       </c>
       <c r="I83" s="10">
         <f>K83</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="J83" s="14" t="n">
         <v>0</v>
@@ -4926,7 +4926,7 @@
       </c>
       <c r="L83" s="10">
         <f>N83</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="M83" s="14" t="n">
         <v>0</v>
@@ -4936,7 +4936,7 @@
       </c>
       <c r="O83" s="10">
         <f>Q83</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="P83" s="14" t="n">
         <v>0</v>
@@ -4946,7 +4946,7 @@
       </c>
       <c r="R83" s="10">
         <f>T83</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="S83" s="14" t="n">
         <v>0</v>
@@ -4956,7 +4956,7 @@
       </c>
       <c r="U83" s="10">
         <f>W83</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="V83" s="14" t="n">
         <v>0</v>
@@ -4966,7 +4966,7 @@
       </c>
       <c r="X83" s="10">
         <f>Z83</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="Y83" s="14" t="n">
         <v>0</v>
@@ -4989,9 +4989,9 @@
           <t>MFJ</t>
         </is>
       </c>
-      <c r="C84" s="7">
+      <c r="C84" s="7" t="str">
         <f>A84&amp;"|"&amp;B84</f>
-        <v/>
+        <v>TX|MFJ</v>
       </c>
       <c r="D84" s="14" t="n">
         <v>0</v>
@@ -5001,7 +5001,7 @@
       </c>
       <c r="F84" s="10">
         <f>H84</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="G84" s="14" t="n">
         <v>0</v>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="I84" s="10">
         <f>K84</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="J84" s="14" t="n">
         <v>0</v>
@@ -5021,7 +5021,7 @@
       </c>
       <c r="L84" s="10">
         <f>N84</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="M84" s="14" t="n">
         <v>0</v>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="O84" s="10">
         <f>Q84</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="P84" s="14" t="n">
         <v>0</v>
@@ -5041,7 +5041,7 @@
       </c>
       <c r="R84" s="10">
         <f>T84</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="S84" s="14" t="n">
         <v>0</v>
@@ -5051,7 +5051,7 @@
       </c>
       <c r="U84" s="10">
         <f>W84</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="V84" s="14" t="n">
         <v>0</v>
@@ -5061,7 +5061,7 @@
       </c>
       <c r="X84" s="10">
         <f>Z84</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="Y84" s="14" t="n">
         <v>0</v>
@@ -5084,9 +5084,9 @@
           <t>Single</t>
         </is>
       </c>
-      <c r="C85" s="7">
+      <c r="C85" s="7" t="str">
         <f>A85&amp;"|"&amp;B85</f>
-        <v/>
+        <v>WA|Single</v>
       </c>
       <c r="D85" s="14" t="n">
         <v>0</v>
@@ -5096,7 +5096,7 @@
       </c>
       <c r="F85" s="10">
         <f>H85</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="G85" s="14" t="n">
         <v>0</v>
@@ -5106,7 +5106,7 @@
       </c>
       <c r="I85" s="10">
         <f>K85</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="J85" s="14" t="n">
         <v>0</v>
@@ -5116,7 +5116,7 @@
       </c>
       <c r="L85" s="10">
         <f>N85</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="M85" s="14" t="n">
         <v>0</v>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="O85" s="10">
         <f>Q85</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="P85" s="14" t="n">
         <v>0</v>
@@ -5136,7 +5136,7 @@
       </c>
       <c r="R85" s="10">
         <f>T85</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="S85" s="14" t="n">
         <v>0</v>
@@ -5146,7 +5146,7 @@
       </c>
       <c r="U85" s="10">
         <f>W85</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="V85" s="14" t="n">
         <v>0</v>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="X85" s="10">
         <f>Z85</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="Y85" s="14" t="n">
         <v>0</v>
@@ -5179,9 +5179,9 @@
           <t>MFJ</t>
         </is>
       </c>
-      <c r="C86" s="7">
+      <c r="C86" s="7" t="str">
         <f>A86&amp;"|"&amp;B86</f>
-        <v/>
+        <v>WA|MFJ</v>
       </c>
       <c r="D86" s="14" t="n">
         <v>0</v>
@@ -5191,7 +5191,7 @@
       </c>
       <c r="F86" s="10">
         <f>H86</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="G86" s="14" t="n">
         <v>0</v>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="I86" s="10">
         <f>K86</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="J86" s="14" t="n">
         <v>0</v>
@@ -5211,7 +5211,7 @@
       </c>
       <c r="L86" s="10">
         <f>N86</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="M86" s="14" t="n">
         <v>0</v>
@@ -5221,7 +5221,7 @@
       </c>
       <c r="O86" s="10">
         <f>Q86</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="P86" s="14" t="n">
         <v>0</v>
@@ -5231,7 +5231,7 @@
       </c>
       <c r="R86" s="10">
         <f>T86</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="S86" s="14" t="n">
         <v>0</v>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="U86" s="10">
         <f>W86</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="V86" s="14" t="n">
         <v>0</v>
@@ -5251,7 +5251,7 @@
       </c>
       <c r="X86" s="10">
         <f>Z86</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="Y86" s="14" t="n">
         <v>0</v>
@@ -5274,9 +5274,9 @@
           <t>Single</t>
         </is>
       </c>
-      <c r="C87" s="7">
+      <c r="C87" s="7" t="str">
         <f>A87&amp;"|"&amp;B87</f>
-        <v/>
+        <v>NV|Single</v>
       </c>
       <c r="D87" s="14" t="n">
         <v>0</v>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="F87" s="10">
         <f>H87</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="G87" s="14" t="n">
         <v>0</v>
@@ -5296,7 +5296,7 @@
       </c>
       <c r="I87" s="10">
         <f>K87</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="J87" s="14" t="n">
         <v>0</v>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="L87" s="10">
         <f>N87</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="M87" s="14" t="n">
         <v>0</v>
@@ -5316,7 +5316,7 @@
       </c>
       <c r="O87" s="10">
         <f>Q87</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="P87" s="14" t="n">
         <v>0</v>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="R87" s="10">
         <f>T87</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="S87" s="14" t="n">
         <v>0</v>
@@ -5336,7 +5336,7 @@
       </c>
       <c r="U87" s="10">
         <f>W87</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="V87" s="14" t="n">
         <v>0</v>
@@ -5346,7 +5346,7 @@
       </c>
       <c r="X87" s="10">
         <f>Z87</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="Y87" s="14" t="n">
         <v>0</v>
@@ -5369,9 +5369,9 @@
           <t>MFJ</t>
         </is>
       </c>
-      <c r="C88" s="7">
+      <c r="C88" s="7" t="str">
         <f>A88&amp;"|"&amp;B88</f>
-        <v/>
+        <v>NV|MFJ</v>
       </c>
       <c r="D88" s="14" t="n">
         <v>0</v>
@@ -5381,7 +5381,7 @@
       </c>
       <c r="F88" s="10">
         <f>H88</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="G88" s="14" t="n">
         <v>0</v>
@@ -5391,7 +5391,7 @@
       </c>
       <c r="I88" s="10">
         <f>K88</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="J88" s="14" t="n">
         <v>0</v>
@@ -5401,7 +5401,7 @@
       </c>
       <c r="L88" s="10">
         <f>N88</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="M88" s="14" t="n">
         <v>0</v>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="O88" s="10">
         <f>Q88</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="P88" s="14" t="n">
         <v>0</v>
@@ -5421,7 +5421,7 @@
       </c>
       <c r="R88" s="10">
         <f>T88</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="S88" s="14" t="n">
         <v>0</v>
@@ -5431,7 +5431,7 @@
       </c>
       <c r="U88" s="10">
         <f>W88</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="V88" s="14" t="n">
         <v>0</v>
@@ -5441,7 +5441,7 @@
       </c>
       <c r="X88" s="10">
         <f>Z88</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="Y88" s="14" t="n">
         <v>0</v>
@@ -5464,9 +5464,9 @@
           <t>Single</t>
         </is>
       </c>
-      <c r="C89" s="7">
+      <c r="C89" s="7" t="str">
         <f>A89&amp;"|"&amp;B89</f>
-        <v/>
+        <v>WY|Single</v>
       </c>
       <c r="D89" s="14" t="n">
         <v>0</v>
@@ -5476,7 +5476,7 @@
       </c>
       <c r="F89" s="10">
         <f>H89</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="G89" s="14" t="n">
         <v>0</v>
@@ -5486,7 +5486,7 @@
       </c>
       <c r="I89" s="10">
         <f>K89</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="J89" s="14" t="n">
         <v>0</v>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="L89" s="10">
         <f>N89</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="M89" s="14" t="n">
         <v>0</v>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="O89" s="10">
         <f>Q89</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="P89" s="14" t="n">
         <v>0</v>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="R89" s="10">
         <f>T89</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="S89" s="14" t="n">
         <v>0</v>
@@ -5526,7 +5526,7 @@
       </c>
       <c r="U89" s="10">
         <f>W89</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="V89" s="14" t="n">
         <v>0</v>
@@ -5536,7 +5536,7 @@
       </c>
       <c r="X89" s="10">
         <f>Z89</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="Y89" s="14" t="n">
         <v>0</v>
@@ -5559,9 +5559,9 @@
           <t>MFJ</t>
         </is>
       </c>
-      <c r="C90" s="7">
+      <c r="C90" s="7" t="str">
         <f>A90&amp;"|"&amp;B90</f>
-        <v/>
+        <v>WY|MFJ</v>
       </c>
       <c r="D90" s="14" t="n">
         <v>0</v>
@@ -5571,7 +5571,7 @@
       </c>
       <c r="F90" s="10">
         <f>H90</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="G90" s="14" t="n">
         <v>0</v>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="I90" s="10">
         <f>K90</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="J90" s="14" t="n">
         <v>0</v>
@@ -5591,7 +5591,7 @@
       </c>
       <c r="L90" s="10">
         <f>N90</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="M90" s="14" t="n">
         <v>0</v>
@@ -5601,7 +5601,7 @@
       </c>
       <c r="O90" s="10">
         <f>Q90</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="P90" s="14" t="n">
         <v>0</v>
@@ -5611,7 +5611,7 @@
       </c>
       <c r="R90" s="10">
         <f>T90</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="S90" s="14" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="U90" s="10">
         <f>W90</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="V90" s="14" t="n">
         <v>0</v>
@@ -5631,7 +5631,7 @@
       </c>
       <c r="X90" s="10">
         <f>Z90</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="Y90" s="14" t="n">
         <v>0</v>
@@ -5654,9 +5654,9 @@
           <t>Single</t>
         </is>
       </c>
-      <c r="C91" s="7">
+      <c r="C91" s="7" t="str">
         <f>A91&amp;"|"&amp;B91</f>
-        <v/>
+        <v>SD|Single</v>
       </c>
       <c r="D91" s="14" t="n">
         <v>0</v>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="F91" s="10">
         <f>H91</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="G91" s="14" t="n">
         <v>0</v>
@@ -5676,7 +5676,7 @@
       </c>
       <c r="I91" s="10">
         <f>K91</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="J91" s="14" t="n">
         <v>0</v>
@@ -5686,7 +5686,7 @@
       </c>
       <c r="L91" s="10">
         <f>N91</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="M91" s="14" t="n">
         <v>0</v>
@@ -5696,7 +5696,7 @@
       </c>
       <c r="O91" s="10">
         <f>Q91</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="P91" s="14" t="n">
         <v>0</v>
@@ -5706,7 +5706,7 @@
       </c>
       <c r="R91" s="10">
         <f>T91</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="S91" s="14" t="n">
         <v>0</v>
@@ -5716,7 +5716,7 @@
       </c>
       <c r="U91" s="10">
         <f>W91</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="V91" s="14" t="n">
         <v>0</v>
@@ -5726,7 +5726,7 @@
       </c>
       <c r="X91" s="10">
         <f>Z91</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="Y91" s="14" t="n">
         <v>0</v>
@@ -5749,9 +5749,9 @@
           <t>MFJ</t>
         </is>
       </c>
-      <c r="C92" s="7">
+      <c r="C92" s="7" t="str">
         <f>A92&amp;"|"&amp;B92</f>
-        <v/>
+        <v>SD|MFJ</v>
       </c>
       <c r="D92" s="14" t="n">
         <v>0</v>
@@ -5761,7 +5761,7 @@
       </c>
       <c r="F92" s="10">
         <f>H92</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="G92" s="14" t="n">
         <v>0</v>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="I92" s="10">
         <f>K92</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="J92" s="14" t="n">
         <v>0</v>
@@ -5781,7 +5781,7 @@
       </c>
       <c r="L92" s="10">
         <f>N92</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="M92" s="14" t="n">
         <v>0</v>
@@ -5791,7 +5791,7 @@
       </c>
       <c r="O92" s="10">
         <f>Q92</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="P92" s="14" t="n">
         <v>0</v>
@@ -5801,7 +5801,7 @@
       </c>
       <c r="R92" s="10">
         <f>T92</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="S92" s="14" t="n">
         <v>0</v>
@@ -5811,7 +5811,7 @@
       </c>
       <c r="U92" s="10">
         <f>W92</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="V92" s="14" t="n">
         <v>0</v>
@@ -5821,7 +5821,7 @@
       </c>
       <c r="X92" s="10">
         <f>Z92</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="Y92" s="14" t="n">
         <v>0</v>
@@ -5844,9 +5844,9 @@
           <t>Single</t>
         </is>
       </c>
-      <c r="C93" s="7">
+      <c r="C93" s="7" t="str">
         <f>A93&amp;"|"&amp;B93</f>
-        <v/>
+        <v>AK|Single</v>
       </c>
       <c r="D93" s="14" t="n">
         <v>0</v>
@@ -5856,7 +5856,7 @@
       </c>
       <c r="F93" s="10">
         <f>H93</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="G93" s="14" t="n">
         <v>0</v>
@@ -5866,7 +5866,7 @@
       </c>
       <c r="I93" s="10">
         <f>K93</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="J93" s="14" t="n">
         <v>0</v>
@@ -5876,7 +5876,7 @@
       </c>
       <c r="L93" s="10">
         <f>N93</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="M93" s="14" t="n">
         <v>0</v>
@@ -5886,7 +5886,7 @@
       </c>
       <c r="O93" s="10">
         <f>Q93</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="P93" s="14" t="n">
         <v>0</v>
@@ -5896,7 +5896,7 @@
       </c>
       <c r="R93" s="10">
         <f>T93</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="S93" s="14" t="n">
         <v>0</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="U93" s="10">
         <f>W93</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="V93" s="14" t="n">
         <v>0</v>
@@ -5916,7 +5916,7 @@
       </c>
       <c r="X93" s="10">
         <f>Z93</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="Y93" s="14" t="n">
         <v>0</v>
@@ -5939,9 +5939,9 @@
           <t>MFJ</t>
         </is>
       </c>
-      <c r="C94" s="7">
+      <c r="C94" s="7" t="str">
         <f>A94&amp;"|"&amp;B94</f>
-        <v/>
+        <v>AK|MFJ</v>
       </c>
       <c r="D94" s="14" t="n">
         <v>0</v>
@@ -5951,7 +5951,7 @@
       </c>
       <c r="F94" s="10">
         <f>H94</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="G94" s="14" t="n">
         <v>0</v>
@@ -5961,7 +5961,7 @@
       </c>
       <c r="I94" s="10">
         <f>K94</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="J94" s="14" t="n">
         <v>0</v>
@@ -5971,7 +5971,7 @@
       </c>
       <c r="L94" s="10">
         <f>N94</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="M94" s="14" t="n">
         <v>0</v>
@@ -5981,7 +5981,7 @@
       </c>
       <c r="O94" s="10">
         <f>Q94</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="P94" s="14" t="n">
         <v>0</v>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="R94" s="10">
         <f>T94</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="S94" s="14" t="n">
         <v>0</v>
@@ -6001,7 +6001,7 @@
       </c>
       <c r="U94" s="10">
         <f>W94</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="V94" s="14" t="n">
         <v>0</v>
@@ -6011,7 +6011,7 @@
       </c>
       <c r="X94" s="10">
         <f>Z94</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="Y94" s="14" t="n">
         <v>0</v>
@@ -6034,9 +6034,9 @@
           <t>Single</t>
         </is>
       </c>
-      <c r="C95" s="7">
+      <c r="C95" s="7" t="str">
         <f>A95&amp;"|"&amp;B95</f>
-        <v/>
+        <v>TN|Single</v>
       </c>
       <c r="D95" s="14" t="n">
         <v>0</v>
@@ -6046,7 +6046,7 @@
       </c>
       <c r="F95" s="10">
         <f>H95</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="G95" s="14" t="n">
         <v>0</v>
@@ -6056,7 +6056,7 @@
       </c>
       <c r="I95" s="10">
         <f>K95</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="J95" s="14" t="n">
         <v>0</v>
@@ -6066,7 +6066,7 @@
       </c>
       <c r="L95" s="10">
         <f>N95</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="M95" s="14" t="n">
         <v>0</v>
@@ -6076,7 +6076,7 @@
       </c>
       <c r="O95" s="10">
         <f>Q95</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="P95" s="14" t="n">
         <v>0</v>
@@ -6086,7 +6086,7 @@
       </c>
       <c r="R95" s="10">
         <f>T95</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="S95" s="14" t="n">
         <v>0</v>
@@ -6096,7 +6096,7 @@
       </c>
       <c r="U95" s="10">
         <f>W95</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="V95" s="14" t="n">
         <v>0</v>
@@ -6106,7 +6106,7 @@
       </c>
       <c r="X95" s="10">
         <f>Z95</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="Y95" s="14" t="n">
         <v>0</v>
@@ -6129,9 +6129,9 @@
           <t>MFJ</t>
         </is>
       </c>
-      <c r="C96" s="7">
+      <c r="C96" s="7" t="str">
         <f>A96&amp;"|"&amp;B96</f>
-        <v/>
+        <v>TN|MFJ</v>
       </c>
       <c r="D96" s="14" t="n">
         <v>0</v>
@@ -6141,7 +6141,7 @@
       </c>
       <c r="F96" s="10">
         <f>H96</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="G96" s="14" t="n">
         <v>0</v>
@@ -6151,7 +6151,7 @@
       </c>
       <c r="I96" s="10">
         <f>K96</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="J96" s="14" t="n">
         <v>0</v>
@@ -6161,7 +6161,7 @@
       </c>
       <c r="L96" s="10">
         <f>N96</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="M96" s="14" t="n">
         <v>0</v>
@@ -6171,7 +6171,7 @@
       </c>
       <c r="O96" s="10">
         <f>Q96</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="P96" s="14" t="n">
         <v>0</v>
@@ -6181,7 +6181,7 @@
       </c>
       <c r="R96" s="10">
         <f>T96</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="S96" s="14" t="n">
         <v>0</v>
@@ -6191,7 +6191,7 @@
       </c>
       <c r="U96" s="10">
         <f>W96</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="V96" s="14" t="n">
         <v>0</v>
@@ -6201,7 +6201,7 @@
       </c>
       <c r="X96" s="10">
         <f>Z96</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="Y96" s="14" t="n">
         <v>0</v>
@@ -6224,9 +6224,9 @@
           <t>Single</t>
         </is>
       </c>
-      <c r="C97" s="7">
+      <c r="C97" s="7" t="str">
         <f>A97&amp;"|"&amp;B97</f>
-        <v/>
+        <v>CO|Single</v>
       </c>
       <c r="D97" s="14" t="n">
         <v>0.044</v>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="F97" s="10">
         <f>H97</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="G97" s="14" t="n">
         <v>0</v>
@@ -6246,7 +6246,7 @@
       </c>
       <c r="I97" s="10">
         <f>K97</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="J97" s="14" t="n">
         <v>0</v>
@@ -6256,7 +6256,7 @@
       </c>
       <c r="L97" s="10">
         <f>N97</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="M97" s="14" t="n">
         <v>0</v>
@@ -6266,7 +6266,7 @@
       </c>
       <c r="O97" s="10">
         <f>Q97</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="P97" s="14" t="n">
         <v>0</v>
@@ -6276,7 +6276,7 @@
       </c>
       <c r="R97" s="10">
         <f>T97</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="S97" s="14" t="n">
         <v>0</v>
@@ -6286,7 +6286,7 @@
       </c>
       <c r="U97" s="10">
         <f>W97</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="V97" s="14" t="n">
         <v>0</v>
@@ -6296,7 +6296,7 @@
       </c>
       <c r="X97" s="10">
         <f>Z97</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="Y97" s="14" t="n">
         <v>0</v>
@@ -6319,9 +6319,9 @@
           <t>MFJ</t>
         </is>
       </c>
-      <c r="C98" s="7">
+      <c r="C98" s="7" t="str">
         <f>A98&amp;"|"&amp;B98</f>
-        <v/>
+        <v>CO|MFJ</v>
       </c>
       <c r="D98" s="14" t="n">
         <v>0.044</v>
@@ -6331,7 +6331,7 @@
       </c>
       <c r="F98" s="10">
         <f>H98</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="G98" s="14" t="n">
         <v>0</v>
@@ -6341,7 +6341,7 @@
       </c>
       <c r="I98" s="10">
         <f>K98</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="J98" s="14" t="n">
         <v>0</v>
@@ -6351,7 +6351,7 @@
       </c>
       <c r="L98" s="10">
         <f>N98</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="M98" s="14" t="n">
         <v>0</v>
@@ -6361,7 +6361,7 @@
       </c>
       <c r="O98" s="10">
         <f>Q98</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="P98" s="14" t="n">
         <v>0</v>
@@ -6371,7 +6371,7 @@
       </c>
       <c r="R98" s="10">
         <f>T98</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="S98" s="14" t="n">
         <v>0</v>
@@ -6381,7 +6381,7 @@
       </c>
       <c r="U98" s="10">
         <f>W98</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="V98" s="14" t="n">
         <v>0</v>
@@ -6391,7 +6391,7 @@
       </c>
       <c r="X98" s="10">
         <f>Z98</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="Y98" s="14" t="n">
         <v>0</v>
@@ -6414,9 +6414,9 @@
           <t>Single</t>
         </is>
       </c>
-      <c r="C99" s="7">
+      <c r="C99" s="7" t="str">
         <f>A99&amp;"|"&amp;B99</f>
-        <v/>
+        <v>IL|Single</v>
       </c>
       <c r="D99" s="14" t="n">
         <v>0.0495</v>
@@ -6426,7 +6426,7 @@
       </c>
       <c r="F99" s="10">
         <f>H99</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="G99" s="14" t="n">
         <v>0</v>
@@ -6436,7 +6436,7 @@
       </c>
       <c r="I99" s="10">
         <f>K99</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="J99" s="14" t="n">
         <v>0</v>
@@ -6446,7 +6446,7 @@
       </c>
       <c r="L99" s="10">
         <f>N99</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="M99" s="14" t="n">
         <v>0</v>
@@ -6456,7 +6456,7 @@
       </c>
       <c r="O99" s="10">
         <f>Q99</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="P99" s="14" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="R99" s="10">
         <f>T99</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="S99" s="14" t="n">
         <v>0</v>
@@ -6476,7 +6476,7 @@
       </c>
       <c r="U99" s="10">
         <f>W99</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="V99" s="14" t="n">
         <v>0</v>
@@ -6486,7 +6486,7 @@
       </c>
       <c r="X99" s="10">
         <f>Z99</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="Y99" s="14" t="n">
         <v>0</v>
@@ -6509,9 +6509,9 @@
           <t>MFJ</t>
         </is>
       </c>
-      <c r="C100" s="7">
+      <c r="C100" s="7" t="str">
         <f>A100&amp;"|"&amp;B100</f>
-        <v/>
+        <v>IL|MFJ</v>
       </c>
       <c r="D100" s="14" t="n">
         <v>0.0495</v>
@@ -6521,7 +6521,7 @@
       </c>
       <c r="F100" s="10">
         <f>H100</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="G100" s="14" t="n">
         <v>0</v>
@@ -6531,7 +6531,7 @@
       </c>
       <c r="I100" s="10">
         <f>K100</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="J100" s="14" t="n">
         <v>0</v>
@@ -6541,7 +6541,7 @@
       </c>
       <c r="L100" s="10">
         <f>N100</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="M100" s="14" t="n">
         <v>0</v>
@@ -6551,7 +6551,7 @@
       </c>
       <c r="O100" s="10">
         <f>Q100</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="P100" s="14" t="n">
         <v>0</v>
@@ -6561,7 +6561,7 @@
       </c>
       <c r="R100" s="10">
         <f>T100</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="S100" s="14" t="n">
         <v>0</v>
@@ -6571,7 +6571,7 @@
       </c>
       <c r="U100" s="10">
         <f>W100</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="V100" s="14" t="n">
         <v>0</v>
@@ -6581,7 +6581,7 @@
       </c>
       <c r="X100" s="10">
         <f>Z100</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="Y100" s="14" t="n">
         <v>0</v>
@@ -6604,9 +6604,9 @@
           <t>Single</t>
         </is>
       </c>
-      <c r="C101" s="7">
+      <c r="C101" s="7" t="str">
         <f>A101&amp;"|"&amp;B101</f>
-        <v/>
+        <v>IN|Single</v>
       </c>
       <c r="D101" s="14" t="n">
         <v>0.0305</v>
@@ -6616,7 +6616,7 @@
       </c>
       <c r="F101" s="10">
         <f>H101</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="G101" s="14" t="n">
         <v>0</v>
@@ -6626,7 +6626,7 @@
       </c>
       <c r="I101" s="10">
         <f>K101</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="J101" s="14" t="n">
         <v>0</v>
@@ -6636,7 +6636,7 @@
       </c>
       <c r="L101" s="10">
         <f>N101</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="M101" s="14" t="n">
         <v>0</v>
@@ -6646,7 +6646,7 @@
       </c>
       <c r="O101" s="10">
         <f>Q101</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="P101" s="14" t="n">
         <v>0</v>
@@ -6656,7 +6656,7 @@
       </c>
       <c r="R101" s="10">
         <f>T101</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="S101" s="14" t="n">
         <v>0</v>
@@ -6666,7 +6666,7 @@
       </c>
       <c r="U101" s="10">
         <f>W101</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="V101" s="14" t="n">
         <v>0</v>
@@ -6676,7 +6676,7 @@
       </c>
       <c r="X101" s="10">
         <f>Z101</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="Y101" s="14" t="n">
         <v>0</v>
@@ -6699,9 +6699,9 @@
           <t>MFJ</t>
         </is>
       </c>
-      <c r="C102" s="7">
+      <c r="C102" s="7" t="str">
         <f>A102&amp;"|"&amp;B102</f>
-        <v/>
+        <v>IN|MFJ</v>
       </c>
       <c r="D102" s="14" t="n">
         <v>0.0305</v>
@@ -6711,7 +6711,7 @@
       </c>
       <c r="F102" s="10">
         <f>H102</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="G102" s="14" t="n">
         <v>0</v>
@@ -6721,7 +6721,7 @@
       </c>
       <c r="I102" s="10">
         <f>K102</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="J102" s="14" t="n">
         <v>0</v>
@@ -6731,7 +6731,7 @@
       </c>
       <c r="L102" s="10">
         <f>N102</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="M102" s="14" t="n">
         <v>0</v>
@@ -6741,7 +6741,7 @@
       </c>
       <c r="O102" s="10">
         <f>Q102</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="P102" s="14" t="n">
         <v>0</v>
@@ -6751,7 +6751,7 @@
       </c>
       <c r="R102" s="10">
         <f>T102</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="S102" s="14" t="n">
         <v>0</v>
@@ -6761,7 +6761,7 @@
       </c>
       <c r="U102" s="10">
         <f>W102</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="V102" s="14" t="n">
         <v>0</v>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="X102" s="10">
         <f>Z102</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="Y102" s="14" t="n">
         <v>0</v>
@@ -6794,9 +6794,9 @@
           <t>Single</t>
         </is>
       </c>
-      <c r="C103" s="7">
+      <c r="C103" s="7" t="str">
         <f>A103&amp;"|"&amp;B103</f>
-        <v/>
+        <v>MI|Single</v>
       </c>
       <c r="D103" s="14" t="n">
         <v>0.0425</v>
@@ -6806,7 +6806,7 @@
       </c>
       <c r="F103" s="10">
         <f>H103</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="G103" s="14" t="n">
         <v>0</v>
@@ -6816,7 +6816,7 @@
       </c>
       <c r="I103" s="10">
         <f>K103</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="J103" s="14" t="n">
         <v>0</v>
@@ -6826,7 +6826,7 @@
       </c>
       <c r="L103" s="10">
         <f>N103</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="M103" s="14" t="n">
         <v>0</v>
@@ -6836,7 +6836,7 @@
       </c>
       <c r="O103" s="10">
         <f>Q103</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="P103" s="14" t="n">
         <v>0</v>
@@ -6846,7 +6846,7 @@
       </c>
       <c r="R103" s="10">
         <f>T103</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="S103" s="14" t="n">
         <v>0</v>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="U103" s="10">
         <f>W103</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="V103" s="14" t="n">
         <v>0</v>
@@ -6866,7 +6866,7 @@
       </c>
       <c r="X103" s="10">
         <f>Z103</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="Y103" s="14" t="n">
         <v>0</v>
@@ -6889,9 +6889,9 @@
           <t>MFJ</t>
         </is>
       </c>
-      <c r="C104" s="7">
+      <c r="C104" s="7" t="str">
         <f>A104&amp;"|"&amp;B104</f>
-        <v/>
+        <v>MI|MFJ</v>
       </c>
       <c r="D104" s="14" t="n">
         <v>0.0425</v>
@@ -6901,7 +6901,7 @@
       </c>
       <c r="F104" s="10">
         <f>H104</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="G104" s="14" t="n">
         <v>0</v>
@@ -6911,7 +6911,7 @@
       </c>
       <c r="I104" s="10">
         <f>K104</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="J104" s="14" t="n">
         <v>0</v>
@@ -6921,7 +6921,7 @@
       </c>
       <c r="L104" s="10">
         <f>N104</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="M104" s="14" t="n">
         <v>0</v>
@@ -6931,7 +6931,7 @@
       </c>
       <c r="O104" s="10">
         <f>Q104</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="P104" s="14" t="n">
         <v>0</v>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="R104" s="10">
         <f>T104</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="S104" s="14" t="n">
         <v>0</v>
@@ -6951,7 +6951,7 @@
       </c>
       <c r="U104" s="10">
         <f>W104</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="V104" s="14" t="n">
         <v>0</v>
@@ -6961,7 +6961,7 @@
       </c>
       <c r="X104" s="10">
         <f>Z104</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="Y104" s="14" t="n">
         <v>0</v>
@@ -6984,9 +6984,9 @@
           <t>Single</t>
         </is>
       </c>
-      <c r="C105" s="7">
+      <c r="C105" s="7" t="str">
         <f>A105&amp;"|"&amp;B105</f>
-        <v/>
+        <v>NC|Single</v>
       </c>
       <c r="D105" s="14" t="n">
         <v>0.045</v>
@@ -6996,7 +6996,7 @@
       </c>
       <c r="F105" s="10">
         <f>H105</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="G105" s="14" t="n">
         <v>0</v>
@@ -7006,7 +7006,7 @@
       </c>
       <c r="I105" s="10">
         <f>K105</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="J105" s="14" t="n">
         <v>0</v>
@@ -7016,7 +7016,7 @@
       </c>
       <c r="L105" s="10">
         <f>N105</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="M105" s="14" t="n">
         <v>0</v>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="O105" s="10">
         <f>Q105</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="P105" s="14" t="n">
         <v>0</v>
@@ -7036,7 +7036,7 @@
       </c>
       <c r="R105" s="10">
         <f>T105</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="S105" s="14" t="n">
         <v>0</v>
@@ -7046,7 +7046,7 @@
       </c>
       <c r="U105" s="10">
         <f>W105</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="V105" s="14" t="n">
         <v>0</v>
@@ -7056,7 +7056,7 @@
       </c>
       <c r="X105" s="10">
         <f>Z105</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="Y105" s="14" t="n">
         <v>0</v>
@@ -7079,9 +7079,9 @@
           <t>MFJ</t>
         </is>
       </c>
-      <c r="C106" s="7">
+      <c r="C106" s="7" t="str">
         <f>A106&amp;"|"&amp;B106</f>
-        <v/>
+        <v>NC|MFJ</v>
       </c>
       <c r="D106" s="14" t="n">
         <v>0.045</v>
@@ -7091,7 +7091,7 @@
       </c>
       <c r="F106" s="10">
         <f>H106</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="G106" s="14" t="n">
         <v>0</v>
@@ -7101,7 +7101,7 @@
       </c>
       <c r="I106" s="10">
         <f>K106</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="J106" s="14" t="n">
         <v>0</v>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="L106" s="10">
         <f>N106</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="M106" s="14" t="n">
         <v>0</v>
@@ -7121,7 +7121,7 @@
       </c>
       <c r="O106" s="10">
         <f>Q106</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="P106" s="14" t="n">
         <v>0</v>
@@ -7131,7 +7131,7 @@
       </c>
       <c r="R106" s="10">
         <f>T106</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="S106" s="14" t="n">
         <v>0</v>
@@ -7141,7 +7141,7 @@
       </c>
       <c r="U106" s="10">
         <f>W106</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="V106" s="14" t="n">
         <v>0</v>
@@ -7151,7 +7151,7 @@
       </c>
       <c r="X106" s="10">
         <f>Z106</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="Y106" s="14" t="n">
         <v>0</v>
@@ -7174,9 +7174,9 @@
           <t>Single</t>
         </is>
       </c>
-      <c r="C107" s="7">
+      <c r="C107" s="7" t="str">
         <f>A107&amp;"|"&amp;B107</f>
-        <v/>
+        <v>PA|Single</v>
       </c>
       <c r="D107" s="14" t="n">
         <v>0.0307</v>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="F107" s="10">
         <f>H107</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="G107" s="14" t="n">
         <v>0</v>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="I107" s="10">
         <f>K107</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="J107" s="14" t="n">
         <v>0</v>
@@ -7206,7 +7206,7 @@
       </c>
       <c r="L107" s="10">
         <f>N107</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="M107" s="14" t="n">
         <v>0</v>
@@ -7216,7 +7216,7 @@
       </c>
       <c r="O107" s="10">
         <f>Q107</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="P107" s="14" t="n">
         <v>0</v>
@@ -7226,7 +7226,7 @@
       </c>
       <c r="R107" s="10">
         <f>T107</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="S107" s="14" t="n">
         <v>0</v>
@@ -7236,7 +7236,7 @@
       </c>
       <c r="U107" s="10">
         <f>W107</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="V107" s="14" t="n">
         <v>0</v>
@@ -7246,7 +7246,7 @@
       </c>
       <c r="X107" s="10">
         <f>Z107</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="Y107" s="14" t="n">
         <v>0</v>
@@ -7269,9 +7269,9 @@
           <t>MFJ</t>
         </is>
       </c>
-      <c r="C108" s="7">
+      <c r="C108" s="7" t="str">
         <f>A108&amp;"|"&amp;B108</f>
-        <v/>
+        <v>PA|MFJ</v>
       </c>
       <c r="D108" s="14" t="n">
         <v>0.0307</v>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="F108" s="10">
         <f>H108</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="G108" s="14" t="n">
         <v>0</v>
@@ -7291,7 +7291,7 @@
       </c>
       <c r="I108" s="10">
         <f>K108</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="J108" s="14" t="n">
         <v>0</v>
@@ -7301,7 +7301,7 @@
       </c>
       <c r="L108" s="10">
         <f>N108</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="M108" s="14" t="n">
         <v>0</v>
@@ -7311,7 +7311,7 @@
       </c>
       <c r="O108" s="10">
         <f>Q108</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="P108" s="14" t="n">
         <v>0</v>
@@ -7321,7 +7321,7 @@
       </c>
       <c r="R108" s="10">
         <f>T108</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="S108" s="14" t="n">
         <v>0</v>
@@ -7331,7 +7331,7 @@
       </c>
       <c r="U108" s="10">
         <f>W108</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="V108" s="14" t="n">
         <v>0</v>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="X108" s="10">
         <f>Z108</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="Y108" s="14" t="n">
         <v>0</v>
@@ -7364,9 +7364,9 @@
           <t>Single</t>
         </is>
       </c>
-      <c r="C109" s="7">
+      <c r="C109" s="7" t="str">
         <f>A109&amp;"|"&amp;B109</f>
-        <v/>
+        <v>UT|Single</v>
       </c>
       <c r="D109" s="14" t="n">
         <v>0.0455</v>
@@ -7376,7 +7376,7 @@
       </c>
       <c r="F109" s="10">
         <f>H109</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="G109" s="14" t="n">
         <v>0</v>
@@ -7386,7 +7386,7 @@
       </c>
       <c r="I109" s="10">
         <f>K109</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="J109" s="14" t="n">
         <v>0</v>
@@ -7396,7 +7396,7 @@
       </c>
       <c r="L109" s="10">
         <f>N109</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="M109" s="14" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="O109" s="10">
         <f>Q109</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="P109" s="14" t="n">
         <v>0</v>
@@ -7416,7 +7416,7 @@
       </c>
       <c r="R109" s="10">
         <f>T109</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="S109" s="14" t="n">
         <v>0</v>
@@ -7426,7 +7426,7 @@
       </c>
       <c r="U109" s="10">
         <f>W109</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="V109" s="14" t="n">
         <v>0</v>
@@ -7436,7 +7436,7 @@
       </c>
       <c r="X109" s="10">
         <f>Z109</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="Y109" s="14" t="n">
         <v>0</v>
@@ -7459,9 +7459,9 @@
           <t>MFJ</t>
         </is>
       </c>
-      <c r="C110" s="7">
+      <c r="C110" s="7" t="str">
         <f>A110&amp;"|"&amp;B110</f>
-        <v/>
+        <v>UT|MFJ</v>
       </c>
       <c r="D110" s="14" t="n">
         <v>0.0455</v>
@@ -7471,7 +7471,7 @@
       </c>
       <c r="F110" s="10">
         <f>H110</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="G110" s="14" t="n">
         <v>0</v>
@@ -7481,7 +7481,7 @@
       </c>
       <c r="I110" s="10">
         <f>K110</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="J110" s="14" t="n">
         <v>0</v>
@@ -7491,7 +7491,7 @@
       </c>
       <c r="L110" s="10">
         <f>N110</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="M110" s="14" t="n">
         <v>0</v>
@@ -7501,7 +7501,7 @@
       </c>
       <c r="O110" s="10">
         <f>Q110</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="P110" s="14" t="n">
         <v>0</v>
@@ -7511,7 +7511,7 @@
       </c>
       <c r="R110" s="10">
         <f>T110</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="S110" s="14" t="n">
         <v>0</v>
@@ -7521,7 +7521,7 @@
       </c>
       <c r="U110" s="10">
         <f>W110</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="V110" s="14" t="n">
         <v>0</v>
@@ -7531,7 +7531,7 @@
       </c>
       <c r="X110" s="10">
         <f>Z110</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="Y110" s="14" t="n">
         <v>0</v>
@@ -7554,9 +7554,9 @@
           <t>Single</t>
         </is>
       </c>
-      <c r="C111" s="7">
+      <c r="C111" s="7" t="str">
         <f>A111&amp;"|"&amp;B111</f>
-        <v/>
+        <v>KY|Single</v>
       </c>
       <c r="D111" s="14" t="n">
         <v>0.04</v>
@@ -7566,7 +7566,7 @@
       </c>
       <c r="F111" s="10">
         <f>H111</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="G111" s="14" t="n">
         <v>0</v>
@@ -7576,7 +7576,7 @@
       </c>
       <c r="I111" s="10">
         <f>K111</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="J111" s="14" t="n">
         <v>0</v>
@@ -7586,7 +7586,7 @@
       </c>
       <c r="L111" s="10">
         <f>N111</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="M111" s="14" t="n">
         <v>0</v>
@@ -7596,7 +7596,7 @@
       </c>
       <c r="O111" s="10">
         <f>Q111</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="P111" s="14" t="n">
         <v>0</v>
@@ -7606,7 +7606,7 @@
       </c>
       <c r="R111" s="10">
         <f>T111</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="S111" s="14" t="n">
         <v>0</v>
@@ -7616,7 +7616,7 @@
       </c>
       <c r="U111" s="10">
         <f>W111</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="V111" s="14" t="n">
         <v>0</v>
@@ -7626,7 +7626,7 @@
       </c>
       <c r="X111" s="10">
         <f>Z111</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="Y111" s="14" t="n">
         <v>0</v>
@@ -7649,9 +7649,9 @@
           <t>MFJ</t>
         </is>
       </c>
-      <c r="C112" s="7">
+      <c r="C112" s="7" t="str">
         <f>A112&amp;"|"&amp;B112</f>
-        <v/>
+        <v>KY|MFJ</v>
       </c>
       <c r="D112" s="14" t="n">
         <v>0.04</v>
@@ -7661,7 +7661,7 @@
       </c>
       <c r="F112" s="10">
         <f>H112</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="G112" s="14" t="n">
         <v>0</v>
@@ -7671,7 +7671,7 @@
       </c>
       <c r="I112" s="10">
         <f>K112</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="J112" s="14" t="n">
         <v>0</v>
@@ -7681,7 +7681,7 @@
       </c>
       <c r="L112" s="10">
         <f>N112</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="M112" s="14" t="n">
         <v>0</v>
@@ -7691,7 +7691,7 @@
       </c>
       <c r="O112" s="10">
         <f>Q112</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="P112" s="14" t="n">
         <v>0</v>
@@ -7701,7 +7701,7 @@
       </c>
       <c r="R112" s="10">
         <f>T112</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="S112" s="14" t="n">
         <v>0</v>
@@ -7711,7 +7711,7 @@
       </c>
       <c r="U112" s="10">
         <f>W112</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="V112" s="14" t="n">
         <v>0</v>
@@ -7721,7 +7721,7 @@
       </c>
       <c r="X112" s="10">
         <f>Z112</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="Y112" s="14" t="n">
         <v>0</v>
@@ -7744,9 +7744,9 @@
           <t>Single</t>
         </is>
       </c>
-      <c r="C113" s="7">
+      <c r="C113" s="7" t="str">
         <f>A113&amp;"|"&amp;B113</f>
-        <v/>
+        <v>AZ|Single</v>
       </c>
       <c r="D113" s="14" t="n">
         <v>0.025</v>
@@ -7756,7 +7756,7 @@
       </c>
       <c r="F113" s="10">
         <f>H113</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="G113" s="14" t="n">
         <v>0</v>
@@ -7766,7 +7766,7 @@
       </c>
       <c r="I113" s="10">
         <f>K113</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="J113" s="14" t="n">
         <v>0</v>
@@ -7776,7 +7776,7 @@
       </c>
       <c r="L113" s="10">
         <f>N113</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="M113" s="14" t="n">
         <v>0</v>
@@ -7786,7 +7786,7 @@
       </c>
       <c r="O113" s="10">
         <f>Q113</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="P113" s="14" t="n">
         <v>0</v>
@@ -7796,7 +7796,7 @@
       </c>
       <c r="R113" s="10">
         <f>T113</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="S113" s="14" t="n">
         <v>0</v>
@@ -7806,7 +7806,7 @@
       </c>
       <c r="U113" s="10">
         <f>W113</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="V113" s="14" t="n">
         <v>0</v>
@@ -7816,7 +7816,7 @@
       </c>
       <c r="X113" s="10">
         <f>Z113</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="Y113" s="14" t="n">
         <v>0</v>
@@ -7839,9 +7839,9 @@
           <t>MFJ</t>
         </is>
       </c>
-      <c r="C114" s="7">
+      <c r="C114" s="7" t="str">
         <f>A114&amp;"|"&amp;B114</f>
-        <v/>
+        <v>AZ|MFJ</v>
       </c>
       <c r="D114" s="14" t="n">
         <v>0.025</v>
@@ -7851,7 +7851,7 @@
       </c>
       <c r="F114" s="10">
         <f>H114</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="G114" s="14" t="n">
         <v>0</v>
@@ -7861,7 +7861,7 @@
       </c>
       <c r="I114" s="10">
         <f>K114</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="J114" s="14" t="n">
         <v>0</v>
@@ -7871,7 +7871,7 @@
       </c>
       <c r="L114" s="10">
         <f>N114</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="M114" s="14" t="n">
         <v>0</v>
@@ -7881,7 +7881,7 @@
       </c>
       <c r="O114" s="10">
         <f>Q114</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="P114" s="14" t="n">
         <v>0</v>
@@ -7891,7 +7891,7 @@
       </c>
       <c r="R114" s="10">
         <f>T114</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="S114" s="14" t="n">
         <v>0</v>
@@ -7901,7 +7901,7 @@
       </c>
       <c r="U114" s="10">
         <f>W114</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="V114" s="14" t="n">
         <v>0</v>
@@ -7911,7 +7911,7 @@
       </c>
       <c r="X114" s="10">
         <f>Z114</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="Y114" s="14" t="n">
         <v>0</v>
@@ -7934,9 +7934,9 @@
           <t>Single</t>
         </is>
       </c>
-      <c r="C115" s="7">
+      <c r="C115" s="7" t="str">
         <f>A115&amp;"|"&amp;B115</f>
-        <v/>
+        <v>GA|Single</v>
       </c>
       <c r="D115" s="14" t="n">
         <v>0.0539</v>
@@ -7946,7 +7946,7 @@
       </c>
       <c r="F115" s="10">
         <f>H115</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="G115" s="14" t="n">
         <v>0</v>
@@ -7956,7 +7956,7 @@
       </c>
       <c r="I115" s="10">
         <f>K115</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="J115" s="14" t="n">
         <v>0</v>
@@ -7966,7 +7966,7 @@
       </c>
       <c r="L115" s="10">
         <f>N115</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="M115" s="14" t="n">
         <v>0</v>
@@ -7976,7 +7976,7 @@
       </c>
       <c r="O115" s="10">
         <f>Q115</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="P115" s="14" t="n">
         <v>0</v>
@@ -7986,7 +7986,7 @@
       </c>
       <c r="R115" s="10">
         <f>T115</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="S115" s="14" t="n">
         <v>0</v>
@@ -7996,7 +7996,7 @@
       </c>
       <c r="U115" s="10">
         <f>W115</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="V115" s="14" t="n">
         <v>0</v>
@@ -8006,7 +8006,7 @@
       </c>
       <c r="X115" s="10">
         <f>Z115</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="Y115" s="14" t="n">
         <v>0</v>
@@ -8029,9 +8029,9 @@
           <t>MFJ</t>
         </is>
       </c>
-      <c r="C116" s="7">
+      <c r="C116" s="7" t="str">
         <f>A116&amp;"|"&amp;B116</f>
-        <v/>
+        <v>GA|MFJ</v>
       </c>
       <c r="D116" s="14" t="n">
         <v>0.0539</v>
@@ -8041,7 +8041,7 @@
       </c>
       <c r="F116" s="10">
         <f>H116</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="G116" s="14" t="n">
         <v>0</v>
@@ -8051,7 +8051,7 @@
       </c>
       <c r="I116" s="10">
         <f>K116</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="J116" s="14" t="n">
         <v>0</v>
@@ -8061,7 +8061,7 @@
       </c>
       <c r="L116" s="10">
         <f>N116</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="M116" s="14" t="n">
         <v>0</v>
@@ -8071,7 +8071,7 @@
       </c>
       <c r="O116" s="10">
         <f>Q116</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="P116" s="14" t="n">
         <v>0</v>
@@ -8081,7 +8081,7 @@
       </c>
       <c r="R116" s="10">
         <f>T116</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="S116" s="14" t="n">
         <v>0</v>
@@ -8091,7 +8091,7 @@
       </c>
       <c r="U116" s="10">
         <f>W116</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="V116" s="14" t="n">
         <v>0</v>
@@ -8101,7 +8101,7 @@
       </c>
       <c r="X116" s="10">
         <f>Z116</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="Y116" s="14" t="n">
         <v>0</v>
@@ -8124,9 +8124,9 @@
           <t>Single</t>
         </is>
       </c>
-      <c r="C117" s="7">
+      <c r="C117" s="7" t="str">
         <f>A117&amp;"|"&amp;B117</f>
-        <v/>
+        <v>MA|Single</v>
       </c>
       <c r="D117" s="14" t="n">
         <v>0.05</v>
@@ -8136,7 +8136,7 @@
       </c>
       <c r="F117" s="10">
         <f>H117</f>
-        <v/>
+        <v>1000000</v>
       </c>
       <c r="G117" s="14" t="n">
         <v>0.09</v>
@@ -8146,7 +8146,7 @@
       </c>
       <c r="I117" s="10">
         <f>K117</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="J117" s="14" t="n">
         <v>0</v>
@@ -8156,7 +8156,7 @@
       </c>
       <c r="L117" s="10">
         <f>N117</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="M117" s="14" t="n">
         <v>0</v>
@@ -8166,7 +8166,7 @@
       </c>
       <c r="O117" s="10">
         <f>Q117</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="P117" s="14" t="n">
         <v>0</v>
@@ -8176,7 +8176,7 @@
       </c>
       <c r="R117" s="10">
         <f>T117</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="S117" s="14" t="n">
         <v>0</v>
@@ -8186,7 +8186,7 @@
       </c>
       <c r="U117" s="10">
         <f>W117</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="V117" s="14" t="n">
         <v>0</v>
@@ -8196,7 +8196,7 @@
       </c>
       <c r="X117" s="10">
         <f>Z117</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="Y117" s="14" t="n">
         <v>0</v>
@@ -8219,9 +8219,9 @@
           <t>MFJ</t>
         </is>
       </c>
-      <c r="C118" s="7">
+      <c r="C118" s="7" t="str">
         <f>A118&amp;"|"&amp;B118</f>
-        <v/>
+        <v>MA|MFJ</v>
       </c>
       <c r="D118" s="14" t="n">
         <v>0.05</v>
@@ -8231,7 +8231,7 @@
       </c>
       <c r="F118" s="10">
         <f>H118</f>
-        <v/>
+        <v>1000000</v>
       </c>
       <c r="G118" s="14" t="n">
         <v>0.09</v>
@@ -8241,7 +8241,7 @@
       </c>
       <c r="I118" s="10">
         <f>K118</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="J118" s="14" t="n">
         <v>0</v>
@@ -8251,7 +8251,7 @@
       </c>
       <c r="L118" s="10">
         <f>N118</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="M118" s="14" t="n">
         <v>0</v>
@@ -8261,7 +8261,7 @@
       </c>
       <c r="O118" s="10">
         <f>Q118</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="P118" s="14" t="n">
         <v>0</v>
@@ -8271,7 +8271,7 @@
       </c>
       <c r="R118" s="10">
         <f>T118</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="S118" s="14" t="n">
         <v>0</v>
@@ -8281,7 +8281,7 @@
       </c>
       <c r="U118" s="10">
         <f>W118</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="V118" s="14" t="n">
         <v>0</v>
@@ -8291,7 +8291,7 @@
       </c>
       <c r="X118" s="10">
         <f>Z118</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="Y118" s="14" t="n">
         <v>0</v>
@@ -8314,9 +8314,9 @@
           <t>Single</t>
         </is>
       </c>
-      <c r="C119" s="7">
+      <c r="C119" s="7" t="str">
         <f>A119&amp;"|"&amp;B119</f>
-        <v/>
+        <v>CA|Single</v>
       </c>
       <c r="D119" s="14" t="n">
         <v>0.01</v>
@@ -8326,7 +8326,7 @@
       </c>
       <c r="F119" s="10">
         <f>H119</f>
-        <v/>
+        <v>10412</v>
       </c>
       <c r="G119" s="14" t="n">
         <v>0.02</v>
@@ -8336,7 +8336,7 @@
       </c>
       <c r="I119" s="10">
         <f>K119</f>
-        <v/>
+        <v>24684</v>
       </c>
       <c r="J119" s="14" t="n">
         <v>0.04</v>
@@ -8346,7 +8346,7 @@
       </c>
       <c r="L119" s="10">
         <f>N119</f>
-        <v/>
+        <v>38959</v>
       </c>
       <c r="M119" s="14" t="n">
         <v>0.06</v>
@@ -8356,7 +8356,7 @@
       </c>
       <c r="O119" s="10">
         <f>Q119</f>
-        <v/>
+        <v>54081</v>
       </c>
       <c r="P119" s="14" t="n">
         <v>0.08</v>
@@ -8366,7 +8366,7 @@
       </c>
       <c r="R119" s="10">
         <f>T119</f>
-        <v/>
+        <v>68350</v>
       </c>
       <c r="S119" s="14" t="n">
         <v>0.093</v>
@@ -8376,7 +8376,7 @@
       </c>
       <c r="U119" s="10">
         <f>W119</f>
-        <v/>
+        <v>349137</v>
       </c>
       <c r="V119" s="14" t="n">
         <v>0.103</v>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="X119" s="10">
         <f>Z119</f>
-        <v/>
+        <v>418961</v>
       </c>
       <c r="Y119" s="14" t="n">
         <v>0.123</v>
@@ -8409,9 +8409,9 @@
           <t>MFJ</t>
         </is>
       </c>
-      <c r="C120" s="7">
+      <c r="C120" s="7" t="str">
         <f>A120&amp;"|"&amp;B120</f>
-        <v/>
+        <v>CA|MFJ</v>
       </c>
       <c r="D120" s="14" t="n">
         <v>0.01</v>
@@ -8421,7 +8421,7 @@
       </c>
       <c r="F120" s="10">
         <f>H120</f>
-        <v/>
+        <v>20824</v>
       </c>
       <c r="G120" s="14" t="n">
         <v>0.02</v>
@@ -8431,7 +8431,7 @@
       </c>
       <c r="I120" s="10">
         <f>K120</f>
-        <v/>
+        <v>49368</v>
       </c>
       <c r="J120" s="14" t="n">
         <v>0.04</v>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="L120" s="10">
         <f>N120</f>
-        <v/>
+        <v>77918</v>
       </c>
       <c r="M120" s="14" t="n">
         <v>0.06</v>
@@ -8451,7 +8451,7 @@
       </c>
       <c r="O120" s="10">
         <f>Q120</f>
-        <v/>
+        <v>108162</v>
       </c>
       <c r="P120" s="14" t="n">
         <v>0.08</v>
@@ -8461,7 +8461,7 @@
       </c>
       <c r="R120" s="10">
         <f>T120</f>
-        <v/>
+        <v>136700</v>
       </c>
       <c r="S120" s="14" t="n">
         <v>0.093</v>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="U120" s="10">
         <f>W120</f>
-        <v/>
+        <v>698274</v>
       </c>
       <c r="V120" s="14" t="n">
         <v>0.103</v>
@@ -8481,7 +8481,7 @@
       </c>
       <c r="X120" s="10">
         <f>Z120</f>
-        <v/>
+        <v>837922</v>
       </c>
       <c r="Y120" s="14" t="n">
         <v>0.123</v>
@@ -8504,9 +8504,9 @@
           <t>Single</t>
         </is>
       </c>
-      <c r="C121" s="7">
+      <c r="C121" s="7" t="str">
         <f>A121&amp;"|"&amp;B121</f>
-        <v/>
+        <v>NY|Single</v>
       </c>
       <c r="D121" s="14" t="n">
         <v>0.04</v>
@@ -8516,7 +8516,7 @@
       </c>
       <c r="F121" s="10">
         <f>H121</f>
-        <v/>
+        <v>8500</v>
       </c>
       <c r="G121" s="14" t="n">
         <v>0.045</v>
@@ -8526,7 +8526,7 @@
       </c>
       <c r="I121" s="10">
         <f>K121</f>
-        <v/>
+        <v>11700</v>
       </c>
       <c r="J121" s="14" t="n">
         <v>0.0525</v>
@@ -8536,7 +8536,7 @@
       </c>
       <c r="L121" s="10">
         <f>N121</f>
-        <v/>
+        <v>13900</v>
       </c>
       <c r="M121" s="14" t="n">
         <v>0.055</v>
@@ -8546,7 +8546,7 @@
       </c>
       <c r="O121" s="10">
         <f>Q121</f>
-        <v/>
+        <v>80650</v>
       </c>
       <c r="P121" s="14" t="n">
         <v>0.06</v>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="R121" s="10">
         <f>T121</f>
-        <v/>
+        <v>215400</v>
       </c>
       <c r="S121" s="14" t="n">
         <v>0.06850000000000001</v>
@@ -8566,7 +8566,7 @@
       </c>
       <c r="U121" s="10">
         <f>W121</f>
-        <v/>
+        <v>1077550</v>
       </c>
       <c r="V121" s="14" t="n">
         <v>0.0965</v>
@@ -8576,7 +8576,7 @@
       </c>
       <c r="X121" s="10">
         <f>Z121</f>
-        <v/>
+        <v>5000000</v>
       </c>
       <c r="Y121" s="14" t="n">
         <v>0.109</v>
@@ -8599,9 +8599,9 @@
           <t>MFJ</t>
         </is>
       </c>
-      <c r="C122" s="7">
+      <c r="C122" s="7" t="str">
         <f>A122&amp;"|"&amp;B122</f>
-        <v/>
+        <v>NY|MFJ</v>
       </c>
       <c r="D122" s="14" t="n">
         <v>0.04</v>
@@ -8611,7 +8611,7 @@
       </c>
       <c r="F122" s="10">
         <f>H122</f>
-        <v/>
+        <v>17150</v>
       </c>
       <c r="G122" s="14" t="n">
         <v>0.045</v>
@@ -8621,7 +8621,7 @@
       </c>
       <c r="I122" s="10">
         <f>K122</f>
-        <v/>
+        <v>23600</v>
       </c>
       <c r="J122" s="14" t="n">
         <v>0.0525</v>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="L122" s="10">
         <f>N122</f>
-        <v/>
+        <v>27900</v>
       </c>
       <c r="M122" s="14" t="n">
         <v>0.055</v>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="O122" s="10">
         <f>Q122</f>
-        <v/>
+        <v>161550</v>
       </c>
       <c r="P122" s="14" t="n">
         <v>0.06</v>
@@ -8651,7 +8651,7 @@
       </c>
       <c r="R122" s="10">
         <f>T122</f>
-        <v/>
+        <v>323200</v>
       </c>
       <c r="S122" s="14" t="n">
         <v>0.06850000000000001</v>
@@ -8661,7 +8661,7 @@
       </c>
       <c r="U122" s="10">
         <f>W122</f>
-        <v/>
+        <v>2155350</v>
       </c>
       <c r="V122" s="14" t="n">
         <v>0.0965</v>
@@ -8671,7 +8671,7 @@
       </c>
       <c r="X122" s="10">
         <f>Z122</f>
-        <v/>
+        <v>5000000</v>
       </c>
       <c r="Y122" s="14" t="n">
         <v>0.109</v>
@@ -8694,9 +8694,9 @@
           <t>Single</t>
         </is>
       </c>
-      <c r="C123" s="7">
+      <c r="C123" s="7" t="str">
         <f>A123&amp;"|"&amp;B123</f>
-        <v/>
+        <v>NJ|Single</v>
       </c>
       <c r="D123" s="14" t="n">
         <v>0.014</v>
@@ -8706,7 +8706,7 @@
       </c>
       <c r="F123" s="10">
         <f>H123</f>
-        <v/>
+        <v>20000</v>
       </c>
       <c r="G123" s="14" t="n">
         <v>0.0175</v>
@@ -8716,7 +8716,7 @@
       </c>
       <c r="I123" s="10">
         <f>K123</f>
-        <v/>
+        <v>35000</v>
       </c>
       <c r="J123" s="14" t="n">
         <v>0.035</v>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="L123" s="10">
         <f>N123</f>
-        <v/>
+        <v>40000</v>
       </c>
       <c r="M123" s="14" t="n">
         <v>0.05525</v>
@@ -8736,7 +8736,7 @@
       </c>
       <c r="O123" s="10">
         <f>Q123</f>
-        <v/>
+        <v>75000</v>
       </c>
       <c r="P123" s="14" t="n">
         <v>0.06370000000000001</v>
@@ -8746,7 +8746,7 @@
       </c>
       <c r="R123" s="10">
         <f>T123</f>
-        <v/>
+        <v>500000</v>
       </c>
       <c r="S123" s="14" t="n">
         <v>0.0897</v>
@@ -8756,7 +8756,7 @@
       </c>
       <c r="U123" s="10">
         <f>W123</f>
-        <v/>
+        <v>1000000</v>
       </c>
       <c r="V123" s="14" t="n">
         <v>0.1075</v>
@@ -8766,7 +8766,7 @@
       </c>
       <c r="X123" s="10">
         <f>Z123</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="Y123" s="14" t="n">
         <v>0</v>
@@ -8789,9 +8789,9 @@
           <t>MFJ</t>
         </is>
       </c>
-      <c r="C124" s="7">
+      <c r="C124" s="7" t="str">
         <f>A124&amp;"|"&amp;B124</f>
-        <v/>
+        <v>NJ|MFJ</v>
       </c>
       <c r="D124" s="14" t="n">
         <v>0.014</v>
@@ -8801,7 +8801,7 @@
       </c>
       <c r="F124" s="10">
         <f>H124</f>
-        <v/>
+        <v>20000</v>
       </c>
       <c r="G124" s="14" t="n">
         <v>0.0175</v>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="I124" s="10">
         <f>K124</f>
-        <v/>
+        <v>50000</v>
       </c>
       <c r="J124" s="14" t="n">
         <v>0.0245</v>
@@ -8821,7 +8821,7 @@
       </c>
       <c r="L124" s="10">
         <f>N124</f>
-        <v/>
+        <v>70000</v>
       </c>
       <c r="M124" s="14" t="n">
         <v>0.035</v>
@@ -8831,7 +8831,7 @@
       </c>
       <c r="O124" s="10">
         <f>Q124</f>
-        <v/>
+        <v>80000</v>
       </c>
       <c r="P124" s="14" t="n">
         <v>0.05525</v>
@@ -8841,7 +8841,7 @@
       </c>
       <c r="R124" s="10">
         <f>T124</f>
-        <v/>
+        <v>150000</v>
       </c>
       <c r="S124" s="14" t="n">
         <v>0.06370000000000001</v>
@@ -8851,7 +8851,7 @@
       </c>
       <c r="U124" s="10">
         <f>W124</f>
-        <v/>
+        <v>500000</v>
       </c>
       <c r="V124" s="14" t="n">
         <v>0.0897</v>
@@ -8861,7 +8861,7 @@
       </c>
       <c r="X124" s="10">
         <f>Z124</f>
-        <v/>
+        <v>1000000</v>
       </c>
       <c r="Y124" s="14" t="n">
         <v>0.1075</v>
@@ -8884,9 +8884,9 @@
           <t>Single</t>
         </is>
       </c>
-      <c r="C125" s="7">
+      <c r="C125" s="7" t="str">
         <f>A125&amp;"|"&amp;B125</f>
-        <v/>
+        <v>OR|Single</v>
       </c>
       <c r="D125" s="14" t="n">
         <v>0.0475</v>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="F125" s="10">
         <f>H125</f>
-        <v/>
+        <v>4300</v>
       </c>
       <c r="G125" s="14" t="n">
         <v>0.0675</v>
@@ -8906,7 +8906,7 @@
       </c>
       <c r="I125" s="10">
         <f>K125</f>
-        <v/>
+        <v>10750</v>
       </c>
       <c r="J125" s="14" t="n">
         <v>0.08749999999999999</v>
@@ -8916,7 +8916,7 @@
       </c>
       <c r="L125" s="10">
         <f>N125</f>
-        <v/>
+        <v>125000</v>
       </c>
       <c r="M125" s="14" t="n">
         <v>0.099</v>
@@ -8926,7 +8926,7 @@
       </c>
       <c r="O125" s="10">
         <f>Q125</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="P125" s="14" t="n">
         <v>0</v>
@@ -8936,7 +8936,7 @@
       </c>
       <c r="R125" s="10">
         <f>T125</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="S125" s="14" t="n">
         <v>0</v>
@@ -8946,7 +8946,7 @@
       </c>
       <c r="U125" s="10">
         <f>W125</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="V125" s="14" t="n">
         <v>0</v>
@@ -8956,7 +8956,7 @@
       </c>
       <c r="X125" s="10">
         <f>Z125</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="Y125" s="14" t="n">
         <v>0</v>
@@ -8979,9 +8979,9 @@
           <t>MFJ</t>
         </is>
       </c>
-      <c r="C126" s="7">
+      <c r="C126" s="7" t="str">
         <f>A126&amp;"|"&amp;B126</f>
-        <v/>
+        <v>OR|MFJ</v>
       </c>
       <c r="D126" s="14" t="n">
         <v>0.0475</v>
@@ -8991,7 +8991,7 @@
       </c>
       <c r="F126" s="10">
         <f>H126</f>
-        <v/>
+        <v>8600</v>
       </c>
       <c r="G126" s="14" t="n">
         <v>0.0675</v>
@@ -9001,7 +9001,7 @@
       </c>
       <c r="I126" s="10">
         <f>K126</f>
-        <v/>
+        <v>21500</v>
       </c>
       <c r="J126" s="14" t="n">
         <v>0.08749999999999999</v>
@@ -9011,7 +9011,7 @@
       </c>
       <c r="L126" s="10">
         <f>N126</f>
-        <v/>
+        <v>250000</v>
       </c>
       <c r="M126" s="14" t="n">
         <v>0.099</v>
@@ -9021,7 +9021,7 @@
       </c>
       <c r="O126" s="10">
         <f>Q126</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="P126" s="14" t="n">
         <v>0</v>
@@ -9031,7 +9031,7 @@
       </c>
       <c r="R126" s="10">
         <f>T126</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="S126" s="14" t="n">
         <v>0</v>
@@ -9041,7 +9041,7 @@
       </c>
       <c r="U126" s="10">
         <f>W126</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="V126" s="14" t="n">
         <v>0</v>
@@ -9051,7 +9051,7 @@
       </c>
       <c r="X126" s="10">
         <f>Z126</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="Y126" s="14" t="n">
         <v>0</v>
@@ -9074,9 +9074,9 @@
           <t>Single</t>
         </is>
       </c>
-      <c r="C127" s="7">
+      <c r="C127" s="7" t="str">
         <f>A127&amp;"|"&amp;B127</f>
-        <v/>
+        <v>MN|Single</v>
       </c>
       <c r="D127" s="14" t="n">
         <v>0.0535</v>
@@ -9086,7 +9086,7 @@
       </c>
       <c r="F127" s="10">
         <f>H127</f>
-        <v/>
+        <v>31690</v>
       </c>
       <c r="G127" s="14" t="n">
         <v>0.068</v>
@@ -9096,7 +9096,7 @@
       </c>
       <c r="I127" s="10">
         <f>K127</f>
-        <v/>
+        <v>104090</v>
       </c>
       <c r="J127" s="14" t="n">
         <v>0.0785</v>
@@ -9106,7 +9106,7 @@
       </c>
       <c r="L127" s="10">
         <f>N127</f>
-        <v/>
+        <v>193240</v>
       </c>
       <c r="M127" s="14" t="n">
         <v>0.0985</v>
@@ -9116,7 +9116,7 @@
       </c>
       <c r="O127" s="10">
         <f>Q127</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="P127" s="14" t="n">
         <v>0</v>
@@ -9126,7 +9126,7 @@
       </c>
       <c r="R127" s="10">
         <f>T127</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="S127" s="14" t="n">
         <v>0</v>
@@ -9136,7 +9136,7 @@
       </c>
       <c r="U127" s="10">
         <f>W127</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="V127" s="14" t="n">
         <v>0</v>
@@ -9146,7 +9146,7 @@
       </c>
       <c r="X127" s="10">
         <f>Z127</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="Y127" s="14" t="n">
         <v>0</v>
@@ -9169,9 +9169,9 @@
           <t>MFJ</t>
         </is>
       </c>
-      <c r="C128" s="7">
+      <c r="C128" s="7" t="str">
         <f>A128&amp;"|"&amp;B128</f>
-        <v/>
+        <v>MN|MFJ</v>
       </c>
       <c r="D128" s="14" t="n">
         <v>0.0535</v>
@@ -9181,7 +9181,7 @@
       </c>
       <c r="F128" s="10">
         <f>H128</f>
-        <v/>
+        <v>46330</v>
       </c>
       <c r="G128" s="14" t="n">
         <v>0.068</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="I128" s="10">
         <f>K128</f>
-        <v/>
+        <v>184040</v>
       </c>
       <c r="J128" s="14" t="n">
         <v>0.0785</v>
@@ -9201,7 +9201,7 @@
       </c>
       <c r="L128" s="10">
         <f>N128</f>
-        <v/>
+        <v>321450</v>
       </c>
       <c r="M128" s="14" t="n">
         <v>0.0985</v>
@@ -9211,7 +9211,7 @@
       </c>
       <c r="O128" s="10">
         <f>Q128</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="P128" s="14" t="n">
         <v>0</v>
@@ -9221,7 +9221,7 @@
       </c>
       <c r="R128" s="10">
         <f>T128</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="S128" s="14" t="n">
         <v>0</v>
@@ -9231,7 +9231,7 @@
       </c>
       <c r="U128" s="10">
         <f>W128</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="V128" s="14" t="n">
         <v>0</v>
@@ -9241,7 +9241,7 @@
       </c>
       <c r="X128" s="10">
         <f>Z128</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="Y128" s="14" t="n">
         <v>0</v>
@@ -9264,9 +9264,9 @@
           <t>Single</t>
         </is>
       </c>
-      <c r="C129" s="7">
+      <c r="C129" s="7" t="str">
         <f>A129&amp;"|"&amp;B129</f>
-        <v/>
+        <v>HI|Single</v>
       </c>
       <c r="D129" s="14" t="n">
         <v>0.014</v>
@@ -9276,7 +9276,7 @@
       </c>
       <c r="F129" s="10">
         <f>H129</f>
-        <v/>
+        <v>9600</v>
       </c>
       <c r="G129" s="14" t="n">
         <v>0.04</v>
@@ -9286,7 +9286,7 @@
       </c>
       <c r="I129" s="10">
         <f>K129</f>
-        <v/>
+        <v>24000</v>
       </c>
       <c r="J129" s="14" t="n">
         <v>0.064</v>
@@ -9296,7 +9296,7 @@
       </c>
       <c r="L129" s="10">
         <f>N129</f>
-        <v/>
+        <v>125000</v>
       </c>
       <c r="M129" s="14" t="n">
         <v>0.076</v>
@@ -9306,7 +9306,7 @@
       </c>
       <c r="O129" s="10">
         <f>Q129</f>
-        <v/>
+        <v>225000</v>
       </c>
       <c r="P129" s="14" t="n">
         <v>0.08749999999999999</v>
@@ -9316,7 +9316,7 @@
       </c>
       <c r="R129" s="10">
         <f>T129</f>
-        <v/>
+        <v>350000</v>
       </c>
       <c r="S129" s="14" t="n">
         <v>0.1</v>
@@ -9326,7 +9326,7 @@
       </c>
       <c r="U129" s="10">
         <f>W129</f>
-        <v/>
+        <v>450000</v>
       </c>
       <c r="V129" s="14" t="n">
         <v>0.11</v>
@@ -9336,7 +9336,7 @@
       </c>
       <c r="X129" s="10">
         <f>Z129</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="Y129" s="14" t="n">
         <v>0</v>
@@ -9359,9 +9359,9 @@
           <t>MFJ</t>
         </is>
       </c>
-      <c r="C130" s="7">
+      <c r="C130" s="7" t="str">
         <f>A130&amp;"|"&amp;B130</f>
-        <v/>
+        <v>HI|MFJ</v>
       </c>
       <c r="D130" s="14" t="n">
         <v>0.014</v>
@@ -9371,7 +9371,7 @@
       </c>
       <c r="F130" s="10">
         <f>H130</f>
-        <v/>
+        <v>19200</v>
       </c>
       <c r="G130" s="14" t="n">
         <v>0.04</v>
@@ -9381,7 +9381,7 @@
       </c>
       <c r="I130" s="10">
         <f>K130</f>
-        <v/>
+        <v>48000</v>
       </c>
       <c r="J130" s="14" t="n">
         <v>0.064</v>
@@ -9391,7 +9391,7 @@
       </c>
       <c r="L130" s="10">
         <f>N130</f>
-        <v/>
+        <v>250000</v>
       </c>
       <c r="M130" s="14" t="n">
         <v>0.076</v>
@@ -9401,7 +9401,7 @@
       </c>
       <c r="O130" s="10">
         <f>Q130</f>
-        <v/>
+        <v>450000</v>
       </c>
       <c r="P130" s="14" t="n">
         <v>0.08749999999999999</v>
@@ -9411,7 +9411,7 @@
       </c>
       <c r="R130" s="10">
         <f>T130</f>
-        <v/>
+        <v>700000</v>
       </c>
       <c r="S130" s="14" t="n">
         <v>0.1</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="U130" s="10">
         <f>W130</f>
-        <v/>
+        <v>900000</v>
       </c>
       <c r="V130" s="14" t="n">
         <v>0.11</v>
@@ -9431,7 +9431,7 @@
       </c>
       <c r="X130" s="10">
         <f>Z130</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="Y130" s="14" t="n">
         <v>0</v>
@@ -9454,9 +9454,9 @@
           <t>Single</t>
         </is>
       </c>
-      <c r="C131" s="7">
+      <c r="C131" s="7" t="str">
         <f>A131&amp;"|"&amp;B131</f>
-        <v/>
+        <v>VA|Single</v>
       </c>
       <c r="D131" s="14" t="n">
         <v>0.02</v>
@@ -9466,7 +9466,7 @@
       </c>
       <c r="F131" s="10">
         <f>H131</f>
-        <v/>
+        <v>3000</v>
       </c>
       <c r="G131" s="14" t="n">
         <v>0.03</v>
@@ -9476,7 +9476,7 @@
       </c>
       <c r="I131" s="10">
         <f>K131</f>
-        <v/>
+        <v>5000</v>
       </c>
       <c r="J131" s="14" t="n">
         <v>0.05</v>
@@ -9486,7 +9486,7 @@
       </c>
       <c r="L131" s="10">
         <f>N131</f>
-        <v/>
+        <v>17000</v>
       </c>
       <c r="M131" s="14" t="n">
         <v>0.0575</v>
@@ -9496,7 +9496,7 @@
       </c>
       <c r="O131" s="10">
         <f>Q131</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="P131" s="14" t="n">
         <v>0</v>
@@ -9506,7 +9506,7 @@
       </c>
       <c r="R131" s="10">
         <f>T131</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="S131" s="14" t="n">
         <v>0</v>
@@ -9516,7 +9516,7 @@
       </c>
       <c r="U131" s="10">
         <f>W131</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="V131" s="14" t="n">
         <v>0</v>
@@ -9526,7 +9526,7 @@
       </c>
       <c r="X131" s="10">
         <f>Z131</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="Y131" s="14" t="n">
         <v>0</v>
@@ -9549,9 +9549,9 @@
           <t>MFJ</t>
         </is>
       </c>
-      <c r="C132" s="7">
+      <c r="C132" s="7" t="str">
         <f>A132&amp;"|"&amp;B132</f>
-        <v/>
+        <v>VA|MFJ</v>
       </c>
       <c r="D132" s="14" t="n">
         <v>0.02</v>
@@ -9561,7 +9561,7 @@
       </c>
       <c r="F132" s="10">
         <f>H132</f>
-        <v/>
+        <v>3000</v>
       </c>
       <c r="G132" s="14" t="n">
         <v>0.03</v>
@@ -9571,7 +9571,7 @@
       </c>
       <c r="I132" s="10">
         <f>K132</f>
-        <v/>
+        <v>5000</v>
       </c>
       <c r="J132" s="14" t="n">
         <v>0.05</v>
@@ -9581,7 +9581,7 @@
       </c>
       <c r="L132" s="10">
         <f>N132</f>
-        <v/>
+        <v>17000</v>
       </c>
       <c r="M132" s="14" t="n">
         <v>0.0575</v>
@@ -9591,7 +9591,7 @@
       </c>
       <c r="O132" s="10">
         <f>Q132</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="P132" s="14" t="n">
         <v>0</v>
@@ -9601,7 +9601,7 @@
       </c>
       <c r="R132" s="10">
         <f>T132</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="S132" s="14" t="n">
         <v>0</v>
@@ -9611,7 +9611,7 @@
       </c>
       <c r="U132" s="10">
         <f>W132</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="V132" s="14" t="n">
         <v>0</v>
@@ -9621,7 +9621,7 @@
       </c>
       <c r="X132" s="10">
         <f>Z132</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="Y132" s="14" t="n">
         <v>0</v>
@@ -9644,9 +9644,9 @@
           <t>Single</t>
         </is>
       </c>
-      <c r="C133" s="7">
+      <c r="C133" s="7" t="str">
         <f>A133&amp;"|"&amp;B133</f>
-        <v/>
+        <v>SC|Single</v>
       </c>
       <c r="D133" s="14" t="n">
         <v>0</v>
@@ -9656,7 +9656,7 @@
       </c>
       <c r="F133" s="10">
         <f>H133</f>
-        <v/>
+        <v>3200</v>
       </c>
       <c r="G133" s="14" t="n">
         <v>0.03</v>
@@ -9666,7 +9666,7 @@
       </c>
       <c r="I133" s="10">
         <f>K133</f>
-        <v/>
+        <v>16040</v>
       </c>
       <c r="J133" s="14" t="n">
         <v>0.062</v>
@@ -9676,7 +9676,7 @@
       </c>
       <c r="L133" s="10">
         <f>N133</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="M133" s="14" t="n">
         <v>0</v>
@@ -9686,7 +9686,7 @@
       </c>
       <c r="O133" s="10">
         <f>Q133</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="P133" s="14" t="n">
         <v>0</v>
@@ -9696,7 +9696,7 @@
       </c>
       <c r="R133" s="10">
         <f>T133</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="S133" s="14" t="n">
         <v>0</v>
@@ -9706,7 +9706,7 @@
       </c>
       <c r="U133" s="10">
         <f>W133</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="V133" s="14" t="n">
         <v>0</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="X133" s="10">
         <f>Z133</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="Y133" s="14" t="n">
         <v>0</v>
@@ -9739,9 +9739,9 @@
           <t>MFJ</t>
         </is>
       </c>
-      <c r="C134" s="7">
+      <c r="C134" s="7" t="str">
         <f>A134&amp;"|"&amp;B134</f>
-        <v/>
+        <v>SC|MFJ</v>
       </c>
       <c r="D134" s="14" t="n">
         <v>0</v>
@@ -9751,7 +9751,7 @@
       </c>
       <c r="F134" s="10">
         <f>H134</f>
-        <v/>
+        <v>3200</v>
       </c>
       <c r="G134" s="14" t="n">
         <v>0.03</v>
@@ -9761,7 +9761,7 @@
       </c>
       <c r="I134" s="10">
         <f>K134</f>
-        <v/>
+        <v>16040</v>
       </c>
       <c r="J134" s="14" t="n">
         <v>0.062</v>
@@ -9771,7 +9771,7 @@
       </c>
       <c r="L134" s="10">
         <f>N134</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="M134" s="14" t="n">
         <v>0</v>
@@ -9781,7 +9781,7 @@
       </c>
       <c r="O134" s="10">
         <f>Q134</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="P134" s="14" t="n">
         <v>0</v>
@@ -9791,7 +9791,7 @@
       </c>
       <c r="R134" s="10">
         <f>T134</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="S134" s="14" t="n">
         <v>0</v>
@@ -9801,7 +9801,7 @@
       </c>
       <c r="U134" s="10">
         <f>W134</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="V134" s="14" t="n">
         <v>0</v>
@@ -9811,7 +9811,7 @@
       </c>
       <c r="X134" s="10">
         <f>Z134</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="Y134" s="14" t="n">
         <v>0</v>
@@ -9834,9 +9834,9 @@
           <t>Single</t>
         </is>
       </c>
-      <c r="C135" s="7">
+      <c r="C135" s="7" t="str">
         <f>A135&amp;"|"&amp;B135</f>
-        <v/>
+        <v>MD|Single</v>
       </c>
       <c r="D135" s="14" t="n">
         <v>0.02</v>
@@ -9846,7 +9846,7 @@
       </c>
       <c r="F135" s="10">
         <f>H135</f>
-        <v/>
+        <v>1000</v>
       </c>
       <c r="G135" s="14" t="n">
         <v>0.03</v>
@@ -9856,7 +9856,7 @@
       </c>
       <c r="I135" s="10">
         <f>K135</f>
-        <v/>
+        <v>2000</v>
       </c>
       <c r="J135" s="14" t="n">
         <v>0.04</v>
@@ -9866,7 +9866,7 @@
       </c>
       <c r="L135" s="10">
         <f>N135</f>
-        <v/>
+        <v>3000</v>
       </c>
       <c r="M135" s="14" t="n">
         <v>0.0475</v>
@@ -9876,7 +9876,7 @@
       </c>
       <c r="O135" s="10">
         <f>Q135</f>
-        <v/>
+        <v>100000</v>
       </c>
       <c r="P135" s="14" t="n">
         <v>0.05</v>
@@ -9886,7 +9886,7 @@
       </c>
       <c r="R135" s="10">
         <f>T135</f>
-        <v/>
+        <v>125000</v>
       </c>
       <c r="S135" s="14" t="n">
         <v>0.0525</v>
@@ -9896,7 +9896,7 @@
       </c>
       <c r="U135" s="10">
         <f>W135</f>
-        <v/>
+        <v>150000</v>
       </c>
       <c r="V135" s="14" t="n">
         <v>0.055</v>
@@ -9906,7 +9906,7 @@
       </c>
       <c r="X135" s="10">
         <f>Z135</f>
-        <v/>
+        <v>250000</v>
       </c>
       <c r="Y135" s="14" t="n">
         <v>0.0575</v>
@@ -9929,9 +9929,9 @@
           <t>MFJ</t>
         </is>
       </c>
-      <c r="C136" s="7">
+      <c r="C136" s="7" t="str">
         <f>A136&amp;"|"&amp;B136</f>
-        <v/>
+        <v>MD|MFJ</v>
       </c>
       <c r="D136" s="14" t="n">
         <v>0.02</v>
@@ -9941,7 +9941,7 @@
       </c>
       <c r="F136" s="10">
         <f>H136</f>
-        <v/>
+        <v>1000</v>
       </c>
       <c r="G136" s="14" t="n">
         <v>0.03</v>
@@ -9951,7 +9951,7 @@
       </c>
       <c r="I136" s="10">
         <f>K136</f>
-        <v/>
+        <v>2000</v>
       </c>
       <c r="J136" s="14" t="n">
         <v>0.04</v>
@@ -9961,7 +9961,7 @@
       </c>
       <c r="L136" s="10">
         <f>N136</f>
-        <v/>
+        <v>3000</v>
       </c>
       <c r="M136" s="14" t="n">
         <v>0.0475</v>
@@ -9971,7 +9971,7 @@
       </c>
       <c r="O136" s="10">
         <f>Q136</f>
-        <v/>
+        <v>150000</v>
       </c>
       <c r="P136" s="14" t="n">
         <v>0.05</v>
@@ -9981,7 +9981,7 @@
       </c>
       <c r="R136" s="10">
         <f>T136</f>
-        <v/>
+        <v>175000</v>
       </c>
       <c r="S136" s="14" t="n">
         <v>0.0525</v>
@@ -9991,7 +9991,7 @@
       </c>
       <c r="U136" s="10">
         <f>W136</f>
-        <v/>
+        <v>225000</v>
       </c>
       <c r="V136" s="14" t="n">
         <v>0.055</v>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="X136" s="10">
         <f>Z136</f>
-        <v/>
+        <v>300000</v>
       </c>
       <c r="Y136" s="14" t="n">
         <v>0.0575</v>
@@ -10024,9 +10024,9 @@
           <t>Single</t>
         </is>
       </c>
-      <c r="C137" s="7">
+      <c r="C137" s="7" t="str">
         <f>A137&amp;"|"&amp;B137</f>
-        <v/>
+        <v>WI|Single</v>
       </c>
       <c r="D137" s="14" t="n">
         <v>0.035</v>
@@ -10036,7 +10036,7 @@
       </c>
       <c r="F137" s="10">
         <f>H137</f>
-        <v/>
+        <v>14320</v>
       </c>
       <c r="G137" s="14" t="n">
         <v>0.044</v>
@@ -10046,7 +10046,7 @@
       </c>
       <c r="I137" s="10">
         <f>K137</f>
-        <v/>
+        <v>28640</v>
       </c>
       <c r="J137" s="14" t="n">
         <v>0.053</v>
@@ -10056,7 +10056,7 @@
       </c>
       <c r="L137" s="10">
         <f>N137</f>
-        <v/>
+        <v>315310</v>
       </c>
       <c r="M137" s="14" t="n">
         <v>0.0765</v>
@@ -10066,7 +10066,7 @@
       </c>
       <c r="O137" s="10">
         <f>Q137</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="P137" s="14" t="n">
         <v>0</v>
@@ -10076,7 +10076,7 @@
       </c>
       <c r="R137" s="10">
         <f>T137</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="S137" s="14" t="n">
         <v>0</v>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="U137" s="10">
         <f>W137</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="V137" s="14" t="n">
         <v>0</v>
@@ -10096,7 +10096,7 @@
       </c>
       <c r="X137" s="10">
         <f>Z137</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="Y137" s="14" t="n">
         <v>0</v>
@@ -10119,9 +10119,9 @@
           <t>MFJ</t>
         </is>
       </c>
-      <c r="C138" s="7">
+      <c r="C138" s="7" t="str">
         <f>A138&amp;"|"&amp;B138</f>
-        <v/>
+        <v>WI|MFJ</v>
       </c>
       <c r="D138" s="14" t="n">
         <v>0.035</v>
@@ -10131,7 +10131,7 @@
       </c>
       <c r="F138" s="10">
         <f>H138</f>
-        <v/>
+        <v>19090</v>
       </c>
       <c r="G138" s="14" t="n">
         <v>0.044</v>
@@ -10141,7 +10141,7 @@
       </c>
       <c r="I138" s="10">
         <f>K138</f>
-        <v/>
+        <v>38190</v>
       </c>
       <c r="J138" s="14" t="n">
         <v>0.053</v>
@@ -10151,7 +10151,7 @@
       </c>
       <c r="L138" s="10">
         <f>N138</f>
-        <v/>
+        <v>420420</v>
       </c>
       <c r="M138" s="14" t="n">
         <v>0.0765</v>
@@ -10161,7 +10161,7 @@
       </c>
       <c r="O138" s="10">
         <f>Q138</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="P138" s="14" t="n">
         <v>0</v>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="R138" s="10">
         <f>T138</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="S138" s="14" t="n">
         <v>0</v>
@@ -10181,7 +10181,7 @@
       </c>
       <c r="U138" s="10">
         <f>W138</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="V138" s="14" t="n">
         <v>0</v>
@@ -10191,7 +10191,7 @@
       </c>
       <c r="X138" s="10">
         <f>Z138</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="Y138" s="14" t="n">
         <v>0</v>
@@ -10214,9 +10214,9 @@
           <t>Single</t>
         </is>
       </c>
-      <c r="C139" s="7">
+      <c r="C139" s="7" t="str">
         <f>A139&amp;"|"&amp;B139</f>
-        <v/>
+        <v>OH|Single</v>
       </c>
       <c r="D139" s="14" t="n">
         <v>0</v>
@@ -10226,7 +10226,7 @@
       </c>
       <c r="F139" s="10">
         <f>H139</f>
-        <v/>
+        <v>26050</v>
       </c>
       <c r="G139" s="14" t="n">
         <v>0.0275</v>
@@ -10236,7 +10236,7 @@
       </c>
       <c r="I139" s="10">
         <f>K139</f>
-        <v/>
+        <v>100000</v>
       </c>
       <c r="J139" s="14" t="n">
         <v>0.035</v>
@@ -10246,7 +10246,7 @@
       </c>
       <c r="L139" s="10">
         <f>N139</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="M139" s="14" t="n">
         <v>0</v>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="O139" s="10">
         <f>Q139</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="P139" s="14" t="n">
         <v>0</v>
@@ -10266,7 +10266,7 @@
       </c>
       <c r="R139" s="10">
         <f>T139</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="S139" s="14" t="n">
         <v>0</v>
@@ -10276,7 +10276,7 @@
       </c>
       <c r="U139" s="10">
         <f>W139</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="V139" s="14" t="n">
         <v>0</v>
@@ -10286,7 +10286,7 @@
       </c>
       <c r="X139" s="10">
         <f>Z139</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="Y139" s="14" t="n">
         <v>0</v>
@@ -10309,9 +10309,9 @@
           <t>MFJ</t>
         </is>
       </c>
-      <c r="C140" s="7">
+      <c r="C140" s="7" t="str">
         <f>A140&amp;"|"&amp;B140</f>
-        <v/>
+        <v>OH|MFJ</v>
       </c>
       <c r="D140" s="14" t="n">
         <v>0</v>
@@ -10321,7 +10321,7 @@
       </c>
       <c r="F140" s="10">
         <f>H140</f>
-        <v/>
+        <v>26050</v>
       </c>
       <c r="G140" s="14" t="n">
         <v>0.0275</v>
@@ -10331,7 +10331,7 @@
       </c>
       <c r="I140" s="10">
         <f>K140</f>
-        <v/>
+        <v>100000</v>
       </c>
       <c r="J140" s="14" t="n">
         <v>0.035</v>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="L140" s="10">
         <f>N140</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="M140" s="14" t="n">
         <v>0</v>
@@ -10351,7 +10351,7 @@
       </c>
       <c r="O140" s="10">
         <f>Q140</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="P140" s="14" t="n">
         <v>0</v>
@@ -10361,7 +10361,7 @@
       </c>
       <c r="R140" s="10">
         <f>T140</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="S140" s="14" t="n">
         <v>0</v>
@@ -10371,7 +10371,7 @@
       </c>
       <c r="U140" s="10">
         <f>W140</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="V140" s="14" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="X140" s="10">
         <f>Z140</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="Y140" s="14" t="n">
         <v>0</v>
@@ -10404,9 +10404,9 @@
           <t>Single</t>
         </is>
       </c>
-      <c r="C141" s="7">
+      <c r="C141" s="7" t="str">
         <f>A141&amp;"|"&amp;B141</f>
-        <v/>
+        <v>DC|Single</v>
       </c>
       <c r="D141" s="14" t="n">
         <v>0.04</v>
@@ -10416,7 +10416,7 @@
       </c>
       <c r="F141" s="10">
         <f>H141</f>
-        <v/>
+        <v>10000</v>
       </c>
       <c r="G141" s="14" t="n">
         <v>0.06</v>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="I141" s="10">
         <f>K141</f>
-        <v/>
+        <v>40000</v>
       </c>
       <c r="J141" s="14" t="n">
         <v>0.065</v>
@@ -10436,7 +10436,7 @@
       </c>
       <c r="L141" s="10">
         <f>N141</f>
-        <v/>
+        <v>60000</v>
       </c>
       <c r="M141" s="14" t="n">
         <v>0.08500000000000001</v>
@@ -10446,7 +10446,7 @@
       </c>
       <c r="O141" s="10">
         <f>Q141</f>
-        <v/>
+        <v>250000</v>
       </c>
       <c r="P141" s="14" t="n">
         <v>0.0925</v>
@@ -10456,7 +10456,7 @@
       </c>
       <c r="R141" s="10">
         <f>T141</f>
-        <v/>
+        <v>500000</v>
       </c>
       <c r="S141" s="14" t="n">
         <v>0.0975</v>
@@ -10466,7 +10466,7 @@
       </c>
       <c r="U141" s="10">
         <f>W141</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="V141" s="14" t="n">
         <v>0</v>
@@ -10476,7 +10476,7 @@
       </c>
       <c r="X141" s="10">
         <f>Z141</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="Y141" s="14" t="n">
         <v>0</v>
@@ -10499,9 +10499,9 @@
           <t>MFJ</t>
         </is>
       </c>
-      <c r="C142" s="7">
+      <c r="C142" s="7" t="str">
         <f>A142&amp;"|"&amp;B142</f>
-        <v/>
+        <v>DC|MFJ</v>
       </c>
       <c r="D142" s="14" t="n">
         <v>0.04</v>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="F142" s="10">
         <f>H142</f>
-        <v/>
+        <v>10000</v>
       </c>
       <c r="G142" s="14" t="n">
         <v>0.06</v>
@@ -10521,7 +10521,7 @@
       </c>
       <c r="I142" s="10">
         <f>K142</f>
-        <v/>
+        <v>40000</v>
       </c>
       <c r="J142" s="14" t="n">
         <v>0.065</v>
@@ -10531,7 +10531,7 @@
       </c>
       <c r="L142" s="10">
         <f>N142</f>
-        <v/>
+        <v>60000</v>
       </c>
       <c r="M142" s="14" t="n">
         <v>0.08500000000000001</v>
@@ -10541,7 +10541,7 @@
       </c>
       <c r="O142" s="10">
         <f>Q142</f>
-        <v/>
+        <v>250000</v>
       </c>
       <c r="P142" s="14" t="n">
         <v>0.0925</v>
@@ -10551,7 +10551,7 @@
       </c>
       <c r="R142" s="10">
         <f>T142</f>
-        <v/>
+        <v>500000</v>
       </c>
       <c r="S142" s="14" t="n">
         <v>0.0975</v>
@@ -10561,7 +10561,7 @@
       </c>
       <c r="U142" s="10">
         <f>W142</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="V142" s="14" t="n">
         <v>0</v>
@@ -10571,7 +10571,7 @@
       </c>
       <c r="X142" s="10">
         <f>Z142</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="Y142" s="14" t="n">
         <v>0</v>
@@ -10594,9 +10594,9 @@
           <t>Single</t>
         </is>
       </c>
-      <c r="C143" s="7">
+      <c r="C143" s="7" t="str">
         <f>A143&amp;"|"&amp;B143</f>
-        <v/>
+        <v>OTHER|Single</v>
       </c>
       <c r="D143" s="14" t="n">
         <v>0</v>
@@ -10606,7 +10606,7 @@
       </c>
       <c r="F143" s="10">
         <f>H143</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="G143" s="14" t="n">
         <v>0</v>
@@ -10616,7 +10616,7 @@
       </c>
       <c r="I143" s="10">
         <f>K143</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="J143" s="14" t="n">
         <v>0</v>
@@ -10626,7 +10626,7 @@
       </c>
       <c r="L143" s="10">
         <f>N143</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="M143" s="14" t="n">
         <v>0</v>
@@ -10636,7 +10636,7 @@
       </c>
       <c r="O143" s="10">
         <f>Q143</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="P143" s="14" t="n">
         <v>0</v>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="R143" s="10">
         <f>T143</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="S143" s="14" t="n">
         <v>0</v>
@@ -10656,7 +10656,7 @@
       </c>
       <c r="U143" s="10">
         <f>W143</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="V143" s="14" t="n">
         <v>0</v>
@@ -10666,7 +10666,7 @@
       </c>
       <c r="X143" s="10">
         <f>Z143</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="Y143" s="14" t="n">
         <v>0</v>
@@ -10689,9 +10689,9 @@
           <t>MFJ</t>
         </is>
       </c>
-      <c r="C144" s="7">
+      <c r="C144" s="7" t="str">
         <f>A144&amp;"|"&amp;B144</f>
-        <v/>
+        <v>OTHER|MFJ</v>
       </c>
       <c r="D144" s="14" t="n">
         <v>0</v>
@@ -10701,7 +10701,7 @@
       </c>
       <c r="F144" s="10">
         <f>H144</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="G144" s="14" t="n">
         <v>0</v>
@@ -10711,7 +10711,7 @@
       </c>
       <c r="I144" s="10">
         <f>K144</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="J144" s="14" t="n">
         <v>0</v>
@@ -10721,7 +10721,7 @@
       </c>
       <c r="L144" s="10">
         <f>N144</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="M144" s="14" t="n">
         <v>0</v>
@@ -10731,7 +10731,7 @@
       </c>
       <c r="O144" s="10">
         <f>Q144</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="P144" s="14" t="n">
         <v>0</v>
@@ -10741,7 +10741,7 @@
       </c>
       <c r="R144" s="10">
         <f>T144</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="S144" s="14" t="n">
         <v>0</v>
@@ -10751,7 +10751,7 @@
       </c>
       <c r="U144" s="10">
         <f>W144</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="V144" s="14" t="n">
         <v>0</v>
@@ -10761,7 +10761,7 @@
       </c>
       <c r="X144" s="10">
         <f>Z144</f>
-        <v/>
+        <v>999999999</v>
       </c>
       <c r="Y144" s="14" t="n">
         <v>0</v>
